--- a/app/templates/informes/GranSuelo/Template_GranSuelo.xlsx
+++ b/app/templates/informes/GranSuelo/Template_GranSuelo.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24332"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\Documents\crmnew\api-geofal-crm\app\templates\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Mi unidad\3.0 Formatos e informes\2026\1.0 Informe de ensayo\1.1 Informe Suelo\INFORME ACREDITADO-E ISO\6.1 JUNIO INICIA 15-06-25\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{23A9E065-AF57-4D72-A6AF-26DA9FEBCC53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F60D475-2E06-4CA0-AB1E-9DE073B60BA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4296" yWindow="2412" windowWidth="16284" windowHeight="9828" tabRatio="547" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="547" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="FORMATO" sheetId="99" r:id="rId1"/>
@@ -1464,15 +1464,6 @@
     <t>Nota:</t>
   </si>
   <si>
-    <t>- Los datos de identificación de la muestra son proporcionados por el cliente.</t>
-  </si>
-  <si>
-    <t>- Los resultados corresponden sólo a los ensayos realizados sobre la muestra proporcionada por el cliente.</t>
-  </si>
-  <si>
-    <t>- Prohibida la reproducción total o parcial del presente informe de ensayo sin la autorización escrita de Geofal S.A.C.</t>
-  </si>
-  <si>
     <t>Observaciones:</t>
   </si>
   <si>
@@ -1504,9 +1495,6 @@
   </si>
   <si>
     <t>Forma de la particula</t>
-  </si>
-  <si>
-    <t xml:space="preserve">- Los resultados de los ensayos no deben ser utilizados como una certificación de conformidad con normas de productos o como certificado del sistema de calidad de Geofal S.A.C. </t>
   </si>
   <si>
     <t>TAMICES</t>
@@ -1802,9 +1790,6 @@
     <t>Mtotal: Masa total</t>
   </si>
   <si>
-    <t>- Este informe de ensayo, al estar en el marco de la acreditación del INACAL - DA, se encuentra dentro del ámbito de reconocimiento multilateral/mutuo de los miembros firmantes de IAAC e ILAC.</t>
-  </si>
-  <si>
     <t>RECEPCIÓN N°</t>
   </si>
   <si>
@@ -2034,9 +2019,6 @@
       </rPr>
       <t>(Reapproved 2025)</t>
     </r>
-  </si>
-  <si>
-    <t>Versión: 08 (2026-02-12)</t>
   </si>
   <si>
     <t>FORMATO N° F-LEM-P-SU-24.01</t>
@@ -2437,6 +2419,24 @@
   </si>
   <si>
     <t>Paso 1. Definición del proceso de medición</t>
+  </si>
+  <si>
+    <t>- El cliente es responsable de los datos de identificación de los puntos de ensayo brindados.</t>
+  </si>
+  <si>
+    <t>- Los resultados expresados se refieren únicamente al ensayo realizado en dicho momento y en las condiciones especificadas en este documento, por lo que GEOFAL S.A.C. no será responsable por los ensayos realizados con la presente muestra en condiciones distintas a las aquí señaladas.</t>
+  </si>
+  <si>
+    <t>- GEOFAL S.A.C. no se hace responsable por el uso incorrecto o inadecuado del presente informe.</t>
+  </si>
+  <si>
+    <t>- Los resultados de los ensayos realizados no deben ser utilizados como una certificación de conformidad con normas de producto o como certificado del sistema de calidad de la entidad que lo produce.</t>
+  </si>
+  <si>
+    <t>- De conformidad con lo dispuesto por el artículo 1321 del Código Civil, queda establecido que en ningún caso la responsabilidad de GEOFAL S.A.C. será mayor al valor del servicio prestado.</t>
+  </si>
+  <si>
+    <t>Versión: 09 (2026-06-15)</t>
   </si>
 </sst>
 </file>
@@ -5624,7 +5624,7 @@
     <xf numFmtId="0" fontId="1" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="52" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1026">
+  <cellXfs count="1029">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="2" fontId="10" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -7458,10 +7458,6 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="4" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="57" fillId="0" borderId="0" xfId="6" quotePrefix="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="53" borderId="99" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -8742,6 +8738,19 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="6" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="6" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="57" fillId="0" borderId="156" xfId="6" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="156" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="52">
@@ -9168,7 +9177,7 @@
                 <a:cs typeface="Arial"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="es-PE"/>
+            <a:endParaRPr lang="es-ES"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="128847232"/>
@@ -9271,7 +9280,7 @@
                 <a:cs typeface="Arial"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="es-PE"/>
+            <a:endParaRPr lang="es-ES"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="128844928"/>
@@ -9314,7 +9323,7 @@
           <a:cs typeface="Arial"/>
         </a:defRPr>
       </a:pPr>
-      <a:endParaRPr lang="es-PE"/>
+      <a:endParaRPr lang="es-ES"/>
     </a:p>
   </c:txPr>
   <c:printSettings>
@@ -9469,7 +9478,7 @@
                 <a:cs typeface="Arial"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="es-PE"/>
+            <a:endParaRPr lang="es-ES"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="131076096"/>
@@ -9506,7 +9515,7 @@
                 <a:cs typeface="Calibri"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="es-PE"/>
+            <a:endParaRPr lang="es-ES"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="131062016"/>
@@ -9544,7 +9553,7 @@
           <a:cs typeface="Calibri"/>
         </a:defRPr>
       </a:pPr>
-      <a:endParaRPr lang="es-PE"/>
+      <a:endParaRPr lang="es-ES"/>
     </a:p>
   </c:txPr>
   <c:printSettings>
@@ -9696,7 +9705,7 @@
                 <a:cs typeface="Arial"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="es-PE"/>
+            <a:endParaRPr lang="es-ES"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="131115264"/>
@@ -9732,7 +9741,7 @@
                 <a:cs typeface="Calibri"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="es-PE"/>
+            <a:endParaRPr lang="es-ES"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="131113728"/>
@@ -9770,7 +9779,7 @@
           <a:cs typeface="Calibri"/>
         </a:defRPr>
       </a:pPr>
-      <a:endParaRPr lang="es-PE"/>
+      <a:endParaRPr lang="es-ES"/>
     </a:p>
   </c:txPr>
   <c:printSettings>
@@ -9922,7 +9931,7 @@
                 <a:cs typeface="Arial"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="es-PE"/>
+            <a:endParaRPr lang="es-ES"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="131289856"/>
@@ -9959,7 +9968,7 @@
                 <a:cs typeface="Calibri"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="es-PE"/>
+            <a:endParaRPr lang="es-ES"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="131283968"/>
@@ -9997,7 +10006,7 @@
           <a:cs typeface="Calibri"/>
         </a:defRPr>
       </a:pPr>
-      <a:endParaRPr lang="es-PE"/>
+      <a:endParaRPr lang="es-ES"/>
     </a:p>
   </c:txPr>
   <c:printSettings>
@@ -10149,7 +10158,7 @@
                 <a:cs typeface="Arial"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="es-PE"/>
+            <a:endParaRPr lang="es-ES"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="131308544"/>
@@ -10185,7 +10194,7 @@
                 <a:cs typeface="Calibri"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="es-PE"/>
+            <a:endParaRPr lang="es-ES"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="131307008"/>
@@ -10223,7 +10232,7 @@
           <a:cs typeface="Calibri"/>
         </a:defRPr>
       </a:pPr>
-      <a:endParaRPr lang="es-PE"/>
+      <a:endParaRPr lang="es-ES"/>
     </a:p>
   </c:txPr>
   <c:printSettings>
@@ -10375,7 +10384,7 @@
                 <a:cs typeface="Arial"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="es-PE"/>
+            <a:endParaRPr lang="es-ES"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="131409408"/>
@@ -10412,7 +10421,7 @@
                 <a:cs typeface="Calibri"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="es-PE"/>
+            <a:endParaRPr lang="es-ES"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="131407872"/>
@@ -10450,7 +10459,7 @@
           <a:cs typeface="Calibri"/>
         </a:defRPr>
       </a:pPr>
-      <a:endParaRPr lang="es-PE"/>
+      <a:endParaRPr lang="es-ES"/>
     </a:p>
   </c:txPr>
   <c:printSettings>
@@ -10612,7 +10621,7 @@
                 <a:cs typeface="Arial"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="es-PE"/>
+            <a:endParaRPr lang="es-ES"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="131448832"/>
@@ -10648,7 +10657,7 @@
                 <a:cs typeface="Calibri"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="es-PE"/>
+            <a:endParaRPr lang="es-ES"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="131442944"/>
@@ -10687,7 +10696,7 @@
           <a:cs typeface="Calibri"/>
         </a:defRPr>
       </a:pPr>
-      <a:endParaRPr lang="es-PE"/>
+      <a:endParaRPr lang="es-ES"/>
     </a:p>
   </c:txPr>
   <c:printSettings>
@@ -11016,7 +11025,7 @@
                 <a:cs typeface="Arial"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="es-PE"/>
+            <a:endParaRPr lang="es-ES"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="131648128"/>
@@ -11119,7 +11128,7 @@
                 <a:cs typeface="Arial"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="es-PE"/>
+            <a:endParaRPr lang="es-ES"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="131645824"/>
@@ -11168,7 +11177,7 @@
           <a:cs typeface="Arial"/>
         </a:defRPr>
       </a:pPr>
-      <a:endParaRPr lang="es-PE"/>
+      <a:endParaRPr lang="es-ES"/>
     </a:p>
   </c:txPr>
   <c:printSettings>
@@ -11320,7 +11329,7 @@
                 <a:cs typeface="Arial"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="es-PE"/>
+            <a:endParaRPr lang="es-ES"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="130499328"/>
@@ -11357,7 +11366,7 @@
                 <a:cs typeface="Calibri"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="es-PE"/>
+            <a:endParaRPr lang="es-ES"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="130497536"/>
@@ -11395,7 +11404,7 @@
           <a:cs typeface="Calibri"/>
         </a:defRPr>
       </a:pPr>
-      <a:endParaRPr lang="es-PE"/>
+      <a:endParaRPr lang="es-ES"/>
     </a:p>
   </c:txPr>
   <c:printSettings>
@@ -11547,7 +11556,7 @@
                 <a:cs typeface="Arial"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="es-PE"/>
+            <a:endParaRPr lang="es-ES"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="130546688"/>
@@ -11584,7 +11593,7 @@
                 <a:cs typeface="Calibri"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="es-PE"/>
+            <a:endParaRPr lang="es-ES"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="130545152"/>
@@ -11622,7 +11631,7 @@
           <a:cs typeface="Calibri"/>
         </a:defRPr>
       </a:pPr>
-      <a:endParaRPr lang="es-PE"/>
+      <a:endParaRPr lang="es-ES"/>
     </a:p>
   </c:txPr>
   <c:printSettings>
@@ -11762,7 +11771,7 @@
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
-            <a:endParaRPr lang="es-PE"/>
+            <a:endParaRPr lang="es-ES"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="130569728"/>
@@ -11792,7 +11801,7 @@
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
-            <a:endParaRPr lang="es-PE"/>
+            <a:endParaRPr lang="es-ES"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="130568192"/>
@@ -11830,7 +11839,7 @@
           <a:cs typeface="Calibri"/>
         </a:defRPr>
       </a:pPr>
-      <a:endParaRPr lang="es-PE"/>
+      <a:endParaRPr lang="es-ES"/>
     </a:p>
   </c:txPr>
   <c:printSettings>
@@ -11982,7 +11991,7 @@
                 <a:cs typeface="Arial"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="es-PE"/>
+            <a:endParaRPr lang="es-ES"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="130744320"/>
@@ -12019,7 +12028,7 @@
                 <a:cs typeface="Calibri"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="es-PE"/>
+            <a:endParaRPr lang="es-ES"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="130607360"/>
@@ -12057,7 +12066,7 @@
           <a:cs typeface="Calibri"/>
         </a:defRPr>
       </a:pPr>
-      <a:endParaRPr lang="es-PE"/>
+      <a:endParaRPr lang="es-ES"/>
     </a:p>
   </c:txPr>
   <c:printSettings>
@@ -12209,7 +12218,7 @@
                 <a:cs typeface="Arial"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="es-PE"/>
+            <a:endParaRPr lang="es-ES"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="130803968"/>
@@ -12246,7 +12255,7 @@
                 <a:cs typeface="Calibri"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="es-PE"/>
+            <a:endParaRPr lang="es-ES"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="130802432"/>
@@ -12284,7 +12293,7 @@
           <a:cs typeface="Calibri"/>
         </a:defRPr>
       </a:pPr>
-      <a:endParaRPr lang="es-PE"/>
+      <a:endParaRPr lang="es-ES"/>
     </a:p>
   </c:txPr>
   <c:printSettings>
@@ -12436,7 +12445,7 @@
                 <a:cs typeface="Arial"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="es-PE"/>
+            <a:endParaRPr lang="es-ES"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="130904832"/>
@@ -12473,7 +12482,7 @@
                 <a:cs typeface="Calibri"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="es-PE"/>
+            <a:endParaRPr lang="es-ES"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="130890752"/>
@@ -12511,7 +12520,7 @@
           <a:cs typeface="Calibri"/>
         </a:defRPr>
       </a:pPr>
-      <a:endParaRPr lang="es-PE"/>
+      <a:endParaRPr lang="es-ES"/>
     </a:p>
   </c:txPr>
   <c:printSettings>
@@ -12663,7 +12672,7 @@
                 <a:cs typeface="Arial"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="es-PE"/>
+            <a:endParaRPr lang="es-ES"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="130948096"/>
@@ -12700,7 +12709,7 @@
                 <a:cs typeface="Calibri"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="es-PE"/>
+            <a:endParaRPr lang="es-ES"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="130946560"/>
@@ -12738,7 +12747,7 @@
           <a:cs typeface="Calibri"/>
         </a:defRPr>
       </a:pPr>
-      <a:endParaRPr lang="es-PE"/>
+      <a:endParaRPr lang="es-ES"/>
     </a:p>
   </c:txPr>
   <c:printSettings>
@@ -12890,7 +12899,7 @@
                 <a:cs typeface="Arial"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="es-PE"/>
+            <a:endParaRPr lang="es-ES"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="131032576"/>
@@ -12927,7 +12936,7 @@
                 <a:cs typeface="Calibri"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="es-PE"/>
+            <a:endParaRPr lang="es-ES"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="131031040"/>
@@ -12965,7 +12974,7 @@
           <a:cs typeface="Calibri"/>
         </a:defRPr>
       </a:pPr>
-      <a:endParaRPr lang="es-PE"/>
+      <a:endParaRPr lang="es-ES"/>
     </a:p>
   </c:txPr>
   <c:printSettings>
@@ -14601,15 +14610,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>376862</xdr:colOff>
-      <xdr:row>88</xdr:row>
-      <xdr:rowOff>40641</xdr:rowOff>
+      <xdr:colOff>376863</xdr:colOff>
+      <xdr:row>87</xdr:row>
+      <xdr:rowOff>124461</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>325479</xdr:colOff>
+      <xdr:colOff>325480</xdr:colOff>
       <xdr:row>92</xdr:row>
-      <xdr:rowOff>34796</xdr:rowOff>
+      <xdr:rowOff>156716</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -14637,7 +14646,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm rot="60000">
-          <a:off x="3257222" y="16179801"/>
+          <a:off x="3257223" y="16476981"/>
           <a:ext cx="1388797" cy="1060955"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -14651,14 +14660,14 @@
     <xdr:from>
       <xdr:col>11</xdr:col>
       <xdr:colOff>437803</xdr:colOff>
-      <xdr:row>88</xdr:row>
-      <xdr:rowOff>108358</xdr:rowOff>
+      <xdr:row>87</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
       <xdr:colOff>826741</xdr:colOff>
       <xdr:row>92</xdr:row>
-      <xdr:rowOff>5170</xdr:rowOff>
+      <xdr:rowOff>68580</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -14673,8 +14682,8 @@
       </xdr:nvSpPr>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="5747991" y="16221483"/>
-          <a:ext cx="1103313" cy="984250"/>
+          <a:off x="5901343" y="16428720"/>
+          <a:ext cx="1120458" cy="1021080"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -14756,15 +14765,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>443948</xdr:colOff>
-      <xdr:row>88</xdr:row>
-      <xdr:rowOff>86139</xdr:rowOff>
+      <xdr:colOff>413468</xdr:colOff>
+      <xdr:row>87</xdr:row>
+      <xdr:rowOff>131859</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>11</xdr:col>
-      <xdr:colOff>394968</xdr:colOff>
-      <xdr:row>92</xdr:row>
-      <xdr:rowOff>121438</xdr:rowOff>
+      <xdr:colOff>364488</xdr:colOff>
+      <xdr:row>93</xdr:row>
+      <xdr:rowOff>29998</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -14792,8 +14801,8 @@
       </xdr:blipFill>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="4770783" y="16180904"/>
-          <a:ext cx="1097333" cy="1095473"/>
+          <a:off x="4734008" y="16484379"/>
+          <a:ext cx="1094020" cy="1102099"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -14911,67 +14920,6 @@
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>17</xdr:col>
-      <xdr:colOff>68580</xdr:colOff>
-      <xdr:row>87</xdr:row>
-      <xdr:rowOff>129540</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>19</xdr:col>
-      <xdr:colOff>703671</xdr:colOff>
-      <xdr:row>92</xdr:row>
-      <xdr:rowOff>174954</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="28" name="Imagen 27">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B93765CD-8FE8-4E05-8800-511290A90C50}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:srcRect/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="9189720" y="16070580"/>
-          <a:ext cx="2646771" cy="1310334"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
       </xdr:spPr>
     </xdr:pic>
     <xdr:clientData/>
@@ -16446,7 +16394,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="-------"/>
@@ -16505,7 +16453,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="datos de ecuacion del anillo"/>
@@ -16624,7 +16572,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink3.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="-------"/>
@@ -16675,7 +16623,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink4.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="-------"/>
@@ -16727,7 +16675,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink5.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="BGA"/>
@@ -16759,7 +16707,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink6.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="-------"/>
@@ -21561,38 +21509,38 @@
   <dimension ref="A1:U67"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.33203125" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.33203125" style="678" customWidth="1"/>
-    <col min="2" max="2" width="2" style="678" customWidth="1"/>
-    <col min="3" max="3" width="11.44140625" style="678" customWidth="1"/>
-    <col min="4" max="4" width="1.109375" style="678" customWidth="1"/>
-    <col min="5" max="5" width="12.5546875" style="678" customWidth="1"/>
-    <col min="6" max="6" width="9.33203125" style="678" customWidth="1"/>
-    <col min="7" max="7" width="8.5546875" style="678" customWidth="1"/>
-    <col min="8" max="8" width="17.5546875" style="678" customWidth="1"/>
-    <col min="9" max="9" width="1" style="678" customWidth="1"/>
-    <col min="10" max="10" width="21.109375" style="678" customWidth="1"/>
-    <col min="11" max="11" width="14.6640625" style="678" customWidth="1"/>
-    <col min="12" max="12" width="6.44140625" style="678" customWidth="1"/>
-    <col min="13" max="13" width="8" style="678" customWidth="1"/>
-    <col min="14" max="15" width="10.6640625" style="678" customWidth="1"/>
-    <col min="16" max="16384" width="10.33203125" style="678"/>
+    <col min="1" max="1" width="11.33203125" style="677" customWidth="1"/>
+    <col min="2" max="2" width="2" style="677" customWidth="1"/>
+    <col min="3" max="3" width="11.44140625" style="677" customWidth="1"/>
+    <col min="4" max="4" width="1.109375" style="677" customWidth="1"/>
+    <col min="5" max="5" width="12.5546875" style="677" customWidth="1"/>
+    <col min="6" max="6" width="9.33203125" style="677" customWidth="1"/>
+    <col min="7" max="7" width="8.5546875" style="677" customWidth="1"/>
+    <col min="8" max="8" width="17.5546875" style="677" customWidth="1"/>
+    <col min="9" max="9" width="1" style="677" customWidth="1"/>
+    <col min="10" max="10" width="21.109375" style="677" customWidth="1"/>
+    <col min="11" max="11" width="14.6640625" style="677" customWidth="1"/>
+    <col min="12" max="12" width="6.44140625" style="677" customWidth="1"/>
+    <col min="13" max="13" width="8" style="677" customWidth="1"/>
+    <col min="14" max="15" width="10.6640625" style="677" customWidth="1"/>
+    <col min="16" max="16384" width="10.33203125" style="677"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:21" ht="12.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="673"/>
-      <c r="B1" s="674"/>
-      <c r="C1" s="674"/>
-      <c r="D1" s="675"/>
-      <c r="E1" s="675"/>
-      <c r="F1" s="675"/>
-      <c r="G1" s="675"/>
-      <c r="H1" s="675"/>
-      <c r="I1" s="676"/>
-      <c r="J1" s="676"/>
-      <c r="K1" s="677"/>
+      <c r="A1" s="672"/>
+      <c r="B1" s="673"/>
+      <c r="C1" s="673"/>
+      <c r="D1" s="674"/>
+      <c r="E1" s="674"/>
+      <c r="F1" s="674"/>
+      <c r="G1" s="674"/>
+      <c r="H1" s="674"/>
+      <c r="I1" s="675"/>
+      <c r="J1" s="675"/>
+      <c r="K1" s="676"/>
     </row>
     <row r="2" spans="1:21" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="679"/>
+      <c r="A2" s="678"/>
       <c r="B2" s="285"/>
       <c r="C2" s="285"/>
       <c r="D2" s="286"/>
@@ -21600,14 +21548,14 @@
       <c r="F2" s="286"/>
       <c r="G2" s="286"/>
       <c r="H2" s="286"/>
-      <c r="K2" s="680"/>
+      <c r="K2" s="679"/>
       <c r="N2" s="291" t="s">
-        <v>558</v>
-      </c>
-      <c r="O2" s="762"/>
+        <v>552</v>
+      </c>
+      <c r="O2" s="761"/>
     </row>
     <row r="3" spans="1:21" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="679"/>
+      <c r="A3" s="678"/>
       <c r="B3" s="285"/>
       <c r="C3" s="285"/>
       <c r="D3" s="286"/>
@@ -21615,14 +21563,14 @@
       <c r="F3" s="286"/>
       <c r="G3" s="286"/>
       <c r="H3" s="286"/>
-      <c r="K3" s="680"/>
+      <c r="K3" s="679"/>
       <c r="N3" s="291" t="s">
         <v>249</v>
       </c>
-      <c r="O3" s="763"/>
+      <c r="O3" s="762"/>
     </row>
     <row r="4" spans="1:21" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="679"/>
+      <c r="A4" s="678"/>
       <c r="B4" s="285"/>
       <c r="C4" s="285"/>
       <c r="D4" s="286"/>
@@ -21630,29 +21578,29 @@
       <c r="F4" s="286"/>
       <c r="G4" s="286"/>
       <c r="H4" s="286"/>
-      <c r="K4" s="680"/>
+      <c r="K4" s="679"/>
       <c r="N4" s="291" t="s">
         <v>235</v>
       </c>
-      <c r="O4" s="763"/>
+      <c r="O4" s="762"/>
     </row>
     <row r="5" spans="1:21" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="681"/>
-      <c r="B5" s="682"/>
-      <c r="C5" s="682"/>
-      <c r="D5" s="682"/>
-      <c r="E5" s="682"/>
-      <c r="F5" s="682"/>
-      <c r="G5" s="682"/>
-      <c r="H5" s="682"/>
-      <c r="I5" s="682"/>
-      <c r="J5" s="682"/>
-      <c r="K5" s="683"/>
+      <c r="A5" s="680"/>
+      <c r="B5" s="681"/>
+      <c r="C5" s="681"/>
+      <c r="D5" s="681"/>
+      <c r="E5" s="681"/>
+      <c r="F5" s="681"/>
+      <c r="G5" s="681"/>
+      <c r="H5" s="681"/>
+      <c r="I5" s="681"/>
+      <c r="J5" s="681"/>
+      <c r="K5" s="682"/>
       <c r="M5"/>
       <c r="N5" s="291" t="s">
         <v>236</v>
       </c>
-      <c r="O5" s="763"/>
+      <c r="O5" s="762"/>
     </row>
     <row r="6" spans="1:21" ht="8.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A6" s="566"/>
@@ -21666,48 +21614,48 @@
       <c r="I6" s="566"/>
       <c r="J6" s="566"/>
       <c r="K6" s="566"/>
-      <c r="N6" s="764"/>
-      <c r="O6" s="765"/>
+      <c r="N6" s="763"/>
+      <c r="O6" s="764"/>
     </row>
     <row r="7" spans="1:21" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="783" t="s">
+      <c r="A7" s="782" t="s">
         <v>21</v>
       </c>
-      <c r="B7" s="783"/>
-      <c r="C7" s="783"/>
-      <c r="D7" s="783"/>
-      <c r="E7" s="783"/>
-      <c r="F7" s="783"/>
-      <c r="G7" s="783"/>
-      <c r="H7" s="783"/>
-      <c r="I7" s="783"/>
-      <c r="J7" s="783"/>
-      <c r="K7" s="783"/>
+      <c r="B7" s="782"/>
+      <c r="C7" s="782"/>
+      <c r="D7" s="782"/>
+      <c r="E7" s="782"/>
+      <c r="F7" s="782"/>
+      <c r="G7" s="782"/>
+      <c r="H7" s="782"/>
+      <c r="I7" s="782"/>
+      <c r="J7" s="782"/>
+      <c r="K7" s="782"/>
       <c r="N7" s="291" t="s">
-        <v>452</v>
-      </c>
-      <c r="O7" s="765"/>
+        <v>447</v>
+      </c>
+      <c r="O7" s="764"/>
     </row>
     <row r="8" spans="1:21" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="784" t="s">
-        <v>486</v>
-      </c>
-      <c r="B8" s="784"/>
-      <c r="C8" s="784"/>
-      <c r="D8" s="784"/>
-      <c r="E8" s="784"/>
-      <c r="F8" s="784"/>
-      <c r="G8" s="784"/>
-      <c r="H8" s="784"/>
-      <c r="I8" s="784"/>
-      <c r="J8" s="784"/>
-      <c r="K8" s="784"/>
+      <c r="A8" s="783" t="s">
+        <v>480</v>
+      </c>
+      <c r="B8" s="783"/>
+      <c r="C8" s="783"/>
+      <c r="D8" s="783"/>
+      <c r="E8" s="783"/>
+      <c r="F8" s="783"/>
+      <c r="G8" s="783"/>
+      <c r="H8" s="783"/>
+      <c r="I8" s="783"/>
+      <c r="J8" s="783"/>
+      <c r="K8" s="783"/>
       <c r="N8" s="291" t="s">
-        <v>559</v>
-      </c>
-      <c r="O8" s="766"/>
-    </row>
-    <row r="9" spans="1:21" ht="4.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>553</v>
+      </c>
+      <c r="O8" s="765"/>
+    </row>
+    <row r="9" spans="1:21" ht="9.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="536"/>
       <c r="B9" s="536"/>
       <c r="C9" s="536"/>
@@ -21720,52 +21668,52 @@
       <c r="J9" s="536"/>
       <c r="K9" s="536"/>
       <c r="N9" s="291" t="s">
-        <v>471</v>
-      </c>
-      <c r="O9" s="765"/>
+        <v>466</v>
+      </c>
+      <c r="O9" s="764"/>
     </row>
     <row r="10" spans="1:21" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B10" s="487"/>
       <c r="C10" s="487"/>
-      <c r="D10" s="785" t="s">
-        <v>487</v>
-      </c>
-      <c r="E10" s="786"/>
-      <c r="F10" s="785" t="s">
-        <v>488</v>
-      </c>
-      <c r="G10" s="786"/>
-      <c r="H10" s="785" t="s">
+      <c r="D10" s="784" t="s">
+        <v>481</v>
+      </c>
+      <c r="E10" s="785"/>
+      <c r="F10" s="784" t="s">
+        <v>482</v>
+      </c>
+      <c r="G10" s="785"/>
+      <c r="H10" s="784" t="s">
         <v>30</v>
       </c>
-      <c r="I10" s="786"/>
-      <c r="J10" s="684" t="s">
-        <v>472</v>
-      </c>
-      <c r="K10" s="685"/>
-      <c r="L10" s="686"/>
-      <c r="M10" s="686"/>
-      <c r="N10" s="764"/>
-      <c r="O10" s="765"/>
+      <c r="I10" s="785"/>
+      <c r="J10" s="683" t="s">
+        <v>467</v>
+      </c>
+      <c r="K10" s="684"/>
+      <c r="L10" s="685"/>
+      <c r="M10" s="685"/>
+      <c r="N10" s="763"/>
+      <c r="O10" s="764"/>
     </row>
     <row r="11" spans="1:21" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="487"/>
       <c r="B11" s="487"/>
       <c r="C11" s="487"/>
-      <c r="D11" s="787"/>
-      <c r="E11" s="788"/>
-      <c r="F11" s="787"/>
-      <c r="G11" s="788"/>
-      <c r="H11" s="787"/>
-      <c r="I11" s="788"/>
-      <c r="J11" s="687"/>
+      <c r="D11" s="786"/>
+      <c r="E11" s="787"/>
+      <c r="F11" s="786"/>
+      <c r="G11" s="787"/>
+      <c r="H11" s="786"/>
+      <c r="I11" s="787"/>
+      <c r="J11" s="686"/>
       <c r="K11" s="387"/>
-      <c r="L11" s="686"/>
-      <c r="M11" s="686"/>
+      <c r="L11" s="685"/>
+      <c r="M11" s="685"/>
       <c r="N11" s="291" t="s">
         <v>251</v>
       </c>
-      <c r="O11" s="765"/>
+      <c r="O11" s="764"/>
     </row>
     <row r="12" spans="1:21" ht="11.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="487"/>
@@ -21778,927 +21726,927 @@
       <c r="H12" s="292"/>
       <c r="I12" s="291"/>
       <c r="J12" s="288"/>
-      <c r="K12" s="688"/>
-      <c r="L12" s="686"/>
-      <c r="M12" s="686"/>
+      <c r="K12" s="687"/>
+      <c r="L12" s="685"/>
+      <c r="M12" s="685"/>
       <c r="N12" s="291" t="s">
         <v>233</v>
       </c>
-      <c r="O12" s="766"/>
+      <c r="O12" s="765"/>
     </row>
     <row r="13" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="789" t="s">
-        <v>489</v>
-      </c>
-      <c r="B13" s="790"/>
-      <c r="C13" s="790"/>
-      <c r="D13" s="790"/>
-      <c r="E13" s="790"/>
-      <c r="F13" s="790"/>
-      <c r="G13" s="790"/>
-      <c r="H13" s="790"/>
-      <c r="I13" s="790"/>
-      <c r="J13" s="790"/>
-      <c r="K13" s="791"/>
-      <c r="L13" s="686"/>
-      <c r="M13" s="686"/>
+      <c r="A13" s="788" t="s">
+        <v>483</v>
+      </c>
+      <c r="B13" s="789"/>
+      <c r="C13" s="789"/>
+      <c r="D13" s="789"/>
+      <c r="E13" s="789"/>
+      <c r="F13" s="789"/>
+      <c r="G13" s="789"/>
+      <c r="H13" s="789"/>
+      <c r="I13" s="789"/>
+      <c r="J13" s="789"/>
+      <c r="K13" s="790"/>
+      <c r="L13" s="685"/>
+      <c r="M13" s="685"/>
       <c r="N13" s="291" t="s">
         <v>234</v>
       </c>
-      <c r="O13" s="766"/>
+      <c r="O13" s="765"/>
     </row>
     <row r="14" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="792" t="s">
-        <v>490</v>
-      </c>
-      <c r="B14" s="793"/>
-      <c r="C14" s="793"/>
-      <c r="D14" s="793"/>
-      <c r="E14" s="793"/>
-      <c r="F14" s="793"/>
-      <c r="G14" s="793"/>
-      <c r="H14" s="793"/>
-      <c r="I14" s="793"/>
-      <c r="J14" s="793"/>
-      <c r="K14" s="794"/>
-      <c r="L14" s="686"/>
-      <c r="M14" s="686"/>
-      <c r="N14" s="764"/>
-      <c r="O14" s="765"/>
+      <c r="A14" s="791" t="s">
+        <v>484</v>
+      </c>
+      <c r="B14" s="792"/>
+      <c r="C14" s="792"/>
+      <c r="D14" s="792"/>
+      <c r="E14" s="792"/>
+      <c r="F14" s="792"/>
+      <c r="G14" s="792"/>
+      <c r="H14" s="792"/>
+      <c r="I14" s="792"/>
+      <c r="J14" s="792"/>
+      <c r="K14" s="793"/>
+      <c r="L14" s="685"/>
+      <c r="M14" s="685"/>
+      <c r="N14" s="763"/>
+      <c r="O14" s="764"/>
     </row>
     <row r="15" spans="1:21" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="M15" s="689"/>
+      <c r="M15" s="688"/>
       <c r="N15" s="291" t="s">
-        <v>560</v>
-      </c>
-      <c r="O15" s="767"/>
-      <c r="P15" s="689"/>
-      <c r="Q15" s="689"/>
-      <c r="R15" s="689"/>
-      <c r="S15" s="689"/>
-      <c r="T15" s="689"/>
-      <c r="U15" s="689"/>
+        <v>554</v>
+      </c>
+      <c r="O15" s="766"/>
+      <c r="P15" s="688"/>
+      <c r="Q15" s="688"/>
+      <c r="R15" s="688"/>
+      <c r="S15" s="688"/>
+      <c r="T15" s="688"/>
+      <c r="U15" s="688"/>
     </row>
     <row r="16" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="795" t="s">
-        <v>491</v>
-      </c>
-      <c r="B16" s="796"/>
-      <c r="C16" s="797"/>
-      <c r="E16" s="798" t="s">
+      <c r="A16" s="794" t="s">
+        <v>485</v>
+      </c>
+      <c r="B16" s="795"/>
+      <c r="C16" s="796"/>
+      <c r="E16" s="797" t="s">
         <v>372</v>
       </c>
-      <c r="F16" s="799"/>
-      <c r="G16" s="799"/>
-      <c r="H16" s="800"/>
-      <c r="J16" s="795" t="s">
-        <v>492</v>
-      </c>
-      <c r="K16" s="797"/>
-      <c r="M16" s="689"/>
+      <c r="F16" s="798"/>
+      <c r="G16" s="798"/>
+      <c r="H16" s="799"/>
+      <c r="J16" s="794" t="s">
+        <v>486</v>
+      </c>
+      <c r="K16" s="796"/>
+      <c r="M16" s="688"/>
       <c r="N16" s="291" t="s">
         <v>245</v>
       </c>
-      <c r="O16" s="767"/>
-      <c r="P16" s="689"/>
-      <c r="R16" s="690"/>
-      <c r="S16" s="689"/>
-      <c r="T16" s="691"/>
-      <c r="U16" s="691"/>
+      <c r="O16" s="766"/>
+      <c r="P16" s="688"/>
+      <c r="R16" s="689"/>
+      <c r="S16" s="688"/>
+      <c r="T16" s="690"/>
+      <c r="U16" s="690"/>
     </row>
     <row r="17" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="692" t="s">
+      <c r="A17" s="691" t="s">
+        <v>487</v>
+      </c>
+      <c r="B17" s="778"/>
+      <c r="C17" s="779"/>
+      <c r="E17" s="692" t="s">
+        <v>488</v>
+      </c>
+      <c r="F17" s="693"/>
+      <c r="G17" s="694"/>
+      <c r="H17" s="695"/>
+      <c r="J17" s="780"/>
+      <c r="K17" s="781"/>
+      <c r="M17" s="688"/>
+      <c r="N17" s="291" t="s">
+        <v>555</v>
+      </c>
+      <c r="O17" s="767"/>
+      <c r="P17" s="688"/>
+      <c r="R17" s="689"/>
+      <c r="S17" s="688"/>
+      <c r="T17" s="690"/>
+      <c r="U17" s="690"/>
+    </row>
+    <row r="18" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="691" t="s">
+        <v>489</v>
+      </c>
+      <c r="B18" s="778"/>
+      <c r="C18" s="779"/>
+      <c r="E18" s="692" t="s">
+        <v>490</v>
+      </c>
+      <c r="F18" s="693"/>
+      <c r="G18" s="694"/>
+      <c r="H18" s="697"/>
+      <c r="M18" s="688"/>
+      <c r="N18" s="696"/>
+      <c r="O18" s="689"/>
+      <c r="P18" s="688"/>
+      <c r="R18" s="689"/>
+      <c r="S18" s="688"/>
+      <c r="T18" s="690"/>
+      <c r="U18" s="690"/>
+    </row>
+    <row r="19" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E19" s="692" t="s">
+        <v>491</v>
+      </c>
+      <c r="F19" s="693"/>
+      <c r="G19" s="694"/>
+      <c r="H19" s="698"/>
+      <c r="J19" s="804" t="s">
+        <v>492</v>
+      </c>
+      <c r="K19" s="805"/>
+      <c r="M19" s="688"/>
+      <c r="N19" s="696"/>
+      <c r="O19" s="689"/>
+      <c r="P19" s="688"/>
+      <c r="R19" s="689"/>
+      <c r="S19" s="688"/>
+      <c r="T19" s="690"/>
+      <c r="U19" s="690"/>
+    </row>
+    <row r="20" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="806" t="s">
         <v>493</v>
       </c>
-      <c r="B17" s="779"/>
-      <c r="C17" s="780"/>
-      <c r="E17" s="693" t="s">
+      <c r="B20" s="807"/>
+      <c r="C20" s="808"/>
+      <c r="E20" s="699" t="s">
         <v>494</v>
       </c>
-      <c r="F17" s="694"/>
-      <c r="G17" s="695"/>
-      <c r="H17" s="696"/>
-      <c r="J17" s="781"/>
-      <c r="K17" s="782"/>
-      <c r="M17" s="689"/>
-      <c r="N17" s="291" t="s">
-        <v>561</v>
-      </c>
-      <c r="O17" s="768"/>
-      <c r="P17" s="689"/>
-      <c r="R17" s="690"/>
-      <c r="S17" s="689"/>
-      <c r="T17" s="691"/>
-      <c r="U17" s="691"/>
-    </row>
-    <row r="18" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="692" t="s">
+      <c r="F20" s="700"/>
+      <c r="G20" s="700"/>
+      <c r="H20" s="701"/>
+      <c r="J20" s="702" t="s">
+        <v>431</v>
+      </c>
+      <c r="K20" s="703"/>
+      <c r="M20" s="688"/>
+      <c r="N20" s="696"/>
+      <c r="O20" s="689"/>
+      <c r="P20" s="688"/>
+      <c r="R20" s="689"/>
+      <c r="S20" s="688"/>
+      <c r="T20" s="690"/>
+      <c r="U20" s="690"/>
+    </row>
+    <row r="21" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="691" t="s">
         <v>495</v>
       </c>
-      <c r="B18" s="779"/>
-      <c r="C18" s="780"/>
-      <c r="E18" s="693" t="s">
+      <c r="B21" s="809"/>
+      <c r="C21" s="810"/>
+      <c r="E21" s="704"/>
+      <c r="F21" s="704"/>
+      <c r="G21" s="704"/>
+      <c r="H21" s="704"/>
+      <c r="J21" s="387" t="s">
         <v>496</v>
       </c>
-      <c r="F18" s="694"/>
-      <c r="G18" s="695"/>
-      <c r="H18" s="698"/>
-      <c r="M18" s="689"/>
-      <c r="N18" s="697"/>
-      <c r="O18" s="690"/>
-      <c r="P18" s="689"/>
-      <c r="R18" s="690"/>
-      <c r="S18" s="689"/>
-      <c r="T18" s="691"/>
-      <c r="U18" s="691"/>
-    </row>
-    <row r="19" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E19" s="693" t="s">
+      <c r="M21" s="688"/>
+      <c r="N21" s="696"/>
+      <c r="O21" s="689"/>
+      <c r="P21" s="688"/>
+      <c r="R21" s="689"/>
+      <c r="S21" s="688"/>
+      <c r="T21" s="690"/>
+      <c r="U21" s="690"/>
+    </row>
+    <row r="22" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="691" t="s">
         <v>497</v>
       </c>
-      <c r="F19" s="694"/>
-      <c r="G19" s="695"/>
-      <c r="H19" s="699"/>
-      <c r="J19" s="805" t="s">
-        <v>498</v>
-      </c>
-      <c r="K19" s="806"/>
-      <c r="M19" s="689"/>
-      <c r="N19" s="697"/>
-      <c r="O19" s="690"/>
-      <c r="P19" s="689"/>
-      <c r="R19" s="690"/>
-      <c r="S19" s="689"/>
-      <c r="T19" s="691"/>
-      <c r="U19" s="691"/>
-    </row>
-    <row r="20" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="807" t="s">
-        <v>499</v>
-      </c>
-      <c r="B20" s="808"/>
-      <c r="C20" s="809"/>
-      <c r="E20" s="700" t="s">
-        <v>500</v>
-      </c>
-      <c r="F20" s="701"/>
-      <c r="G20" s="701"/>
-      <c r="H20" s="702"/>
-      <c r="J20" s="703" t="s">
-        <v>435</v>
-      </c>
-      <c r="K20" s="704"/>
-      <c r="M20" s="689"/>
-      <c r="N20" s="697"/>
-      <c r="O20" s="690"/>
-      <c r="P20" s="689"/>
-      <c r="R20" s="690"/>
-      <c r="S20" s="689"/>
-      <c r="T20" s="691"/>
-      <c r="U20" s="691"/>
-    </row>
-    <row r="21" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="692" t="s">
-        <v>501</v>
-      </c>
-      <c r="B21" s="810"/>
-      <c r="C21" s="811"/>
-      <c r="E21" s="705"/>
-      <c r="F21" s="705"/>
-      <c r="G21" s="705"/>
-      <c r="H21" s="705"/>
-      <c r="J21" s="387" t="s">
-        <v>502</v>
-      </c>
-      <c r="M21" s="689"/>
-      <c r="N21" s="697"/>
-      <c r="O21" s="690"/>
-      <c r="P21" s="689"/>
-      <c r="R21" s="690"/>
-      <c r="S21" s="689"/>
-      <c r="T21" s="691"/>
-      <c r="U21" s="691"/>
-    </row>
-    <row r="22" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="692" t="s">
-        <v>503</v>
-      </c>
-      <c r="B22" s="810"/>
-      <c r="C22" s="811"/>
-      <c r="E22" s="805" t="s">
+      <c r="B22" s="809"/>
+      <c r="C22" s="810"/>
+      <c r="E22" s="804" t="s">
         <v>369</v>
       </c>
-      <c r="F22" s="812"/>
-      <c r="G22" s="812"/>
-      <c r="H22" s="806"/>
-      <c r="I22" s="706"/>
+      <c r="F22" s="811"/>
+      <c r="G22" s="811"/>
+      <c r="H22" s="805"/>
+      <c r="I22" s="705"/>
       <c r="J22" s="488" t="s">
         <v>370</v>
       </c>
-      <c r="K22" s="707"/>
-      <c r="M22" s="689"/>
-      <c r="N22" s="697"/>
-      <c r="O22" s="690"/>
-      <c r="P22" s="689"/>
-      <c r="R22" s="690"/>
-      <c r="S22" s="689"/>
-      <c r="T22" s="691"/>
-      <c r="U22" s="691"/>
+      <c r="K22" s="706"/>
+      <c r="M22" s="688"/>
+      <c r="N22" s="696"/>
+      <c r="O22" s="689"/>
+      <c r="P22" s="688"/>
+      <c r="R22" s="689"/>
+      <c r="S22" s="688"/>
+      <c r="T22" s="690"/>
+      <c r="U22" s="690"/>
     </row>
     <row r="23" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E23" s="693" t="s">
+      <c r="E23" s="692" t="s">
+        <v>498</v>
+      </c>
+      <c r="F23" s="693"/>
+      <c r="G23" s="694"/>
+      <c r="H23" s="697"/>
+      <c r="J23" s="707" t="s">
+        <v>499</v>
+      </c>
+      <c r="K23" s="697"/>
+      <c r="M23" s="688"/>
+      <c r="N23" s="696"/>
+      <c r="O23" s="689"/>
+      <c r="P23" s="688"/>
+      <c r="R23" s="689"/>
+      <c r="S23" s="688"/>
+      <c r="T23" s="690"/>
+      <c r="U23" s="690"/>
+    </row>
+    <row r="24" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="794" t="s">
+        <v>500</v>
+      </c>
+      <c r="B24" s="795"/>
+      <c r="C24" s="796"/>
+      <c r="E24" s="692" t="s">
+        <v>501</v>
+      </c>
+      <c r="F24" s="693"/>
+      <c r="G24" s="694"/>
+      <c r="H24" s="697"/>
+      <c r="J24" s="708" t="s">
+        <v>502</v>
+      </c>
+      <c r="K24" s="707"/>
+      <c r="M24" s="688"/>
+      <c r="N24" s="696"/>
+      <c r="O24" s="689"/>
+      <c r="P24" s="688"/>
+      <c r="R24" s="689"/>
+      <c r="S24" s="688"/>
+      <c r="T24" s="690"/>
+      <c r="U24" s="690"/>
+    </row>
+    <row r="25" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="709" t="s">
+        <v>503</v>
+      </c>
+      <c r="B25" s="710"/>
+      <c r="C25" s="697"/>
+      <c r="E25" s="692" t="s">
         <v>504</v>
       </c>
-      <c r="F23" s="694"/>
-      <c r="G23" s="695"/>
-      <c r="H23" s="698"/>
-      <c r="J23" s="708" t="s">
+      <c r="F25" s="693"/>
+      <c r="G25" s="694"/>
+      <c r="H25" s="697"/>
+      <c r="J25" s="692" t="s">
+        <v>425</v>
+      </c>
+      <c r="K25" s="697"/>
+      <c r="M25" s="688"/>
+      <c r="N25" s="696"/>
+      <c r="O25" s="689"/>
+      <c r="P25" s="688"/>
+      <c r="R25" s="689"/>
+      <c r="S25" s="688"/>
+      <c r="T25" s="690"/>
+      <c r="U25" s="690"/>
+    </row>
+    <row r="26" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="709" t="s">
         <v>505</v>
       </c>
-      <c r="K23" s="698"/>
-      <c r="M23" s="689"/>
-      <c r="N23" s="697"/>
-      <c r="O23" s="690"/>
-      <c r="P23" s="689"/>
-      <c r="R23" s="690"/>
-      <c r="S23" s="689"/>
-      <c r="T23" s="691"/>
-      <c r="U23" s="691"/>
-    </row>
-    <row r="24" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="795" t="s">
+      <c r="B26" s="711"/>
+      <c r="C26" s="697"/>
+      <c r="E26" s="692" t="s">
         <v>506</v>
       </c>
-      <c r="B24" s="796"/>
-      <c r="C24" s="797"/>
-      <c r="E24" s="693" t="s">
+      <c r="F26" s="693"/>
+      <c r="G26" s="694"/>
+      <c r="H26" s="697"/>
+      <c r="J26" s="692" t="s">
         <v>507</v>
       </c>
-      <c r="F24" s="694"/>
-      <c r="G24" s="695"/>
-      <c r="H24" s="698"/>
-      <c r="J24" s="709" t="s">
+      <c r="K26" s="697"/>
+      <c r="M26" s="688"/>
+      <c r="N26" s="696"/>
+      <c r="O26" s="689"/>
+      <c r="P26" s="688"/>
+      <c r="R26" s="689"/>
+      <c r="S26" s="688"/>
+      <c r="T26" s="690"/>
+      <c r="U26" s="690"/>
+    </row>
+    <row r="27" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="709" t="s">
         <v>508</v>
       </c>
-      <c r="K24" s="708"/>
-      <c r="M24" s="689"/>
-      <c r="N24" s="697"/>
-      <c r="O24" s="690"/>
-      <c r="P24" s="689"/>
-      <c r="R24" s="690"/>
-      <c r="S24" s="689"/>
-      <c r="T24" s="691"/>
-      <c r="U24" s="691"/>
-    </row>
-    <row r="25" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="710" t="s">
+      <c r="B27" s="711"/>
+      <c r="C27" s="712"/>
+      <c r="I27" s="713"/>
+      <c r="J27" s="692" t="s">
         <v>509</v>
       </c>
-      <c r="B25" s="711"/>
-      <c r="C25" s="698"/>
-      <c r="E25" s="693" t="s">
+      <c r="K27" s="697"/>
+      <c r="M27" s="688"/>
+      <c r="N27" s="696"/>
+      <c r="O27" s="689"/>
+      <c r="P27" s="688"/>
+      <c r="R27" s="689"/>
+      <c r="S27" s="688"/>
+      <c r="T27" s="690"/>
+      <c r="U27" s="690"/>
+    </row>
+    <row r="28" spans="1:21" ht="3.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="688"/>
+      <c r="B28" s="690"/>
+      <c r="C28" s="714"/>
+      <c r="I28" s="713"/>
+      <c r="J28" s="715"/>
+      <c r="M28" s="688"/>
+      <c r="N28" s="696"/>
+      <c r="O28" s="689"/>
+      <c r="P28" s="688"/>
+      <c r="R28" s="689"/>
+      <c r="S28" s="688"/>
+      <c r="T28" s="690"/>
+      <c r="U28" s="690"/>
+    </row>
+    <row r="29" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E29" s="716" t="s">
         <v>510</v>
-      </c>
-      <c r="F25" s="694"/>
-      <c r="G25" s="695"/>
-      <c r="H25" s="698"/>
-      <c r="J25" s="693" t="s">
-        <v>429</v>
-      </c>
-      <c r="K25" s="698"/>
-      <c r="M25" s="689"/>
-      <c r="N25" s="697"/>
-      <c r="O25" s="690"/>
-      <c r="P25" s="689"/>
-      <c r="R25" s="690"/>
-      <c r="S25" s="689"/>
-      <c r="T25" s="691"/>
-      <c r="U25" s="691"/>
-    </row>
-    <row r="26" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="710" t="s">
-        <v>511</v>
-      </c>
-      <c r="B26" s="712"/>
-      <c r="C26" s="698"/>
-      <c r="E26" s="693" t="s">
-        <v>512</v>
-      </c>
-      <c r="F26" s="694"/>
-      <c r="G26" s="695"/>
-      <c r="H26" s="698"/>
-      <c r="J26" s="693" t="s">
-        <v>513</v>
-      </c>
-      <c r="K26" s="698"/>
-      <c r="M26" s="689"/>
-      <c r="N26" s="697"/>
-      <c r="O26" s="690"/>
-      <c r="P26" s="689"/>
-      <c r="R26" s="690"/>
-      <c r="S26" s="689"/>
-      <c r="T26" s="691"/>
-      <c r="U26" s="691"/>
-    </row>
-    <row r="27" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="710" t="s">
-        <v>514</v>
-      </c>
-      <c r="B27" s="712"/>
-      <c r="C27" s="713"/>
-      <c r="I27" s="714"/>
-      <c r="J27" s="693" t="s">
-        <v>515</v>
-      </c>
-      <c r="K27" s="698"/>
-      <c r="M27" s="689"/>
-      <c r="N27" s="697"/>
-      <c r="O27" s="690"/>
-      <c r="P27" s="689"/>
-      <c r="R27" s="690"/>
-      <c r="S27" s="689"/>
-      <c r="T27" s="691"/>
-      <c r="U27" s="691"/>
-    </row>
-    <row r="28" spans="1:21" ht="3.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="689"/>
-      <c r="B28" s="691"/>
-      <c r="C28" s="715"/>
-      <c r="I28" s="714"/>
-      <c r="J28" s="716"/>
-      <c r="M28" s="689"/>
-      <c r="N28" s="697"/>
-      <c r="O28" s="690"/>
-      <c r="P28" s="689"/>
-      <c r="R28" s="690"/>
-      <c r="S28" s="689"/>
-      <c r="T28" s="691"/>
-      <c r="U28" s="691"/>
-    </row>
-    <row r="29" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E29" s="717" t="s">
-        <v>516</v>
       </c>
       <c r="F29" s="488"/>
       <c r="G29" s="488"/>
       <c r="H29" s="488"/>
       <c r="I29" s="488"/>
       <c r="J29" s="488"/>
-      <c r="K29" s="707"/>
-      <c r="M29" s="689"/>
-      <c r="N29" s="697"/>
-      <c r="O29" s="690"/>
-      <c r="P29" s="689"/>
-      <c r="R29" s="690"/>
-      <c r="S29" s="689"/>
-      <c r="T29" s="691"/>
-      <c r="U29" s="691"/>
+      <c r="K29" s="706"/>
+      <c r="M29" s="688"/>
+      <c r="N29" s="696"/>
+      <c r="O29" s="689"/>
+      <c r="P29" s="688"/>
+      <c r="R29" s="689"/>
+      <c r="S29" s="688"/>
+      <c r="T29" s="690"/>
+      <c r="U29" s="690"/>
     </row>
     <row r="30" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="718" t="s">
+      <c r="A30" s="717" t="s">
+        <v>511</v>
+      </c>
+      <c r="B30" s="718"/>
+      <c r="C30" s="719"/>
+      <c r="E30" s="692" t="s">
+        <v>512</v>
+      </c>
+      <c r="F30" s="720"/>
+      <c r="G30" s="693"/>
+      <c r="H30" s="693"/>
+      <c r="I30" s="693"/>
+      <c r="J30" s="694"/>
+      <c r="K30" s="697"/>
+      <c r="M30" s="688"/>
+      <c r="N30" s="696"/>
+      <c r="O30" s="689"/>
+      <c r="P30" s="688"/>
+      <c r="R30" s="689"/>
+      <c r="S30" s="688"/>
+      <c r="T30" s="690"/>
+      <c r="U30" s="690"/>
+    </row>
+    <row r="31" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="709" t="s">
+        <v>513</v>
+      </c>
+      <c r="B31" s="812"/>
+      <c r="C31" s="812"/>
+      <c r="E31" s="692" t="s">
+        <v>514</v>
+      </c>
+      <c r="F31" s="720"/>
+      <c r="G31" s="693"/>
+      <c r="H31" s="693"/>
+      <c r="I31" s="693"/>
+      <c r="J31" s="694"/>
+      <c r="K31" s="697"/>
+      <c r="M31" s="688"/>
+      <c r="N31" s="696"/>
+      <c r="O31" s="689"/>
+      <c r="P31" s="688"/>
+      <c r="R31" s="689"/>
+      <c r="S31" s="688"/>
+      <c r="T31" s="690"/>
+      <c r="U31" s="690"/>
+    </row>
+    <row r="32" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="709" t="s">
+        <v>515</v>
+      </c>
+      <c r="B32" s="812"/>
+      <c r="C32" s="812"/>
+      <c r="E32" s="692" t="s">
+        <v>516</v>
+      </c>
+      <c r="F32" s="720"/>
+      <c r="G32" s="693"/>
+      <c r="H32" s="693"/>
+      <c r="I32" s="693"/>
+      <c r="J32" s="694"/>
+      <c r="K32" s="697"/>
+      <c r="M32" s="688"/>
+      <c r="N32" s="696"/>
+      <c r="O32" s="689"/>
+      <c r="P32" s="688"/>
+      <c r="R32" s="689"/>
+      <c r="S32" s="688"/>
+      <c r="T32" s="690"/>
+      <c r="U32" s="690"/>
+    </row>
+    <row r="33" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E33" s="692" t="s">
         <v>517</v>
       </c>
-      <c r="B30" s="719"/>
-      <c r="C30" s="720"/>
-      <c r="E30" s="693" t="s">
+      <c r="F33" s="693"/>
+      <c r="G33" s="693"/>
+      <c r="H33" s="693"/>
+      <c r="I33" s="693"/>
+      <c r="J33" s="694"/>
+      <c r="K33" s="697"/>
+      <c r="M33" s="688"/>
+      <c r="N33" s="696"/>
+      <c r="O33" s="689"/>
+      <c r="P33" s="688"/>
+      <c r="R33" s="689"/>
+      <c r="S33" s="688"/>
+      <c r="T33" s="690"/>
+      <c r="U33" s="690"/>
+    </row>
+    <row r="34" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="806" t="s">
         <v>518</v>
       </c>
-      <c r="F30" s="721"/>
-      <c r="G30" s="694"/>
-      <c r="H30" s="694"/>
-      <c r="I30" s="694"/>
-      <c r="J30" s="695"/>
-      <c r="K30" s="698"/>
-      <c r="M30" s="689"/>
-      <c r="N30" s="697"/>
-      <c r="O30" s="690"/>
-      <c r="P30" s="689"/>
-      <c r="R30" s="690"/>
-      <c r="S30" s="689"/>
-      <c r="T30" s="691"/>
-      <c r="U30" s="691"/>
-    </row>
-    <row r="31" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="710" t="s">
+      <c r="B34" s="807"/>
+      <c r="C34" s="808"/>
+      <c r="E34" s="813" t="s">
         <v>519</v>
       </c>
-      <c r="B31" s="813"/>
-      <c r="C31" s="813"/>
-      <c r="E31" s="693" t="s">
+      <c r="F34" s="814"/>
+      <c r="G34" s="800"/>
+      <c r="H34" s="801"/>
+      <c r="I34" s="721"/>
+      <c r="J34" s="722" t="s">
         <v>520</v>
       </c>
-      <c r="F31" s="721"/>
-      <c r="G31" s="694"/>
-      <c r="H31" s="694"/>
-      <c r="I31" s="694"/>
-      <c r="J31" s="695"/>
-      <c r="K31" s="698"/>
-      <c r="M31" s="689"/>
-      <c r="N31" s="697"/>
-      <c r="O31" s="690"/>
-      <c r="P31" s="689"/>
-      <c r="R31" s="690"/>
-      <c r="S31" s="689"/>
-      <c r="T31" s="691"/>
-      <c r="U31" s="691"/>
-    </row>
-    <row r="32" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="710" t="s">
+      <c r="K34" s="723"/>
+      <c r="M34" s="688"/>
+      <c r="N34" s="696"/>
+      <c r="O34" s="689"/>
+      <c r="R34" s="689"/>
+      <c r="S34" s="688"/>
+      <c r="T34" s="690"/>
+      <c r="U34" s="690"/>
+    </row>
+    <row r="35" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="724" t="s">
         <v>521</v>
       </c>
-      <c r="B32" s="813"/>
-      <c r="C32" s="813"/>
-      <c r="E32" s="693" t="s">
+      <c r="B35" s="704"/>
+      <c r="C35" s="725"/>
+      <c r="E35" s="815"/>
+      <c r="F35" s="816"/>
+      <c r="G35" s="802"/>
+      <c r="H35" s="803"/>
+      <c r="J35" s="726" t="s">
         <v>522</v>
       </c>
-      <c r="F32" s="721"/>
-      <c r="G32" s="694"/>
-      <c r="H32" s="694"/>
-      <c r="I32" s="694"/>
-      <c r="J32" s="695"/>
-      <c r="K32" s="698"/>
-      <c r="M32" s="689"/>
-      <c r="N32" s="697"/>
-      <c r="O32" s="690"/>
-      <c r="P32" s="689"/>
-      <c r="R32" s="690"/>
-      <c r="S32" s="689"/>
-      <c r="T32" s="691"/>
-      <c r="U32" s="691"/>
-    </row>
-    <row r="33" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E33" s="693" t="s">
+      <c r="K35" s="727"/>
+      <c r="M35" s="688"/>
+      <c r="N35" s="696"/>
+      <c r="O35" s="689"/>
+      <c r="R35" s="689"/>
+      <c r="S35" s="688"/>
+      <c r="T35" s="690"/>
+      <c r="U35" s="690"/>
+    </row>
+    <row r="36" spans="1:21" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="728"/>
+      <c r="B36" s="700"/>
+      <c r="C36" s="729"/>
+      <c r="I36" s="730"/>
+      <c r="J36" s="731"/>
+      <c r="K36" s="731"/>
+      <c r="L36" s="685"/>
+      <c r="P36" s="688"/>
+    </row>
+    <row r="37" spans="1:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="806" t="s">
         <v>523</v>
       </c>
-      <c r="F33" s="694"/>
-      <c r="G33" s="694"/>
-      <c r="H33" s="694"/>
-      <c r="I33" s="694"/>
-      <c r="J33" s="695"/>
-      <c r="K33" s="698"/>
-      <c r="M33" s="689"/>
-      <c r="N33" s="697"/>
-      <c r="O33" s="690"/>
-      <c r="P33" s="689"/>
-      <c r="R33" s="690"/>
-      <c r="S33" s="689"/>
-      <c r="T33" s="691"/>
-      <c r="U33" s="691"/>
-    </row>
-    <row r="34" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="807" t="s">
+      <c r="B37" s="807"/>
+      <c r="C37" s="808"/>
+      <c r="E37" s="824" t="s">
         <v>524</v>
       </c>
-      <c r="B34" s="808"/>
-      <c r="C34" s="809"/>
-      <c r="E34" s="814" t="s">
+      <c r="F37" s="825"/>
+      <c r="G37" s="825"/>
+      <c r="H37" s="825"/>
+      <c r="I37" s="826"/>
+      <c r="K37" s="817" t="s">
         <v>525</v>
       </c>
-      <c r="F34" s="815"/>
-      <c r="G34" s="801"/>
-      <c r="H34" s="802"/>
-      <c r="I34" s="722"/>
-      <c r="J34" s="723" t="s">
+      <c r="L37" s="685"/>
+    </row>
+    <row r="38" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="732" t="s">
+        <v>521</v>
+      </c>
+      <c r="C38" s="733"/>
+      <c r="E38" s="734" t="s">
+        <v>551</v>
+      </c>
+      <c r="F38" s="786" t="s">
         <v>526</v>
       </c>
-      <c r="K34" s="724"/>
-      <c r="M34" s="689"/>
-      <c r="N34" s="697"/>
-      <c r="O34" s="690"/>
-      <c r="R34" s="690"/>
-      <c r="S34" s="689"/>
-      <c r="T34" s="691"/>
-      <c r="U34" s="691"/>
-    </row>
-    <row r="35" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="725" t="s">
+      <c r="G38" s="787"/>
+      <c r="H38" s="786" t="s">
         <v>527</v>
       </c>
-      <c r="B35" s="705"/>
-      <c r="C35" s="726"/>
-      <c r="E35" s="816"/>
-      <c r="F35" s="817"/>
-      <c r="G35" s="803"/>
-      <c r="H35" s="804"/>
-      <c r="J35" s="727" t="s">
+      <c r="I38" s="787"/>
+      <c r="K38" s="817"/>
+      <c r="L38" s="685"/>
+    </row>
+    <row r="39" spans="1:21" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="728"/>
+      <c r="B39" s="700"/>
+      <c r="C39" s="729"/>
+      <c r="I39" s="730"/>
+      <c r="J39" s="418"/>
+      <c r="K39" s="735"/>
+      <c r="L39" s="685"/>
+    </row>
+    <row r="40" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="736" t="s">
         <v>528</v>
       </c>
-      <c r="K35" s="728"/>
-      <c r="M35" s="689"/>
-      <c r="N35" s="697"/>
-      <c r="O35" s="690"/>
-      <c r="R35" s="690"/>
-      <c r="S35" s="689"/>
-      <c r="T35" s="691"/>
-      <c r="U35" s="691"/>
-    </row>
-    <row r="36" spans="1:21" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="729"/>
-      <c r="B36" s="701"/>
-      <c r="C36" s="730"/>
-      <c r="I36" s="731"/>
-      <c r="J36" s="732"/>
-      <c r="K36" s="732"/>
-      <c r="L36" s="686"/>
-      <c r="P36" s="689"/>
-    </row>
-    <row r="37" spans="1:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="807" t="s">
+      <c r="C40" s="737" t="s">
         <v>529</v>
       </c>
-      <c r="B37" s="808"/>
-      <c r="C37" s="809"/>
-      <c r="E37" s="825" t="s">
+      <c r="D40" s="804" t="s">
         <v>530</v>
       </c>
-      <c r="F37" s="826"/>
-      <c r="G37" s="826"/>
-      <c r="H37" s="826"/>
-      <c r="I37" s="827"/>
-      <c r="K37" s="818" t="s">
+      <c r="E40" s="805"/>
+      <c r="I40" s="738" t="s">
         <v>531</v>
       </c>
-      <c r="L37" s="686"/>
-    </row>
-    <row r="38" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="733" t="s">
-        <v>527</v>
-      </c>
-      <c r="C38" s="734"/>
-      <c r="E38" s="735" t="s">
-        <v>557</v>
-      </c>
-      <c r="F38" s="787" t="s">
+      <c r="L40" s="685"/>
+    </row>
+    <row r="41" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="736" t="s">
         <v>532</v>
       </c>
-      <c r="G38" s="788"/>
-      <c r="H38" s="787" t="s">
+      <c r="C41" s="737" t="s">
         <v>533</v>
       </c>
-      <c r="I38" s="788"/>
-      <c r="K38" s="818"/>
-      <c r="L38" s="686"/>
-    </row>
-    <row r="39" spans="1:21" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="729"/>
-      <c r="B39" s="701"/>
-      <c r="C39" s="730"/>
-      <c r="I39" s="731"/>
-      <c r="J39" s="418"/>
-      <c r="K39" s="736"/>
-      <c r="L39" s="686"/>
-    </row>
-    <row r="40" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="737" t="s">
+      <c r="D41" s="804" t="s">
+        <v>366</v>
+      </c>
+      <c r="E41" s="805"/>
+      <c r="J41" s="739"/>
+      <c r="L41" s="685"/>
+    </row>
+    <row r="42" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="740" t="s">
         <v>534</v>
       </c>
-      <c r="C40" s="738" t="s">
+      <c r="C42" s="741">
+        <v>75</v>
+      </c>
+      <c r="D42" s="742"/>
+      <c r="E42" s="743"/>
+      <c r="F42" s="730"/>
+      <c r="G42" s="387"/>
+      <c r="H42" s="739"/>
+      <c r="J42" s="739"/>
+      <c r="K42" s="744"/>
+      <c r="L42" s="685"/>
+    </row>
+    <row r="43" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="740" t="s">
         <v>535</v>
       </c>
-      <c r="D40" s="805" t="s">
+      <c r="C43" s="741">
+        <v>50</v>
+      </c>
+      <c r="D43" s="742"/>
+      <c r="E43" s="743"/>
+    </row>
+    <row r="44" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="740" t="s">
         <v>536</v>
       </c>
-      <c r="E40" s="806"/>
-      <c r="I40" s="739" t="s">
+      <c r="C44" s="741">
+        <v>37.5</v>
+      </c>
+      <c r="D44" s="742"/>
+      <c r="E44" s="743"/>
+    </row>
+    <row r="45" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="740" t="s">
         <v>537</v>
       </c>
-      <c r="L40" s="686"/>
-    </row>
-    <row r="41" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="737" t="s">
+      <c r="C45" s="741">
+        <v>25</v>
+      </c>
+      <c r="D45" s="742"/>
+      <c r="E45" s="743"/>
+      <c r="L45" s="685"/>
+      <c r="M45" s="685"/>
+    </row>
+    <row r="46" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="740" t="s">
         <v>538</v>
       </c>
-      <c r="C41" s="738" t="s">
+      <c r="C46" s="741">
+        <v>19</v>
+      </c>
+      <c r="D46" s="742"/>
+      <c r="E46" s="743"/>
+      <c r="L46" s="685"/>
+      <c r="M46" s="685"/>
+    </row>
+    <row r="47" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="740" t="s">
         <v>539</v>
       </c>
-      <c r="D41" s="805" t="s">
-        <v>366</v>
-      </c>
-      <c r="E41" s="806"/>
-      <c r="J41" s="740"/>
-      <c r="L41" s="686"/>
-    </row>
-    <row r="42" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="741" t="s">
-        <v>540</v>
-      </c>
-      <c r="C42" s="742">
-        <v>75</v>
-      </c>
-      <c r="D42" s="743"/>
-      <c r="E42" s="744"/>
-      <c r="F42" s="731"/>
-      <c r="G42" s="387"/>
-      <c r="H42" s="740"/>
-      <c r="J42" s="740"/>
-      <c r="K42" s="745"/>
-      <c r="L42" s="686"/>
-    </row>
-    <row r="43" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="741" t="s">
-        <v>541</v>
-      </c>
-      <c r="C43" s="742">
-        <v>50</v>
-      </c>
-      <c r="D43" s="743"/>
-      <c r="E43" s="744"/>
-    </row>
-    <row r="44" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="741" t="s">
-        <v>542</v>
-      </c>
-      <c r="C44" s="742">
-        <v>37.5</v>
-      </c>
-      <c r="D44" s="743"/>
-      <c r="E44" s="744"/>
-    </row>
-    <row r="45" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="741" t="s">
-        <v>543</v>
-      </c>
-      <c r="C45" s="742">
-        <v>25</v>
-      </c>
-      <c r="D45" s="743"/>
-      <c r="E45" s="744"/>
-      <c r="L45" s="686"/>
-      <c r="M45" s="686"/>
-    </row>
-    <row r="46" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="741" t="s">
-        <v>544</v>
-      </c>
-      <c r="C46" s="742">
-        <v>19</v>
-      </c>
-      <c r="D46" s="743"/>
-      <c r="E46" s="744"/>
-      <c r="L46" s="686"/>
-      <c r="M46" s="686"/>
-    </row>
-    <row r="47" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="741" t="s">
-        <v>545</v>
-      </c>
-      <c r="C47" s="742">
+      <c r="C47" s="741">
         <v>9.5</v>
       </c>
-      <c r="D47" s="743"/>
-      <c r="E47" s="744"/>
-      <c r="L47" s="686"/>
+      <c r="D47" s="742"/>
+      <c r="E47" s="743"/>
+      <c r="L47" s="685"/>
     </row>
     <row r="48" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="741" t="s">
-        <v>435</v>
-      </c>
-      <c r="C48" s="742">
+      <c r="A48" s="740" t="s">
+        <v>431</v>
+      </c>
+      <c r="C48" s="741">
         <v>4.75</v>
       </c>
-      <c r="D48" s="743"/>
-      <c r="E48" s="744"/>
-      <c r="L48" s="686"/>
-      <c r="M48" s="686"/>
+      <c r="D48" s="742"/>
+      <c r="E48" s="743"/>
+      <c r="L48" s="685"/>
+      <c r="M48" s="685"/>
     </row>
     <row r="49" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="266"/>
-      <c r="C49" s="746"/>
-      <c r="D49" s="747"/>
-      <c r="E49" s="747"/>
-      <c r="G49" s="748" t="s">
-        <v>546</v>
-      </c>
-      <c r="L49" s="686"/>
-      <c r="M49" s="686"/>
+      <c r="C49" s="745"/>
+      <c r="D49" s="746"/>
+      <c r="E49" s="746"/>
+      <c r="G49" s="747" t="s">
+        <v>540</v>
+      </c>
+      <c r="L49" s="685"/>
+      <c r="M49" s="685"/>
     </row>
     <row r="50" spans="1:18" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="389" t="s">
         <v>232</v>
       </c>
-      <c r="C50" s="749">
+      <c r="C50" s="748">
         <v>2</v>
       </c>
-      <c r="D50" s="743"/>
-      <c r="E50" s="750"/>
-      <c r="G50" s="820" t="s">
-        <v>547</v>
-      </c>
-      <c r="H50" s="821"/>
-      <c r="I50" s="820" t="s">
-        <v>548</v>
-      </c>
-      <c r="J50" s="821"/>
-      <c r="L50" s="686"/>
-      <c r="M50" s="686"/>
+      <c r="D50" s="742"/>
+      <c r="E50" s="749"/>
+      <c r="G50" s="819" t="s">
+        <v>541</v>
+      </c>
+      <c r="H50" s="820"/>
+      <c r="I50" s="819" t="s">
+        <v>542</v>
+      </c>
+      <c r="J50" s="820"/>
+      <c r="L50" s="685"/>
+      <c r="M50" s="685"/>
     </row>
     <row r="51" spans="1:18" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="389" t="s">
         <v>238</v>
       </c>
-      <c r="C51" s="749">
+      <c r="C51" s="748">
         <v>0.85</v>
       </c>
-      <c r="D51" s="743"/>
-      <c r="E51" s="750"/>
-      <c r="G51" s="751" t="s">
-        <v>549</v>
-      </c>
-      <c r="H51" s="752"/>
-      <c r="I51" s="822"/>
-      <c r="J51" s="823"/>
-      <c r="L51" s="686"/>
-      <c r="M51" s="686"/>
+      <c r="D51" s="742"/>
+      <c r="E51" s="749"/>
+      <c r="G51" s="750" t="s">
+        <v>543</v>
+      </c>
+      <c r="H51" s="751"/>
+      <c r="I51" s="821"/>
+      <c r="J51" s="822"/>
+      <c r="L51" s="685"/>
+      <c r="M51" s="685"/>
     </row>
     <row r="52" spans="1:18" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="389" t="s">
-        <v>550</v>
-      </c>
-      <c r="C52" s="749">
+        <v>544</v>
+      </c>
+      <c r="C52" s="748">
         <v>0.42499999999999999</v>
       </c>
-      <c r="D52" s="743"/>
-      <c r="E52" s="750"/>
-      <c r="G52" s="751" t="s">
-        <v>551</v>
-      </c>
-      <c r="H52" s="752"/>
-      <c r="I52" s="822"/>
-      <c r="J52" s="823"/>
-      <c r="L52" s="686"/>
-      <c r="M52" s="686"/>
+      <c r="D52" s="742"/>
+      <c r="E52" s="749"/>
+      <c r="G52" s="750" t="s">
+        <v>545</v>
+      </c>
+      <c r="H52" s="751"/>
+      <c r="I52" s="821"/>
+      <c r="J52" s="822"/>
+      <c r="L52" s="685"/>
+      <c r="M52" s="685"/>
     </row>
     <row r="53" spans="1:18" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="389" t="s">
         <v>239</v>
       </c>
-      <c r="C53" s="749">
+      <c r="C53" s="748">
         <v>0.25</v>
       </c>
-      <c r="D53" s="743"/>
-      <c r="E53" s="750"/>
-      <c r="L53" s="686"/>
-      <c r="M53" s="686"/>
+      <c r="D53" s="742"/>
+      <c r="E53" s="749"/>
+      <c r="L53" s="685"/>
+      <c r="M53" s="685"/>
     </row>
     <row r="54" spans="1:18" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="389" t="s">
         <v>241</v>
       </c>
-      <c r="C54" s="749">
+      <c r="C54" s="748">
         <v>0.15</v>
       </c>
-      <c r="D54" s="743"/>
-      <c r="E54" s="750"/>
-      <c r="G54" s="745" t="s">
-        <v>390</v>
+      <c r="D54" s="742"/>
+      <c r="E54" s="749"/>
+      <c r="G54" s="744" t="s">
+        <v>387</v>
       </c>
     </row>
     <row r="55" spans="1:18" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="389" t="s">
         <v>240</v>
       </c>
-      <c r="C55" s="749">
+      <c r="C55" s="748">
         <v>0.106</v>
       </c>
-      <c r="D55" s="743"/>
-      <c r="E55" s="750"/>
-      <c r="G55" s="678" t="s">
-        <v>552</v>
+      <c r="D55" s="742"/>
+      <c r="E55" s="749"/>
+      <c r="G55" s="677" t="s">
+        <v>546</v>
       </c>
     </row>
     <row r="56" spans="1:18" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="389" t="s">
         <v>242</v>
       </c>
-      <c r="C56" s="749">
+      <c r="C56" s="748">
         <v>7.4999999999999997E-2</v>
       </c>
-      <c r="D56" s="743"/>
-      <c r="E56" s="750"/>
-      <c r="H56" s="691"/>
-      <c r="I56" s="691"/>
-      <c r="J56" s="691"/>
-      <c r="K56" s="691"/>
-      <c r="L56" s="686"/>
-      <c r="M56" s="686"/>
+      <c r="D56" s="742"/>
+      <c r="E56" s="749"/>
+      <c r="H56" s="690"/>
+      <c r="I56" s="690"/>
+      <c r="J56" s="690"/>
+      <c r="K56" s="690"/>
+      <c r="L56" s="685"/>
+      <c r="M56" s="685"/>
     </row>
     <row r="57" spans="1:18" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="389" t="s">
-        <v>553</v>
-      </c>
-      <c r="C57" s="753" t="s">
+        <v>547</v>
+      </c>
+      <c r="C57" s="752" t="s">
         <v>262</v>
       </c>
-      <c r="D57" s="743"/>
-      <c r="E57" s="750"/>
-      <c r="G57" s="754"/>
-      <c r="H57" s="755"/>
-      <c r="I57" s="691"/>
-      <c r="J57" s="691"/>
-      <c r="K57" s="691"/>
-      <c r="L57" s="686"/>
-      <c r="M57" s="686"/>
-      <c r="O57" s="756"/>
-      <c r="P57" s="757"/>
-      <c r="Q57" s="757"/>
-      <c r="R57" s="757"/>
+      <c r="D57" s="742"/>
+      <c r="E57" s="749"/>
+      <c r="G57" s="753"/>
+      <c r="H57" s="754"/>
+      <c r="I57" s="690"/>
+      <c r="J57" s="690"/>
+      <c r="K57" s="690"/>
+      <c r="L57" s="685"/>
+      <c r="M57" s="685"/>
+      <c r="O57" s="755"/>
+      <c r="P57" s="756"/>
+      <c r="Q57" s="756"/>
+      <c r="R57" s="756"/>
     </row>
     <row r="58" spans="1:18" ht="3.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="O58" s="758"/>
-      <c r="P58" s="759"/>
-      <c r="R58" s="754"/>
+      <c r="O58" s="757"/>
+      <c r="P58" s="758"/>
+      <c r="R58" s="753"/>
     </row>
     <row r="59" spans="1:18" ht="9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="L59" s="686"/>
-      <c r="M59" s="686"/>
-      <c r="O59" s="758"/>
-      <c r="P59" s="759"/>
-      <c r="R59" s="760"/>
+      <c r="L59" s="685"/>
+      <c r="M59" s="685"/>
+      <c r="O59" s="757"/>
+      <c r="P59" s="758"/>
+      <c r="R59" s="759"/>
     </row>
     <row r="60" spans="1:18" ht="6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="761"/>
-      <c r="B60" s="745"/>
-      <c r="C60" s="745"/>
-      <c r="D60" s="745"/>
-      <c r="E60" s="745"/>
-      <c r="F60" s="745"/>
-      <c r="G60" s="745"/>
-      <c r="H60" s="745"/>
-      <c r="I60" s="745"/>
-      <c r="J60" s="745"/>
-      <c r="K60" s="745"/>
-      <c r="L60" s="686"/>
-      <c r="M60" s="686"/>
+      <c r="A60" s="760"/>
+      <c r="B60" s="744"/>
+      <c r="C60" s="744"/>
+      <c r="D60" s="744"/>
+      <c r="E60" s="744"/>
+      <c r="F60" s="744"/>
+      <c r="G60" s="744"/>
+      <c r="H60" s="744"/>
+      <c r="I60" s="744"/>
+      <c r="J60" s="744"/>
+      <c r="K60" s="744"/>
+      <c r="L60" s="685"/>
+      <c r="M60" s="685"/>
     </row>
     <row r="61" spans="1:18" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="260" t="s">
         <v>23</v>
       </c>
-      <c r="B61" s="745"/>
-      <c r="C61" s="745"/>
-      <c r="D61" s="745"/>
-      <c r="E61" s="745"/>
-      <c r="F61" s="745"/>
-      <c r="G61" s="745"/>
-      <c r="H61" s="745"/>
-      <c r="I61" s="745"/>
-      <c r="J61" s="745"/>
-      <c r="K61" s="745"/>
-      <c r="L61" s="686"/>
-      <c r="M61" s="686"/>
+      <c r="B61" s="744"/>
+      <c r="C61" s="744"/>
+      <c r="D61" s="744"/>
+      <c r="E61" s="744"/>
+      <c r="F61" s="744"/>
+      <c r="G61" s="744"/>
+      <c r="H61" s="744"/>
+      <c r="I61" s="744"/>
+      <c r="J61" s="744"/>
+      <c r="K61" s="744"/>
+      <c r="L61" s="685"/>
+      <c r="M61" s="685"/>
     </row>
     <row r="62" spans="1:18" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="427" t="s">
-        <v>554</v>
+        <v>548</v>
       </c>
       <c r="B62" s="487"/>
       <c r="C62" s="487"/>
       <c r="D62" s="487"/>
-      <c r="E62" s="824"/>
-      <c r="F62" s="824"/>
-      <c r="G62" s="824"/>
-      <c r="H62" s="824"/>
-      <c r="I62" s="824"/>
-      <c r="J62" s="824"/>
-      <c r="K62" s="745"/>
-      <c r="L62" s="686"/>
-      <c r="M62" s="686"/>
-    </row>
-    <row r="63" spans="1:18" ht="9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B63" s="745"/>
-      <c r="C63" s="745"/>
-      <c r="D63" s="745"/>
-      <c r="E63" s="745"/>
-      <c r="F63" s="745"/>
-      <c r="G63" s="745"/>
-      <c r="H63" s="745"/>
-      <c r="I63" s="745"/>
-      <c r="J63" s="745"/>
-      <c r="K63" s="745"/>
-      <c r="L63" s="686"/>
-      <c r="M63" s="686"/>
+      <c r="E62" s="823"/>
+      <c r="F62" s="823"/>
+      <c r="G62" s="823"/>
+      <c r="H62" s="823"/>
+      <c r="I62" s="823"/>
+      <c r="J62" s="823"/>
+      <c r="K62" s="744"/>
+      <c r="L62" s="685"/>
+      <c r="M62" s="685"/>
+    </row>
+    <row r="63" spans="1:18" ht="1.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B63" s="744"/>
+      <c r="C63" s="744"/>
+      <c r="D63" s="744"/>
+      <c r="E63" s="744"/>
+      <c r="F63" s="744"/>
+      <c r="G63" s="744"/>
+      <c r="H63" s="744"/>
+      <c r="I63" s="744"/>
+      <c r="J63" s="744"/>
+      <c r="K63" s="744"/>
+      <c r="L63" s="685"/>
+      <c r="M63" s="685"/>
     </row>
     <row r="64" spans="1:18" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D64" s="260"/>
       <c r="F64" s="260" t="s">
-        <v>555</v>
+        <v>549</v>
       </c>
       <c r="G64" s="260"/>
     </row>
     <row r="65" spans="1:11" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="819" t="s">
-        <v>556</v>
-      </c>
-      <c r="B65" s="819"/>
-      <c r="C65" s="819"/>
-      <c r="D65" s="819"/>
-      <c r="E65" s="819"/>
-      <c r="F65" s="819"/>
-      <c r="G65" s="819"/>
-      <c r="H65" s="819"/>
-      <c r="I65" s="819"/>
-      <c r="J65" s="819"/>
-      <c r="K65" s="819"/>
+      <c r="A65" s="818" t="s">
+        <v>550</v>
+      </c>
+      <c r="B65" s="818"/>
+      <c r="C65" s="818"/>
+      <c r="D65" s="818"/>
+      <c r="E65" s="818"/>
+      <c r="F65" s="818"/>
+      <c r="G65" s="818"/>
+      <c r="H65" s="818"/>
+      <c r="I65" s="818"/>
+      <c r="J65" s="818"/>
+      <c r="K65" s="818"/>
     </row>
     <row r="66" spans="1:11" ht="15.9" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="67" spans="1:11" ht="15.9" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -22840,7 +22788,7 @@
         <v>362</v>
       </c>
       <c r="R2" s="531" t="s">
-        <v>446</v>
+        <v>442</v>
       </c>
       <c r="S2" s="386"/>
       <c r="T2" s="279"/>
@@ -22865,14 +22813,14 @@
         <v>363</v>
       </c>
       <c r="R3" s="531" t="s">
-        <v>446</v>
+        <v>442</v>
       </c>
       <c r="S3" s="386"/>
       <c r="U3" s="562" t="s">
-        <v>472</v>
+        <v>467</v>
       </c>
       <c r="V3" s="542" t="s">
-        <v>446</v>
+        <v>442</v>
       </c>
       <c r="W3" s="284">
         <f>+FORMATO!J11</f>
@@ -22913,24 +22861,24 @@
       <c r="L5" s="566"/>
       <c r="M5" s="566"/>
       <c r="N5" s="566"/>
-      <c r="Q5" s="873" t="s">
+      <c r="Q5" s="872" t="s">
         <v>369</v>
       </c>
-      <c r="R5" s="874"/>
-      <c r="S5" s="874"/>
-      <c r="T5" s="874"/>
-      <c r="U5" s="874"/>
-      <c r="V5" s="875"/>
+      <c r="R5" s="873"/>
+      <c r="S5" s="873"/>
+      <c r="T5" s="873"/>
+      <c r="U5" s="873"/>
+      <c r="V5" s="874"/>
       <c r="X5" s="476" t="s">
         <v>370</v>
       </c>
       <c r="Y5" s="477"/>
       <c r="Z5" s="478"/>
-      <c r="AC5" s="658" t="s">
-        <v>476</v>
-      </c>
-      <c r="AD5" s="658" t="s">
-        <v>477</v>
+      <c r="AC5" s="657" t="s">
+        <v>471</v>
+      </c>
+      <c r="AD5" s="657" t="s">
+        <v>472</v>
       </c>
     </row>
     <row r="6" spans="1:30" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -22950,13 +22898,13 @@
       <c r="N6" s="566"/>
       <c r="Q6" s="567"/>
       <c r="R6" s="568" t="s">
-        <v>420</v>
+        <v>416</v>
       </c>
       <c r="S6" s="569" t="s">
         <v>85</v>
       </c>
       <c r="T6" s="563" t="s">
-        <v>429</v>
+        <v>425</v>
       </c>
       <c r="U6" s="563" t="s">
         <v>199</v>
@@ -22973,32 +22921,32 @@
       </c>
       <c r="AA6" s="279"/>
       <c r="AB6" s="279"/>
-      <c r="AC6" s="658" t="s">
-        <v>478</v>
-      </c>
-      <c r="AD6" s="658" t="s">
+      <c r="AC6" s="657" t="s">
+        <v>473</v>
+      </c>
+      <c r="AD6" s="657" t="s">
         <v>366</v>
       </c>
     </row>
     <row r="7" spans="1:30" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="783" t="s">
+      <c r="A7" s="782" t="s">
         <v>21</v>
       </c>
-      <c r="B7" s="783"/>
-      <c r="C7" s="783"/>
-      <c r="D7" s="783"/>
-      <c r="E7" s="783"/>
-      <c r="F7" s="783"/>
-      <c r="G7" s="783"/>
-      <c r="H7" s="783"/>
-      <c r="I7" s="783"/>
-      <c r="J7" s="783"/>
-      <c r="K7" s="783"/>
-      <c r="L7" s="783"/>
-      <c r="M7" s="783"/>
-      <c r="N7" s="783"/>
+      <c r="B7" s="782"/>
+      <c r="C7" s="782"/>
+      <c r="D7" s="782"/>
+      <c r="E7" s="782"/>
+      <c r="F7" s="782"/>
+      <c r="G7" s="782"/>
+      <c r="H7" s="782"/>
+      <c r="I7" s="782"/>
+      <c r="J7" s="782"/>
+      <c r="K7" s="782"/>
+      <c r="L7" s="782"/>
+      <c r="M7" s="782"/>
+      <c r="N7" s="782"/>
       <c r="Q7" s="480" t="s">
-        <v>426</v>
+        <v>422</v>
       </c>
       <c r="R7" s="571"/>
       <c r="S7" s="569"/>
@@ -23015,7 +22963,7 @@
         <v>0</v>
       </c>
       <c r="X7" s="481" t="s">
-        <v>430</v>
+        <v>426</v>
       </c>
       <c r="Y7" s="604">
         <f>+IF(R3="Global",FORMATO!K23,FORMATO!K25)</f>
@@ -23027,32 +22975,32 @@
       </c>
       <c r="AA7" s="279"/>
       <c r="AB7" s="279"/>
-      <c r="AC7" s="659">
+      <c r="AC7" s="658">
         <v>3</v>
       </c>
-      <c r="AD7" s="659">
+      <c r="AD7" s="658">
         <v>70000</v>
       </c>
     </row>
     <row r="8" spans="1:30" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="885">
+      <c r="A8" s="884">
         <v>0</v>
       </c>
-      <c r="B8" s="885"/>
-      <c r="C8" s="885"/>
-      <c r="D8" s="885"/>
-      <c r="E8" s="885"/>
-      <c r="F8" s="885"/>
-      <c r="G8" s="885"/>
-      <c r="H8" s="885"/>
-      <c r="I8" s="885"/>
-      <c r="J8" s="885"/>
-      <c r="K8" s="885"/>
-      <c r="L8" s="885"/>
-      <c r="M8" s="885"/>
-      <c r="N8" s="885"/>
+      <c r="B8" s="884"/>
+      <c r="C8" s="884"/>
+      <c r="D8" s="884"/>
+      <c r="E8" s="884"/>
+      <c r="F8" s="884"/>
+      <c r="G8" s="884"/>
+      <c r="H8" s="884"/>
+      <c r="I8" s="884"/>
+      <c r="J8" s="884"/>
+      <c r="K8" s="884"/>
+      <c r="L8" s="884"/>
+      <c r="M8" s="884"/>
+      <c r="N8" s="884"/>
       <c r="Q8" s="480" t="s">
-        <v>427</v>
+        <v>423</v>
       </c>
       <c r="R8" s="571"/>
       <c r="S8" s="569"/>
@@ -23069,7 +23017,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="X8" s="485" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
       <c r="Y8" s="604">
         <f>+IF(R3="Global",FORMATO!K23,FORMATO!K26)</f>
@@ -23084,29 +23032,29 @@
       <c r="AC8" s="596">
         <v>2</v>
       </c>
-      <c r="AD8" s="659">
+      <c r="AD8" s="658">
         <v>25000</v>
       </c>
     </row>
     <row r="9" spans="1:30" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="482" t="s">
-        <v>469</v>
+        <v>464</v>
       </c>
       <c r="B9" s="287" t="s">
         <v>0</v>
       </c>
-      <c r="C9" s="887">
+      <c r="C9" s="886">
         <f>+FORMATO!O2</f>
         <v>0</v>
       </c>
-      <c r="D9" s="887"/>
-      <c r="E9" s="887"/>
-      <c r="F9" s="887"/>
-      <c r="G9" s="887"/>
-      <c r="H9" s="887"/>
-      <c r="I9" s="887"/>
-      <c r="J9" s="887"/>
-      <c r="K9" s="887"/>
+      <c r="D9" s="886"/>
+      <c r="E9" s="886"/>
+      <c r="F9" s="886"/>
+      <c r="G9" s="886"/>
+      <c r="H9" s="886"/>
+      <c r="I9" s="886"/>
+      <c r="J9" s="886"/>
+      <c r="K9" s="886"/>
       <c r="L9" s="289" t="s">
         <v>31</v>
       </c>
@@ -23117,7 +23065,7 @@
         <v>243</v>
       </c>
       <c r="Q9" s="480" t="s">
-        <v>428</v>
+        <v>424</v>
       </c>
       <c r="R9" s="571"/>
       <c r="S9" s="571"/>
@@ -23137,10 +23085,10 @@
       </c>
       <c r="AA9" s="279"/>
       <c r="AB9" s="279"/>
-      <c r="AC9" s="660">
+      <c r="AC9" s="659">
         <v>1.5</v>
       </c>
-      <c r="AD9" s="659">
+      <c r="AD9" s="658">
         <v>10000</v>
       </c>
     </row>
@@ -23151,25 +23099,25 @@
       <c r="B10" s="288" t="s">
         <v>0</v>
       </c>
-      <c r="C10" s="887">
+      <c r="C10" s="886">
         <f>+FORMATO!O3</f>
         <v>0</v>
       </c>
-      <c r="D10" s="887"/>
-      <c r="E10" s="887"/>
-      <c r="F10" s="887"/>
-      <c r="G10" s="887"/>
-      <c r="H10" s="887"/>
-      <c r="I10" s="887"/>
-      <c r="J10" s="887"/>
-      <c r="K10" s="887"/>
-      <c r="L10" s="769" t="s">
-        <v>452</v>
+      <c r="D10" s="886"/>
+      <c r="E10" s="886"/>
+      <c r="F10" s="886"/>
+      <c r="G10" s="886"/>
+      <c r="H10" s="886"/>
+      <c r="I10" s="886"/>
+      <c r="J10" s="886"/>
+      <c r="K10" s="886"/>
+      <c r="L10" s="768" t="s">
+        <v>447</v>
       </c>
       <c r="M10" s="288" t="s">
         <v>0</v>
       </c>
-      <c r="N10" s="671">
+      <c r="N10" s="670">
         <f>+FORMATO!O7</f>
         <v>0</v>
       </c>
@@ -23179,7 +23127,7 @@
       <c r="AC10" s="596">
         <v>1</v>
       </c>
-      <c r="AD10" s="659">
+      <c r="AD10" s="658">
         <v>3000</v>
       </c>
     </row>
@@ -23190,48 +23138,48 @@
       <c r="B11" s="288" t="s">
         <v>0</v>
       </c>
-      <c r="C11" s="887">
+      <c r="C11" s="886">
         <f>+FORMATO!O4</f>
         <v>0</v>
       </c>
-      <c r="D11" s="887"/>
-      <c r="E11" s="887"/>
-      <c r="F11" s="887"/>
-      <c r="G11" s="887"/>
-      <c r="H11" s="887"/>
-      <c r="I11" s="887"/>
-      <c r="J11" s="887"/>
-      <c r="K11" s="887"/>
+      <c r="D11" s="886"/>
+      <c r="E11" s="886"/>
+      <c r="F11" s="886"/>
+      <c r="G11" s="886"/>
+      <c r="H11" s="886"/>
+      <c r="I11" s="886"/>
+      <c r="J11" s="886"/>
+      <c r="K11" s="886"/>
       <c r="L11" s="291" t="s">
-        <v>471</v>
+        <v>466</v>
       </c>
       <c r="M11" s="288" t="s">
         <v>0</v>
       </c>
-      <c r="N11" s="671">
+      <c r="N11" s="670">
         <f>+FORMATO!O9</f>
         <v>0</v>
       </c>
       <c r="O11" s="572"/>
       <c r="P11" s="572"/>
-      <c r="Q11" s="876" t="s">
+      <c r="Q11" s="875" t="s">
         <v>40</v>
       </c>
-      <c r="R11" s="886"/>
-      <c r="S11" s="886"/>
-      <c r="T11" s="886"/>
-      <c r="U11" s="886"/>
-      <c r="V11" s="877"/>
+      <c r="R11" s="885"/>
+      <c r="S11" s="885"/>
+      <c r="T11" s="885"/>
+      <c r="U11" s="885"/>
+      <c r="V11" s="876"/>
       <c r="X11" s="573" t="s">
         <v>198</v>
       </c>
       <c r="Y11" s="574"/>
       <c r="Z11" s="564"/>
-      <c r="AA11" s="653"/>
-      <c r="AC11" s="660">
+      <c r="AA11" s="652"/>
+      <c r="AC11" s="659">
         <v>0.75</v>
       </c>
-      <c r="AD11" s="659">
+      <c r="AD11" s="658">
         <v>1300</v>
       </c>
     </row>
@@ -23242,32 +23190,32 @@
       <c r="B12" s="288" t="s">
         <v>0</v>
       </c>
-      <c r="C12" s="887">
+      <c r="C12" s="886">
         <f>+FORMATO!O5</f>
         <v>0</v>
       </c>
-      <c r="D12" s="887"/>
-      <c r="E12" s="887"/>
-      <c r="F12" s="887"/>
-      <c r="G12" s="887"/>
-      <c r="H12" s="887"/>
-      <c r="I12" s="887"/>
-      <c r="J12" s="887"/>
-      <c r="K12" s="887"/>
-      <c r="L12" s="769" t="s">
+      <c r="D12" s="886"/>
+      <c r="E12" s="886"/>
+      <c r="F12" s="886"/>
+      <c r="G12" s="886"/>
+      <c r="H12" s="886"/>
+      <c r="I12" s="886"/>
+      <c r="J12" s="886"/>
+      <c r="K12" s="886"/>
+      <c r="L12" s="768" t="s">
         <v>253</v>
       </c>
       <c r="M12" s="288" t="s">
         <v>0</v>
       </c>
-      <c r="N12" s="651">
+      <c r="N12" s="650">
         <f>+FORMATO!O8</f>
         <v>0</v>
       </c>
       <c r="O12" s="572"/>
       <c r="P12" s="572"/>
       <c r="Q12" s="480" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
       <c r="R12" s="488"/>
       <c r="S12" s="488"/>
@@ -23284,11 +23232,11 @@
       <c r="Z12" s="565" t="s">
         <v>195</v>
       </c>
-      <c r="AA12" s="654"/>
-      <c r="AC12" s="661" t="s">
-        <v>479</v>
-      </c>
-      <c r="AD12" s="659">
+      <c r="AA12" s="653"/>
+      <c r="AC12" s="660" t="s">
+        <v>474</v>
+      </c>
+      <c r="AD12" s="658">
         <v>200</v>
       </c>
     </row>
@@ -23312,7 +23260,7 @@
       <c r="O13" s="572"/>
       <c r="P13" s="572"/>
       <c r="Q13" s="480" t="s">
-        <v>433</v>
+        <v>429</v>
       </c>
       <c r="R13" s="491"/>
       <c r="S13" s="491"/>
@@ -23326,39 +23274,39 @@
         <v>196</v>
       </c>
       <c r="Y13" s="306"/>
-      <c r="Z13" s="666" t="str">
+      <c r="Z13" s="665" t="str">
         <f>+Balanza!B11</f>
         <v>EQP-0046</v>
       </c>
-      <c r="AA13" s="655"/>
+      <c r="AA13" s="654"/>
       <c r="AC13" s="596" t="s">
-        <v>480</v>
-      </c>
-      <c r="AD13" s="659">
+        <v>475</v>
+      </c>
+      <c r="AD13" s="658">
         <v>200</v>
       </c>
     </row>
     <row r="14" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="878" t="s">
+      <c r="A14" s="877" t="s">
         <v>250</v>
       </c>
-      <c r="B14" s="879"/>
-      <c r="C14" s="879"/>
-      <c r="D14" s="880"/>
-      <c r="E14" s="879"/>
-      <c r="F14" s="880"/>
-      <c r="G14" s="880"/>
-      <c r="H14" s="880"/>
-      <c r="I14" s="880"/>
-      <c r="J14" s="880"/>
-      <c r="K14" s="880"/>
-      <c r="L14" s="880"/>
-      <c r="M14" s="880"/>
-      <c r="N14" s="881"/>
+      <c r="B14" s="878"/>
+      <c r="C14" s="878"/>
+      <c r="D14" s="879"/>
+      <c r="E14" s="878"/>
+      <c r="F14" s="879"/>
+      <c r="G14" s="879"/>
+      <c r="H14" s="879"/>
+      <c r="I14" s="879"/>
+      <c r="J14" s="879"/>
+      <c r="K14" s="879"/>
+      <c r="L14" s="879"/>
+      <c r="M14" s="879"/>
+      <c r="N14" s="880"/>
       <c r="O14" s="572"/>
       <c r="P14" s="572"/>
       <c r="Q14" s="480" t="s">
-        <v>434</v>
+        <v>430</v>
       </c>
       <c r="R14" s="491"/>
       <c r="S14" s="491"/>
@@ -23369,38 +23317,38 @@
         <v>0</v>
       </c>
       <c r="X14" s="577" t="s">
-        <v>419</v>
+        <v>415</v>
       </c>
       <c r="Y14" s="306"/>
-      <c r="Z14" s="667">
+      <c r="Z14" s="666">
         <f>+Balanza!B7</f>
         <v>-3.2899999999999998E-6</v>
       </c>
-      <c r="AA14" s="656"/>
+      <c r="AA14" s="655"/>
       <c r="AC14" s="596" t="s">
-        <v>446</v>
-      </c>
-      <c r="AD14" s="659" t="s">
-        <v>446</v>
+        <v>442</v>
+      </c>
+      <c r="AD14" s="658" t="s">
+        <v>442</v>
       </c>
     </row>
     <row r="15" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="882" t="s">
-        <v>484</v>
-      </c>
-      <c r="B15" s="883"/>
-      <c r="C15" s="883"/>
-      <c r="D15" s="883"/>
-      <c r="E15" s="883"/>
-      <c r="F15" s="883"/>
-      <c r="G15" s="883"/>
-      <c r="H15" s="883"/>
-      <c r="I15" s="883"/>
-      <c r="J15" s="883"/>
-      <c r="K15" s="883"/>
-      <c r="L15" s="883"/>
-      <c r="M15" s="883"/>
-      <c r="N15" s="884"/>
+      <c r="A15" s="881" t="s">
+        <v>479</v>
+      </c>
+      <c r="B15" s="882"/>
+      <c r="C15" s="882"/>
+      <c r="D15" s="882"/>
+      <c r="E15" s="882"/>
+      <c r="F15" s="882"/>
+      <c r="G15" s="882"/>
+      <c r="H15" s="882"/>
+      <c r="I15" s="882"/>
+      <c r="J15" s="882"/>
+      <c r="K15" s="882"/>
+      <c r="L15" s="882"/>
+      <c r="M15" s="882"/>
+      <c r="N15" s="883"/>
       <c r="O15" s="572"/>
       <c r="P15" s="572"/>
       <c r="V15" s="387"/>
@@ -23408,11 +23356,11 @@
         <v>197</v>
       </c>
       <c r="Y15" s="557"/>
-      <c r="Z15" s="668">
+      <c r="Z15" s="667">
         <f>+Balanza!C12</f>
         <v>46132</v>
       </c>
-      <c r="AA15" s="657"/>
+      <c r="AA15" s="656"/>
       <c r="AB15" s="579"/>
     </row>
     <row r="16" spans="1:30" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -23432,14 +23380,14 @@
       <c r="N16" s="298"/>
       <c r="O16" s="572"/>
       <c r="P16" s="572"/>
-      <c r="Q16" s="876" t="s">
-        <v>442</v>
-      </c>
-      <c r="R16" s="886"/>
-      <c r="S16" s="886"/>
-      <c r="T16" s="886"/>
-      <c r="U16" s="886"/>
-      <c r="V16" s="877"/>
+      <c r="Q16" s="875" t="s">
+        <v>438</v>
+      </c>
+      <c r="R16" s="885"/>
+      <c r="S16" s="885"/>
+      <c r="T16" s="885"/>
+      <c r="U16" s="885"/>
+      <c r="V16" s="876"/>
       <c r="W16" s="580"/>
     </row>
     <row r="17" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -23461,7 +23409,7 @@
       <c r="N17" s="302"/>
       <c r="P17" s="572"/>
       <c r="Q17" s="480" t="s">
-        <v>438</v>
+        <v>434</v>
       </c>
       <c r="R17" s="493"/>
       <c r="S17" s="571"/>
@@ -23474,14 +23422,14 @@
         <f>U17+(U17*$Z$14)</f>
         <v>0</v>
       </c>
-      <c r="X17" s="858" t="s">
-        <v>437</v>
-      </c>
-      <c r="Y17" s="859"/>
-      <c r="Z17" s="859"/>
-      <c r="AA17" s="860"/>
+      <c r="X17" s="857" t="s">
+        <v>433</v>
+      </c>
+      <c r="Y17" s="858"/>
+      <c r="Z17" s="858"/>
+      <c r="AA17" s="859"/>
       <c r="AB17" s="601" t="s">
-        <v>445</v>
+        <v>441</v>
       </c>
     </row>
     <row r="18" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -23508,13 +23456,13 @@
       <c r="M18" s="301" t="s">
         <v>0</v>
       </c>
-      <c r="N18" s="672">
+      <c r="N18" s="671">
         <f>+FORMATO!O11</f>
         <v>0</v>
       </c>
       <c r="P18" s="572"/>
       <c r="Q18" s="494" t="s">
-        <v>439</v>
+        <v>435</v>
       </c>
       <c r="R18" s="495"/>
       <c r="S18" s="571"/>
@@ -23527,7 +23475,7 @@
         <v>0</v>
       </c>
       <c r="X18" s="611" t="s">
-        <v>443</v>
+        <v>439</v>
       </c>
       <c r="Y18" s="569"/>
       <c r="Z18" s="612" t="s">
@@ -23561,13 +23509,13 @@
       <c r="M19" s="301" t="s">
         <v>0</v>
       </c>
-      <c r="N19" s="652">
+      <c r="N19" s="651">
         <f>+FORMATO!O12</f>
         <v>0</v>
       </c>
       <c r="P19" s="572"/>
       <c r="Q19" s="494" t="s">
-        <v>440</v>
+        <v>436</v>
       </c>
       <c r="R19" s="495"/>
       <c r="S19" s="571"/>
@@ -23581,7 +23529,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="X19" s="608" t="s">
-        <v>441</v>
+        <v>437</v>
       </c>
       <c r="Y19" s="609"/>
       <c r="Z19" s="613">
@@ -23616,7 +23564,7 @@
       <c r="M20" s="301" t="s">
         <v>0</v>
       </c>
-      <c r="N20" s="652">
+      <c r="N20" s="651">
         <f>+FORMATO!O13</f>
         <v>0</v>
       </c>
@@ -23637,7 +23585,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="X20" s="605" t="s">
-        <v>444</v>
+        <v>440</v>
       </c>
       <c r="Y20" s="606"/>
       <c r="Z20" s="606"/>
@@ -23656,7 +23604,7 @@
         <v>0</v>
       </c>
       <c r="E21" s="530" t="s">
-        <v>425</v>
+        <v>421</v>
       </c>
       <c r="F21" s="499"/>
       <c r="G21" s="582"/>
@@ -23665,7 +23613,7 @@
       <c r="J21" s="582"/>
       <c r="K21" s="583"/>
       <c r="L21" s="539" t="s">
-        <v>421</v>
+        <v>417</v>
       </c>
       <c r="M21" s="540" t="s">
         <v>0</v>
@@ -23676,7 +23624,7 @@
       </c>
       <c r="P21" s="572"/>
       <c r="X21" s="600" t="s">
-        <v>436</v>
+        <v>432</v>
       </c>
       <c r="Y21" s="571"/>
       <c r="Z21" s="569"/>
@@ -23686,7 +23634,7 @@
       </c>
     </row>
     <row r="22" spans="1:32" ht="10.199999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="631"/>
+      <c r="A22" s="630"/>
       <c r="B22" s="419"/>
       <c r="C22" s="419"/>
       <c r="D22" s="421"/>
@@ -23697,37 +23645,37 @@
       <c r="I22" s="421"/>
       <c r="J22" s="421"/>
       <c r="K22" s="421"/>
-      <c r="L22" s="632"/>
-      <c r="M22" s="632"/>
-      <c r="N22" s="633"/>
+      <c r="L22" s="631"/>
+      <c r="M22" s="631"/>
+      <c r="N22" s="632"/>
       <c r="O22" s="572"/>
       <c r="P22" s="584"/>
     </row>
     <row r="23" spans="1:32" ht="31.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="634"/>
-      <c r="B23" s="625"/>
-      <c r="C23" s="625"/>
-      <c r="D23" s="625"/>
-      <c r="E23" s="863" t="s">
-        <v>453</v>
-      </c>
-      <c r="F23" s="869"/>
-      <c r="G23" s="869"/>
-      <c r="H23" s="869"/>
-      <c r="I23" s="869"/>
-      <c r="J23" s="864"/>
-      <c r="K23" s="861" t="s">
+      <c r="A23" s="633"/>
+      <c r="B23" s="624"/>
+      <c r="C23" s="624"/>
+      <c r="D23" s="624"/>
+      <c r="E23" s="862" t="s">
+        <v>448</v>
+      </c>
+      <c r="F23" s="868"/>
+      <c r="G23" s="868"/>
+      <c r="H23" s="868"/>
+      <c r="I23" s="868"/>
+      <c r="J23" s="863"/>
+      <c r="K23" s="860" t="s">
         <v>385</v>
       </c>
-      <c r="L23" s="625"/>
-      <c r="M23" s="635"/>
+      <c r="L23" s="624"/>
+      <c r="M23" s="634"/>
       <c r="N23" s="307"/>
       <c r="O23" s="572"/>
       <c r="P23" s="585"/>
-      <c r="Q23" s="876" t="s">
+      <c r="Q23" s="875" t="s">
         <v>357</v>
       </c>
-      <c r="R23" s="877"/>
+      <c r="R23" s="876"/>
       <c r="S23" s="388" t="s">
         <v>356</v>
       </c>
@@ -23744,10 +23692,10 @@
         <v>375</v>
       </c>
       <c r="X23" s="501"/>
-      <c r="Y23" s="662" t="s">
-        <v>481</v>
-      </c>
-      <c r="Z23" s="663">
+      <c r="Y23" s="661" t="s">
+        <v>476</v>
+      </c>
+      <c r="Z23" s="662">
         <v>3</v>
       </c>
       <c r="AC23" s="586"/>
@@ -23756,23 +23704,23 @@
       <c r="AF23" s="502"/>
     </row>
     <row r="24" spans="1:32" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="634"/>
-      <c r="B24" s="625"/>
-      <c r="C24" s="625"/>
-      <c r="D24" s="625"/>
-      <c r="E24" s="863" t="s">
+      <c r="A24" s="633"/>
+      <c r="B24" s="624"/>
+      <c r="C24" s="624"/>
+      <c r="D24" s="624"/>
+      <c r="E24" s="862" t="s">
         <v>358</v>
       </c>
-      <c r="F24" s="869"/>
-      <c r="G24" s="869"/>
-      <c r="H24" s="864"/>
-      <c r="I24" s="863" t="s">
-        <v>462</v>
-      </c>
-      <c r="J24" s="864"/>
-      <c r="K24" s="862"/>
-      <c r="L24" s="625"/>
-      <c r="M24" s="635"/>
+      <c r="F24" s="868"/>
+      <c r="G24" s="868"/>
+      <c r="H24" s="863"/>
+      <c r="I24" s="862" t="s">
+        <v>457</v>
+      </c>
+      <c r="J24" s="863"/>
+      <c r="K24" s="861"/>
+      <c r="L24" s="624"/>
+      <c r="M24" s="634"/>
       <c r="N24" s="307"/>
       <c r="O24" s="572"/>
       <c r="P24" s="587"/>
@@ -23780,7 +23728,7 @@
         <v>358</v>
       </c>
       <c r="R24" s="503" t="s">
-        <v>423</v>
+        <v>419</v>
       </c>
       <c r="S24" s="503" t="s">
         <v>366</v>
@@ -23798,14 +23746,14 @@
         <v>359</v>
       </c>
       <c r="X24" s="501"/>
-      <c r="Y24" s="662" t="s">
-        <v>482</v>
-      </c>
-      <c r="Z24" s="664">
+      <c r="Y24" s="661" t="s">
+        <v>477</v>
+      </c>
+      <c r="Z24" s="663">
         <f>+INDEX(AC7:AD14,MATCH(Z23,AC7:AC14,0),2)</f>
         <v>70000</v>
       </c>
-      <c r="AA24" s="665" t="e">
+      <c r="AA24" s="664" t="e">
         <f>+IF((V9)&gt;Z24,"Cumple","No Cumple")</f>
         <v>#DIV/0!</v>
       </c>
@@ -23815,26 +23763,26 @@
       <c r="AF24" s="502"/>
     </row>
     <row r="25" spans="1:32" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="636"/>
-      <c r="B25" s="627"/>
-      <c r="C25" s="627"/>
-      <c r="D25" s="627"/>
-      <c r="E25" s="870" t="s">
+      <c r="A25" s="635"/>
+      <c r="B25" s="626"/>
+      <c r="C25" s="626"/>
+      <c r="D25" s="626"/>
+      <c r="E25" s="869" t="s">
         <v>350</v>
       </c>
-      <c r="F25" s="871"/>
-      <c r="G25" s="871"/>
-      <c r="H25" s="872"/>
-      <c r="I25" s="865" t="s">
-        <v>454</v>
-      </c>
-      <c r="J25" s="866"/>
-      <c r="K25" s="621" t="e">
+      <c r="F25" s="870"/>
+      <c r="G25" s="870"/>
+      <c r="H25" s="871"/>
+      <c r="I25" s="864" t="s">
+        <v>449</v>
+      </c>
+      <c r="J25" s="865"/>
+      <c r="K25" s="620" t="e">
         <f>IF($I$66="Método A",FIXED(($W$25),0),FIXED(($W$25),1))</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="L25" s="626"/>
-      <c r="M25" s="637"/>
+      <c r="L25" s="625"/>
+      <c r="M25" s="636"/>
       <c r="N25" s="310"/>
       <c r="O25" s="588"/>
       <c r="P25" s="587"/>
@@ -23844,7 +23792,7 @@
       <c r="R25" s="389">
         <v>75</v>
       </c>
-      <c r="S25" s="670">
+      <c r="S25" s="669">
         <f>+FORMATO!E42</f>
         <v>0</v>
       </c>
@@ -23871,26 +23819,26 @@
       <c r="AF25" s="502"/>
     </row>
     <row r="26" spans="1:32" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="636"/>
-      <c r="B26" s="627"/>
-      <c r="C26" s="627"/>
-      <c r="D26" s="627"/>
-      <c r="E26" s="836" t="s">
+      <c r="A26" s="635"/>
+      <c r="B26" s="626"/>
+      <c r="C26" s="626"/>
+      <c r="D26" s="626"/>
+      <c r="E26" s="835" t="s">
         <v>351</v>
       </c>
-      <c r="F26" s="837"/>
-      <c r="G26" s="837"/>
-      <c r="H26" s="838"/>
-      <c r="I26" s="867" t="s">
-        <v>455</v>
-      </c>
-      <c r="J26" s="868"/>
-      <c r="K26" s="622" t="e">
+      <c r="F26" s="836"/>
+      <c r="G26" s="836"/>
+      <c r="H26" s="837"/>
+      <c r="I26" s="866" t="s">
+        <v>450</v>
+      </c>
+      <c r="J26" s="867"/>
+      <c r="K26" s="621" t="e">
         <f>IF($I$66="Método A",FIXED(($W$26),0),FIXED(($W$26),1))</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="L26" s="626"/>
-      <c r="M26" s="624"/>
+      <c r="L26" s="625"/>
+      <c r="M26" s="623"/>
       <c r="N26" s="313"/>
       <c r="O26" s="572"/>
       <c r="P26" s="572"/>
@@ -23900,7 +23848,7 @@
       <c r="R26" s="389">
         <v>50</v>
       </c>
-      <c r="S26" s="670">
+      <c r="S26" s="669">
         <f>+FORMATO!E43</f>
         <v>0</v>
       </c>
@@ -23927,26 +23875,26 @@
       <c r="AF26" s="502"/>
     </row>
     <row r="27" spans="1:32" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="638"/>
-      <c r="B27" s="628"/>
-      <c r="C27" s="628"/>
-      <c r="D27" s="628"/>
-      <c r="E27" s="831" t="s">
+      <c r="A27" s="637"/>
+      <c r="B27" s="627"/>
+      <c r="C27" s="627"/>
+      <c r="D27" s="627"/>
+      <c r="E27" s="830" t="s">
         <v>353</v>
       </c>
-      <c r="F27" s="832"/>
-      <c r="G27" s="832"/>
-      <c r="H27" s="833"/>
-      <c r="I27" s="834" t="s">
-        <v>456</v>
-      </c>
-      <c r="J27" s="835"/>
-      <c r="K27" s="622" t="e">
+      <c r="F27" s="831"/>
+      <c r="G27" s="831"/>
+      <c r="H27" s="832"/>
+      <c r="I27" s="833" t="s">
+        <v>451</v>
+      </c>
+      <c r="J27" s="834"/>
+      <c r="K27" s="621" t="e">
         <f>IF($I$66="Método A",FIXED(($W$27),0),FIXED(($W$27),1))</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="L27" s="626"/>
-      <c r="M27" s="624"/>
+      <c r="L27" s="625"/>
+      <c r="M27" s="623"/>
       <c r="N27" s="313"/>
       <c r="O27" s="572"/>
       <c r="P27" s="572"/>
@@ -23956,7 +23904,7 @@
       <c r="R27" s="389">
         <v>37.5</v>
       </c>
-      <c r="S27" s="670">
+      <c r="S27" s="669">
         <f>+FORMATO!E44</f>
         <v>0</v>
       </c>
@@ -23983,26 +23931,26 @@
       <c r="AF27" s="502"/>
     </row>
     <row r="28" spans="1:32" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="636"/>
-      <c r="B28" s="627"/>
-      <c r="C28" s="627"/>
-      <c r="D28" s="627"/>
-      <c r="E28" s="836" t="s">
+      <c r="A28" s="635"/>
+      <c r="B28" s="626"/>
+      <c r="C28" s="626"/>
+      <c r="D28" s="626"/>
+      <c r="E28" s="835" t="s">
         <v>352</v>
       </c>
-      <c r="F28" s="837"/>
-      <c r="G28" s="837"/>
-      <c r="H28" s="838"/>
-      <c r="I28" s="834" t="s">
-        <v>457</v>
-      </c>
-      <c r="J28" s="835"/>
-      <c r="K28" s="622" t="e">
+      <c r="F28" s="836"/>
+      <c r="G28" s="836"/>
+      <c r="H28" s="837"/>
+      <c r="I28" s="833" t="s">
+        <v>452</v>
+      </c>
+      <c r="J28" s="834"/>
+      <c r="K28" s="621" t="e">
         <f>IF($I$66="Método A",FIXED(($W$28),0),FIXED(($W$28),1))</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="L28" s="626"/>
-      <c r="M28" s="624"/>
+      <c r="L28" s="625"/>
+      <c r="M28" s="623"/>
       <c r="N28" s="313"/>
       <c r="O28" s="572"/>
       <c r="P28" s="572"/>
@@ -24012,7 +23960,7 @@
       <c r="R28" s="389">
         <v>25</v>
       </c>
-      <c r="S28" s="670">
+      <c r="S28" s="669">
         <f>+FORMATO!E45</f>
         <v>0</v>
       </c>
@@ -24039,26 +23987,26 @@
       <c r="AF28" s="502"/>
     </row>
     <row r="29" spans="1:32" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="636"/>
-      <c r="B29" s="627"/>
-      <c r="C29" s="627"/>
-      <c r="D29" s="627"/>
-      <c r="E29" s="836" t="s">
+      <c r="A29" s="635"/>
+      <c r="B29" s="626"/>
+      <c r="C29" s="626"/>
+      <c r="D29" s="626"/>
+      <c r="E29" s="835" t="s">
         <v>354</v>
       </c>
-      <c r="F29" s="837"/>
-      <c r="G29" s="837"/>
-      <c r="H29" s="838"/>
-      <c r="I29" s="834" t="s">
-        <v>458</v>
-      </c>
-      <c r="J29" s="835"/>
-      <c r="K29" s="622" t="e">
+      <c r="F29" s="836"/>
+      <c r="G29" s="836"/>
+      <c r="H29" s="837"/>
+      <c r="I29" s="833" t="s">
+        <v>453</v>
+      </c>
+      <c r="J29" s="834"/>
+      <c r="K29" s="621" t="e">
         <f>IF($I$66="Método A",FIXED(($W$29),0),FIXED(($W$29),1))</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="L29" s="626"/>
-      <c r="M29" s="624"/>
+      <c r="L29" s="625"/>
+      <c r="M29" s="623"/>
       <c r="N29" s="313"/>
       <c r="O29" s="572"/>
       <c r="P29" s="572"/>
@@ -24068,7 +24016,7 @@
       <c r="R29" s="504">
         <v>19</v>
       </c>
-      <c r="S29" s="670">
+      <c r="S29" s="669">
         <f>+FORMATO!E46</f>
         <v>0</v>
       </c>
@@ -24095,26 +24043,26 @@
       <c r="AF29" s="502"/>
     </row>
     <row r="30" spans="1:32" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="636"/>
-      <c r="B30" s="627"/>
-      <c r="C30" s="627"/>
-      <c r="D30" s="627"/>
-      <c r="E30" s="836" t="s">
+      <c r="A30" s="635"/>
+      <c r="B30" s="626"/>
+      <c r="C30" s="626"/>
+      <c r="D30" s="626"/>
+      <c r="E30" s="835" t="s">
         <v>355</v>
       </c>
-      <c r="F30" s="837"/>
-      <c r="G30" s="837"/>
-      <c r="H30" s="838"/>
-      <c r="I30" s="834" t="s">
-        <v>459</v>
-      </c>
-      <c r="J30" s="835"/>
-      <c r="K30" s="622" t="e">
+      <c r="F30" s="836"/>
+      <c r="G30" s="836"/>
+      <c r="H30" s="837"/>
+      <c r="I30" s="833" t="s">
+        <v>454</v>
+      </c>
+      <c r="J30" s="834"/>
+      <c r="K30" s="621" t="e">
         <f>IF($I$66="Método A",FIXED(($W$30),0),FIXED(($W$30),1))</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="L30" s="626"/>
-      <c r="M30" s="624"/>
+      <c r="L30" s="625"/>
+      <c r="M30" s="623"/>
       <c r="N30" s="313"/>
       <c r="O30" s="572"/>
       <c r="P30" s="572"/>
@@ -24124,7 +24072,7 @@
       <c r="R30" s="389">
         <v>9.5</v>
       </c>
-      <c r="S30" s="670">
+      <c r="S30" s="669">
         <f>+FORMATO!E47</f>
         <v>0</v>
       </c>
@@ -24151,26 +24099,26 @@
       <c r="AF30" s="502"/>
     </row>
     <row r="31" spans="1:32" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="636"/>
-      <c r="B31" s="627"/>
-      <c r="C31" s="627"/>
-      <c r="D31" s="627"/>
-      <c r="E31" s="836" t="s">
+      <c r="A31" s="635"/>
+      <c r="B31" s="626"/>
+      <c r="C31" s="626"/>
+      <c r="D31" s="626"/>
+      <c r="E31" s="835" t="s">
         <v>231</v>
       </c>
-      <c r="F31" s="837"/>
-      <c r="G31" s="837"/>
-      <c r="H31" s="838"/>
-      <c r="I31" s="839" t="s">
-        <v>460</v>
-      </c>
-      <c r="J31" s="840"/>
-      <c r="K31" s="622" t="e">
+      <c r="F31" s="836"/>
+      <c r="G31" s="836"/>
+      <c r="H31" s="837"/>
+      <c r="I31" s="838" t="s">
+        <v>455</v>
+      </c>
+      <c r="J31" s="839"/>
+      <c r="K31" s="621" t="e">
         <f>IF($I$66="Método A",FIXED(($W$31),0),FIXED(($W$31),1))</f>
         <v>#DIV/0!</v>
       </c>
       <c r="L31" s="305"/>
-      <c r="M31" s="624"/>
+      <c r="M31" s="623"/>
       <c r="N31" s="313"/>
       <c r="O31" s="572"/>
       <c r="P31" s="572"/>
@@ -24180,7 +24128,7 @@
       <c r="R31" s="389">
         <v>4.75</v>
       </c>
-      <c r="S31" s="670">
+      <c r="S31" s="669">
         <f>+FORMATO!E48</f>
         <v>0</v>
       </c>
@@ -24192,7 +24140,7 @@
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="V31" s="647" t="e">
+      <c r="V31" s="646" t="e">
         <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
@@ -24211,26 +24159,26 @@
       <c r="AF31" s="502"/>
     </row>
     <row r="32" spans="1:32" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="636"/>
-      <c r="B32" s="627"/>
-      <c r="C32" s="627"/>
-      <c r="D32" s="627"/>
-      <c r="E32" s="836" t="s">
+      <c r="A32" s="635"/>
+      <c r="B32" s="626"/>
+      <c r="C32" s="626"/>
+      <c r="D32" s="626"/>
+      <c r="E32" s="835" t="s">
         <v>232</v>
       </c>
-      <c r="F32" s="837"/>
-      <c r="G32" s="837"/>
-      <c r="H32" s="838"/>
-      <c r="I32" s="839" t="s">
-        <v>461</v>
-      </c>
-      <c r="J32" s="840"/>
-      <c r="K32" s="622" t="e">
+      <c r="F32" s="836"/>
+      <c r="G32" s="836"/>
+      <c r="H32" s="837"/>
+      <c r="I32" s="838" t="s">
+        <v>456</v>
+      </c>
+      <c r="J32" s="839"/>
+      <c r="K32" s="621" t="e">
         <f>IF($I$66="Método A",FIXED(($W$32),0),FIXED(($W$32),1))</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="L32" s="639"/>
-      <c r="M32" s="624"/>
+      <c r="L32" s="638"/>
+      <c r="M32" s="623"/>
       <c r="N32" s="313"/>
       <c r="O32" s="572"/>
       <c r="P32" s="572"/>
@@ -24240,7 +24188,7 @@
       <c r="R32" s="389">
         <v>2</v>
       </c>
-      <c r="S32" s="670">
+      <c r="S32" s="669">
         <f>+FORMATO!E50</f>
         <v>0</v>
       </c>
@@ -24271,26 +24219,26 @@
       <c r="AF32" s="502"/>
     </row>
     <row r="33" spans="1:31" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="636"/>
-      <c r="B33" s="627"/>
-      <c r="C33" s="627"/>
-      <c r="D33" s="627"/>
-      <c r="E33" s="836" t="s">
+      <c r="A33" s="635"/>
+      <c r="B33" s="626"/>
+      <c r="C33" s="626"/>
+      <c r="D33" s="626"/>
+      <c r="E33" s="835" t="s">
         <v>238</v>
       </c>
-      <c r="F33" s="837"/>
-      <c r="G33" s="837"/>
-      <c r="H33" s="838"/>
-      <c r="I33" s="841" t="s">
-        <v>463</v>
-      </c>
-      <c r="J33" s="842"/>
-      <c r="K33" s="622" t="e">
+      <c r="F33" s="836"/>
+      <c r="G33" s="836"/>
+      <c r="H33" s="837"/>
+      <c r="I33" s="840" t="s">
+        <v>458</v>
+      </c>
+      <c r="J33" s="841"/>
+      <c r="K33" s="621" t="e">
         <f>IF($I$66="Método A",FIXED(($W$33),0),FIXED(($W$33),1))</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="L33" s="639"/>
-      <c r="M33" s="624"/>
+      <c r="L33" s="638"/>
+      <c r="M33" s="623"/>
       <c r="N33" s="313"/>
       <c r="O33" s="572"/>
       <c r="P33" s="572"/>
@@ -24300,7 +24248,7 @@
       <c r="R33" s="507">
         <v>0.85</v>
       </c>
-      <c r="S33" s="670">
+      <c r="S33" s="669">
         <f>+FORMATO!E51</f>
         <v>0</v>
       </c>
@@ -24323,36 +24271,36 @@
       <c r="X33" s="506"/>
     </row>
     <row r="34" spans="1:31" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="636"/>
-      <c r="B34" s="627"/>
-      <c r="C34" s="627"/>
-      <c r="D34" s="627"/>
-      <c r="E34" s="836" t="s">
-        <v>422</v>
-      </c>
-      <c r="F34" s="837"/>
-      <c r="G34" s="837"/>
-      <c r="H34" s="838"/>
-      <c r="I34" s="841" t="s">
-        <v>464</v>
-      </c>
-      <c r="J34" s="842"/>
-      <c r="K34" s="622" t="e">
+      <c r="A34" s="635"/>
+      <c r="B34" s="626"/>
+      <c r="C34" s="626"/>
+      <c r="D34" s="626"/>
+      <c r="E34" s="835" t="s">
+        <v>418</v>
+      </c>
+      <c r="F34" s="836"/>
+      <c r="G34" s="836"/>
+      <c r="H34" s="837"/>
+      <c r="I34" s="840" t="s">
+        <v>459</v>
+      </c>
+      <c r="J34" s="841"/>
+      <c r="K34" s="621" t="e">
         <f>IF($I$66="Método A",FIXED(($W$34),0),FIXED(($W$34),1))</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="L34" s="640"/>
-      <c r="M34" s="624"/>
+      <c r="L34" s="639"/>
+      <c r="M34" s="623"/>
       <c r="N34" s="313"/>
       <c r="O34" s="572"/>
       <c r="P34" s="572"/>
       <c r="Q34" s="389" t="s">
-        <v>422</v>
+        <v>418</v>
       </c>
       <c r="R34" s="389">
         <v>0.42499999999999999</v>
       </c>
-      <c r="S34" s="670">
+      <c r="S34" s="669">
         <f>+FORMATO!E52</f>
         <v>0</v>
       </c>
@@ -24364,7 +24312,7 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="V34" s="647" t="e">
+      <c r="V34" s="646" t="e">
         <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
@@ -24379,26 +24327,26 @@
       <c r="AE34" s="590"/>
     </row>
     <row r="35" spans="1:31" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="636"/>
-      <c r="B35" s="627"/>
-      <c r="C35" s="627"/>
-      <c r="D35" s="627"/>
-      <c r="E35" s="836" t="s">
+      <c r="A35" s="635"/>
+      <c r="B35" s="626"/>
+      <c r="C35" s="626"/>
+      <c r="D35" s="626"/>
+      <c r="E35" s="835" t="s">
         <v>239</v>
       </c>
-      <c r="F35" s="837"/>
-      <c r="G35" s="837"/>
-      <c r="H35" s="838"/>
-      <c r="I35" s="841" t="s">
-        <v>465</v>
-      </c>
-      <c r="J35" s="842"/>
-      <c r="K35" s="622" t="e">
+      <c r="F35" s="836"/>
+      <c r="G35" s="836"/>
+      <c r="H35" s="837"/>
+      <c r="I35" s="840" t="s">
+        <v>460</v>
+      </c>
+      <c r="J35" s="841"/>
+      <c r="K35" s="621" t="e">
         <f>IF($I$66="Método A",FIXED(($W$35),0),FIXED(($W$35),1))</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="L35" s="640"/>
-      <c r="M35" s="624"/>
+      <c r="L35" s="639"/>
+      <c r="M35" s="623"/>
       <c r="N35" s="313"/>
       <c r="O35" s="572"/>
       <c r="P35" s="572"/>
@@ -24408,7 +24356,7 @@
       <c r="R35" s="507">
         <v>0.25</v>
       </c>
-      <c r="S35" s="670">
+      <c r="S35" s="669">
         <f>+FORMATO!E53</f>
         <v>0</v>
       </c>
@@ -24435,26 +24383,26 @@
       <c r="AE35" s="589"/>
     </row>
     <row r="36" spans="1:31" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="636"/>
-      <c r="B36" s="627"/>
-      <c r="C36" s="627"/>
-      <c r="D36" s="627"/>
-      <c r="E36" s="836" t="s">
+      <c r="A36" s="635"/>
+      <c r="B36" s="626"/>
+      <c r="C36" s="626"/>
+      <c r="D36" s="626"/>
+      <c r="E36" s="835" t="s">
         <v>241</v>
       </c>
-      <c r="F36" s="837"/>
-      <c r="G36" s="837"/>
-      <c r="H36" s="838"/>
-      <c r="I36" s="841" t="s">
-        <v>466</v>
-      </c>
-      <c r="J36" s="842"/>
-      <c r="K36" s="622" t="e">
+      <c r="F36" s="836"/>
+      <c r="G36" s="836"/>
+      <c r="H36" s="837"/>
+      <c r="I36" s="840" t="s">
+        <v>461</v>
+      </c>
+      <c r="J36" s="841"/>
+      <c r="K36" s="621" t="e">
         <f>IF($I$66="Método A",FIXED(($W$36),0),FIXED(($W$36),1))</f>
         <v>#DIV/0!</v>
       </c>
       <c r="L36" s="305"/>
-      <c r="M36" s="624"/>
+      <c r="M36" s="623"/>
       <c r="N36" s="313"/>
       <c r="O36" s="572"/>
       <c r="P36" s="572"/>
@@ -24464,7 +24412,7 @@
       <c r="R36" s="507">
         <v>0.15</v>
       </c>
-      <c r="S36" s="670">
+      <c r="S36" s="669">
         <f>+FORMATO!E54</f>
         <v>0</v>
       </c>
@@ -24490,26 +24438,26 @@
       <c r="AA36" s="515"/>
     </row>
     <row r="37" spans="1:31" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="636"/>
-      <c r="B37" s="627"/>
-      <c r="C37" s="627"/>
-      <c r="D37" s="627"/>
-      <c r="E37" s="836" t="s">
+      <c r="A37" s="635"/>
+      <c r="B37" s="626"/>
+      <c r="C37" s="626"/>
+      <c r="D37" s="626"/>
+      <c r="E37" s="835" t="s">
         <v>240</v>
       </c>
-      <c r="F37" s="837"/>
-      <c r="G37" s="837"/>
-      <c r="H37" s="838"/>
-      <c r="I37" s="841" t="s">
-        <v>467</v>
-      </c>
-      <c r="J37" s="842"/>
-      <c r="K37" s="622" t="e">
+      <c r="F37" s="836"/>
+      <c r="G37" s="836"/>
+      <c r="H37" s="837"/>
+      <c r="I37" s="840" t="s">
+        <v>462</v>
+      </c>
+      <c r="J37" s="841"/>
+      <c r="K37" s="621" t="e">
         <f>IF($I$66="Método A",FIXED(($W$37),0),FIXED(($W$37),1))</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="L37" s="639"/>
-      <c r="M37" s="624"/>
+      <c r="L37" s="638"/>
+      <c r="M37" s="623"/>
       <c r="N37" s="313"/>
       <c r="O37" s="572"/>
       <c r="P37" s="572"/>
@@ -24519,7 +24467,7 @@
       <c r="R37" s="389">
         <v>0.106</v>
       </c>
-      <c r="S37" s="670">
+      <c r="S37" s="669">
         <f>+FORMATO!E55</f>
         <v>0</v>
       </c>
@@ -24545,26 +24493,26 @@
       <c r="AA37" s="591"/>
     </row>
     <row r="38" spans="1:31" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="636"/>
-      <c r="B38" s="627"/>
-      <c r="C38" s="627"/>
-      <c r="D38" s="627"/>
-      <c r="E38" s="891" t="s">
+      <c r="A38" s="635"/>
+      <c r="B38" s="626"/>
+      <c r="C38" s="626"/>
+      <c r="D38" s="626"/>
+      <c r="E38" s="890" t="s">
         <v>242</v>
       </c>
-      <c r="F38" s="892"/>
-      <c r="G38" s="892"/>
-      <c r="H38" s="893"/>
-      <c r="I38" s="897" t="s">
-        <v>468</v>
-      </c>
-      <c r="J38" s="898"/>
+      <c r="F38" s="891"/>
+      <c r="G38" s="891"/>
+      <c r="H38" s="892"/>
+      <c r="I38" s="896" t="s">
+        <v>463</v>
+      </c>
+      <c r="J38" s="897"/>
       <c r="K38" s="317" t="e">
         <f>IF($I$66="Método A",FIXED(($W$38),0),FIXED(($W$38),1))</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="L38" s="639"/>
-      <c r="M38" s="624"/>
+      <c r="L38" s="638"/>
+      <c r="M38" s="623"/>
       <c r="N38" s="313"/>
       <c r="O38" s="572"/>
       <c r="P38" s="572"/>
@@ -24574,7 +24522,7 @@
       <c r="R38" s="389">
         <v>7.4999999999999997E-2</v>
       </c>
-      <c r="S38" s="670">
+      <c r="S38" s="669">
         <f>+FORMATO!E56</f>
         <v>0</v>
       </c>
@@ -24602,19 +24550,19 @@
       <c r="AD38" s="589"/>
     </row>
     <row r="39" spans="1:31" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="641"/>
-      <c r="B39" s="642"/>
-      <c r="C39" s="642"/>
+      <c r="A39" s="640"/>
+      <c r="B39" s="641"/>
+      <c r="C39" s="641"/>
       <c r="D39" s="306"/>
       <c r="E39" s="306"/>
       <c r="F39" s="306"/>
       <c r="G39" s="306"/>
       <c r="H39" s="306"/>
       <c r="I39" s="306"/>
-      <c r="J39" s="624"/>
-      <c r="K39" s="624"/>
-      <c r="L39" s="624"/>
-      <c r="M39" s="624"/>
+      <c r="J39" s="623"/>
+      <c r="K39" s="623"/>
+      <c r="L39" s="623"/>
+      <c r="M39" s="623"/>
       <c r="N39" s="313"/>
       <c r="O39" s="572"/>
       <c r="P39" s="572"/>
@@ -24624,7 +24572,7 @@
       <c r="R39" s="389">
         <v>0.01</v>
       </c>
-      <c r="S39" s="670">
+      <c r="S39" s="669">
         <f>+FORMATO!E57</f>
         <v>0</v>
       </c>
@@ -24653,19 +24601,19 @@
       <c r="AD39" s="515"/>
     </row>
     <row r="40" spans="1:31" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="641"/>
-      <c r="B40" s="642"/>
-      <c r="C40" s="642"/>
+      <c r="A40" s="640"/>
+      <c r="B40" s="641"/>
+      <c r="C40" s="641"/>
       <c r="D40" s="306"/>
       <c r="E40" s="306"/>
       <c r="F40" s="306"/>
       <c r="G40" s="306"/>
       <c r="H40" s="306"/>
       <c r="I40" s="306"/>
-      <c r="J40" s="624"/>
-      <c r="K40" s="624"/>
-      <c r="L40" s="624"/>
-      <c r="M40" s="624"/>
+      <c r="J40" s="623"/>
+      <c r="K40" s="623"/>
+      <c r="L40" s="623"/>
+      <c r="M40" s="623"/>
       <c r="N40" s="313"/>
       <c r="O40" s="572"/>
       <c r="P40" s="572"/>
@@ -24675,82 +24623,82 @@
       <c r="AD40" s="515"/>
     </row>
     <row r="41" spans="1:31" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="641"/>
-      <c r="B41" s="642"/>
-      <c r="C41" s="642"/>
+      <c r="A41" s="640"/>
+      <c r="B41" s="641"/>
+      <c r="C41" s="641"/>
       <c r="D41" s="306"/>
       <c r="E41" s="306"/>
       <c r="F41" s="306"/>
       <c r="G41" s="306"/>
       <c r="H41" s="306"/>
       <c r="I41" s="306"/>
-      <c r="J41" s="624"/>
-      <c r="K41" s="624"/>
-      <c r="L41" s="624"/>
-      <c r="M41" s="624"/>
+      <c r="J41" s="623"/>
+      <c r="K41" s="623"/>
+      <c r="L41" s="623"/>
+      <c r="M41" s="623"/>
       <c r="N41" s="313"/>
       <c r="O41" s="572"/>
       <c r="P41" s="572"/>
-      <c r="Q41" s="844" t="s">
-        <v>424</v>
-      </c>
-      <c r="R41" s="845"/>
-      <c r="S41" s="845"/>
-      <c r="T41" s="846"/>
+      <c r="Q41" s="843" t="s">
+        <v>420</v>
+      </c>
+      <c r="R41" s="844"/>
+      <c r="S41" s="844"/>
+      <c r="T41" s="845"/>
       <c r="AA41" s="515"/>
       <c r="AB41" s="515"/>
       <c r="AC41" s="515"/>
       <c r="AD41" s="515"/>
     </row>
     <row r="42" spans="1:31" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="641"/>
-      <c r="B42" s="642"/>
-      <c r="C42" s="642"/>
+      <c r="A42" s="640"/>
+      <c r="B42" s="641"/>
+      <c r="C42" s="641"/>
       <c r="D42" s="306"/>
       <c r="E42" s="306"/>
       <c r="F42" s="306"/>
       <c r="G42" s="306"/>
       <c r="H42" s="306"/>
       <c r="I42" s="306"/>
-      <c r="J42" s="624"/>
-      <c r="K42" s="624"/>
-      <c r="L42" s="624"/>
-      <c r="M42" s="624"/>
+      <c r="J42" s="623"/>
+      <c r="K42" s="623"/>
+      <c r="L42" s="623"/>
+      <c r="M42" s="623"/>
       <c r="N42" s="313"/>
       <c r="O42" s="572"/>
       <c r="P42" s="572"/>
-      <c r="Q42" s="847"/>
-      <c r="R42" s="848"/>
-      <c r="S42" s="848"/>
-      <c r="T42" s="849"/>
-      <c r="U42" s="624"/>
-      <c r="V42" s="624"/>
+      <c r="Q42" s="846"/>
+      <c r="R42" s="847"/>
+      <c r="S42" s="847"/>
+      <c r="T42" s="848"/>
+      <c r="U42" s="623"/>
+      <c r="V42" s="623"/>
       <c r="AA42" s="515"/>
       <c r="AB42" s="515"/>
       <c r="AC42" s="515"/>
       <c r="AD42" s="515"/>
     </row>
     <row r="43" spans="1:31" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="641"/>
-      <c r="B43" s="642"/>
-      <c r="C43" s="642"/>
+      <c r="A43" s="640"/>
+      <c r="B43" s="641"/>
+      <c r="C43" s="641"/>
       <c r="D43" s="306"/>
       <c r="E43" s="306"/>
       <c r="F43" s="306"/>
       <c r="G43" s="306"/>
       <c r="H43" s="306"/>
       <c r="I43" s="306"/>
-      <c r="J43" s="624"/>
-      <c r="K43" s="624"/>
-      <c r="L43" s="624"/>
-      <c r="M43" s="624"/>
+      <c r="J43" s="623"/>
+      <c r="K43" s="623"/>
+      <c r="L43" s="623"/>
+      <c r="M43" s="623"/>
       <c r="N43" s="313"/>
       <c r="O43" s="572"/>
       <c r="P43" s="572"/>
-      <c r="Q43" s="850" t="s">
+      <c r="Q43" s="849" t="s">
         <v>34</v>
       </c>
-      <c r="R43" s="852" t="e">
+      <c r="R43" s="851" t="e">
         <f>$V$31</f>
         <v>#DIV/0!</v>
       </c>
@@ -24761,32 +24709,32 @@
         <f>SUM($U$25:$U$29)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="U43" s="624"/>
-      <c r="V43" s="624"/>
+      <c r="U43" s="623"/>
+      <c r="V43" s="623"/>
       <c r="AA43" s="515"/>
       <c r="AB43" s="515"/>
       <c r="AC43" s="579"/>
       <c r="AD43" s="515"/>
     </row>
     <row r="44" spans="1:31" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="641"/>
-      <c r="B44" s="642"/>
-      <c r="C44" s="642"/>
+      <c r="A44" s="640"/>
+      <c r="B44" s="641"/>
+      <c r="C44" s="641"/>
       <c r="D44" s="306"/>
       <c r="E44" s="306"/>
       <c r="F44" s="306"/>
       <c r="G44" s="306"/>
       <c r="H44" s="306"/>
       <c r="I44" s="306"/>
-      <c r="J44" s="624"/>
-      <c r="K44" s="624"/>
-      <c r="L44" s="624"/>
-      <c r="M44" s="624"/>
+      <c r="J44" s="623"/>
+      <c r="K44" s="623"/>
+      <c r="L44" s="623"/>
+      <c r="M44" s="623"/>
       <c r="N44" s="313"/>
       <c r="O44" s="572"/>
       <c r="P44" s="572"/>
-      <c r="Q44" s="851"/>
-      <c r="R44" s="853"/>
+      <c r="Q44" s="850"/>
+      <c r="R44" s="852"/>
       <c r="S44" s="311" t="s">
         <v>36</v>
       </c>
@@ -24794,8 +24742,8 @@
         <f>SUM($U$30:$U$31)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="U44" s="630"/>
-      <c r="V44" s="630"/>
+      <c r="U44" s="629"/>
+      <c r="V44" s="629"/>
       <c r="Y44" s="279"/>
       <c r="Z44" s="279"/>
       <c r="AA44" s="515"/>
@@ -24804,26 +24752,26 @@
       <c r="AD44" s="592"/>
     </row>
     <row r="45" spans="1:31" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="641"/>
-      <c r="B45" s="642"/>
-      <c r="C45" s="642"/>
+      <c r="A45" s="640"/>
+      <c r="B45" s="641"/>
+      <c r="C45" s="641"/>
       <c r="D45" s="306"/>
       <c r="E45" s="306"/>
       <c r="F45" s="306"/>
       <c r="G45" s="306"/>
       <c r="H45" s="306"/>
       <c r="I45" s="306"/>
-      <c r="J45" s="624"/>
-      <c r="K45" s="624"/>
-      <c r="L45" s="624"/>
-      <c r="M45" s="624"/>
+      <c r="J45" s="623"/>
+      <c r="K45" s="623"/>
+      <c r="L45" s="623"/>
+      <c r="M45" s="623"/>
       <c r="N45" s="313"/>
       <c r="O45" s="572"/>
       <c r="P45" s="572"/>
-      <c r="Q45" s="854" t="s">
+      <c r="Q45" s="853" t="s">
         <v>37</v>
       </c>
-      <c r="R45" s="856" t="e">
+      <c r="R45" s="855" t="e">
         <f>100-(R43+R48)</f>
         <v>#DIV/0!</v>
       </c>
@@ -24834,8 +24782,8 @@
         <f>SUM($U$32:$U$32)</f>
         <v>0</v>
       </c>
-      <c r="U45" s="630"/>
-      <c r="V45" s="630"/>
+      <c r="U45" s="629"/>
+      <c r="V45" s="629"/>
       <c r="W45" s="515"/>
       <c r="Y45" s="515"/>
       <c r="Z45" s="279"/>
@@ -24845,24 +24793,24 @@
       <c r="AD45" s="515"/>
     </row>
     <row r="46" spans="1:31" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="641"/>
-      <c r="B46" s="642"/>
-      <c r="C46" s="642"/>
+      <c r="A46" s="640"/>
+      <c r="B46" s="641"/>
+      <c r="C46" s="641"/>
       <c r="D46" s="306"/>
       <c r="E46" s="306"/>
       <c r="F46" s="306"/>
       <c r="G46" s="306"/>
       <c r="H46" s="306"/>
       <c r="I46" s="306"/>
-      <c r="J46" s="624"/>
-      <c r="K46" s="624"/>
-      <c r="L46" s="624"/>
-      <c r="M46" s="624"/>
+      <c r="J46" s="623"/>
+      <c r="K46" s="623"/>
+      <c r="L46" s="623"/>
+      <c r="M46" s="623"/>
       <c r="N46" s="313"/>
       <c r="O46" s="572"/>
       <c r="P46" s="572"/>
-      <c r="Q46" s="855"/>
-      <c r="R46" s="857"/>
+      <c r="Q46" s="854"/>
+      <c r="R46" s="856"/>
       <c r="S46" s="311" t="s">
         <v>38</v>
       </c>
@@ -24870,8 +24818,8 @@
         <f>SUM($U$33:$U$35)</f>
         <v>0</v>
       </c>
-      <c r="U46" s="623"/>
-      <c r="V46" s="623"/>
+      <c r="U46" s="622"/>
+      <c r="V46" s="622"/>
       <c r="Y46" s="279"/>
       <c r="Z46" s="279"/>
       <c r="AA46" s="515"/>
@@ -24880,24 +24828,24 @@
       <c r="AD46" s="515"/>
     </row>
     <row r="47" spans="1:31" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="641"/>
-      <c r="B47" s="642"/>
-      <c r="C47" s="642"/>
+      <c r="A47" s="640"/>
+      <c r="B47" s="641"/>
+      <c r="C47" s="641"/>
       <c r="D47" s="306"/>
       <c r="E47" s="306"/>
       <c r="F47" s="306"/>
       <c r="G47" s="306"/>
       <c r="H47" s="306"/>
       <c r="I47" s="306"/>
-      <c r="J47" s="624"/>
-      <c r="K47" s="624"/>
-      <c r="L47" s="624"/>
-      <c r="M47" s="624"/>
+      <c r="J47" s="623"/>
+      <c r="K47" s="623"/>
+      <c r="L47" s="623"/>
+      <c r="M47" s="623"/>
       <c r="N47" s="313"/>
       <c r="O47" s="572"/>
       <c r="P47" s="572"/>
-      <c r="Q47" s="851"/>
-      <c r="R47" s="853"/>
+      <c r="Q47" s="850"/>
+      <c r="R47" s="852"/>
       <c r="S47" s="311" t="s">
         <v>36</v>
       </c>
@@ -24905,26 +24853,26 @@
         <f>SUM($U$36:$U$38)</f>
         <v>0</v>
       </c>
-      <c r="U47" s="630"/>
-      <c r="V47" s="630"/>
+      <c r="U47" s="629"/>
+      <c r="V47" s="629"/>
       <c r="AB47" s="515"/>
       <c r="AC47" s="593"/>
       <c r="AD47" s="515"/>
     </row>
     <row r="48" spans="1:31" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="641"/>
-      <c r="B48" s="642"/>
-      <c r="C48" s="642"/>
+      <c r="A48" s="640"/>
+      <c r="B48" s="641"/>
+      <c r="C48" s="641"/>
       <c r="D48" s="306"/>
       <c r="E48" s="306"/>
       <c r="F48" s="306"/>
       <c r="G48" s="306"/>
       <c r="H48" s="306"/>
       <c r="I48" s="306"/>
-      <c r="J48" s="624"/>
-      <c r="K48" s="624"/>
-      <c r="L48" s="624"/>
-      <c r="M48" s="624"/>
+      <c r="J48" s="623"/>
+      <c r="K48" s="623"/>
+      <c r="L48" s="623"/>
+      <c r="M48" s="623"/>
       <c r="N48" s="313"/>
       <c r="O48" s="572"/>
       <c r="P48" s="572"/>
@@ -24940,27 +24888,27 @@
         <f>$U$39</f>
         <v>0</v>
       </c>
-      <c r="U48" s="623"/>
-      <c r="V48" s="623"/>
+      <c r="U48" s="622"/>
+      <c r="V48" s="622"/>
       <c r="W48" s="279"/>
       <c r="AB48" s="515"/>
       <c r="AC48" s="515"/>
       <c r="AD48" s="515"/>
     </row>
     <row r="49" spans="1:30" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="641"/>
-      <c r="B49" s="642"/>
-      <c r="C49" s="642"/>
+      <c r="A49" s="640"/>
+      <c r="B49" s="641"/>
+      <c r="C49" s="641"/>
       <c r="D49" s="306"/>
       <c r="E49" s="306"/>
       <c r="F49" s="306"/>
       <c r="G49" s="306"/>
       <c r="H49" s="306"/>
       <c r="I49" s="306"/>
-      <c r="J49" s="624"/>
-      <c r="K49" s="624"/>
-      <c r="L49" s="624"/>
-      <c r="M49" s="624"/>
+      <c r="J49" s="623"/>
+      <c r="K49" s="623"/>
+      <c r="L49" s="623"/>
+      <c r="M49" s="623"/>
       <c r="N49" s="313"/>
       <c r="O49" s="572"/>
       <c r="P49" s="572"/>
@@ -24968,27 +24916,27 @@
       <c r="R49" s="319"/>
       <c r="S49" s="319"/>
       <c r="T49" s="319"/>
-      <c r="U49" s="623"/>
-      <c r="V49" s="623"/>
+      <c r="U49" s="622"/>
+      <c r="V49" s="622"/>
       <c r="W49" s="279"/>
       <c r="AB49" s="515"/>
       <c r="AC49" s="515"/>
       <c r="AD49" s="515"/>
     </row>
     <row r="50" spans="1:30" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="641"/>
-      <c r="B50" s="642"/>
-      <c r="C50" s="642"/>
+      <c r="A50" s="640"/>
+      <c r="B50" s="641"/>
+      <c r="C50" s="641"/>
       <c r="D50" s="306"/>
       <c r="E50" s="306"/>
       <c r="F50" s="306"/>
       <c r="G50" s="306"/>
       <c r="H50" s="306"/>
       <c r="I50" s="306"/>
-      <c r="J50" s="624"/>
-      <c r="K50" s="624"/>
-      <c r="L50" s="624"/>
-      <c r="M50" s="624"/>
+      <c r="J50" s="623"/>
+      <c r="K50" s="623"/>
+      <c r="L50" s="623"/>
+      <c r="M50" s="623"/>
       <c r="N50" s="313"/>
       <c r="O50" s="572"/>
       <c r="P50" s="572"/>
@@ -25004,19 +24952,19 @@
       <c r="AD50" s="515"/>
     </row>
     <row r="51" spans="1:30" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="641"/>
-      <c r="B51" s="642"/>
-      <c r="C51" s="642"/>
+      <c r="A51" s="640"/>
+      <c r="B51" s="641"/>
+      <c r="C51" s="641"/>
       <c r="D51" s="306"/>
       <c r="E51" s="306"/>
       <c r="F51" s="306"/>
       <c r="G51" s="306"/>
       <c r="H51" s="306"/>
       <c r="I51" s="306"/>
-      <c r="J51" s="624"/>
-      <c r="K51" s="624"/>
-      <c r="L51" s="624"/>
-      <c r="M51" s="624"/>
+      <c r="J51" s="623"/>
+      <c r="K51" s="623"/>
+      <c r="L51" s="623"/>
+      <c r="M51" s="623"/>
       <c r="N51" s="313"/>
       <c r="O51" s="572"/>
       <c r="P51" s="572"/>
@@ -25036,19 +24984,19 @@
       <c r="AD51" s="515"/>
     </row>
     <row r="52" spans="1:30" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="641"/>
-      <c r="B52" s="642"/>
-      <c r="C52" s="642"/>
+      <c r="A52" s="640"/>
+      <c r="B52" s="641"/>
+      <c r="C52" s="641"/>
       <c r="D52" s="306"/>
       <c r="E52" s="306"/>
       <c r="F52" s="306"/>
       <c r="G52" s="306"/>
       <c r="H52" s="306"/>
       <c r="I52" s="306"/>
-      <c r="J52" s="624"/>
-      <c r="K52" s="624"/>
-      <c r="L52" s="624"/>
-      <c r="M52" s="624"/>
+      <c r="J52" s="623"/>
+      <c r="K52" s="623"/>
+      <c r="L52" s="623"/>
+      <c r="M52" s="623"/>
       <c r="N52" s="313"/>
       <c r="O52" s="572"/>
       <c r="P52" s="572"/>
@@ -25056,8 +25004,8 @@
       <c r="R52" s="319"/>
       <c r="S52" s="319"/>
       <c r="T52" s="319"/>
-      <c r="U52" s="629"/>
-      <c r="V52" s="629"/>
+      <c r="U52" s="628"/>
+      <c r="V52" s="628"/>
       <c r="W52" s="279"/>
       <c r="X52" s="391"/>
       <c r="Y52" s="518"/>
@@ -25068,19 +25016,19 @@
       <c r="AD52" s="515"/>
     </row>
     <row r="53" spans="1:30" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="641"/>
-      <c r="B53" s="642"/>
-      <c r="C53" s="642"/>
+      <c r="A53" s="640"/>
+      <c r="B53" s="641"/>
+      <c r="C53" s="641"/>
       <c r="D53" s="306"/>
       <c r="E53" s="306"/>
       <c r="F53" s="306"/>
       <c r="G53" s="306"/>
       <c r="H53" s="306"/>
       <c r="I53" s="306"/>
-      <c r="J53" s="624"/>
-      <c r="K53" s="624"/>
-      <c r="L53" s="624"/>
-      <c r="M53" s="624"/>
+      <c r="J53" s="623"/>
+      <c r="K53" s="623"/>
+      <c r="L53" s="623"/>
+      <c r="M53" s="623"/>
       <c r="N53" s="313"/>
       <c r="O53" s="572"/>
       <c r="P53" s="572"/>
@@ -25088,8 +25036,8 @@
       <c r="R53" s="319"/>
       <c r="S53" s="319"/>
       <c r="T53" s="319"/>
-      <c r="U53" s="629"/>
-      <c r="V53" s="629"/>
+      <c r="U53" s="628"/>
+      <c r="V53" s="628"/>
       <c r="W53" s="279"/>
       <c r="X53" s="391"/>
       <c r="Y53" s="518"/>
@@ -25100,19 +25048,19 @@
       <c r="AD53" s="515"/>
     </row>
     <row r="54" spans="1:30" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="641"/>
-      <c r="B54" s="642"/>
-      <c r="C54" s="642"/>
+      <c r="A54" s="640"/>
+      <c r="B54" s="641"/>
+      <c r="C54" s="641"/>
       <c r="D54" s="306"/>
       <c r="E54" s="306"/>
       <c r="F54" s="306"/>
       <c r="G54" s="306"/>
       <c r="H54" s="306"/>
       <c r="I54" s="306"/>
-      <c r="J54" s="624"/>
-      <c r="K54" s="624"/>
-      <c r="L54" s="624"/>
-      <c r="M54" s="624"/>
+      <c r="J54" s="623"/>
+      <c r="K54" s="623"/>
+      <c r="L54" s="623"/>
+      <c r="M54" s="623"/>
       <c r="N54" s="313"/>
       <c r="O54" s="572"/>
       <c r="P54" s="572"/>
@@ -25120,8 +25068,8 @@
       <c r="R54" s="319"/>
       <c r="S54" s="319"/>
       <c r="T54" s="319"/>
-      <c r="U54" s="629"/>
-      <c r="V54" s="629"/>
+      <c r="U54" s="628"/>
+      <c r="V54" s="628"/>
       <c r="W54" s="279"/>
       <c r="X54" s="391"/>
       <c r="Y54" s="518"/>
@@ -25132,19 +25080,19 @@
       <c r="AD54" s="515"/>
     </row>
     <row r="55" spans="1:30" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="641"/>
-      <c r="B55" s="642"/>
-      <c r="C55" s="642"/>
-      <c r="D55" s="624"/>
-      <c r="E55" s="624"/>
-      <c r="F55" s="624"/>
-      <c r="G55" s="624"/>
-      <c r="H55" s="624"/>
-      <c r="I55" s="624"/>
-      <c r="J55" s="624"/>
-      <c r="K55" s="624"/>
-      <c r="L55" s="624"/>
-      <c r="M55" s="624"/>
+      <c r="A55" s="640"/>
+      <c r="B55" s="641"/>
+      <c r="C55" s="641"/>
+      <c r="D55" s="623"/>
+      <c r="E55" s="623"/>
+      <c r="F55" s="623"/>
+      <c r="G55" s="623"/>
+      <c r="H55" s="623"/>
+      <c r="I55" s="623"/>
+      <c r="J55" s="623"/>
+      <c r="K55" s="623"/>
+      <c r="L55" s="623"/>
+      <c r="M55" s="623"/>
       <c r="N55" s="313"/>
       <c r="O55" s="572"/>
       <c r="P55" s="572"/>
@@ -25152,8 +25100,8 @@
       <c r="R55" s="319"/>
       <c r="S55" s="319"/>
       <c r="T55" s="319"/>
-      <c r="U55" s="629"/>
-      <c r="V55" s="629"/>
+      <c r="U55" s="628"/>
+      <c r="V55" s="628"/>
       <c r="W55" s="279"/>
       <c r="X55" s="391"/>
       <c r="Y55" s="518"/>
@@ -25164,28 +25112,28 @@
       <c r="AD55" s="515"/>
     </row>
     <row r="56" spans="1:30" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="643"/>
-      <c r="B56" s="644"/>
-      <c r="C56" s="644"/>
-      <c r="D56" s="645"/>
-      <c r="E56" s="645"/>
-      <c r="F56" s="645"/>
-      <c r="G56" s="645"/>
-      <c r="H56" s="645"/>
-      <c r="I56" s="645"/>
-      <c r="J56" s="645"/>
-      <c r="K56" s="645"/>
-      <c r="L56" s="645"/>
-      <c r="M56" s="645"/>
-      <c r="N56" s="646"/>
+      <c r="A56" s="642"/>
+      <c r="B56" s="643"/>
+      <c r="C56" s="643"/>
+      <c r="D56" s="644"/>
+      <c r="E56" s="644"/>
+      <c r="F56" s="644"/>
+      <c r="G56" s="644"/>
+      <c r="H56" s="644"/>
+      <c r="I56" s="644"/>
+      <c r="J56" s="644"/>
+      <c r="K56" s="644"/>
+      <c r="L56" s="644"/>
+      <c r="M56" s="644"/>
+      <c r="N56" s="645"/>
       <c r="O56" s="572"/>
       <c r="P56" s="572"/>
       <c r="Q56" s="319"/>
       <c r="R56" s="319"/>
       <c r="S56" s="319"/>
       <c r="T56" s="319"/>
-      <c r="U56" s="629"/>
-      <c r="V56" s="629"/>
+      <c r="U56" s="628"/>
+      <c r="V56" s="628"/>
       <c r="W56" s="279"/>
       <c r="X56" s="391"/>
       <c r="Y56" s="518"/>
@@ -25216,8 +25164,8 @@
       <c r="R57" s="319"/>
       <c r="S57" s="319"/>
       <c r="T57" s="319"/>
-      <c r="U57" s="629"/>
-      <c r="V57" s="629"/>
+      <c r="U57" s="628"/>
+      <c r="V57" s="628"/>
       <c r="W57" s="279"/>
       <c r="X57" s="279"/>
       <c r="Y57" s="518"/>
@@ -25295,7 +25243,7 @@
     </row>
     <row r="60" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="319" t="s">
-        <v>485</v>
+        <v>576</v>
       </c>
       <c r="B60" s="319"/>
       <c r="C60" s="319"/>
@@ -25489,7 +25437,7 @@
     </row>
     <row r="66" spans="1:30" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="546" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="B66" s="425"/>
       <c r="C66" s="425"/>
@@ -25498,12 +25446,12 @@
       <c r="F66" s="306"/>
       <c r="G66" s="306"/>
       <c r="H66" s="306"/>
-      <c r="I66" s="889" t="str">
+      <c r="I66" s="888" t="str">
         <f>+R2</f>
         <v>-</v>
       </c>
-      <c r="J66" s="889"/>
-      <c r="K66" s="889"/>
+      <c r="J66" s="888"/>
+      <c r="K66" s="888"/>
       <c r="L66" s="423"/>
       <c r="M66" s="423"/>
       <c r="N66" s="547"/>
@@ -25526,7 +25474,7 @@
     </row>
     <row r="67" spans="1:30" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="546" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="B67" s="425"/>
       <c r="C67" s="425"/>
@@ -25535,11 +25483,11 @@
       <c r="F67" s="306"/>
       <c r="G67" s="306"/>
       <c r="H67" s="306"/>
-      <c r="I67" s="889" t="s">
-        <v>446</v>
-      </c>
-      <c r="J67" s="889"/>
-      <c r="K67" s="889"/>
+      <c r="I67" s="888" t="s">
+        <v>442</v>
+      </c>
+      <c r="J67" s="888"/>
+      <c r="K67" s="888"/>
       <c r="L67" s="423"/>
       <c r="M67" s="423"/>
       <c r="N67" s="547"/>
@@ -25562,7 +25510,7 @@
     </row>
     <row r="68" spans="1:30" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="546" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="B68" s="425"/>
       <c r="C68" s="425"/>
@@ -25571,11 +25519,11 @@
       <c r="F68" s="548"/>
       <c r="G68" s="548"/>
       <c r="H68" s="548"/>
-      <c r="I68" s="889" t="s">
-        <v>446</v>
-      </c>
-      <c r="J68" s="889"/>
-      <c r="K68" s="889"/>
+      <c r="I68" s="888" t="s">
+        <v>442</v>
+      </c>
+      <c r="J68" s="888"/>
+      <c r="K68" s="888"/>
       <c r="L68" s="423"/>
       <c r="M68" s="423"/>
       <c r="N68" s="547"/>
@@ -25598,7 +25546,7 @@
     </row>
     <row r="69" spans="1:30" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="546" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="B69" s="425"/>
       <c r="C69" s="425"/>
@@ -25607,11 +25555,11 @@
       <c r="F69" s="548"/>
       <c r="G69" s="548"/>
       <c r="H69" s="548"/>
-      <c r="I69" s="843" t="s">
+      <c r="I69" s="842" t="s">
         <v>252</v>
       </c>
-      <c r="J69" s="843"/>
-      <c r="K69" s="843"/>
+      <c r="J69" s="842"/>
+      <c r="K69" s="842"/>
       <c r="L69" s="423"/>
       <c r="M69" s="423"/>
       <c r="N69" s="547"/>
@@ -25634,7 +25582,7 @@
     </row>
     <row r="70" spans="1:30" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="546" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="B70" s="425"/>
       <c r="C70" s="425"/>
@@ -25643,11 +25591,11 @@
       <c r="F70" s="548"/>
       <c r="G70" s="548"/>
       <c r="H70" s="548"/>
-      <c r="I70" s="889" t="s">
-        <v>446</v>
-      </c>
-      <c r="J70" s="889"/>
-      <c r="K70" s="889"/>
+      <c r="I70" s="888" t="s">
+        <v>442</v>
+      </c>
+      <c r="J70" s="888"/>
+      <c r="K70" s="888"/>
       <c r="L70" s="423"/>
       <c r="M70" s="423"/>
       <c r="N70" s="547"/>
@@ -25670,7 +25618,7 @@
     </row>
     <row r="71" spans="1:30" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="546" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="B71" s="425"/>
       <c r="C71" s="425"/>
@@ -25679,11 +25627,11 @@
       <c r="F71" s="548"/>
       <c r="G71" s="548"/>
       <c r="H71" s="548"/>
-      <c r="I71" s="843" t="s">
+      <c r="I71" s="842" t="s">
         <v>252</v>
       </c>
-      <c r="J71" s="843"/>
-      <c r="K71" s="843"/>
+      <c r="J71" s="842"/>
+      <c r="K71" s="842"/>
       <c r="L71" s="423"/>
       <c r="M71" s="423"/>
       <c r="N71" s="547"/>
@@ -25706,7 +25654,7 @@
     </row>
     <row r="72" spans="1:30" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="546" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="B72" s="425"/>
       <c r="C72" s="425"/>
@@ -25715,11 +25663,11 @@
       <c r="F72" s="306"/>
       <c r="G72" s="306"/>
       <c r="H72" s="306"/>
-      <c r="I72" s="894" t="s">
-        <v>446</v>
-      </c>
-      <c r="J72" s="895"/>
-      <c r="K72" s="896"/>
+      <c r="I72" s="893" t="s">
+        <v>442</v>
+      </c>
+      <c r="J72" s="894"/>
+      <c r="K72" s="895"/>
       <c r="L72" s="319"/>
       <c r="M72" s="319"/>
       <c r="N72" s="549"/>
@@ -25807,7 +25755,7 @@
     </row>
     <row r="75" spans="1:30" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="546" t="s">
-        <v>475</v>
+        <v>470</v>
       </c>
       <c r="B75" s="427"/>
       <c r="C75" s="427"/>
@@ -25815,14 +25763,14 @@
       <c r="E75" s="306"/>
       <c r="F75" s="306"/>
       <c r="H75" s="306"/>
-      <c r="I75" s="843"/>
-      <c r="J75" s="843"/>
-      <c r="K75" s="843"/>
-      <c r="L75" s="828">
+      <c r="I75" s="842"/>
+      <c r="J75" s="842"/>
+      <c r="K75" s="842"/>
+      <c r="L75" s="827">
         <v>0</v>
       </c>
-      <c r="M75" s="829"/>
-      <c r="N75" s="830"/>
+      <c r="M75" s="828"/>
+      <c r="N75" s="829"/>
       <c r="O75" s="572"/>
       <c r="P75" s="572"/>
       <c r="Q75" s="426"/>
@@ -25842,7 +25790,7 @@
     </row>
     <row r="76" spans="1:30" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="546" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="B76" s="427"/>
       <c r="C76" s="427"/>
@@ -25850,11 +25798,11 @@
       <c r="E76" s="306"/>
       <c r="F76" s="306"/>
       <c r="H76" s="306"/>
-      <c r="I76" s="889" t="s">
-        <v>446</v>
-      </c>
-      <c r="J76" s="889"/>
-      <c r="K76" s="889"/>
+      <c r="I76" s="888" t="s">
+        <v>442</v>
+      </c>
+      <c r="J76" s="888"/>
+      <c r="K76" s="888"/>
       <c r="L76" s="306"/>
       <c r="M76" s="306"/>
       <c r="N76" s="554"/>
@@ -25877,7 +25825,7 @@
     </row>
     <row r="77" spans="1:30" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="546" t="s">
-        <v>470</v>
+        <v>465</v>
       </c>
       <c r="B77" s="321"/>
       <c r="C77" s="321"/>
@@ -25885,12 +25833,12 @@
       <c r="E77" s="306"/>
       <c r="F77" s="306"/>
       <c r="H77" s="306"/>
-      <c r="I77" s="890">
+      <c r="I77" s="889">
         <f>+FORMATO!H19</f>
         <v>0</v>
       </c>
-      <c r="J77" s="843"/>
-      <c r="K77" s="843"/>
+      <c r="J77" s="842"/>
+      <c r="K77" s="842"/>
       <c r="L77" s="306"/>
       <c r="M77" s="306"/>
       <c r="N77" s="554"/>
@@ -25913,7 +25861,7 @@
     </row>
     <row r="78" spans="1:30" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="546" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
       <c r="B78" s="427"/>
       <c r="C78" s="427"/>
@@ -25921,12 +25869,12 @@
       <c r="E78" s="306"/>
       <c r="F78" s="306"/>
       <c r="H78" s="306"/>
-      <c r="I78" s="889">
+      <c r="I78" s="888">
         <f>+FORMATO!H20</f>
         <v>0</v>
       </c>
-      <c r="J78" s="889"/>
-      <c r="K78" s="889"/>
+      <c r="J78" s="888"/>
+      <c r="K78" s="888"/>
       <c r="L78" s="306"/>
       <c r="M78" s="306"/>
       <c r="N78" s="554"/>
@@ -26014,22 +25962,22 @@
       <c r="AD80" s="515"/>
     </row>
     <row r="81" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A81" s="429" t="s">
-        <v>387</v>
-      </c>
-      <c r="B81" s="429"/>
-      <c r="C81" s="429"/>
-      <c r="D81" s="155"/>
-      <c r="E81" s="155"/>
-      <c r="F81" s="155"/>
-      <c r="G81" s="428"/>
-      <c r="H81" s="428"/>
-      <c r="I81" s="428"/>
-      <c r="J81" s="428"/>
-      <c r="K81" s="428"/>
-      <c r="L81" s="428"/>
-      <c r="M81" s="428"/>
-      <c r="N81" s="428"/>
+      <c r="A81" s="1026" t="s">
+        <v>571</v>
+      </c>
+      <c r="B81" s="1026"/>
+      <c r="C81" s="1026"/>
+      <c r="D81" s="1026"/>
+      <c r="E81" s="1026"/>
+      <c r="F81" s="1026"/>
+      <c r="G81" s="1026"/>
+      <c r="H81" s="1026"/>
+      <c r="I81" s="1026"/>
+      <c r="J81" s="1026"/>
+      <c r="K81" s="1026"/>
+      <c r="L81" s="1026"/>
+      <c r="M81" s="1026"/>
+      <c r="N81" s="1026"/>
       <c r="O81" s="428"/>
       <c r="P81" s="428"/>
       <c r="Q81" s="426"/>
@@ -26047,15 +25995,23 @@
       <c r="AC81" s="515"/>
       <c r="AD81" s="515"/>
     </row>
-    <row r="82" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A82" s="429" t="s">
-        <v>388</v>
-      </c>
-      <c r="B82" s="429"/>
-      <c r="C82" s="429"/>
-      <c r="D82" s="429"/>
-      <c r="E82" s="429"/>
-      <c r="F82" s="429"/>
+    <row r="82" spans="1:30" ht="35.4" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A82" s="1025" t="s">
+        <v>572</v>
+      </c>
+      <c r="B82" s="1025"/>
+      <c r="C82" s="1025"/>
+      <c r="D82" s="1025"/>
+      <c r="E82" s="1025"/>
+      <c r="F82" s="1025"/>
+      <c r="G82" s="1025"/>
+      <c r="H82" s="1025"/>
+      <c r="I82" s="1025"/>
+      <c r="J82" s="1025"/>
+      <c r="K82" s="1025"/>
+      <c r="L82" s="1025"/>
+      <c r="M82" s="1025"/>
+      <c r="N82" s="1025"/>
       <c r="Q82" s="426"/>
       <c r="R82" s="521"/>
       <c r="S82" s="521"/>
@@ -26071,23 +26027,23 @@
       <c r="AC82" s="515"/>
       <c r="AD82" s="515"/>
     </row>
-    <row r="83" spans="1:30" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A83" s="888" t="s">
-        <v>401</v>
-      </c>
-      <c r="B83" s="888"/>
-      <c r="C83" s="888"/>
-      <c r="D83" s="888"/>
-      <c r="E83" s="888"/>
-      <c r="F83" s="888"/>
-      <c r="G83" s="888"/>
-      <c r="H83" s="888"/>
-      <c r="I83" s="888"/>
-      <c r="J83" s="888"/>
-      <c r="K83" s="888"/>
-      <c r="L83" s="888"/>
-      <c r="M83" s="888"/>
-      <c r="N83" s="888"/>
+    <row r="83" spans="1:30" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A83" s="1025" t="s">
+        <v>573</v>
+      </c>
+      <c r="B83" s="1025"/>
+      <c r="C83" s="1025"/>
+      <c r="D83" s="1025"/>
+      <c r="E83" s="1025"/>
+      <c r="F83" s="1025"/>
+      <c r="G83" s="1025"/>
+      <c r="H83" s="1025"/>
+      <c r="I83" s="1025"/>
+      <c r="J83" s="1025"/>
+      <c r="K83" s="1025"/>
+      <c r="L83" s="1025"/>
+      <c r="M83" s="1025"/>
+      <c r="N83" s="1025"/>
       <c r="O83" s="430"/>
       <c r="P83" s="430"/>
       <c r="AA83" s="515"/>
@@ -26095,43 +26051,51 @@
       <c r="AC83" s="515"/>
       <c r="AD83" s="515"/>
     </row>
-    <row r="84" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A84" s="429" t="s">
-        <v>389</v>
-      </c>
-      <c r="B84" s="429"/>
-      <c r="C84" s="429"/>
-      <c r="D84" s="429"/>
-      <c r="E84" s="429"/>
-      <c r="F84" s="429"/>
+    <row r="84" spans="1:30" ht="26.4" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A84" s="1025" t="s">
+        <v>574</v>
+      </c>
+      <c r="B84" s="1025"/>
+      <c r="C84" s="1025"/>
+      <c r="D84" s="1025"/>
+      <c r="E84" s="1025"/>
+      <c r="F84" s="1025"/>
+      <c r="G84" s="1025"/>
+      <c r="H84" s="1025"/>
+      <c r="I84" s="1025"/>
+      <c r="J84" s="1025"/>
+      <c r="K84" s="1025"/>
+      <c r="L84" s="1025"/>
+      <c r="M84" s="1025"/>
+      <c r="N84" s="1025"/>
       <c r="AA84" s="515"/>
       <c r="AB84" s="515"/>
       <c r="AC84" s="515"/>
       <c r="AD84" s="515"/>
     </row>
-    <row r="85" spans="1:30" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A85" s="888" t="s">
-        <v>451</v>
-      </c>
-      <c r="B85" s="888"/>
-      <c r="C85" s="888"/>
-      <c r="D85" s="888"/>
-      <c r="E85" s="888"/>
-      <c r="F85" s="888"/>
-      <c r="G85" s="888"/>
-      <c r="H85" s="888"/>
-      <c r="I85" s="888"/>
-      <c r="J85" s="888"/>
-      <c r="K85" s="888"/>
-      <c r="L85" s="888"/>
-      <c r="M85" s="888"/>
-      <c r="N85" s="888"/>
+    <row r="85" spans="1:30" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A85" s="887" t="s">
+        <v>575</v>
+      </c>
+      <c r="B85" s="887"/>
+      <c r="C85" s="887"/>
+      <c r="D85" s="887"/>
+      <c r="E85" s="887"/>
+      <c r="F85" s="887"/>
+      <c r="G85" s="887"/>
+      <c r="H85" s="887"/>
+      <c r="I85" s="887"/>
+      <c r="J85" s="887"/>
+      <c r="K85" s="887"/>
+      <c r="L85" s="887"/>
+      <c r="M85" s="887"/>
+      <c r="N85" s="887"/>
       <c r="AA85" s="515"/>
       <c r="AB85" s="515"/>
       <c r="AC85" s="515"/>
       <c r="AD85" s="515"/>
     </row>
-    <row r="86" spans="1:30" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:30" ht="5.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="429"/>
       <c r="B86" s="429"/>
       <c r="C86" s="429"/>
@@ -26145,18 +26109,27 @@
     </row>
     <row r="87" spans="1:30" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="523" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="B87" s="523"/>
       <c r="C87" s="523"/>
       <c r="D87" s="429"/>
-      <c r="E87" s="619"/>
+      <c r="E87" s="1027"/>
+      <c r="F87" s="1028"/>
+      <c r="G87" s="1028"/>
+      <c r="H87" s="1028"/>
+      <c r="I87" s="1028"/>
+      <c r="J87" s="1028"/>
+      <c r="K87" s="1028"/>
+      <c r="L87" s="1028"/>
+      <c r="M87" s="1028"/>
+      <c r="N87" s="1028"/>
       <c r="AA87" s="515"/>
       <c r="AB87" s="515"/>
       <c r="AC87" s="515"/>
       <c r="AD87" s="515"/>
     </row>
-    <row r="88" spans="1:30" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:30" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="429"/>
       <c r="H88" s="305"/>
       <c r="I88" s="305"/>
@@ -26172,7 +26145,7 @@
       <c r="AC88" s="515"/>
       <c r="AD88" s="515"/>
     </row>
-    <row r="89" spans="1:30" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:30" ht="28.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="155"/>
       <c r="B89" s="155"/>
       <c r="C89" s="155"/>
@@ -26266,7 +26239,7 @@
     </row>
     <row r="94" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A94" s="319" t="s">
-        <v>485</v>
+        <v>576</v>
       </c>
       <c r="B94" s="319"/>
       <c r="C94" s="319"/>
@@ -26281,16 +26254,17 @@
       <c r="L94" s="305"/>
       <c r="M94" s="305"/>
       <c r="N94" s="524" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
     </row>
   </sheetData>
+  <sheetProtection algorithmName="SHA-512" hashValue="/VGRqQwqpkrRTbVhtH1fc7EpWnllZxXz+nKi9og9PvVMm2n3OZAMMBri1H59qiH66uQBtMOS5yzZDOE2WlhmjA==" saltValue="103vsF1FSBvBwIZa5p921Q==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <protectedRanges>
     <protectedRange sqref="F11:F13 F16" name="Rango3_3_1_1_1_1_1_1_1_1"/>
     <protectedRange sqref="F10" name="Rango3_3_1_1_1_1_1_2_1"/>
   </protectedRanges>
   <dataConsolidate/>
-  <mergeCells count="64">
+  <mergeCells count="67">
     <mergeCell ref="E37:H37"/>
     <mergeCell ref="E38:H38"/>
     <mergeCell ref="I75:K75"/>
@@ -26306,6 +26280,9 @@
     <mergeCell ref="I77:K77"/>
     <mergeCell ref="I78:K78"/>
     <mergeCell ref="A83:N83"/>
+    <mergeCell ref="A81:N81"/>
+    <mergeCell ref="A82:N82"/>
+    <mergeCell ref="A84:N84"/>
     <mergeCell ref="Q5:V5"/>
     <mergeCell ref="A7:N7"/>
     <mergeCell ref="Q23:R23"/>
@@ -26426,72 +26403,72 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="905"/>
-      <c r="B1" s="906"/>
-      <c r="C1" s="911" t="s">
+      <c r="A1" s="904"/>
+      <c r="B1" s="905"/>
+      <c r="C1" s="910" t="s">
         <v>321</v>
       </c>
-      <c r="D1" s="912"/>
-      <c r="E1" s="912"/>
-      <c r="F1" s="912"/>
-      <c r="G1" s="912"/>
-      <c r="H1" s="912"/>
-      <c r="I1" s="913"/>
+      <c r="D1" s="911"/>
+      <c r="E1" s="911"/>
+      <c r="F1" s="911"/>
+      <c r="G1" s="911"/>
+      <c r="H1" s="911"/>
+      <c r="I1" s="912"/>
       <c r="J1" s="343" t="s">
         <v>320</v>
       </c>
-      <c r="K1" s="773" t="s">
+      <c r="K1" s="772" t="s">
         <v>319</v>
       </c>
     </row>
     <row r="2" spans="1:11" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="907"/>
-      <c r="B2" s="908"/>
-      <c r="C2" s="914"/>
-      <c r="D2" s="915"/>
-      <c r="E2" s="915"/>
-      <c r="F2" s="915"/>
-      <c r="G2" s="915"/>
-      <c r="H2" s="915"/>
-      <c r="I2" s="916"/>
+      <c r="A2" s="906"/>
+      <c r="B2" s="907"/>
+      <c r="C2" s="913"/>
+      <c r="D2" s="914"/>
+      <c r="E2" s="914"/>
+      <c r="F2" s="914"/>
+      <c r="G2" s="914"/>
+      <c r="H2" s="914"/>
+      <c r="I2" s="915"/>
       <c r="J2" s="343" t="s">
         <v>318</v>
       </c>
-      <c r="K2" s="774">
+      <c r="K2" s="773">
         <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:11" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="907"/>
-      <c r="B3" s="908"/>
-      <c r="C3" s="914"/>
-      <c r="D3" s="915"/>
-      <c r="E3" s="915"/>
-      <c r="F3" s="915"/>
-      <c r="G3" s="915"/>
-      <c r="H3" s="915"/>
-      <c r="I3" s="916"/>
+      <c r="A3" s="906"/>
+      <c r="B3" s="907"/>
+      <c r="C3" s="913"/>
+      <c r="D3" s="914"/>
+      <c r="E3" s="914"/>
+      <c r="F3" s="914"/>
+      <c r="G3" s="914"/>
+      <c r="H3" s="914"/>
+      <c r="I3" s="915"/>
       <c r="J3" s="343" t="s">
         <v>317</v>
       </c>
-      <c r="K3" s="775">
+      <c r="K3" s="774">
         <v>46146</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="909"/>
-      <c r="B4" s="910"/>
-      <c r="C4" s="917"/>
-      <c r="D4" s="918"/>
-      <c r="E4" s="918"/>
-      <c r="F4" s="918"/>
-      <c r="G4" s="918"/>
-      <c r="H4" s="918"/>
-      <c r="I4" s="919"/>
+      <c r="A4" s="908"/>
+      <c r="B4" s="909"/>
+      <c r="C4" s="916"/>
+      <c r="D4" s="917"/>
+      <c r="E4" s="917"/>
+      <c r="F4" s="917"/>
+      <c r="G4" s="917"/>
+      <c r="H4" s="917"/>
+      <c r="I4" s="918"/>
       <c r="J4" s="343" t="s">
         <v>316</v>
       </c>
-      <c r="K4" s="773" t="s">
+      <c r="K4" s="772" t="s">
         <v>315</v>
       </c>
     </row>
@@ -26548,7 +26525,7 @@
     </row>
     <row r="9" spans="1:11" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="347" t="s">
-        <v>575</v>
+        <v>569</v>
       </c>
       <c r="B9" s="340" t="s">
         <v>345</v>
@@ -26565,7 +26542,7 @@
     </row>
     <row r="11" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="143" t="s">
-        <v>576</v>
+        <v>570</v>
       </c>
       <c r="B11" s="403"/>
       <c r="C11" s="403"/>
@@ -26611,7 +26588,7 @@
     </row>
     <row r="15" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="616" t="s">
-        <v>448</v>
+        <v>444</v>
       </c>
       <c r="B15" s="614"/>
       <c r="C15" s="615"/>
@@ -26623,7 +26600,7 @@
     </row>
     <row r="16" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="616" t="s">
-        <v>449</v>
+        <v>445</v>
       </c>
       <c r="B16" s="614"/>
       <c r="C16" s="615"/>
@@ -26635,7 +26612,7 @@
     </row>
     <row r="17" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="616" t="s">
-        <v>450</v>
+        <v>446</v>
       </c>
       <c r="B17" s="614"/>
       <c r="C17" s="615"/>
@@ -26804,19 +26781,19 @@
       <c r="H32" s="403"/>
     </row>
     <row r="34" spans="1:11" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A34" s="902" t="s">
+      <c r="A34" s="901" t="s">
         <v>309</v>
       </c>
-      <c r="B34" s="903"/>
-      <c r="C34" s="903"/>
-      <c r="D34" s="903"/>
-      <c r="E34" s="903"/>
-      <c r="F34" s="903"/>
-      <c r="G34" s="903"/>
-      <c r="H34" s="903"/>
-      <c r="I34" s="903"/>
-      <c r="J34" s="903"/>
-      <c r="K34" s="904"/>
+      <c r="B34" s="902"/>
+      <c r="C34" s="902"/>
+      <c r="D34" s="902"/>
+      <c r="E34" s="902"/>
+      <c r="F34" s="902"/>
+      <c r="G34" s="902"/>
+      <c r="H34" s="902"/>
+      <c r="I34" s="902"/>
+      <c r="J34" s="902"/>
+      <c r="K34" s="903"/>
     </row>
     <row r="35" spans="1:11" ht="38.4" x14ac:dyDescent="0.25">
       <c r="A35" s="348" t="s">
@@ -26826,7 +26803,7 @@
         <v>307</v>
       </c>
       <c r="C35" s="348" t="s">
-        <v>447</v>
+        <v>443</v>
       </c>
       <c r="D35" s="348" t="s">
         <v>306</v>
@@ -26885,7 +26862,7 @@
     </row>
     <row r="38" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="455" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="B38" s="375">
         <f>Balanza!D29</f>
@@ -27215,7 +27192,7 @@
     </row>
     <row r="51" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="452" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="B51" s="375">
         <f>Balanza!D30</f>
@@ -27545,7 +27522,7 @@
     </row>
     <row r="64" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="456" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="B64" s="375">
         <f>Balanza!D31</f>
@@ -27875,7 +27852,7 @@
     </row>
     <row r="77" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="456" t="s">
-        <v>409</v>
+        <v>405</v>
       </c>
       <c r="B77" s="375">
         <f>Balanza!D32</f>
@@ -28205,7 +28182,7 @@
     </row>
     <row r="90" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="456" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="B90" s="375">
         <f>Balanza!D33</f>
@@ -28535,7 +28512,7 @@
     </row>
     <row r="103" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="456" t="s">
-        <v>411</v>
+        <v>407</v>
       </c>
       <c r="B103" s="375">
         <f>Balanza!D34</f>
@@ -28865,7 +28842,7 @@
     </row>
     <row r="116" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" s="456" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="B116" s="375">
         <f>Balanza!D35</f>
@@ -29227,7 +29204,7 @@
     </row>
     <row r="130" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A130" s="456" t="s">
-        <v>413</v>
+        <v>409</v>
       </c>
       <c r="B130" s="375">
         <f>Balanza!D36</f>
@@ -29584,7 +29561,7 @@
     </row>
     <row r="144" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A144" s="456" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="B144" s="375">
         <f>Balanza!D37</f>
@@ -29941,7 +29918,7 @@
     </row>
     <row r="158" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A158" s="456" t="s">
-        <v>415</v>
+        <v>411</v>
       </c>
       <c r="B158" s="375">
         <f>Balanza!D38</f>
@@ -30298,7 +30275,7 @@
     </row>
     <row r="172" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A172" s="456" t="s">
-        <v>416</v>
+        <v>412</v>
       </c>
       <c r="B172" s="375">
         <f>Balanza!D39</f>
@@ -30655,7 +30632,7 @@
     </row>
     <row r="186" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A186" s="456" t="s">
-        <v>417</v>
+        <v>413</v>
       </c>
       <c r="B186" s="375">
         <f>Balanza!D40</f>
@@ -31369,7 +31346,7 @@
     </row>
     <row r="214" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A214" s="456" t="s">
-        <v>418</v>
+        <v>414</v>
       </c>
       <c r="B214" s="375">
         <f>Balanza!D42</f>
@@ -31674,22 +31651,22 @@
       <c r="J224" s="345"/>
     </row>
     <row r="227" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A227" s="776" t="s">
-        <v>569</v>
-      </c>
-      <c r="B227" s="920" t="s">
-        <v>570</v>
-      </c>
-      <c r="C227" s="921"/>
-      <c r="D227" s="777"/>
-      <c r="E227" s="922" t="s">
-        <v>571</v>
-      </c>
-      <c r="F227" s="922"/>
-      <c r="G227" s="923" t="s">
-        <v>572</v>
-      </c>
-      <c r="H227" s="924"/>
+      <c r="A227" s="775" t="s">
+        <v>563</v>
+      </c>
+      <c r="B227" s="919" t="s">
+        <v>564</v>
+      </c>
+      <c r="C227" s="920"/>
+      <c r="D227" s="776"/>
+      <c r="E227" s="921" t="s">
+        <v>565</v>
+      </c>
+      <c r="F227" s="921"/>
+      <c r="G227" s="922" t="s">
+        <v>566</v>
+      </c>
+      <c r="H227" s="923"/>
     </row>
     <row r="228" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A228" s="403"/>
@@ -31702,22 +31679,22 @@
       <c r="H228" s="403"/>
     </row>
     <row r="229" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A229" s="778" t="s">
-        <v>573</v>
-      </c>
-      <c r="B229" s="899">
+      <c r="A229" s="777" t="s">
+        <v>567</v>
+      </c>
+      <c r="B229" s="898">
         <v>44944</v>
       </c>
-      <c r="C229" s="900"/>
+      <c r="C229" s="899"/>
       <c r="D229" s="403"/>
-      <c r="E229" s="901" t="s">
-        <v>574</v>
-      </c>
-      <c r="F229" s="901"/>
-      <c r="G229" s="899">
+      <c r="E229" s="900" t="s">
+        <v>568</v>
+      </c>
+      <c r="F229" s="900"/>
+      <c r="G229" s="898">
         <v>44944</v>
       </c>
-      <c r="H229" s="900"/>
+      <c r="H229" s="899"/>
     </row>
     <row r="230" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A230" s="403"/>
@@ -31783,8 +31760,8 @@
       <c r="G6" s="399"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A7" s="770" t="s">
-        <v>562</v>
+      <c r="A7" s="769" t="s">
+        <v>556</v>
       </c>
       <c r="B7" s="336">
         <v>-3.2899999999999998E-6</v>
@@ -31796,7 +31773,7 @@
       <c r="G7" s="328"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8" s="771" t="s">
+      <c r="A8" s="770" t="s">
         <v>343</v>
       </c>
       <c r="B8" s="329">
@@ -31811,11 +31788,11 @@
       <c r="G8" s="328"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A9" s="771" t="s">
-        <v>563</v>
+      <c r="A9" s="770" t="s">
+        <v>557</v>
       </c>
       <c r="B9" s="337" t="s">
-        <v>564</v>
+        <v>558</v>
       </c>
       <c r="C9" s="329"/>
       <c r="D9" s="328"/>
@@ -31824,14 +31801,14 @@
       <c r="G9" s="328"/>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A10" s="771" t="s">
+      <c r="A10" s="770" t="s">
         <v>257</v>
       </c>
       <c r="B10" s="337">
         <v>0.1</v>
       </c>
       <c r="C10" s="329" t="s">
-        <v>565</v>
+        <v>559</v>
       </c>
       <c r="D10" s="395"/>
       <c r="E10" s="328"/>
@@ -31839,11 +31816,11 @@
       <c r="G10" s="328"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A11" s="771" t="s">
-        <v>566</v>
+      <c r="A11" s="770" t="s">
+        <v>560</v>
       </c>
       <c r="B11" s="329" t="s">
-        <v>567</v>
+        <v>561</v>
       </c>
       <c r="C11" s="328"/>
       <c r="D11" s="395"/>
@@ -31852,11 +31829,11 @@
       <c r="G11" s="328"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A12" s="771" t="s">
-        <v>568</v>
+      <c r="A12" s="770" t="s">
+        <v>562</v>
       </c>
       <c r="B12" s="395"/>
-      <c r="C12" s="772">
+      <c r="C12" s="771">
         <v>46132</v>
       </c>
       <c r="D12" s="395"/>
@@ -31900,8 +31877,8 @@
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A15" s="649"/>
-      <c r="B15" s="650"/>
+      <c r="A15" s="648"/>
+      <c r="B15" s="649"/>
       <c r="C15" s="432"/>
       <c r="D15" s="432"/>
       <c r="E15" s="432"/>
@@ -31910,8 +31887,8 @@
       <c r="H15" s="432"/>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A16" s="649"/>
-      <c r="B16" s="650"/>
+      <c r="A16" s="648"/>
+      <c r="B16" s="649"/>
       <c r="C16" s="432"/>
       <c r="D16" s="432"/>
       <c r="E16" s="432"/>
@@ -32106,17 +32083,17 @@
     </row>
     <row r="27" spans="1:15" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="401"/>
-      <c r="B27" s="928" t="s">
-        <v>402</v>
-      </c>
-      <c r="C27" s="930" t="s">
-        <v>403</v>
-      </c>
-      <c r="D27" s="930" t="s">
-        <v>404</v>
-      </c>
-      <c r="E27" s="932" t="s">
-        <v>405</v>
+      <c r="B27" s="927" t="s">
+        <v>398</v>
+      </c>
+      <c r="C27" s="929" t="s">
+        <v>399</v>
+      </c>
+      <c r="D27" s="929" t="s">
+        <v>400</v>
+      </c>
+      <c r="E27" s="931" t="s">
+        <v>401</v>
       </c>
       <c r="H27" s="405"/>
       <c r="I27" s="401"/>
@@ -32134,10 +32111,10 @@
     </row>
     <row r="28" spans="1:15" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28" s="401"/>
-      <c r="B28" s="929"/>
-      <c r="C28" s="931"/>
-      <c r="D28" s="931"/>
-      <c r="E28" s="933"/>
+      <c r="B28" s="928"/>
+      <c r="C28" s="930"/>
+      <c r="D28" s="930"/>
+      <c r="E28" s="932"/>
       <c r="H28" s="405"/>
       <c r="I28" s="401"/>
       <c r="J28" s="334" t="s">
@@ -32659,12 +32636,12 @@
       <c r="H45" s="327"/>
     </row>
     <row r="46" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A46" s="925" t="s">
+      <c r="A46" s="924" t="s">
         <v>334</v>
       </c>
-      <c r="B46" s="926"/>
-      <c r="C46" s="927"/>
-      <c r="D46" s="648">
+      <c r="B46" s="925"/>
+      <c r="C46" s="926"/>
+      <c r="D46" s="647">
         <v>45792</v>
       </c>
       <c r="E46" s="395"/>
@@ -32736,14 +32713,14 @@
       <c r="A49" s="396" t="s">
         <v>310</v>
       </c>
-      <c r="B49" s="620" t="s">
-        <v>473</v>
+      <c r="B49" s="619" t="s">
+        <v>468</v>
       </c>
       <c r="C49" s="397" t="s">
-        <v>474</v>
-      </c>
-      <c r="D49" s="669" t="s">
-        <v>483</v>
+        <v>469</v>
+      </c>
+      <c r="D49" s="668" t="s">
+        <v>478</v>
       </c>
       <c r="E49" s="397"/>
     </row>
@@ -33082,35 +33059,35 @@
       <c r="K7" s="150"/>
     </row>
     <row r="8" spans="1:19" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="935" t="s">
+      <c r="A8" s="934" t="s">
         <v>21</v>
       </c>
-      <c r="B8" s="935"/>
-      <c r="C8" s="935"/>
-      <c r="D8" s="935"/>
-      <c r="E8" s="935"/>
-      <c r="F8" s="935"/>
-      <c r="G8" s="935"/>
-      <c r="H8" s="935"/>
-      <c r="I8" s="935"/>
-      <c r="J8" s="935"/>
-      <c r="K8" s="935"/>
+      <c r="B8" s="934"/>
+      <c r="C8" s="934"/>
+      <c r="D8" s="934"/>
+      <c r="E8" s="934"/>
+      <c r="F8" s="934"/>
+      <c r="G8" s="934"/>
+      <c r="H8" s="934"/>
+      <c r="I8" s="934"/>
+      <c r="J8" s="934"/>
+      <c r="K8" s="934"/>
     </row>
     <row r="9" spans="1:19" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="936">
+      <c r="A9" s="935">
         <f>+K13</f>
         <v>10</v>
       </c>
-      <c r="B9" s="936"/>
-      <c r="C9" s="936"/>
-      <c r="D9" s="936"/>
-      <c r="E9" s="936"/>
-      <c r="F9" s="936"/>
-      <c r="G9" s="936"/>
-      <c r="H9" s="936"/>
-      <c r="I9" s="936"/>
-      <c r="J9" s="936"/>
-      <c r="K9" s="936"/>
+      <c r="B9" s="935"/>
+      <c r="C9" s="935"/>
+      <c r="D9" s="935"/>
+      <c r="E9" s="935"/>
+      <c r="F9" s="935"/>
+      <c r="G9" s="935"/>
+      <c r="H9" s="935"/>
+      <c r="I9" s="935"/>
+      <c r="J9" s="935"/>
+      <c r="K9" s="935"/>
       <c r="O9" s="151"/>
     </row>
     <row r="10" spans="1:19" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
@@ -33133,15 +33110,15 @@
       <c r="B11" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="C11" s="937">
+      <c r="C11" s="936">
         <f>+A.Granul!F10</f>
         <v>0</v>
       </c>
-      <c r="D11" s="937"/>
-      <c r="E11" s="937"/>
-      <c r="F11" s="937"/>
-      <c r="G11" s="937"/>
-      <c r="H11" s="937"/>
+      <c r="D11" s="936"/>
+      <c r="E11" s="936"/>
+      <c r="F11" s="936"/>
+      <c r="G11" s="936"/>
+      <c r="H11" s="936"/>
       <c r="I11" s="153" t="s">
         <v>31</v>
       </c>
@@ -33162,15 +33139,15 @@
       <c r="B12" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="C12" s="937">
+      <c r="C12" s="936">
         <f>+A.Granul!F11</f>
         <v>0</v>
       </c>
-      <c r="D12" s="937"/>
-      <c r="E12" s="937"/>
-      <c r="F12" s="937"/>
-      <c r="G12" s="937"/>
-      <c r="H12" s="937"/>
+      <c r="D12" s="936"/>
+      <c r="E12" s="936"/>
+      <c r="F12" s="936"/>
+      <c r="G12" s="936"/>
+      <c r="H12" s="936"/>
       <c r="I12" s="15" t="s">
         <v>19</v>
       </c>
@@ -33195,15 +33172,15 @@
       <c r="B13" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="C13" s="937">
+      <c r="C13" s="936">
         <f>+A.Granul!F12</f>
         <v>0</v>
       </c>
-      <c r="D13" s="937"/>
-      <c r="E13" s="937"/>
-      <c r="F13" s="937"/>
-      <c r="G13" s="937"/>
-      <c r="H13" s="937"/>
+      <c r="D13" s="936"/>
+      <c r="E13" s="936"/>
+      <c r="F13" s="936"/>
+      <c r="G13" s="936"/>
+      <c r="H13" s="936"/>
       <c r="I13" s="15" t="s">
         <v>20</v>
       </c>
@@ -33217,8 +33194,8 @@
       <c r="M13" s="156"/>
       <c r="P13" s="159"/>
       <c r="Q13" s="159"/>
-      <c r="R13" s="934"/>
-      <c r="S13" s="934"/>
+      <c r="R13" s="933"/>
+      <c r="S13" s="933"/>
     </row>
     <row r="14" spans="1:19" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="13"/>
@@ -33240,19 +33217,19 @@
       <c r="S14" s="164"/>
     </row>
     <row r="15" spans="1:19" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="939" t="s">
+      <c r="A15" s="938" t="s">
         <v>171</v>
       </c>
-      <c r="B15" s="940"/>
-      <c r="C15" s="940"/>
-      <c r="D15" s="940"/>
-      <c r="E15" s="940"/>
-      <c r="F15" s="940"/>
-      <c r="G15" s="940"/>
-      <c r="H15" s="940"/>
-      <c r="I15" s="940"/>
-      <c r="J15" s="940"/>
-      <c r="K15" s="941"/>
+      <c r="B15" s="939"/>
+      <c r="C15" s="939"/>
+      <c r="D15" s="939"/>
+      <c r="E15" s="939"/>
+      <c r="F15" s="939"/>
+      <c r="G15" s="939"/>
+      <c r="H15" s="939"/>
+      <c r="I15" s="939"/>
+      <c r="J15" s="939"/>
+      <c r="K15" s="940"/>
       <c r="L15" s="156"/>
       <c r="M15" s="156"/>
       <c r="P15" s="159"/>
@@ -33261,19 +33238,19 @@
       <c r="S15" s="164"/>
     </row>
     <row r="16" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="942" t="s">
+      <c r="A16" s="941" t="s">
         <v>191</v>
       </c>
-      <c r="B16" s="943"/>
-      <c r="C16" s="943"/>
-      <c r="D16" s="943"/>
-      <c r="E16" s="943"/>
-      <c r="F16" s="943"/>
-      <c r="G16" s="943"/>
-      <c r="H16" s="943"/>
-      <c r="I16" s="943"/>
-      <c r="J16" s="943"/>
-      <c r="K16" s="944"/>
+      <c r="B16" s="942"/>
+      <c r="C16" s="942"/>
+      <c r="D16" s="942"/>
+      <c r="E16" s="942"/>
+      <c r="F16" s="942"/>
+      <c r="G16" s="942"/>
+      <c r="H16" s="942"/>
+      <c r="I16" s="942"/>
+      <c r="J16" s="942"/>
+      <c r="K16" s="943"/>
       <c r="L16" s="156"/>
       <c r="M16" s="156"/>
       <c r="P16" s="159"/>
@@ -33301,19 +33278,19 @@
       <c r="S17" s="164"/>
     </row>
     <row r="18" spans="1:21" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="945" t="s">
+      <c r="A18" s="944" t="s">
         <v>26</v>
       </c>
-      <c r="B18" s="946"/>
-      <c r="C18" s="946"/>
-      <c r="D18" s="946"/>
-      <c r="E18" s="946"/>
-      <c r="F18" s="946"/>
-      <c r="G18" s="946"/>
-      <c r="H18" s="946"/>
-      <c r="I18" s="946"/>
-      <c r="J18" s="946"/>
-      <c r="K18" s="947"/>
+      <c r="B18" s="945"/>
+      <c r="C18" s="945"/>
+      <c r="D18" s="945"/>
+      <c r="E18" s="945"/>
+      <c r="F18" s="945"/>
+      <c r="G18" s="945"/>
+      <c r="H18" s="945"/>
+      <c r="I18" s="945"/>
+      <c r="J18" s="945"/>
+      <c r="K18" s="946"/>
       <c r="M18" s="156"/>
       <c r="P18" s="159"/>
       <c r="Q18" s="159"/>
@@ -33438,8 +33415,8 @@
     </row>
     <row r="23" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="176"/>
-      <c r="I23" s="948"/>
-      <c r="J23" s="948"/>
+      <c r="I23" s="947"/>
+      <c r="J23" s="947"/>
       <c r="K23" s="177"/>
       <c r="L23" s="156"/>
       <c r="M23" s="178"/>
@@ -33447,41 +33424,41 @@
     </row>
     <row r="24" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="180"/>
-      <c r="D24" s="949" t="s">
+      <c r="D24" s="948" t="s">
         <v>174</v>
       </c>
-      <c r="E24" s="950"/>
-      <c r="F24" s="950"/>
-      <c r="G24" s="951" t="s">
+      <c r="E24" s="949"/>
+      <c r="F24" s="949"/>
+      <c r="G24" s="950" t="s">
         <v>175</v>
       </c>
-      <c r="H24" s="952"/>
-      <c r="I24" s="953"/>
-      <c r="J24" s="953"/>
+      <c r="H24" s="951"/>
+      <c r="I24" s="952"/>
+      <c r="J24" s="952"/>
       <c r="K24" s="181"/>
       <c r="L24" s="156"/>
       <c r="M24" s="182"/>
-      <c r="O24" s="954" t="s">
+      <c r="O24" s="953" t="s">
         <v>174</v>
       </c>
-      <c r="P24" s="955"/>
+      <c r="P24" s="954"/>
       <c r="Q24" s="183" t="s">
         <v>173</v>
       </c>
-      <c r="R24" s="954" t="s">
+      <c r="R24" s="953" t="s">
         <v>175</v>
       </c>
-      <c r="S24" s="956"/>
+      <c r="S24" s="955"/>
       <c r="T24" s="183" t="s">
         <v>173</v>
       </c>
     </row>
     <row r="25" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="180"/>
-      <c r="B25" s="957" t="s">
+      <c r="B25" s="956" t="s">
         <v>176</v>
       </c>
-      <c r="C25" s="958"/>
+      <c r="C25" s="957"/>
       <c r="D25" s="184" t="str">
         <f>IF($Q$24="NO","",O25)</f>
         <v/>
@@ -33502,8 +33479,8 @@
         <f>IF($T$24="NO","",S25)</f>
         <v/>
       </c>
-      <c r="I25" s="953"/>
-      <c r="J25" s="953"/>
+      <c r="I25" s="952"/>
+      <c r="J25" s="952"/>
       <c r="K25" s="181"/>
       <c r="L25" s="156"/>
       <c r="M25" s="182"/>
@@ -33552,8 +33529,8 @@
         <f>IF($T$24="NO","",S26)</f>
         <v/>
       </c>
-      <c r="I26" s="959"/>
-      <c r="J26" s="959"/>
+      <c r="I26" s="958"/>
+      <c r="J26" s="958"/>
       <c r="K26" s="194"/>
       <c r="L26" s="195"/>
       <c r="M26" s="182"/>
@@ -34331,19 +34308,19 @@
       <c r="Q49"/>
     </row>
     <row r="50" spans="1:17" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="938" t="s">
+      <c r="A50" s="937" t="s">
         <v>192</v>
       </c>
-      <c r="B50" s="938"/>
-      <c r="C50" s="938"/>
-      <c r="D50" s="938"/>
-      <c r="E50" s="938"/>
-      <c r="F50" s="938"/>
-      <c r="G50" s="938"/>
-      <c r="H50" s="938"/>
-      <c r="I50" s="938"/>
-      <c r="J50" s="938"/>
-      <c r="K50" s="938"/>
+      <c r="B50" s="937"/>
+      <c r="C50" s="937"/>
+      <c r="D50" s="937"/>
+      <c r="E50" s="937"/>
+      <c r="F50" s="937"/>
+      <c r="G50" s="937"/>
+      <c r="H50" s="937"/>
+      <c r="I50" s="937"/>
+      <c r="J50" s="937"/>
+      <c r="K50" s="937"/>
     </row>
     <row r="51" spans="1:17" ht="15.9" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="52" spans="1:17" ht="15.9" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -34408,15 +34385,15 @@
       <c r="A1" s="94" t="s">
         <v>97</v>
       </c>
-      <c r="B1" s="960" t="s">
+      <c r="B1" s="959" t="s">
         <v>98</v>
       </c>
-      <c r="C1" s="960"/>
-      <c r="D1" s="960"/>
-      <c r="E1" s="960"/>
-      <c r="F1" s="960"/>
-      <c r="G1" s="960"/>
-      <c r="H1" s="960"/>
+      <c r="C1" s="959"/>
+      <c r="D1" s="959"/>
+      <c r="E1" s="959"/>
+      <c r="F1" s="959"/>
+      <c r="G1" s="959"/>
+      <c r="H1" s="959"/>
       <c r="I1" s="94"/>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.25">
@@ -34554,29 +34531,29 @@
     </row>
     <row r="8" spans="1:17" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="94"/>
-      <c r="B8" s="961" t="s">
+      <c r="B8" s="960" t="s">
         <v>110</v>
       </c>
-      <c r="C8" s="961"/>
-      <c r="D8" s="961"/>
+      <c r="C8" s="960"/>
+      <c r="D8" s="960"/>
       <c r="E8" s="103" t="s">
         <v>111</v>
       </c>
       <c r="F8" s="104" t="s">
         <v>112</v>
       </c>
-      <c r="G8" s="962" t="s">
+      <c r="G8" s="961" t="s">
         <v>113</v>
       </c>
-      <c r="H8" s="962"/>
+      <c r="H8" s="961"/>
       <c r="I8" s="94"/>
       <c r="L8" s="247" t="s">
         <v>114</v>
       </c>
-      <c r="M8" s="963" t="s">
+      <c r="M8" s="962" t="s">
         <v>115</v>
       </c>
-      <c r="N8" s="963"/>
+      <c r="N8" s="962"/>
       <c r="O8" s="248" t="s">
         <v>116</v>
       </c>
@@ -34589,13 +34566,13 @@
     </row>
     <row r="9" spans="1:17" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="94"/>
-      <c r="B9" s="964" t="s">
+      <c r="B9" s="963" t="s">
         <v>119</v>
       </c>
-      <c r="C9" s="966" t="s">
+      <c r="C9" s="965" t="s">
         <v>120</v>
       </c>
-      <c r="D9" s="968" t="s">
+      <c r="D9" s="967" t="s">
         <v>121</v>
       </c>
       <c r="E9" s="106" t="s">
@@ -34604,10 +34581,10 @@
       <c r="F9" s="107" t="s">
         <v>123</v>
       </c>
-      <c r="G9" s="969" t="s">
+      <c r="G9" s="968" t="s">
         <v>124</v>
       </c>
-      <c r="H9" s="970"/>
+      <c r="H9" s="969"/>
       <c r="I9" s="94"/>
       <c r="L9" s="249" t="e">
         <f>IF(AND(N_200&lt;50,(100-N_40)&gt;=0.5*(100-N_200),N_200&lt;5,CU&gt;=4,CC&gt;=1,CC&lt;=3),"GW","")</f>
@@ -34636,19 +34613,19 @@
     </row>
     <row r="10" spans="1:17" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="94"/>
-      <c r="B10" s="964"/>
-      <c r="C10" s="966"/>
-      <c r="D10" s="968"/>
+      <c r="B10" s="963"/>
+      <c r="C10" s="965"/>
+      <c r="D10" s="967"/>
       <c r="E10" s="108" t="s">
         <v>125</v>
       </c>
       <c r="F10" s="109" t="s">
         <v>126</v>
       </c>
-      <c r="G10" s="971" t="s">
+      <c r="G10" s="970" t="s">
         <v>127</v>
       </c>
-      <c r="H10" s="972"/>
+      <c r="H10" s="971"/>
       <c r="I10" s="94"/>
       <c r="L10" s="249" t="e">
         <f>IF(AND(N_200&lt;50,(100-N_40)&gt;=0.5*(100-N_200),N_200&lt;5,OR(CU&lt;4,CC&lt;1,CC&gt;3)),"GP","")</f>
@@ -34673,9 +34650,9 @@
     </row>
     <row r="11" spans="1:17" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="94"/>
-      <c r="B11" s="964"/>
-      <c r="C11" s="966"/>
-      <c r="D11" s="968" t="s">
+      <c r="B11" s="963"/>
+      <c r="C11" s="965"/>
+      <c r="D11" s="967" t="s">
         <v>128</v>
       </c>
       <c r="E11" s="108" t="s">
@@ -34687,7 +34664,7 @@
       <c r="G11" s="111" t="s">
         <v>131</v>
       </c>
-      <c r="H11" s="973" t="s">
+      <c r="H11" s="972" t="s">
         <v>132</v>
       </c>
       <c r="I11" s="94"/>
@@ -34708,9 +34685,9 @@
     </row>
     <row r="12" spans="1:17" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="94"/>
-      <c r="B12" s="964"/>
-      <c r="C12" s="967"/>
-      <c r="D12" s="968"/>
+      <c r="B12" s="963"/>
+      <c r="C12" s="966"/>
+      <c r="D12" s="967"/>
       <c r="E12" s="112" t="s">
         <v>133</v>
       </c>
@@ -34720,7 +34697,7 @@
       <c r="G12" s="111" t="s">
         <v>135</v>
       </c>
-      <c r="H12" s="974"/>
+      <c r="H12" s="973"/>
       <c r="I12" s="94"/>
       <c r="L12" s="249" t="e">
         <f>IF(AND(N_200&lt;50,(100-N_40)&gt;=0.5*(100-N_200),N_200&gt;=12,IP&gt;=7,IP&gt;=0.73*(Ll-20)),"GC","")</f>
@@ -34736,11 +34713,11 @@
     </row>
     <row r="13" spans="1:17" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="94"/>
-      <c r="B13" s="964"/>
-      <c r="C13" s="966" t="s">
+      <c r="B13" s="963"/>
+      <c r="C13" s="965" t="s">
         <v>136</v>
       </c>
-      <c r="D13" s="968" t="s">
+      <c r="D13" s="967" t="s">
         <v>137</v>
       </c>
       <c r="E13" s="113" t="s">
@@ -34749,10 +34726,10 @@
       <c r="F13" s="114" t="s">
         <v>139</v>
       </c>
-      <c r="G13" s="975" t="s">
+      <c r="G13" s="974" t="s">
         <v>140</v>
       </c>
-      <c r="H13" s="976"/>
+      <c r="H13" s="975"/>
       <c r="I13" s="94"/>
       <c r="L13" s="249" t="e">
         <f>IF(AND(N_200&lt;50,(100-N_40)&lt;0.5*(100-N_200),N_200&lt;5,CU&gt;=6,CC&gt;=1,CC&lt;=3),"SW","")</f>
@@ -34777,19 +34754,19 @@
     </row>
     <row r="14" spans="1:17" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="94"/>
-      <c r="B14" s="964"/>
-      <c r="C14" s="966"/>
-      <c r="D14" s="968"/>
+      <c r="B14" s="963"/>
+      <c r="C14" s="965"/>
+      <c r="D14" s="967"/>
       <c r="E14" s="113" t="s">
         <v>141</v>
       </c>
       <c r="F14" s="114" t="s">
         <v>142</v>
       </c>
-      <c r="G14" s="975" t="s">
+      <c r="G14" s="974" t="s">
         <v>143</v>
       </c>
-      <c r="H14" s="976"/>
+      <c r="H14" s="975"/>
       <c r="I14" s="94"/>
       <c r="L14" s="249" t="e">
         <f>IF(AND(N_200&lt;50,(100-N_40)&lt;0.5*(100-N_200),N_200&lt;5,OR(CU&lt;6,CC&lt;1,CC&gt;3)),"SP","")</f>
@@ -34814,9 +34791,9 @@
     </row>
     <row r="15" spans="1:17" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="94"/>
-      <c r="B15" s="964"/>
-      <c r="C15" s="966"/>
-      <c r="D15" s="968" t="s">
+      <c r="B15" s="963"/>
+      <c r="C15" s="965"/>
+      <c r="D15" s="967" t="s">
         <v>144</v>
       </c>
       <c r="E15" s="113" t="s">
@@ -34828,7 +34805,7 @@
       <c r="G15" s="116" t="s">
         <v>147</v>
       </c>
-      <c r="H15" s="979" t="s">
+      <c r="H15" s="978" t="s">
         <v>148</v>
       </c>
       <c r="I15" s="94"/>
@@ -34849,9 +34826,9 @@
     </row>
     <row r="16" spans="1:17" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="94"/>
-      <c r="B16" s="965"/>
-      <c r="C16" s="966"/>
-      <c r="D16" s="968"/>
+      <c r="B16" s="964"/>
+      <c r="C16" s="965"/>
+      <c r="D16" s="967"/>
       <c r="E16" s="117" t="s">
         <v>149</v>
       </c>
@@ -34861,7 +34838,7 @@
       <c r="G16" s="114" t="s">
         <v>151</v>
       </c>
-      <c r="H16" s="980"/>
+      <c r="H16" s="979"/>
       <c r="I16" s="94"/>
       <c r="L16" s="249" t="e">
         <f>IF(AND(N_200&lt;50,(100-N_40)&lt;0.5*(100-N_200),N_200&gt;=12,IP&gt;=7,IP&gt;=0.73*(Ll-20)),"SC","")</f>
@@ -34877,23 +34854,23 @@
     </row>
     <row r="17" spans="1:16" ht="48" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="94"/>
-      <c r="B17" s="981" t="s">
+      <c r="B17" s="980" t="s">
         <v>152</v>
       </c>
-      <c r="C17" s="984" t="s">
+      <c r="C17" s="983" t="s">
         <v>153</v>
       </c>
-      <c r="D17" s="985"/>
+      <c r="D17" s="984"/>
       <c r="E17" s="118" t="s">
         <v>154</v>
       </c>
       <c r="F17" s="119" t="s">
         <v>155</v>
       </c>
-      <c r="G17" s="990" t="s">
+      <c r="G17" s="989" t="s">
         <v>156</v>
       </c>
-      <c r="H17" s="991"/>
+      <c r="H17" s="990"/>
       <c r="I17" s="94"/>
       <c r="L17" s="249" t="e">
         <f>IF(AND(OR(L2="Inorganico"),N_200&gt;=50,Ll&lt;50,OR(IP&lt;4,AND(IP&lt;0.73*(Ll-20)))),"ML","")</f>
@@ -34909,17 +34886,17 @@
     </row>
     <row r="18" spans="1:16" ht="50.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="94"/>
-      <c r="B18" s="982"/>
-      <c r="C18" s="986"/>
-      <c r="D18" s="987"/>
+      <c r="B18" s="981"/>
+      <c r="C18" s="985"/>
+      <c r="D18" s="986"/>
       <c r="E18" s="118" t="s">
         <v>157</v>
       </c>
       <c r="F18" s="119" t="s">
         <v>158</v>
       </c>
-      <c r="G18" s="992"/>
-      <c r="H18" s="993"/>
+      <c r="G18" s="991"/>
+      <c r="H18" s="992"/>
       <c r="I18" s="94"/>
       <c r="L18" s="249" t="e">
         <f>IF(AND(OR(L2="Inorganico"),N_200&gt;=50,Ll&lt;50,IP&gt;=7,IP&gt;=0.73*(Ll-20)),"CL","")</f>
@@ -34935,9 +34912,9 @@
     </row>
     <row r="19" spans="1:16" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="94"/>
-      <c r="B19" s="982"/>
-      <c r="C19" s="988"/>
-      <c r="D19" s="989"/>
+      <c r="B19" s="981"/>
+      <c r="C19" s="987"/>
+      <c r="D19" s="988"/>
       <c r="E19" s="118" t="s">
         <v>159</v>
       </c>
@@ -34961,11 +34938,11 @@
     </row>
     <row r="20" spans="1:16" ht="39" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="94"/>
-      <c r="B20" s="982"/>
-      <c r="C20" s="986" t="s">
+      <c r="B20" s="981"/>
+      <c r="C20" s="985" t="s">
         <v>161</v>
       </c>
-      <c r="D20" s="994"/>
+      <c r="D20" s="993"/>
       <c r="E20" s="122" t="s">
         <v>162</v>
       </c>
@@ -34989,9 +34966,9 @@
     </row>
     <row r="21" spans="1:16" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="94"/>
-      <c r="B21" s="982"/>
-      <c r="C21" s="986"/>
-      <c r="D21" s="994"/>
+      <c r="B21" s="981"/>
+      <c r="C21" s="985"/>
+      <c r="D21" s="993"/>
       <c r="E21" s="122" t="s">
         <v>164</v>
       </c>
@@ -35015,9 +34992,9 @@
     </row>
     <row r="22" spans="1:16" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="94"/>
-      <c r="B22" s="982"/>
-      <c r="C22" s="988"/>
-      <c r="D22" s="995"/>
+      <c r="B22" s="981"/>
+      <c r="C22" s="987"/>
+      <c r="D22" s="994"/>
       <c r="E22" s="124" t="s">
         <v>166</v>
       </c>
@@ -35041,11 +35018,11 @@
     </row>
     <row r="23" spans="1:16" ht="39" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="94"/>
-      <c r="B23" s="982"/>
-      <c r="C23" s="984" t="s">
+      <c r="B23" s="981"/>
+      <c r="C23" s="983" t="s">
         <v>168</v>
       </c>
-      <c r="D23" s="985"/>
+      <c r="D23" s="984"/>
       <c r="E23" s="125" t="s">
         <v>169</v>
       </c>
@@ -35069,7 +35046,7 @@
     </row>
     <row r="24" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A24" s="94"/>
-      <c r="B24" s="983"/>
+      <c r="B24" s="982"/>
       <c r="C24" s="127"/>
       <c r="D24" s="128"/>
       <c r="E24" s="129"/>
@@ -35165,10 +35142,10 @@
       <c r="F31" s="135"/>
     </row>
     <row r="32" spans="1:16" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="977" t="s">
+      <c r="A32" s="976" t="s">
         <v>200</v>
       </c>
-      <c r="B32" s="978"/>
+      <c r="B32" s="977"/>
       <c r="F32" s="135"/>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.25">
@@ -35817,71 +35794,71 @@
     </row>
     <row r="4" spans="1:16" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="21"/>
-      <c r="B4" s="1002" t="s">
+      <c r="B4" s="1001" t="s">
         <v>42</v>
       </c>
-      <c r="C4" s="1003"/>
-      <c r="D4" s="1004" t="s">
+      <c r="C4" s="1002"/>
+      <c r="D4" s="1003" t="s">
         <v>43</v>
       </c>
-      <c r="E4" s="1004"/>
-      <c r="F4" s="1004"/>
-      <c r="G4" s="1004"/>
-      <c r="H4" s="1004"/>
-      <c r="I4" s="1004"/>
-      <c r="J4" s="1004"/>
-      <c r="K4" s="1005" t="s">
+      <c r="E4" s="1003"/>
+      <c r="F4" s="1003"/>
+      <c r="G4" s="1003"/>
+      <c r="H4" s="1003"/>
+      <c r="I4" s="1003"/>
+      <c r="J4" s="1003"/>
+      <c r="K4" s="1004" t="s">
         <v>44</v>
       </c>
-      <c r="L4" s="1006"/>
-      <c r="M4" s="1006"/>
-      <c r="N4" s="1006"/>
-      <c r="O4" s="1007"/>
+      <c r="L4" s="1005"/>
+      <c r="M4" s="1005"/>
+      <c r="N4" s="1005"/>
+      <c r="O4" s="1006"/>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5" s="21"/>
-      <c r="B5" s="1008" t="s">
+      <c r="B5" s="1007" t="s">
         <v>45</v>
       </c>
-      <c r="C5" s="1009"/>
-      <c r="D5" s="1012" t="s">
+      <c r="C5" s="1008"/>
+      <c r="D5" s="1011" t="s">
         <v>46</v>
       </c>
-      <c r="E5" s="1013"/>
-      <c r="F5" s="1014" t="s">
+      <c r="E5" s="1012"/>
+      <c r="F5" s="1013" t="s">
         <v>47</v>
       </c>
-      <c r="G5" s="1012" t="s">
+      <c r="G5" s="1011" t="s">
         <v>48</v>
       </c>
-      <c r="H5" s="1016"/>
-      <c r="I5" s="1016"/>
-      <c r="J5" s="1013"/>
-      <c r="K5" s="1017" t="s">
+      <c r="H5" s="1015"/>
+      <c r="I5" s="1015"/>
+      <c r="J5" s="1012"/>
+      <c r="K5" s="1016" t="s">
         <v>49</v>
       </c>
-      <c r="L5" s="1019" t="s">
+      <c r="L5" s="1018" t="s">
         <v>50</v>
       </c>
-      <c r="M5" s="1021" t="s">
+      <c r="M5" s="1020" t="s">
         <v>51</v>
       </c>
-      <c r="N5" s="1023" t="s">
+      <c r="N5" s="1022" t="s">
         <v>52</v>
       </c>
-      <c r="O5" s="1024"/>
+      <c r="O5" s="1023"/>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6" s="21"/>
-      <c r="B6" s="1010"/>
-      <c r="C6" s="1011"/>
+      <c r="B6" s="1009"/>
+      <c r="C6" s="1010"/>
       <c r="D6" s="25" t="s">
         <v>53</v>
       </c>
       <c r="E6" s="26" t="s">
         <v>54</v>
       </c>
-      <c r="F6" s="1015"/>
+      <c r="F6" s="1014"/>
       <c r="G6" s="25" t="s">
         <v>55</v>
       </c>
@@ -35894,9 +35871,9 @@
       <c r="J6" s="26" t="s">
         <v>58</v>
       </c>
-      <c r="K6" s="1018"/>
-      <c r="L6" s="1020"/>
-      <c r="M6" s="1022"/>
+      <c r="K6" s="1017"/>
+      <c r="L6" s="1019"/>
+      <c r="M6" s="1021"/>
       <c r="N6" s="29" t="s">
         <v>59</v>
       </c>
@@ -36296,21 +36273,21 @@
         <f>+D38</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="D23" s="996">
+      <c r="D23" s="995">
         <v>0</v>
       </c>
-      <c r="E23" s="997"/>
+      <c r="E23" s="996"/>
       <c r="F23" s="82">
         <v>0</v>
       </c>
-      <c r="G23" s="996">
+      <c r="G23" s="995">
         <v>0</v>
       </c>
-      <c r="H23" s="998"/>
-      <c r="I23" s="999" t="s">
+      <c r="H23" s="997"/>
+      <c r="I23" s="998" t="s">
         <v>87</v>
       </c>
-      <c r="J23" s="997"/>
+      <c r="J23" s="996"/>
       <c r="K23" s="83" t="s">
         <v>88</v>
       </c>
@@ -36373,11 +36350,11 @@
       <c r="G26" s="88"/>
       <c r="H26" s="23"/>
       <c r="I26" s="23"/>
-      <c r="J26" s="1000" t="e">
+      <c r="J26" s="999" t="e">
         <f>+D31&amp;" "&amp;F38</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="K26" s="1001"/>
+      <c r="K26" s="1000"/>
       <c r="L26" s="21"/>
       <c r="M26" s="21"/>
       <c r="N26" s="21"/>
@@ -36637,10 +36614,10 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="1025" t="s">
+      <c r="A2" s="1024" t="s">
         <v>10</v>
       </c>
-      <c r="B2" s="1025"/>
+      <c r="B2" s="1024"/>
       <c r="C2" s="5" t="s">
         <v>11</v>
       </c>

--- a/app/templates/informes/GranSuelo/Template_GranSuelo.xlsx
+++ b/app/templates/informes/GranSuelo/Template_GranSuelo.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24332"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27928"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Mi unidad\3.0 Formatos e informes\2026\1.0 Informe de ensayo\1.1 Informe Suelo\INFORME ACREDITADO-E ISO\6.1 JUNIO INICIA 15-06-25\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\Documents\crmnew\api-geofal-crm\app\templates\informes\GranSuelo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F60D475-2E06-4CA0-AB1E-9DE073B60BA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CBD1F228-E4A5-4B77-B363-0DD4D34E6181}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="547" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -180,7 +180,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1031" uniqueCount="577">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1031" uniqueCount="578">
   <si>
     <t>:</t>
   </si>
@@ -2438,6 +2438,9 @@
   <si>
     <t>Versión: 09 (2026-06-15)</t>
   </si>
+  <si>
+    <t>Versión: 09 (11-06-2026)</t>
+  </si>
 </sst>
 </file>
 
@@ -2471,7 +2474,7 @@
     <numFmt numFmtId="188" formatCode="&quot;Ref. Informe N°&quot;000&quot;-26 SU22&quot;"/>
     <numFmt numFmtId="189" formatCode="&quot;FORMATO F-LEM-P-SU-11.01&quot;"/>
   </numFmts>
-  <fonts count="110" x14ac:knownFonts="1">
+  <fonts count="111" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -3177,6 +3180,12 @@
       <b/>
       <sz val="10"/>
       <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="9"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
@@ -5624,7 +5633,7 @@
     <xf numFmtId="0" fontId="1" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="52" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1029">
+  <cellXfs count="1030">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="2" fontId="10" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -7953,6 +7962,13 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="4" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="57" fillId="0" borderId="156" xfId="6" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="156" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="77" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection hidden="1"/>
@@ -8323,6 +8339,15 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="6" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="6" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="110" fillId="0" borderId="0" xfId="6" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="158" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -8738,19 +8763,6 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="6" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="6" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="57" fillId="0" borderId="156" xfId="6" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="156" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="52">
@@ -9177,7 +9189,7 @@
                 <a:cs typeface="Arial"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="es-ES"/>
+            <a:endParaRPr lang="es-PE"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="128847232"/>
@@ -9280,7 +9292,7 @@
                 <a:cs typeface="Arial"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="es-ES"/>
+            <a:endParaRPr lang="es-PE"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="128844928"/>
@@ -9323,7 +9335,7 @@
           <a:cs typeface="Arial"/>
         </a:defRPr>
       </a:pPr>
-      <a:endParaRPr lang="es-ES"/>
+      <a:endParaRPr lang="es-PE"/>
     </a:p>
   </c:txPr>
   <c:printSettings>
@@ -9478,7 +9490,7 @@
                 <a:cs typeface="Arial"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="es-ES"/>
+            <a:endParaRPr lang="es-PE"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="131076096"/>
@@ -9515,7 +9527,7 @@
                 <a:cs typeface="Calibri"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="es-ES"/>
+            <a:endParaRPr lang="es-PE"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="131062016"/>
@@ -9553,7 +9565,7 @@
           <a:cs typeface="Calibri"/>
         </a:defRPr>
       </a:pPr>
-      <a:endParaRPr lang="es-ES"/>
+      <a:endParaRPr lang="es-PE"/>
     </a:p>
   </c:txPr>
   <c:printSettings>
@@ -9705,7 +9717,7 @@
                 <a:cs typeface="Arial"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="es-ES"/>
+            <a:endParaRPr lang="es-PE"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="131115264"/>
@@ -9741,7 +9753,7 @@
                 <a:cs typeface="Calibri"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="es-ES"/>
+            <a:endParaRPr lang="es-PE"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="131113728"/>
@@ -9779,7 +9791,7 @@
           <a:cs typeface="Calibri"/>
         </a:defRPr>
       </a:pPr>
-      <a:endParaRPr lang="es-ES"/>
+      <a:endParaRPr lang="es-PE"/>
     </a:p>
   </c:txPr>
   <c:printSettings>
@@ -9931,7 +9943,7 @@
                 <a:cs typeface="Arial"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="es-ES"/>
+            <a:endParaRPr lang="es-PE"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="131289856"/>
@@ -9968,7 +9980,7 @@
                 <a:cs typeface="Calibri"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="es-ES"/>
+            <a:endParaRPr lang="es-PE"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="131283968"/>
@@ -10006,7 +10018,7 @@
           <a:cs typeface="Calibri"/>
         </a:defRPr>
       </a:pPr>
-      <a:endParaRPr lang="es-ES"/>
+      <a:endParaRPr lang="es-PE"/>
     </a:p>
   </c:txPr>
   <c:printSettings>
@@ -10158,7 +10170,7 @@
                 <a:cs typeface="Arial"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="es-ES"/>
+            <a:endParaRPr lang="es-PE"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="131308544"/>
@@ -10194,7 +10206,7 @@
                 <a:cs typeface="Calibri"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="es-ES"/>
+            <a:endParaRPr lang="es-PE"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="131307008"/>
@@ -10232,7 +10244,7 @@
           <a:cs typeface="Calibri"/>
         </a:defRPr>
       </a:pPr>
-      <a:endParaRPr lang="es-ES"/>
+      <a:endParaRPr lang="es-PE"/>
     </a:p>
   </c:txPr>
   <c:printSettings>
@@ -10384,7 +10396,7 @@
                 <a:cs typeface="Arial"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="es-ES"/>
+            <a:endParaRPr lang="es-PE"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="131409408"/>
@@ -10421,7 +10433,7 @@
                 <a:cs typeface="Calibri"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="es-ES"/>
+            <a:endParaRPr lang="es-PE"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="131407872"/>
@@ -10459,7 +10471,7 @@
           <a:cs typeface="Calibri"/>
         </a:defRPr>
       </a:pPr>
-      <a:endParaRPr lang="es-ES"/>
+      <a:endParaRPr lang="es-PE"/>
     </a:p>
   </c:txPr>
   <c:printSettings>
@@ -10621,7 +10633,7 @@
                 <a:cs typeface="Arial"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="es-ES"/>
+            <a:endParaRPr lang="es-PE"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="131448832"/>
@@ -10657,7 +10669,7 @@
                 <a:cs typeface="Calibri"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="es-ES"/>
+            <a:endParaRPr lang="es-PE"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="131442944"/>
@@ -10696,7 +10708,7 @@
           <a:cs typeface="Calibri"/>
         </a:defRPr>
       </a:pPr>
-      <a:endParaRPr lang="es-ES"/>
+      <a:endParaRPr lang="es-PE"/>
     </a:p>
   </c:txPr>
   <c:printSettings>
@@ -11025,7 +11037,7 @@
                 <a:cs typeface="Arial"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="es-ES"/>
+            <a:endParaRPr lang="es-PE"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="131648128"/>
@@ -11128,7 +11140,7 @@
                 <a:cs typeface="Arial"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="es-ES"/>
+            <a:endParaRPr lang="es-PE"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="131645824"/>
@@ -11177,7 +11189,7 @@
           <a:cs typeface="Arial"/>
         </a:defRPr>
       </a:pPr>
-      <a:endParaRPr lang="es-ES"/>
+      <a:endParaRPr lang="es-PE"/>
     </a:p>
   </c:txPr>
   <c:printSettings>
@@ -11329,7 +11341,7 @@
                 <a:cs typeface="Arial"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="es-ES"/>
+            <a:endParaRPr lang="es-PE"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="130499328"/>
@@ -11366,7 +11378,7 @@
                 <a:cs typeface="Calibri"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="es-ES"/>
+            <a:endParaRPr lang="es-PE"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="130497536"/>
@@ -11404,7 +11416,7 @@
           <a:cs typeface="Calibri"/>
         </a:defRPr>
       </a:pPr>
-      <a:endParaRPr lang="es-ES"/>
+      <a:endParaRPr lang="es-PE"/>
     </a:p>
   </c:txPr>
   <c:printSettings>
@@ -11556,7 +11568,7 @@
                 <a:cs typeface="Arial"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="es-ES"/>
+            <a:endParaRPr lang="es-PE"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="130546688"/>
@@ -11593,7 +11605,7 @@
                 <a:cs typeface="Calibri"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="es-ES"/>
+            <a:endParaRPr lang="es-PE"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="130545152"/>
@@ -11631,7 +11643,7 @@
           <a:cs typeface="Calibri"/>
         </a:defRPr>
       </a:pPr>
-      <a:endParaRPr lang="es-ES"/>
+      <a:endParaRPr lang="es-PE"/>
     </a:p>
   </c:txPr>
   <c:printSettings>
@@ -11771,7 +11783,7 @@
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
-            <a:endParaRPr lang="es-ES"/>
+            <a:endParaRPr lang="es-PE"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="130569728"/>
@@ -11801,7 +11813,7 @@
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
-            <a:endParaRPr lang="es-ES"/>
+            <a:endParaRPr lang="es-PE"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="130568192"/>
@@ -11839,7 +11851,7 @@
           <a:cs typeface="Calibri"/>
         </a:defRPr>
       </a:pPr>
-      <a:endParaRPr lang="es-ES"/>
+      <a:endParaRPr lang="es-PE"/>
     </a:p>
   </c:txPr>
   <c:printSettings>
@@ -11991,7 +12003,7 @@
                 <a:cs typeface="Arial"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="es-ES"/>
+            <a:endParaRPr lang="es-PE"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="130744320"/>
@@ -12028,7 +12040,7 @@
                 <a:cs typeface="Calibri"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="es-ES"/>
+            <a:endParaRPr lang="es-PE"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="130607360"/>
@@ -12066,7 +12078,7 @@
           <a:cs typeface="Calibri"/>
         </a:defRPr>
       </a:pPr>
-      <a:endParaRPr lang="es-ES"/>
+      <a:endParaRPr lang="es-PE"/>
     </a:p>
   </c:txPr>
   <c:printSettings>
@@ -12218,7 +12230,7 @@
                 <a:cs typeface="Arial"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="es-ES"/>
+            <a:endParaRPr lang="es-PE"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="130803968"/>
@@ -12255,7 +12267,7 @@
                 <a:cs typeface="Calibri"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="es-ES"/>
+            <a:endParaRPr lang="es-PE"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="130802432"/>
@@ -12293,7 +12305,7 @@
           <a:cs typeface="Calibri"/>
         </a:defRPr>
       </a:pPr>
-      <a:endParaRPr lang="es-ES"/>
+      <a:endParaRPr lang="es-PE"/>
     </a:p>
   </c:txPr>
   <c:printSettings>
@@ -12445,7 +12457,7 @@
                 <a:cs typeface="Arial"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="es-ES"/>
+            <a:endParaRPr lang="es-PE"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="130904832"/>
@@ -12482,7 +12494,7 @@
                 <a:cs typeface="Calibri"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="es-ES"/>
+            <a:endParaRPr lang="es-PE"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="130890752"/>
@@ -12520,7 +12532,7 @@
           <a:cs typeface="Calibri"/>
         </a:defRPr>
       </a:pPr>
-      <a:endParaRPr lang="es-ES"/>
+      <a:endParaRPr lang="es-PE"/>
     </a:p>
   </c:txPr>
   <c:printSettings>
@@ -12672,7 +12684,7 @@
                 <a:cs typeface="Arial"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="es-ES"/>
+            <a:endParaRPr lang="es-PE"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="130948096"/>
@@ -12709,7 +12721,7 @@
                 <a:cs typeface="Calibri"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="es-ES"/>
+            <a:endParaRPr lang="es-PE"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="130946560"/>
@@ -12747,7 +12759,7 @@
           <a:cs typeface="Calibri"/>
         </a:defRPr>
       </a:pPr>
-      <a:endParaRPr lang="es-ES"/>
+      <a:endParaRPr lang="es-PE"/>
     </a:p>
   </c:txPr>
   <c:printSettings>
@@ -12899,7 +12911,7 @@
                 <a:cs typeface="Arial"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="es-ES"/>
+            <a:endParaRPr lang="es-PE"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="131032576"/>
@@ -12936,7 +12948,7 @@
                 <a:cs typeface="Calibri"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="es-ES"/>
+            <a:endParaRPr lang="es-PE"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="131031040"/>
@@ -12974,7 +12986,7 @@
           <a:cs typeface="Calibri"/>
         </a:defRPr>
       </a:pPr>
-      <a:endParaRPr lang="es-ES"/>
+      <a:endParaRPr lang="es-PE"/>
     </a:p>
   </c:txPr>
   <c:printSettings>
@@ -16394,7 +16406,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="-------"/>
@@ -16453,7 +16465,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="datos de ecuacion del anillo"/>
@@ -16572,7 +16584,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink3.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="-------"/>
@@ -16623,7 +16635,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink4.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="-------"/>
@@ -16675,7 +16687,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink5.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="BGA"/>
@@ -16707,7 +16719,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink6.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="-------"/>
@@ -21618,38 +21630,38 @@
       <c r="O6" s="764"/>
     </row>
     <row r="7" spans="1:21" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="782" t="s">
+      <c r="A7" s="784" t="s">
         <v>21</v>
       </c>
-      <c r="B7" s="782"/>
-      <c r="C7" s="782"/>
-      <c r="D7" s="782"/>
-      <c r="E7" s="782"/>
-      <c r="F7" s="782"/>
-      <c r="G7" s="782"/>
-      <c r="H7" s="782"/>
-      <c r="I7" s="782"/>
-      <c r="J7" s="782"/>
-      <c r="K7" s="782"/>
+      <c r="B7" s="784"/>
+      <c r="C7" s="784"/>
+      <c r="D7" s="784"/>
+      <c r="E7" s="784"/>
+      <c r="F7" s="784"/>
+      <c r="G7" s="784"/>
+      <c r="H7" s="784"/>
+      <c r="I7" s="784"/>
+      <c r="J7" s="784"/>
+      <c r="K7" s="784"/>
       <c r="N7" s="291" t="s">
         <v>447</v>
       </c>
       <c r="O7" s="764"/>
     </row>
     <row r="8" spans="1:21" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="783" t="s">
+      <c r="A8" s="785" t="s">
         <v>480</v>
       </c>
-      <c r="B8" s="783"/>
-      <c r="C8" s="783"/>
-      <c r="D8" s="783"/>
-      <c r="E8" s="783"/>
-      <c r="F8" s="783"/>
-      <c r="G8" s="783"/>
-      <c r="H8" s="783"/>
-      <c r="I8" s="783"/>
-      <c r="J8" s="783"/>
-      <c r="K8" s="783"/>
+      <c r="B8" s="785"/>
+      <c r="C8" s="785"/>
+      <c r="D8" s="785"/>
+      <c r="E8" s="785"/>
+      <c r="F8" s="785"/>
+      <c r="G8" s="785"/>
+      <c r="H8" s="785"/>
+      <c r="I8" s="785"/>
+      <c r="J8" s="785"/>
+      <c r="K8" s="785"/>
       <c r="N8" s="291" t="s">
         <v>553</v>
       </c>
@@ -21675,18 +21687,18 @@
     <row r="10" spans="1:21" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B10" s="487"/>
       <c r="C10" s="487"/>
-      <c r="D10" s="784" t="s">
+      <c r="D10" s="786" t="s">
         <v>481</v>
       </c>
-      <c r="E10" s="785"/>
-      <c r="F10" s="784" t="s">
+      <c r="E10" s="787"/>
+      <c r="F10" s="786" t="s">
         <v>482</v>
       </c>
-      <c r="G10" s="785"/>
-      <c r="H10" s="784" t="s">
+      <c r="G10" s="787"/>
+      <c r="H10" s="786" t="s">
         <v>30</v>
       </c>
-      <c r="I10" s="785"/>
+      <c r="I10" s="787"/>
       <c r="J10" s="683" t="s">
         <v>467</v>
       </c>
@@ -21700,12 +21712,12 @@
       <c r="A11" s="487"/>
       <c r="B11" s="487"/>
       <c r="C11" s="487"/>
-      <c r="D11" s="786"/>
-      <c r="E11" s="787"/>
-      <c r="F11" s="786"/>
-      <c r="G11" s="787"/>
-      <c r="H11" s="786"/>
-      <c r="I11" s="787"/>
+      <c r="D11" s="788"/>
+      <c r="E11" s="789"/>
+      <c r="F11" s="788"/>
+      <c r="G11" s="789"/>
+      <c r="H11" s="788"/>
+      <c r="I11" s="789"/>
       <c r="J11" s="686"/>
       <c r="K11" s="387"/>
       <c r="L11" s="685"/>
@@ -21735,19 +21747,19 @@
       <c r="O12" s="765"/>
     </row>
     <row r="13" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="788" t="s">
+      <c r="A13" s="790" t="s">
         <v>483</v>
       </c>
-      <c r="B13" s="789"/>
-      <c r="C13" s="789"/>
-      <c r="D13" s="789"/>
-      <c r="E13" s="789"/>
-      <c r="F13" s="789"/>
-      <c r="G13" s="789"/>
-      <c r="H13" s="789"/>
-      <c r="I13" s="789"/>
-      <c r="J13" s="789"/>
-      <c r="K13" s="790"/>
+      <c r="B13" s="791"/>
+      <c r="C13" s="791"/>
+      <c r="D13" s="791"/>
+      <c r="E13" s="791"/>
+      <c r="F13" s="791"/>
+      <c r="G13" s="791"/>
+      <c r="H13" s="791"/>
+      <c r="I13" s="791"/>
+      <c r="J13" s="791"/>
+      <c r="K13" s="792"/>
       <c r="L13" s="685"/>
       <c r="M13" s="685"/>
       <c r="N13" s="291" t="s">
@@ -21756,19 +21768,19 @@
       <c r="O13" s="765"/>
     </row>
     <row r="14" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="791" t="s">
+      <c r="A14" s="793" t="s">
         <v>484</v>
       </c>
-      <c r="B14" s="792"/>
-      <c r="C14" s="792"/>
-      <c r="D14" s="792"/>
-      <c r="E14" s="792"/>
-      <c r="F14" s="792"/>
-      <c r="G14" s="792"/>
-      <c r="H14" s="792"/>
-      <c r="I14" s="792"/>
-      <c r="J14" s="792"/>
-      <c r="K14" s="793"/>
+      <c r="B14" s="794"/>
+      <c r="C14" s="794"/>
+      <c r="D14" s="794"/>
+      <c r="E14" s="794"/>
+      <c r="F14" s="794"/>
+      <c r="G14" s="794"/>
+      <c r="H14" s="794"/>
+      <c r="I14" s="794"/>
+      <c r="J14" s="794"/>
+      <c r="K14" s="795"/>
       <c r="L14" s="685"/>
       <c r="M14" s="685"/>
       <c r="N14" s="763"/>
@@ -21788,21 +21800,21 @@
       <c r="U15" s="688"/>
     </row>
     <row r="16" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="794" t="s">
+      <c r="A16" s="796" t="s">
         <v>485</v>
       </c>
-      <c r="B16" s="795"/>
-      <c r="C16" s="796"/>
-      <c r="E16" s="797" t="s">
+      <c r="B16" s="797"/>
+      <c r="C16" s="798"/>
+      <c r="E16" s="799" t="s">
         <v>372</v>
       </c>
-      <c r="F16" s="798"/>
-      <c r="G16" s="798"/>
-      <c r="H16" s="799"/>
-      <c r="J16" s="794" t="s">
+      <c r="F16" s="800"/>
+      <c r="G16" s="800"/>
+      <c r="H16" s="801"/>
+      <c r="J16" s="796" t="s">
         <v>486</v>
       </c>
-      <c r="K16" s="796"/>
+      <c r="K16" s="798"/>
       <c r="M16" s="688"/>
       <c r="N16" s="291" t="s">
         <v>245</v>
@@ -21818,16 +21830,16 @@
       <c r="A17" s="691" t="s">
         <v>487</v>
       </c>
-      <c r="B17" s="778"/>
-      <c r="C17" s="779"/>
+      <c r="B17" s="780"/>
+      <c r="C17" s="781"/>
       <c r="E17" s="692" t="s">
         <v>488</v>
       </c>
       <c r="F17" s="693"/>
       <c r="G17" s="694"/>
       <c r="H17" s="695"/>
-      <c r="J17" s="780"/>
-      <c r="K17" s="781"/>
+      <c r="J17" s="782"/>
+      <c r="K17" s="783"/>
       <c r="M17" s="688"/>
       <c r="N17" s="291" t="s">
         <v>555</v>
@@ -21843,8 +21855,8 @@
       <c r="A18" s="691" t="s">
         <v>489</v>
       </c>
-      <c r="B18" s="778"/>
-      <c r="C18" s="779"/>
+      <c r="B18" s="780"/>
+      <c r="C18" s="781"/>
       <c r="E18" s="692" t="s">
         <v>490</v>
       </c>
@@ -21867,10 +21879,10 @@
       <c r="F19" s="693"/>
       <c r="G19" s="694"/>
       <c r="H19" s="698"/>
-      <c r="J19" s="804" t="s">
+      <c r="J19" s="806" t="s">
         <v>492</v>
       </c>
-      <c r="K19" s="805"/>
+      <c r="K19" s="807"/>
       <c r="M19" s="688"/>
       <c r="N19" s="696"/>
       <c r="O19" s="689"/>
@@ -21881,11 +21893,11 @@
       <c r="U19" s="690"/>
     </row>
     <row r="20" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="806" t="s">
+      <c r="A20" s="808" t="s">
         <v>493</v>
       </c>
-      <c r="B20" s="807"/>
-      <c r="C20" s="808"/>
+      <c r="B20" s="809"/>
+      <c r="C20" s="810"/>
       <c r="E20" s="699" t="s">
         <v>494</v>
       </c>
@@ -21909,8 +21921,8 @@
       <c r="A21" s="691" t="s">
         <v>495</v>
       </c>
-      <c r="B21" s="809"/>
-      <c r="C21" s="810"/>
+      <c r="B21" s="811"/>
+      <c r="C21" s="812"/>
       <c r="E21" s="704"/>
       <c r="F21" s="704"/>
       <c r="G21" s="704"/>
@@ -21931,14 +21943,14 @@
       <c r="A22" s="691" t="s">
         <v>497</v>
       </c>
-      <c r="B22" s="809"/>
-      <c r="C22" s="810"/>
-      <c r="E22" s="804" t="s">
+      <c r="B22" s="811"/>
+      <c r="C22" s="812"/>
+      <c r="E22" s="806" t="s">
         <v>369</v>
       </c>
-      <c r="F22" s="811"/>
-      <c r="G22" s="811"/>
-      <c r="H22" s="805"/>
+      <c r="F22" s="813"/>
+      <c r="G22" s="813"/>
+      <c r="H22" s="807"/>
       <c r="I22" s="705"/>
       <c r="J22" s="488" t="s">
         <v>370</v>
@@ -21974,11 +21986,11 @@
       <c r="U23" s="690"/>
     </row>
     <row r="24" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="794" t="s">
+      <c r="A24" s="796" t="s">
         <v>500</v>
       </c>
-      <c r="B24" s="795"/>
-      <c r="C24" s="796"/>
+      <c r="B24" s="797"/>
+      <c r="C24" s="798"/>
       <c r="E24" s="692" t="s">
         <v>501</v>
       </c>
@@ -22130,8 +22142,8 @@
       <c r="A31" s="709" t="s">
         <v>513</v>
       </c>
-      <c r="B31" s="812"/>
-      <c r="C31" s="812"/>
+      <c r="B31" s="814"/>
+      <c r="C31" s="814"/>
       <c r="E31" s="692" t="s">
         <v>514</v>
       </c>
@@ -22154,8 +22166,8 @@
       <c r="A32" s="709" t="s">
         <v>515</v>
       </c>
-      <c r="B32" s="812"/>
-      <c r="C32" s="812"/>
+      <c r="B32" s="814"/>
+      <c r="C32" s="814"/>
       <c r="E32" s="692" t="s">
         <v>516</v>
       </c>
@@ -22194,17 +22206,17 @@
       <c r="U33" s="690"/>
     </row>
     <row r="34" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="806" t="s">
+      <c r="A34" s="808" t="s">
         <v>518</v>
       </c>
-      <c r="B34" s="807"/>
-      <c r="C34" s="808"/>
-      <c r="E34" s="813" t="s">
+      <c r="B34" s="809"/>
+      <c r="C34" s="810"/>
+      <c r="E34" s="815" t="s">
         <v>519</v>
       </c>
-      <c r="F34" s="814"/>
-      <c r="G34" s="800"/>
-      <c r="H34" s="801"/>
+      <c r="F34" s="816"/>
+      <c r="G34" s="802"/>
+      <c r="H34" s="803"/>
       <c r="I34" s="721"/>
       <c r="J34" s="722" t="s">
         <v>520</v>
@@ -22224,10 +22236,10 @@
       </c>
       <c r="B35" s="704"/>
       <c r="C35" s="725"/>
-      <c r="E35" s="815"/>
-      <c r="F35" s="816"/>
-      <c r="G35" s="802"/>
-      <c r="H35" s="803"/>
+      <c r="E35" s="817"/>
+      <c r="F35" s="818"/>
+      <c r="G35" s="804"/>
+      <c r="H35" s="805"/>
       <c r="J35" s="726" t="s">
         <v>522</v>
       </c>
@@ -22251,19 +22263,19 @@
       <c r="P36" s="688"/>
     </row>
     <row r="37" spans="1:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="806" t="s">
+      <c r="A37" s="808" t="s">
         <v>523</v>
       </c>
-      <c r="B37" s="807"/>
-      <c r="C37" s="808"/>
-      <c r="E37" s="824" t="s">
+      <c r="B37" s="809"/>
+      <c r="C37" s="810"/>
+      <c r="E37" s="826" t="s">
         <v>524</v>
       </c>
-      <c r="F37" s="825"/>
-      <c r="G37" s="825"/>
-      <c r="H37" s="825"/>
-      <c r="I37" s="826"/>
-      <c r="K37" s="817" t="s">
+      <c r="F37" s="827"/>
+      <c r="G37" s="827"/>
+      <c r="H37" s="827"/>
+      <c r="I37" s="828"/>
+      <c r="K37" s="819" t="s">
         <v>525</v>
       </c>
       <c r="L37" s="685"/>
@@ -22276,15 +22288,15 @@
       <c r="E38" s="734" t="s">
         <v>551</v>
       </c>
-      <c r="F38" s="786" t="s">
+      <c r="F38" s="788" t="s">
         <v>526</v>
       </c>
-      <c r="G38" s="787"/>
-      <c r="H38" s="786" t="s">
+      <c r="G38" s="789"/>
+      <c r="H38" s="788" t="s">
         <v>527</v>
       </c>
-      <c r="I38" s="787"/>
-      <c r="K38" s="817"/>
+      <c r="I38" s="789"/>
+      <c r="K38" s="819"/>
       <c r="L38" s="685"/>
     </row>
     <row r="39" spans="1:21" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -22303,10 +22315,10 @@
       <c r="C40" s="737" t="s">
         <v>529</v>
       </c>
-      <c r="D40" s="804" t="s">
+      <c r="D40" s="806" t="s">
         <v>530</v>
       </c>
-      <c r="E40" s="805"/>
+      <c r="E40" s="807"/>
       <c r="I40" s="738" t="s">
         <v>531</v>
       </c>
@@ -22319,10 +22331,10 @@
       <c r="C41" s="737" t="s">
         <v>533</v>
       </c>
-      <c r="D41" s="804" t="s">
+      <c r="D41" s="806" t="s">
         <v>366</v>
       </c>
-      <c r="E41" s="805"/>
+      <c r="E41" s="807"/>
       <c r="J41" s="739"/>
       <c r="L41" s="685"/>
     </row>
@@ -22429,14 +22441,14 @@
       </c>
       <c r="D50" s="742"/>
       <c r="E50" s="749"/>
-      <c r="G50" s="819" t="s">
+      <c r="G50" s="821" t="s">
         <v>541</v>
       </c>
-      <c r="H50" s="820"/>
-      <c r="I50" s="819" t="s">
+      <c r="H50" s="822"/>
+      <c r="I50" s="821" t="s">
         <v>542</v>
       </c>
-      <c r="J50" s="820"/>
+      <c r="J50" s="822"/>
       <c r="L50" s="685"/>
       <c r="M50" s="685"/>
     </row>
@@ -22453,8 +22465,8 @@
         <v>543</v>
       </c>
       <c r="H51" s="751"/>
-      <c r="I51" s="821"/>
-      <c r="J51" s="822"/>
+      <c r="I51" s="823"/>
+      <c r="J51" s="824"/>
       <c r="L51" s="685"/>
       <c r="M51" s="685"/>
     </row>
@@ -22471,8 +22483,8 @@
         <v>545</v>
       </c>
       <c r="H52" s="751"/>
-      <c r="I52" s="821"/>
-      <c r="J52" s="822"/>
+      <c r="I52" s="823"/>
+      <c r="J52" s="824"/>
       <c r="L52" s="685"/>
       <c r="M52" s="685"/>
     </row>
@@ -22602,12 +22614,12 @@
       <c r="B62" s="487"/>
       <c r="C62" s="487"/>
       <c r="D62" s="487"/>
-      <c r="E62" s="823"/>
-      <c r="F62" s="823"/>
-      <c r="G62" s="823"/>
-      <c r="H62" s="823"/>
-      <c r="I62" s="823"/>
-      <c r="J62" s="823"/>
+      <c r="E62" s="825"/>
+      <c r="F62" s="825"/>
+      <c r="G62" s="825"/>
+      <c r="H62" s="825"/>
+      <c r="I62" s="825"/>
+      <c r="J62" s="825"/>
       <c r="K62" s="744"/>
       <c r="L62" s="685"/>
       <c r="M62" s="685"/>
@@ -22634,19 +22646,19 @@
       <c r="G64" s="260"/>
     </row>
     <row r="65" spans="1:11" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="818" t="s">
+      <c r="A65" s="820" t="s">
         <v>550</v>
       </c>
-      <c r="B65" s="818"/>
-      <c r="C65" s="818"/>
-      <c r="D65" s="818"/>
-      <c r="E65" s="818"/>
-      <c r="F65" s="818"/>
-      <c r="G65" s="818"/>
-      <c r="H65" s="818"/>
-      <c r="I65" s="818"/>
-      <c r="J65" s="818"/>
-      <c r="K65" s="818"/>
+      <c r="B65" s="820"/>
+      <c r="C65" s="820"/>
+      <c r="D65" s="820"/>
+      <c r="E65" s="820"/>
+      <c r="F65" s="820"/>
+      <c r="G65" s="820"/>
+      <c r="H65" s="820"/>
+      <c r="I65" s="820"/>
+      <c r="J65" s="820"/>
+      <c r="K65" s="820"/>
     </row>
     <row r="66" spans="1:11" ht="15.9" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="67" spans="1:11" ht="15.9" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -22861,14 +22873,14 @@
       <c r="L5" s="566"/>
       <c r="M5" s="566"/>
       <c r="N5" s="566"/>
-      <c r="Q5" s="872" t="s">
+      <c r="Q5" s="874" t="s">
         <v>369</v>
       </c>
-      <c r="R5" s="873"/>
-      <c r="S5" s="873"/>
-      <c r="T5" s="873"/>
-      <c r="U5" s="873"/>
-      <c r="V5" s="874"/>
+      <c r="R5" s="875"/>
+      <c r="S5" s="875"/>
+      <c r="T5" s="875"/>
+      <c r="U5" s="875"/>
+      <c r="V5" s="876"/>
       <c r="X5" s="476" t="s">
         <v>370</v>
       </c>
@@ -22929,22 +22941,22 @@
       </c>
     </row>
     <row r="7" spans="1:30" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="782" t="s">
+      <c r="A7" s="784" t="s">
         <v>21</v>
       </c>
-      <c r="B7" s="782"/>
-      <c r="C7" s="782"/>
-      <c r="D7" s="782"/>
-      <c r="E7" s="782"/>
-      <c r="F7" s="782"/>
-      <c r="G7" s="782"/>
-      <c r="H7" s="782"/>
-      <c r="I7" s="782"/>
-      <c r="J7" s="782"/>
-      <c r="K7" s="782"/>
-      <c r="L7" s="782"/>
-      <c r="M7" s="782"/>
-      <c r="N7" s="782"/>
+      <c r="B7" s="784"/>
+      <c r="C7" s="784"/>
+      <c r="D7" s="784"/>
+      <c r="E7" s="784"/>
+      <c r="F7" s="784"/>
+      <c r="G7" s="784"/>
+      <c r="H7" s="784"/>
+      <c r="I7" s="784"/>
+      <c r="J7" s="784"/>
+      <c r="K7" s="784"/>
+      <c r="L7" s="784"/>
+      <c r="M7" s="784"/>
+      <c r="N7" s="784"/>
       <c r="Q7" s="480" t="s">
         <v>422</v>
       </c>
@@ -22983,22 +22995,22 @@
       </c>
     </row>
     <row r="8" spans="1:30" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="884">
+      <c r="A8" s="886">
         <v>0</v>
       </c>
-      <c r="B8" s="884"/>
-      <c r="C8" s="884"/>
-      <c r="D8" s="884"/>
-      <c r="E8" s="884"/>
-      <c r="F8" s="884"/>
-      <c r="G8" s="884"/>
-      <c r="H8" s="884"/>
-      <c r="I8" s="884"/>
-      <c r="J8" s="884"/>
-      <c r="K8" s="884"/>
-      <c r="L8" s="884"/>
-      <c r="M8" s="884"/>
-      <c r="N8" s="884"/>
+      <c r="B8" s="886"/>
+      <c r="C8" s="886"/>
+      <c r="D8" s="886"/>
+      <c r="E8" s="886"/>
+      <c r="F8" s="886"/>
+      <c r="G8" s="886"/>
+      <c r="H8" s="886"/>
+      <c r="I8" s="886"/>
+      <c r="J8" s="886"/>
+      <c r="K8" s="886"/>
+      <c r="L8" s="886"/>
+      <c r="M8" s="886"/>
+      <c r="N8" s="886"/>
       <c r="Q8" s="480" t="s">
         <v>423</v>
       </c>
@@ -23043,18 +23055,18 @@
       <c r="B9" s="287" t="s">
         <v>0</v>
       </c>
-      <c r="C9" s="886">
+      <c r="C9" s="888">
         <f>+FORMATO!O2</f>
         <v>0</v>
       </c>
-      <c r="D9" s="886"/>
-      <c r="E9" s="886"/>
-      <c r="F9" s="886"/>
-      <c r="G9" s="886"/>
-      <c r="H9" s="886"/>
-      <c r="I9" s="886"/>
-      <c r="J9" s="886"/>
-      <c r="K9" s="886"/>
+      <c r="D9" s="888"/>
+      <c r="E9" s="888"/>
+      <c r="F9" s="888"/>
+      <c r="G9" s="888"/>
+      <c r="H9" s="888"/>
+      <c r="I9" s="888"/>
+      <c r="J9" s="888"/>
+      <c r="K9" s="888"/>
       <c r="L9" s="289" t="s">
         <v>31</v>
       </c>
@@ -23099,18 +23111,18 @@
       <c r="B10" s="288" t="s">
         <v>0</v>
       </c>
-      <c r="C10" s="886">
+      <c r="C10" s="888">
         <f>+FORMATO!O3</f>
         <v>0</v>
       </c>
-      <c r="D10" s="886"/>
-      <c r="E10" s="886"/>
-      <c r="F10" s="886"/>
-      <c r="G10" s="886"/>
-      <c r="H10" s="886"/>
-      <c r="I10" s="886"/>
-      <c r="J10" s="886"/>
-      <c r="K10" s="886"/>
+      <c r="D10" s="888"/>
+      <c r="E10" s="888"/>
+      <c r="F10" s="888"/>
+      <c r="G10" s="888"/>
+      <c r="H10" s="888"/>
+      <c r="I10" s="888"/>
+      <c r="J10" s="888"/>
+      <c r="K10" s="888"/>
       <c r="L10" s="768" t="s">
         <v>447</v>
       </c>
@@ -23138,18 +23150,18 @@
       <c r="B11" s="288" t="s">
         <v>0</v>
       </c>
-      <c r="C11" s="886">
+      <c r="C11" s="888">
         <f>+FORMATO!O4</f>
         <v>0</v>
       </c>
-      <c r="D11" s="886"/>
-      <c r="E11" s="886"/>
-      <c r="F11" s="886"/>
-      <c r="G11" s="886"/>
-      <c r="H11" s="886"/>
-      <c r="I11" s="886"/>
-      <c r="J11" s="886"/>
-      <c r="K11" s="886"/>
+      <c r="D11" s="888"/>
+      <c r="E11" s="888"/>
+      <c r="F11" s="888"/>
+      <c r="G11" s="888"/>
+      <c r="H11" s="888"/>
+      <c r="I11" s="888"/>
+      <c r="J11" s="888"/>
+      <c r="K11" s="888"/>
       <c r="L11" s="291" t="s">
         <v>466</v>
       </c>
@@ -23162,14 +23174,14 @@
       </c>
       <c r="O11" s="572"/>
       <c r="P11" s="572"/>
-      <c r="Q11" s="875" t="s">
+      <c r="Q11" s="877" t="s">
         <v>40</v>
       </c>
-      <c r="R11" s="885"/>
-      <c r="S11" s="885"/>
-      <c r="T11" s="885"/>
-      <c r="U11" s="885"/>
-      <c r="V11" s="876"/>
+      <c r="R11" s="887"/>
+      <c r="S11" s="887"/>
+      <c r="T11" s="887"/>
+      <c r="U11" s="887"/>
+      <c r="V11" s="878"/>
       <c r="X11" s="573" t="s">
         <v>198</v>
       </c>
@@ -23190,18 +23202,18 @@
       <c r="B12" s="288" t="s">
         <v>0</v>
       </c>
-      <c r="C12" s="886">
+      <c r="C12" s="888">
         <f>+FORMATO!O5</f>
         <v>0</v>
       </c>
-      <c r="D12" s="886"/>
-      <c r="E12" s="886"/>
-      <c r="F12" s="886"/>
-      <c r="G12" s="886"/>
-      <c r="H12" s="886"/>
-      <c r="I12" s="886"/>
-      <c r="J12" s="886"/>
-      <c r="K12" s="886"/>
+      <c r="D12" s="888"/>
+      <c r="E12" s="888"/>
+      <c r="F12" s="888"/>
+      <c r="G12" s="888"/>
+      <c r="H12" s="888"/>
+      <c r="I12" s="888"/>
+      <c r="J12" s="888"/>
+      <c r="K12" s="888"/>
       <c r="L12" s="768" t="s">
         <v>253</v>
       </c>
@@ -23287,22 +23299,22 @@
       </c>
     </row>
     <row r="14" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="877" t="s">
+      <c r="A14" s="879" t="s">
         <v>250</v>
       </c>
-      <c r="B14" s="878"/>
-      <c r="C14" s="878"/>
-      <c r="D14" s="879"/>
-      <c r="E14" s="878"/>
-      <c r="F14" s="879"/>
-      <c r="G14" s="879"/>
-      <c r="H14" s="879"/>
-      <c r="I14" s="879"/>
-      <c r="J14" s="879"/>
-      <c r="K14" s="879"/>
-      <c r="L14" s="879"/>
-      <c r="M14" s="879"/>
-      <c r="N14" s="880"/>
+      <c r="B14" s="880"/>
+      <c r="C14" s="880"/>
+      <c r="D14" s="881"/>
+      <c r="E14" s="880"/>
+      <c r="F14" s="881"/>
+      <c r="G14" s="881"/>
+      <c r="H14" s="881"/>
+      <c r="I14" s="881"/>
+      <c r="J14" s="881"/>
+      <c r="K14" s="881"/>
+      <c r="L14" s="881"/>
+      <c r="M14" s="881"/>
+      <c r="N14" s="882"/>
       <c r="O14" s="572"/>
       <c r="P14" s="572"/>
       <c r="Q14" s="480" t="s">
@@ -23333,22 +23345,22 @@
       </c>
     </row>
     <row r="15" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="881" t="s">
+      <c r="A15" s="883" t="s">
         <v>479</v>
       </c>
-      <c r="B15" s="882"/>
-      <c r="C15" s="882"/>
-      <c r="D15" s="882"/>
-      <c r="E15" s="882"/>
-      <c r="F15" s="882"/>
-      <c r="G15" s="882"/>
-      <c r="H15" s="882"/>
-      <c r="I15" s="882"/>
-      <c r="J15" s="882"/>
-      <c r="K15" s="882"/>
-      <c r="L15" s="882"/>
-      <c r="M15" s="882"/>
-      <c r="N15" s="883"/>
+      <c r="B15" s="884"/>
+      <c r="C15" s="884"/>
+      <c r="D15" s="884"/>
+      <c r="E15" s="884"/>
+      <c r="F15" s="884"/>
+      <c r="G15" s="884"/>
+      <c r="H15" s="884"/>
+      <c r="I15" s="884"/>
+      <c r="J15" s="884"/>
+      <c r="K15" s="884"/>
+      <c r="L15" s="884"/>
+      <c r="M15" s="884"/>
+      <c r="N15" s="885"/>
       <c r="O15" s="572"/>
       <c r="P15" s="572"/>
       <c r="V15" s="387"/>
@@ -23380,14 +23392,14 @@
       <c r="N16" s="298"/>
       <c r="O16" s="572"/>
       <c r="P16" s="572"/>
-      <c r="Q16" s="875" t="s">
+      <c r="Q16" s="877" t="s">
         <v>438</v>
       </c>
-      <c r="R16" s="885"/>
-      <c r="S16" s="885"/>
-      <c r="T16" s="885"/>
-      <c r="U16" s="885"/>
-      <c r="V16" s="876"/>
+      <c r="R16" s="887"/>
+      <c r="S16" s="887"/>
+      <c r="T16" s="887"/>
+      <c r="U16" s="887"/>
+      <c r="V16" s="878"/>
       <c r="W16" s="580"/>
     </row>
     <row r="17" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -23422,12 +23434,12 @@
         <f>U17+(U17*$Z$14)</f>
         <v>0</v>
       </c>
-      <c r="X17" s="857" t="s">
+      <c r="X17" s="859" t="s">
         <v>433</v>
       </c>
-      <c r="Y17" s="858"/>
-      <c r="Z17" s="858"/>
-      <c r="AA17" s="859"/>
+      <c r="Y17" s="860"/>
+      <c r="Z17" s="860"/>
+      <c r="AA17" s="861"/>
       <c r="AB17" s="601" t="s">
         <v>441</v>
       </c>
@@ -23656,15 +23668,15 @@
       <c r="B23" s="624"/>
       <c r="C23" s="624"/>
       <c r="D23" s="624"/>
-      <c r="E23" s="862" t="s">
+      <c r="E23" s="864" t="s">
         <v>448</v>
       </c>
-      <c r="F23" s="868"/>
-      <c r="G23" s="868"/>
-      <c r="H23" s="868"/>
-      <c r="I23" s="868"/>
-      <c r="J23" s="863"/>
-      <c r="K23" s="860" t="s">
+      <c r="F23" s="870"/>
+      <c r="G23" s="870"/>
+      <c r="H23" s="870"/>
+      <c r="I23" s="870"/>
+      <c r="J23" s="865"/>
+      <c r="K23" s="862" t="s">
         <v>385</v>
       </c>
       <c r="L23" s="624"/>
@@ -23672,10 +23684,10 @@
       <c r="N23" s="307"/>
       <c r="O23" s="572"/>
       <c r="P23" s="585"/>
-      <c r="Q23" s="875" t="s">
+      <c r="Q23" s="877" t="s">
         <v>357</v>
       </c>
-      <c r="R23" s="876"/>
+      <c r="R23" s="878"/>
       <c r="S23" s="388" t="s">
         <v>356</v>
       </c>
@@ -23708,17 +23720,17 @@
       <c r="B24" s="624"/>
       <c r="C24" s="624"/>
       <c r="D24" s="624"/>
-      <c r="E24" s="862" t="s">
+      <c r="E24" s="864" t="s">
         <v>358</v>
       </c>
-      <c r="F24" s="868"/>
-      <c r="G24" s="868"/>
-      <c r="H24" s="863"/>
-      <c r="I24" s="862" t="s">
+      <c r="F24" s="870"/>
+      <c r="G24" s="870"/>
+      <c r="H24" s="865"/>
+      <c r="I24" s="864" t="s">
         <v>457</v>
       </c>
-      <c r="J24" s="863"/>
-      <c r="K24" s="861"/>
+      <c r="J24" s="865"/>
+      <c r="K24" s="863"/>
       <c r="L24" s="624"/>
       <c r="M24" s="634"/>
       <c r="N24" s="307"/>
@@ -23767,16 +23779,16 @@
       <c r="B25" s="626"/>
       <c r="C25" s="626"/>
       <c r="D25" s="626"/>
-      <c r="E25" s="869" t="s">
+      <c r="E25" s="871" t="s">
         <v>350</v>
       </c>
-      <c r="F25" s="870"/>
-      <c r="G25" s="870"/>
-      <c r="H25" s="871"/>
-      <c r="I25" s="864" t="s">
+      <c r="F25" s="872"/>
+      <c r="G25" s="872"/>
+      <c r="H25" s="873"/>
+      <c r="I25" s="866" t="s">
         <v>449</v>
       </c>
-      <c r="J25" s="865"/>
+      <c r="J25" s="867"/>
       <c r="K25" s="620" t="e">
         <f>IF($I$66="Método A",FIXED(($W$25),0),FIXED(($W$25),1))</f>
         <v>#DIV/0!</v>
@@ -23823,16 +23835,16 @@
       <c r="B26" s="626"/>
       <c r="C26" s="626"/>
       <c r="D26" s="626"/>
-      <c r="E26" s="835" t="s">
+      <c r="E26" s="837" t="s">
         <v>351</v>
       </c>
-      <c r="F26" s="836"/>
-      <c r="G26" s="836"/>
-      <c r="H26" s="837"/>
-      <c r="I26" s="866" t="s">
+      <c r="F26" s="838"/>
+      <c r="G26" s="838"/>
+      <c r="H26" s="839"/>
+      <c r="I26" s="868" t="s">
         <v>450</v>
       </c>
-      <c r="J26" s="867"/>
+      <c r="J26" s="869"/>
       <c r="K26" s="621" t="e">
         <f>IF($I$66="Método A",FIXED(($W$26),0),FIXED(($W$26),1))</f>
         <v>#DIV/0!</v>
@@ -23879,16 +23891,16 @@
       <c r="B27" s="627"/>
       <c r="C27" s="627"/>
       <c r="D27" s="627"/>
-      <c r="E27" s="830" t="s">
+      <c r="E27" s="832" t="s">
         <v>353</v>
       </c>
-      <c r="F27" s="831"/>
-      <c r="G27" s="831"/>
-      <c r="H27" s="832"/>
-      <c r="I27" s="833" t="s">
+      <c r="F27" s="833"/>
+      <c r="G27" s="833"/>
+      <c r="H27" s="834"/>
+      <c r="I27" s="835" t="s">
         <v>451</v>
       </c>
-      <c r="J27" s="834"/>
+      <c r="J27" s="836"/>
       <c r="K27" s="621" t="e">
         <f>IF($I$66="Método A",FIXED(($W$27),0),FIXED(($W$27),1))</f>
         <v>#DIV/0!</v>
@@ -23935,16 +23947,16 @@
       <c r="B28" s="626"/>
       <c r="C28" s="626"/>
       <c r="D28" s="626"/>
-      <c r="E28" s="835" t="s">
+      <c r="E28" s="837" t="s">
         <v>352</v>
       </c>
-      <c r="F28" s="836"/>
-      <c r="G28" s="836"/>
-      <c r="H28" s="837"/>
-      <c r="I28" s="833" t="s">
+      <c r="F28" s="838"/>
+      <c r="G28" s="838"/>
+      <c r="H28" s="839"/>
+      <c r="I28" s="835" t="s">
         <v>452</v>
       </c>
-      <c r="J28" s="834"/>
+      <c r="J28" s="836"/>
       <c r="K28" s="621" t="e">
         <f>IF($I$66="Método A",FIXED(($W$28),0),FIXED(($W$28),1))</f>
         <v>#DIV/0!</v>
@@ -23991,16 +24003,16 @@
       <c r="B29" s="626"/>
       <c r="C29" s="626"/>
       <c r="D29" s="626"/>
-      <c r="E29" s="835" t="s">
+      <c r="E29" s="837" t="s">
         <v>354</v>
       </c>
-      <c r="F29" s="836"/>
-      <c r="G29" s="836"/>
-      <c r="H29" s="837"/>
-      <c r="I29" s="833" t="s">
+      <c r="F29" s="838"/>
+      <c r="G29" s="838"/>
+      <c r="H29" s="839"/>
+      <c r="I29" s="835" t="s">
         <v>453</v>
       </c>
-      <c r="J29" s="834"/>
+      <c r="J29" s="836"/>
       <c r="K29" s="621" t="e">
         <f>IF($I$66="Método A",FIXED(($W$29),0),FIXED(($W$29),1))</f>
         <v>#DIV/0!</v>
@@ -24047,16 +24059,16 @@
       <c r="B30" s="626"/>
       <c r="C30" s="626"/>
       <c r="D30" s="626"/>
-      <c r="E30" s="835" t="s">
+      <c r="E30" s="837" t="s">
         <v>355</v>
       </c>
-      <c r="F30" s="836"/>
-      <c r="G30" s="836"/>
-      <c r="H30" s="837"/>
-      <c r="I30" s="833" t="s">
+      <c r="F30" s="838"/>
+      <c r="G30" s="838"/>
+      <c r="H30" s="839"/>
+      <c r="I30" s="835" t="s">
         <v>454</v>
       </c>
-      <c r="J30" s="834"/>
+      <c r="J30" s="836"/>
       <c r="K30" s="621" t="e">
         <f>IF($I$66="Método A",FIXED(($W$30),0),FIXED(($W$30),1))</f>
         <v>#DIV/0!</v>
@@ -24103,16 +24115,16 @@
       <c r="B31" s="626"/>
       <c r="C31" s="626"/>
       <c r="D31" s="626"/>
-      <c r="E31" s="835" t="s">
+      <c r="E31" s="837" t="s">
         <v>231</v>
       </c>
-      <c r="F31" s="836"/>
-      <c r="G31" s="836"/>
-      <c r="H31" s="837"/>
-      <c r="I31" s="838" t="s">
+      <c r="F31" s="838"/>
+      <c r="G31" s="838"/>
+      <c r="H31" s="839"/>
+      <c r="I31" s="840" t="s">
         <v>455</v>
       </c>
-      <c r="J31" s="839"/>
+      <c r="J31" s="841"/>
       <c r="K31" s="621" t="e">
         <f>IF($I$66="Método A",FIXED(($W$31),0),FIXED(($W$31),1))</f>
         <v>#DIV/0!</v>
@@ -24163,16 +24175,16 @@
       <c r="B32" s="626"/>
       <c r="C32" s="626"/>
       <c r="D32" s="626"/>
-      <c r="E32" s="835" t="s">
+      <c r="E32" s="837" t="s">
         <v>232</v>
       </c>
-      <c r="F32" s="836"/>
-      <c r="G32" s="836"/>
-      <c r="H32" s="837"/>
-      <c r="I32" s="838" t="s">
+      <c r="F32" s="838"/>
+      <c r="G32" s="838"/>
+      <c r="H32" s="839"/>
+      <c r="I32" s="840" t="s">
         <v>456</v>
       </c>
-      <c r="J32" s="839"/>
+      <c r="J32" s="841"/>
       <c r="K32" s="621" t="e">
         <f>IF($I$66="Método A",FIXED(($W$32),0),FIXED(($W$32),1))</f>
         <v>#DIV/0!</v>
@@ -24223,16 +24235,16 @@
       <c r="B33" s="626"/>
       <c r="C33" s="626"/>
       <c r="D33" s="626"/>
-      <c r="E33" s="835" t="s">
+      <c r="E33" s="837" t="s">
         <v>238</v>
       </c>
-      <c r="F33" s="836"/>
-      <c r="G33" s="836"/>
-      <c r="H33" s="837"/>
-      <c r="I33" s="840" t="s">
+      <c r="F33" s="838"/>
+      <c r="G33" s="838"/>
+      <c r="H33" s="839"/>
+      <c r="I33" s="842" t="s">
         <v>458</v>
       </c>
-      <c r="J33" s="841"/>
+      <c r="J33" s="843"/>
       <c r="K33" s="621" t="e">
         <f>IF($I$66="Método A",FIXED(($W$33),0),FIXED(($W$33),1))</f>
         <v>#DIV/0!</v>
@@ -24275,16 +24287,16 @@
       <c r="B34" s="626"/>
       <c r="C34" s="626"/>
       <c r="D34" s="626"/>
-      <c r="E34" s="835" t="s">
+      <c r="E34" s="837" t="s">
         <v>418</v>
       </c>
-      <c r="F34" s="836"/>
-      <c r="G34" s="836"/>
-      <c r="H34" s="837"/>
-      <c r="I34" s="840" t="s">
+      <c r="F34" s="838"/>
+      <c r="G34" s="838"/>
+      <c r="H34" s="839"/>
+      <c r="I34" s="842" t="s">
         <v>459</v>
       </c>
-      <c r="J34" s="841"/>
+      <c r="J34" s="843"/>
       <c r="K34" s="621" t="e">
         <f>IF($I$66="Método A",FIXED(($W$34),0),FIXED(($W$34),1))</f>
         <v>#DIV/0!</v>
@@ -24331,16 +24343,16 @@
       <c r="B35" s="626"/>
       <c r="C35" s="626"/>
       <c r="D35" s="626"/>
-      <c r="E35" s="835" t="s">
+      <c r="E35" s="837" t="s">
         <v>239</v>
       </c>
-      <c r="F35" s="836"/>
-      <c r="G35" s="836"/>
-      <c r="H35" s="837"/>
-      <c r="I35" s="840" t="s">
+      <c r="F35" s="838"/>
+      <c r="G35" s="838"/>
+      <c r="H35" s="839"/>
+      <c r="I35" s="842" t="s">
         <v>460</v>
       </c>
-      <c r="J35" s="841"/>
+      <c r="J35" s="843"/>
       <c r="K35" s="621" t="e">
         <f>IF($I$66="Método A",FIXED(($W$35),0),FIXED(($W$35),1))</f>
         <v>#DIV/0!</v>
@@ -24387,16 +24399,16 @@
       <c r="B36" s="626"/>
       <c r="C36" s="626"/>
       <c r="D36" s="626"/>
-      <c r="E36" s="835" t="s">
+      <c r="E36" s="837" t="s">
         <v>241</v>
       </c>
-      <c r="F36" s="836"/>
-      <c r="G36" s="836"/>
-      <c r="H36" s="837"/>
-      <c r="I36" s="840" t="s">
+      <c r="F36" s="838"/>
+      <c r="G36" s="838"/>
+      <c r="H36" s="839"/>
+      <c r="I36" s="842" t="s">
         <v>461</v>
       </c>
-      <c r="J36" s="841"/>
+      <c r="J36" s="843"/>
       <c r="K36" s="621" t="e">
         <f>IF($I$66="Método A",FIXED(($W$36),0),FIXED(($W$36),1))</f>
         <v>#DIV/0!</v>
@@ -24442,16 +24454,16 @@
       <c r="B37" s="626"/>
       <c r="C37" s="626"/>
       <c r="D37" s="626"/>
-      <c r="E37" s="835" t="s">
+      <c r="E37" s="837" t="s">
         <v>240</v>
       </c>
-      <c r="F37" s="836"/>
-      <c r="G37" s="836"/>
-      <c r="H37" s="837"/>
-      <c r="I37" s="840" t="s">
+      <c r="F37" s="838"/>
+      <c r="G37" s="838"/>
+      <c r="H37" s="839"/>
+      <c r="I37" s="842" t="s">
         <v>462</v>
       </c>
-      <c r="J37" s="841"/>
+      <c r="J37" s="843"/>
       <c r="K37" s="621" t="e">
         <f>IF($I$66="Método A",FIXED(($W$37),0),FIXED(($W$37),1))</f>
         <v>#DIV/0!</v>
@@ -24497,16 +24509,16 @@
       <c r="B38" s="626"/>
       <c r="C38" s="626"/>
       <c r="D38" s="626"/>
-      <c r="E38" s="890" t="s">
+      <c r="E38" s="895" t="s">
         <v>242</v>
       </c>
-      <c r="F38" s="891"/>
-      <c r="G38" s="891"/>
-      <c r="H38" s="892"/>
-      <c r="I38" s="896" t="s">
+      <c r="F38" s="896"/>
+      <c r="G38" s="896"/>
+      <c r="H38" s="897"/>
+      <c r="I38" s="901" t="s">
         <v>463</v>
       </c>
-      <c r="J38" s="897"/>
+      <c r="J38" s="902"/>
       <c r="K38" s="317" t="e">
         <f>IF($I$66="Método A",FIXED(($W$38),0),FIXED(($W$38),1))</f>
         <v>#DIV/0!</v>
@@ -24639,12 +24651,12 @@
       <c r="N41" s="313"/>
       <c r="O41" s="572"/>
       <c r="P41" s="572"/>
-      <c r="Q41" s="843" t="s">
+      <c r="Q41" s="845" t="s">
         <v>420</v>
       </c>
-      <c r="R41" s="844"/>
-      <c r="S41" s="844"/>
-      <c r="T41" s="845"/>
+      <c r="R41" s="846"/>
+      <c r="S41" s="846"/>
+      <c r="T41" s="847"/>
       <c r="AA41" s="515"/>
       <c r="AB41" s="515"/>
       <c r="AC41" s="515"/>
@@ -24667,10 +24679,10 @@
       <c r="N42" s="313"/>
       <c r="O42" s="572"/>
       <c r="P42" s="572"/>
-      <c r="Q42" s="846"/>
-      <c r="R42" s="847"/>
-      <c r="S42" s="847"/>
-      <c r="T42" s="848"/>
+      <c r="Q42" s="848"/>
+      <c r="R42" s="849"/>
+      <c r="S42" s="849"/>
+      <c r="T42" s="850"/>
       <c r="U42" s="623"/>
       <c r="V42" s="623"/>
       <c r="AA42" s="515"/>
@@ -24695,10 +24707,10 @@
       <c r="N43" s="313"/>
       <c r="O43" s="572"/>
       <c r="P43" s="572"/>
-      <c r="Q43" s="849" t="s">
+      <c r="Q43" s="851" t="s">
         <v>34</v>
       </c>
-      <c r="R43" s="851" t="e">
+      <c r="R43" s="853" t="e">
         <f>$V$31</f>
         <v>#DIV/0!</v>
       </c>
@@ -24733,8 +24745,8 @@
       <c r="N44" s="313"/>
       <c r="O44" s="572"/>
       <c r="P44" s="572"/>
-      <c r="Q44" s="850"/>
-      <c r="R44" s="852"/>
+      <c r="Q44" s="852"/>
+      <c r="R44" s="854"/>
       <c r="S44" s="311" t="s">
         <v>36</v>
       </c>
@@ -24768,10 +24780,10 @@
       <c r="N45" s="313"/>
       <c r="O45" s="572"/>
       <c r="P45" s="572"/>
-      <c r="Q45" s="853" t="s">
+      <c r="Q45" s="855" t="s">
         <v>37</v>
       </c>
-      <c r="R45" s="855" t="e">
+      <c r="R45" s="857" t="e">
         <f>100-(R43+R48)</f>
         <v>#DIV/0!</v>
       </c>
@@ -24809,8 +24821,8 @@
       <c r="N46" s="313"/>
       <c r="O46" s="572"/>
       <c r="P46" s="572"/>
-      <c r="Q46" s="854"/>
-      <c r="R46" s="856"/>
+      <c r="Q46" s="856"/>
+      <c r="R46" s="858"/>
       <c r="S46" s="311" t="s">
         <v>38</v>
       </c>
@@ -24844,8 +24856,8 @@
       <c r="N47" s="313"/>
       <c r="O47" s="572"/>
       <c r="P47" s="572"/>
-      <c r="Q47" s="850"/>
-      <c r="R47" s="852"/>
+      <c r="Q47" s="852"/>
+      <c r="R47" s="854"/>
       <c r="S47" s="311" t="s">
         <v>36</v>
       </c>
@@ -25446,12 +25458,12 @@
       <c r="F66" s="306"/>
       <c r="G66" s="306"/>
       <c r="H66" s="306"/>
-      <c r="I66" s="888" t="str">
+      <c r="I66" s="890" t="str">
         <f>+R2</f>
         <v>-</v>
       </c>
-      <c r="J66" s="888"/>
-      <c r="K66" s="888"/>
+      <c r="J66" s="890"/>
+      <c r="K66" s="890"/>
       <c r="L66" s="423"/>
       <c r="M66" s="423"/>
       <c r="N66" s="547"/>
@@ -25483,11 +25495,11 @@
       <c r="F67" s="306"/>
       <c r="G67" s="306"/>
       <c r="H67" s="306"/>
-      <c r="I67" s="888" t="s">
+      <c r="I67" s="890" t="s">
         <v>442</v>
       </c>
-      <c r="J67" s="888"/>
-      <c r="K67" s="888"/>
+      <c r="J67" s="890"/>
+      <c r="K67" s="890"/>
       <c r="L67" s="423"/>
       <c r="M67" s="423"/>
       <c r="N67" s="547"/>
@@ -25519,11 +25531,11 @@
       <c r="F68" s="548"/>
       <c r="G68" s="548"/>
       <c r="H68" s="548"/>
-      <c r="I68" s="888" t="s">
+      <c r="I68" s="890" t="s">
         <v>442</v>
       </c>
-      <c r="J68" s="888"/>
-      <c r="K68" s="888"/>
+      <c r="J68" s="890"/>
+      <c r="K68" s="890"/>
       <c r="L68" s="423"/>
       <c r="M68" s="423"/>
       <c r="N68" s="547"/>
@@ -25555,11 +25567,11 @@
       <c r="F69" s="548"/>
       <c r="G69" s="548"/>
       <c r="H69" s="548"/>
-      <c r="I69" s="842" t="s">
+      <c r="I69" s="844" t="s">
         <v>252</v>
       </c>
-      <c r="J69" s="842"/>
-      <c r="K69" s="842"/>
+      <c r="J69" s="844"/>
+      <c r="K69" s="844"/>
       <c r="L69" s="423"/>
       <c r="M69" s="423"/>
       <c r="N69" s="547"/>
@@ -25591,11 +25603,11 @@
       <c r="F70" s="548"/>
       <c r="G70" s="548"/>
       <c r="H70" s="548"/>
-      <c r="I70" s="888" t="s">
+      <c r="I70" s="890" t="s">
         <v>442</v>
       </c>
-      <c r="J70" s="888"/>
-      <c r="K70" s="888"/>
+      <c r="J70" s="890"/>
+      <c r="K70" s="890"/>
       <c r="L70" s="423"/>
       <c r="M70" s="423"/>
       <c r="N70" s="547"/>
@@ -25627,11 +25639,11 @@
       <c r="F71" s="548"/>
       <c r="G71" s="548"/>
       <c r="H71" s="548"/>
-      <c r="I71" s="842" t="s">
+      <c r="I71" s="844" t="s">
         <v>252</v>
       </c>
-      <c r="J71" s="842"/>
-      <c r="K71" s="842"/>
+      <c r="J71" s="844"/>
+      <c r="K71" s="844"/>
       <c r="L71" s="423"/>
       <c r="M71" s="423"/>
       <c r="N71" s="547"/>
@@ -25663,11 +25675,11 @@
       <c r="F72" s="306"/>
       <c r="G72" s="306"/>
       <c r="H72" s="306"/>
-      <c r="I72" s="893" t="s">
+      <c r="I72" s="898" t="s">
         <v>442</v>
       </c>
-      <c r="J72" s="894"/>
-      <c r="K72" s="895"/>
+      <c r="J72" s="899"/>
+      <c r="K72" s="900"/>
       <c r="L72" s="319"/>
       <c r="M72" s="319"/>
       <c r="N72" s="549"/>
@@ -25763,14 +25775,14 @@
       <c r="E75" s="306"/>
       <c r="F75" s="306"/>
       <c r="H75" s="306"/>
-      <c r="I75" s="842"/>
-      <c r="J75" s="842"/>
-      <c r="K75" s="842"/>
-      <c r="L75" s="827">
+      <c r="I75" s="844"/>
+      <c r="J75" s="844"/>
+      <c r="K75" s="844"/>
+      <c r="L75" s="829">
         <v>0</v>
       </c>
-      <c r="M75" s="828"/>
-      <c r="N75" s="829"/>
+      <c r="M75" s="830"/>
+      <c r="N75" s="831"/>
       <c r="O75" s="572"/>
       <c r="P75" s="572"/>
       <c r="Q75" s="426"/>
@@ -25798,11 +25810,11 @@
       <c r="E76" s="306"/>
       <c r="F76" s="306"/>
       <c r="H76" s="306"/>
-      <c r="I76" s="888" t="s">
+      <c r="I76" s="890" t="s">
         <v>442</v>
       </c>
-      <c r="J76" s="888"/>
-      <c r="K76" s="888"/>
+      <c r="J76" s="890"/>
+      <c r="K76" s="890"/>
       <c r="L76" s="306"/>
       <c r="M76" s="306"/>
       <c r="N76" s="554"/>
@@ -25833,12 +25845,12 @@
       <c r="E77" s="306"/>
       <c r="F77" s="306"/>
       <c r="H77" s="306"/>
-      <c r="I77" s="889">
+      <c r="I77" s="891">
         <f>+FORMATO!H19</f>
         <v>0</v>
       </c>
-      <c r="J77" s="842"/>
-      <c r="K77" s="842"/>
+      <c r="J77" s="844"/>
+      <c r="K77" s="844"/>
       <c r="L77" s="306"/>
       <c r="M77" s="306"/>
       <c r="N77" s="554"/>
@@ -25869,12 +25881,12 @@
       <c r="E78" s="306"/>
       <c r="F78" s="306"/>
       <c r="H78" s="306"/>
-      <c r="I78" s="888">
+      <c r="I78" s="890">
         <f>+FORMATO!H20</f>
         <v>0</v>
       </c>
-      <c r="J78" s="888"/>
-      <c r="K78" s="888"/>
+      <c r="J78" s="890"/>
+      <c r="K78" s="890"/>
       <c r="L78" s="306"/>
       <c r="M78" s="306"/>
       <c r="N78" s="554"/>
@@ -25962,22 +25974,22 @@
       <c r="AD80" s="515"/>
     </row>
     <row r="81" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A81" s="1026" t="s">
+      <c r="A81" s="893" t="s">
         <v>571</v>
       </c>
-      <c r="B81" s="1026"/>
-      <c r="C81" s="1026"/>
-      <c r="D81" s="1026"/>
-      <c r="E81" s="1026"/>
-      <c r="F81" s="1026"/>
-      <c r="G81" s="1026"/>
-      <c r="H81" s="1026"/>
-      <c r="I81" s="1026"/>
-      <c r="J81" s="1026"/>
-      <c r="K81" s="1026"/>
-      <c r="L81" s="1026"/>
-      <c r="M81" s="1026"/>
-      <c r="N81" s="1026"/>
+      <c r="B81" s="893"/>
+      <c r="C81" s="893"/>
+      <c r="D81" s="893"/>
+      <c r="E81" s="893"/>
+      <c r="F81" s="893"/>
+      <c r="G81" s="893"/>
+      <c r="H81" s="893"/>
+      <c r="I81" s="893"/>
+      <c r="J81" s="893"/>
+      <c r="K81" s="893"/>
+      <c r="L81" s="893"/>
+      <c r="M81" s="893"/>
+      <c r="N81" s="893"/>
       <c r="O81" s="428"/>
       <c r="P81" s="428"/>
       <c r="Q81" s="426"/>
@@ -25996,22 +26008,22 @@
       <c r="AD81" s="515"/>
     </row>
     <row r="82" spans="1:30" ht="35.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A82" s="1025" t="s">
+      <c r="A82" s="894" t="s">
         <v>572</v>
       </c>
-      <c r="B82" s="1025"/>
-      <c r="C82" s="1025"/>
-      <c r="D82" s="1025"/>
-      <c r="E82" s="1025"/>
-      <c r="F82" s="1025"/>
-      <c r="G82" s="1025"/>
-      <c r="H82" s="1025"/>
-      <c r="I82" s="1025"/>
-      <c r="J82" s="1025"/>
-      <c r="K82" s="1025"/>
-      <c r="L82" s="1025"/>
-      <c r="M82" s="1025"/>
-      <c r="N82" s="1025"/>
+      <c r="B82" s="894"/>
+      <c r="C82" s="894"/>
+      <c r="D82" s="894"/>
+      <c r="E82" s="894"/>
+      <c r="F82" s="894"/>
+      <c r="G82" s="894"/>
+      <c r="H82" s="894"/>
+      <c r="I82" s="894"/>
+      <c r="J82" s="894"/>
+      <c r="K82" s="894"/>
+      <c r="L82" s="894"/>
+      <c r="M82" s="894"/>
+      <c r="N82" s="894"/>
       <c r="Q82" s="426"/>
       <c r="R82" s="521"/>
       <c r="S82" s="521"/>
@@ -26028,22 +26040,22 @@
       <c r="AD82" s="515"/>
     </row>
     <row r="83" spans="1:30" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A83" s="1025" t="s">
+      <c r="A83" s="892" t="s">
         <v>573</v>
       </c>
-      <c r="B83" s="1025"/>
-      <c r="C83" s="1025"/>
-      <c r="D83" s="1025"/>
-      <c r="E83" s="1025"/>
-      <c r="F83" s="1025"/>
-      <c r="G83" s="1025"/>
-      <c r="H83" s="1025"/>
-      <c r="I83" s="1025"/>
-      <c r="J83" s="1025"/>
-      <c r="K83" s="1025"/>
-      <c r="L83" s="1025"/>
-      <c r="M83" s="1025"/>
-      <c r="N83" s="1025"/>
+      <c r="B83" s="892"/>
+      <c r="C83" s="892"/>
+      <c r="D83" s="892"/>
+      <c r="E83" s="892"/>
+      <c r="F83" s="892"/>
+      <c r="G83" s="892"/>
+      <c r="H83" s="892"/>
+      <c r="I83" s="892"/>
+      <c r="J83" s="892"/>
+      <c r="K83" s="892"/>
+      <c r="L83" s="892"/>
+      <c r="M83" s="892"/>
+      <c r="N83" s="892"/>
       <c r="O83" s="430"/>
       <c r="P83" s="430"/>
       <c r="AA83" s="515"/>
@@ -26052,44 +26064,44 @@
       <c r="AD83" s="515"/>
     </row>
     <row r="84" spans="1:30" ht="26.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A84" s="1025" t="s">
+      <c r="A84" s="892" t="s">
         <v>574</v>
       </c>
-      <c r="B84" s="1025"/>
-      <c r="C84" s="1025"/>
-      <c r="D84" s="1025"/>
-      <c r="E84" s="1025"/>
-      <c r="F84" s="1025"/>
-      <c r="G84" s="1025"/>
-      <c r="H84" s="1025"/>
-      <c r="I84" s="1025"/>
-      <c r="J84" s="1025"/>
-      <c r="K84" s="1025"/>
-      <c r="L84" s="1025"/>
-      <c r="M84" s="1025"/>
-      <c r="N84" s="1025"/>
+      <c r="B84" s="892"/>
+      <c r="C84" s="892"/>
+      <c r="D84" s="892"/>
+      <c r="E84" s="892"/>
+      <c r="F84" s="892"/>
+      <c r="G84" s="892"/>
+      <c r="H84" s="892"/>
+      <c r="I84" s="892"/>
+      <c r="J84" s="892"/>
+      <c r="K84" s="892"/>
+      <c r="L84" s="892"/>
+      <c r="M84" s="892"/>
+      <c r="N84" s="892"/>
       <c r="AA84" s="515"/>
       <c r="AB84" s="515"/>
       <c r="AC84" s="515"/>
       <c r="AD84" s="515"/>
     </row>
     <row r="85" spans="1:30" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A85" s="887" t="s">
+      <c r="A85" s="889" t="s">
         <v>575</v>
       </c>
-      <c r="B85" s="887"/>
-      <c r="C85" s="887"/>
-      <c r="D85" s="887"/>
-      <c r="E85" s="887"/>
-      <c r="F85" s="887"/>
-      <c r="G85" s="887"/>
-      <c r="H85" s="887"/>
-      <c r="I85" s="887"/>
-      <c r="J85" s="887"/>
-      <c r="K85" s="887"/>
-      <c r="L85" s="887"/>
-      <c r="M85" s="887"/>
-      <c r="N85" s="887"/>
+      <c r="B85" s="889"/>
+      <c r="C85" s="889"/>
+      <c r="D85" s="889"/>
+      <c r="E85" s="889"/>
+      <c r="F85" s="889"/>
+      <c r="G85" s="889"/>
+      <c r="H85" s="889"/>
+      <c r="I85" s="889"/>
+      <c r="J85" s="889"/>
+      <c r="K85" s="889"/>
+      <c r="L85" s="889"/>
+      <c r="M85" s="889"/>
+      <c r="N85" s="889"/>
       <c r="AA85" s="515"/>
       <c r="AB85" s="515"/>
       <c r="AC85" s="515"/>
@@ -26114,16 +26126,16 @@
       <c r="B87" s="523"/>
       <c r="C87" s="523"/>
       <c r="D87" s="429"/>
-      <c r="E87" s="1027"/>
-      <c r="F87" s="1028"/>
-      <c r="G87" s="1028"/>
-      <c r="H87" s="1028"/>
-      <c r="I87" s="1028"/>
-      <c r="J87" s="1028"/>
-      <c r="K87" s="1028"/>
-      <c r="L87" s="1028"/>
-      <c r="M87" s="1028"/>
-      <c r="N87" s="1028"/>
+      <c r="E87" s="778"/>
+      <c r="F87" s="779"/>
+      <c r="G87" s="779"/>
+      <c r="H87" s="779"/>
+      <c r="I87" s="779"/>
+      <c r="J87" s="779"/>
+      <c r="K87" s="779"/>
+      <c r="L87" s="779"/>
+      <c r="M87" s="779"/>
+      <c r="N87" s="779"/>
       <c r="AA87" s="515"/>
       <c r="AB87" s="515"/>
       <c r="AC87" s="515"/>
@@ -26239,7 +26251,7 @@
     </row>
     <row r="94" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A94" s="319" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="B94" s="319"/>
       <c r="C94" s="319"/>
@@ -26258,7 +26270,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="/VGRqQwqpkrRTbVhtH1fc7EpWnllZxXz+nKi9og9PvVMm2n3OZAMMBri1H59qiH66uQBtMOS5yzZDOE2WlhmjA==" saltValue="103vsF1FSBvBwIZa5p921Q==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection sheet="1" objects="1" scenarios="1"/>
   <protectedRanges>
     <protectedRange sqref="F11:F13 F16" name="Rango3_3_1_1_1_1_1_1_1_1"/>
     <protectedRange sqref="F10" name="Rango3_3_1_1_1_1_1_2_1"/>
@@ -26403,17 +26415,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="904"/>
-      <c r="B1" s="905"/>
-      <c r="C1" s="910" t="s">
+      <c r="A1" s="909"/>
+      <c r="B1" s="910"/>
+      <c r="C1" s="915" t="s">
         <v>321</v>
       </c>
-      <c r="D1" s="911"/>
-      <c r="E1" s="911"/>
-      <c r="F1" s="911"/>
-      <c r="G1" s="911"/>
-      <c r="H1" s="911"/>
-      <c r="I1" s="912"/>
+      <c r="D1" s="916"/>
+      <c r="E1" s="916"/>
+      <c r="F1" s="916"/>
+      <c r="G1" s="916"/>
+      <c r="H1" s="916"/>
+      <c r="I1" s="917"/>
       <c r="J1" s="343" t="s">
         <v>320</v>
       </c>
@@ -26422,15 +26434,15 @@
       </c>
     </row>
     <row r="2" spans="1:11" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="906"/>
-      <c r="B2" s="907"/>
-      <c r="C2" s="913"/>
-      <c r="D2" s="914"/>
-      <c r="E2" s="914"/>
-      <c r="F2" s="914"/>
-      <c r="G2" s="914"/>
-      <c r="H2" s="914"/>
-      <c r="I2" s="915"/>
+      <c r="A2" s="911"/>
+      <c r="B2" s="912"/>
+      <c r="C2" s="918"/>
+      <c r="D2" s="919"/>
+      <c r="E2" s="919"/>
+      <c r="F2" s="919"/>
+      <c r="G2" s="919"/>
+      <c r="H2" s="919"/>
+      <c r="I2" s="920"/>
       <c r="J2" s="343" t="s">
         <v>318</v>
       </c>
@@ -26439,15 +26451,15 @@
       </c>
     </row>
     <row r="3" spans="1:11" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="906"/>
-      <c r="B3" s="907"/>
-      <c r="C3" s="913"/>
-      <c r="D3" s="914"/>
-      <c r="E3" s="914"/>
-      <c r="F3" s="914"/>
-      <c r="G3" s="914"/>
-      <c r="H3" s="914"/>
-      <c r="I3" s="915"/>
+      <c r="A3" s="911"/>
+      <c r="B3" s="912"/>
+      <c r="C3" s="918"/>
+      <c r="D3" s="919"/>
+      <c r="E3" s="919"/>
+      <c r="F3" s="919"/>
+      <c r="G3" s="919"/>
+      <c r="H3" s="919"/>
+      <c r="I3" s="920"/>
       <c r="J3" s="343" t="s">
         <v>317</v>
       </c>
@@ -26456,15 +26468,15 @@
       </c>
     </row>
     <row r="4" spans="1:11" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="908"/>
-      <c r="B4" s="909"/>
-      <c r="C4" s="916"/>
-      <c r="D4" s="917"/>
-      <c r="E4" s="917"/>
-      <c r="F4" s="917"/>
-      <c r="G4" s="917"/>
-      <c r="H4" s="917"/>
-      <c r="I4" s="918"/>
+      <c r="A4" s="913"/>
+      <c r="B4" s="914"/>
+      <c r="C4" s="921"/>
+      <c r="D4" s="922"/>
+      <c r="E4" s="922"/>
+      <c r="F4" s="922"/>
+      <c r="G4" s="922"/>
+      <c r="H4" s="922"/>
+      <c r="I4" s="923"/>
       <c r="J4" s="343" t="s">
         <v>316</v>
       </c>
@@ -26781,19 +26793,19 @@
       <c r="H32" s="403"/>
     </row>
     <row r="34" spans="1:11" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A34" s="901" t="s">
+      <c r="A34" s="906" t="s">
         <v>309</v>
       </c>
-      <c r="B34" s="902"/>
-      <c r="C34" s="902"/>
-      <c r="D34" s="902"/>
-      <c r="E34" s="902"/>
-      <c r="F34" s="902"/>
-      <c r="G34" s="902"/>
-      <c r="H34" s="902"/>
-      <c r="I34" s="902"/>
-      <c r="J34" s="902"/>
-      <c r="K34" s="903"/>
+      <c r="B34" s="907"/>
+      <c r="C34" s="907"/>
+      <c r="D34" s="907"/>
+      <c r="E34" s="907"/>
+      <c r="F34" s="907"/>
+      <c r="G34" s="907"/>
+      <c r="H34" s="907"/>
+      <c r="I34" s="907"/>
+      <c r="J34" s="907"/>
+      <c r="K34" s="908"/>
     </row>
     <row r="35" spans="1:11" ht="38.4" x14ac:dyDescent="0.25">
       <c r="A35" s="348" t="s">
@@ -31654,19 +31666,19 @@
       <c r="A227" s="775" t="s">
         <v>563</v>
       </c>
-      <c r="B227" s="919" t="s">
+      <c r="B227" s="924" t="s">
         <v>564</v>
       </c>
-      <c r="C227" s="920"/>
+      <c r="C227" s="925"/>
       <c r="D227" s="776"/>
-      <c r="E227" s="921" t="s">
+      <c r="E227" s="926" t="s">
         <v>565</v>
       </c>
-      <c r="F227" s="921"/>
-      <c r="G227" s="922" t="s">
+      <c r="F227" s="926"/>
+      <c r="G227" s="927" t="s">
         <v>566</v>
       </c>
-      <c r="H227" s="923"/>
+      <c r="H227" s="928"/>
     </row>
     <row r="228" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A228" s="403"/>
@@ -31682,19 +31694,19 @@
       <c r="A229" s="777" t="s">
         <v>567</v>
       </c>
-      <c r="B229" s="898">
+      <c r="B229" s="903">
         <v>44944</v>
       </c>
-      <c r="C229" s="899"/>
+      <c r="C229" s="904"/>
       <c r="D229" s="403"/>
-      <c r="E229" s="900" t="s">
+      <c r="E229" s="905" t="s">
         <v>568</v>
       </c>
-      <c r="F229" s="900"/>
-      <c r="G229" s="898">
+      <c r="F229" s="905"/>
+      <c r="G229" s="903">
         <v>44944</v>
       </c>
-      <c r="H229" s="899"/>
+      <c r="H229" s="904"/>
     </row>
     <row r="230" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A230" s="403"/>
@@ -32083,16 +32095,16 @@
     </row>
     <row r="27" spans="1:15" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="401"/>
-      <c r="B27" s="927" t="s">
+      <c r="B27" s="932" t="s">
         <v>398</v>
       </c>
-      <c r="C27" s="929" t="s">
+      <c r="C27" s="934" t="s">
         <v>399</v>
       </c>
-      <c r="D27" s="929" t="s">
+      <c r="D27" s="934" t="s">
         <v>400</v>
       </c>
-      <c r="E27" s="931" t="s">
+      <c r="E27" s="936" t="s">
         <v>401</v>
       </c>
       <c r="H27" s="405"/>
@@ -32111,10 +32123,10 @@
     </row>
     <row r="28" spans="1:15" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28" s="401"/>
-      <c r="B28" s="928"/>
-      <c r="C28" s="930"/>
-      <c r="D28" s="930"/>
-      <c r="E28" s="932"/>
+      <c r="B28" s="933"/>
+      <c r="C28" s="935"/>
+      <c r="D28" s="935"/>
+      <c r="E28" s="937"/>
       <c r="H28" s="405"/>
       <c r="I28" s="401"/>
       <c r="J28" s="334" t="s">
@@ -32636,11 +32648,11 @@
       <c r="H45" s="327"/>
     </row>
     <row r="46" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A46" s="924" t="s">
+      <c r="A46" s="929" t="s">
         <v>334</v>
       </c>
-      <c r="B46" s="925"/>
-      <c r="C46" s="926"/>
+      <c r="B46" s="930"/>
+      <c r="C46" s="931"/>
       <c r="D46" s="647">
         <v>45792</v>
       </c>
@@ -33059,35 +33071,35 @@
       <c r="K7" s="150"/>
     </row>
     <row r="8" spans="1:19" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="934" t="s">
+      <c r="A8" s="939" t="s">
         <v>21</v>
       </c>
-      <c r="B8" s="934"/>
-      <c r="C8" s="934"/>
-      <c r="D8" s="934"/>
-      <c r="E8" s="934"/>
-      <c r="F8" s="934"/>
-      <c r="G8" s="934"/>
-      <c r="H8" s="934"/>
-      <c r="I8" s="934"/>
-      <c r="J8" s="934"/>
-      <c r="K8" s="934"/>
+      <c r="B8" s="939"/>
+      <c r="C8" s="939"/>
+      <c r="D8" s="939"/>
+      <c r="E8" s="939"/>
+      <c r="F8" s="939"/>
+      <c r="G8" s="939"/>
+      <c r="H8" s="939"/>
+      <c r="I8" s="939"/>
+      <c r="J8" s="939"/>
+      <c r="K8" s="939"/>
     </row>
     <row r="9" spans="1:19" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="935">
+      <c r="A9" s="940">
         <f>+K13</f>
         <v>10</v>
       </c>
-      <c r="B9" s="935"/>
-      <c r="C9" s="935"/>
-      <c r="D9" s="935"/>
-      <c r="E9" s="935"/>
-      <c r="F9" s="935"/>
-      <c r="G9" s="935"/>
-      <c r="H9" s="935"/>
-      <c r="I9" s="935"/>
-      <c r="J9" s="935"/>
-      <c r="K9" s="935"/>
+      <c r="B9" s="940"/>
+      <c r="C9" s="940"/>
+      <c r="D9" s="940"/>
+      <c r="E9" s="940"/>
+      <c r="F9" s="940"/>
+      <c r="G9" s="940"/>
+      <c r="H9" s="940"/>
+      <c r="I9" s="940"/>
+      <c r="J9" s="940"/>
+      <c r="K9" s="940"/>
       <c r="O9" s="151"/>
     </row>
     <row r="10" spans="1:19" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
@@ -33110,15 +33122,15 @@
       <c r="B11" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="C11" s="936">
+      <c r="C11" s="941">
         <f>+A.Granul!F10</f>
         <v>0</v>
       </c>
-      <c r="D11" s="936"/>
-      <c r="E11" s="936"/>
-      <c r="F11" s="936"/>
-      <c r="G11" s="936"/>
-      <c r="H11" s="936"/>
+      <c r="D11" s="941"/>
+      <c r="E11" s="941"/>
+      <c r="F11" s="941"/>
+      <c r="G11" s="941"/>
+      <c r="H11" s="941"/>
       <c r="I11" s="153" t="s">
         <v>31</v>
       </c>
@@ -33139,15 +33151,15 @@
       <c r="B12" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="C12" s="936">
+      <c r="C12" s="941">
         <f>+A.Granul!F11</f>
         <v>0</v>
       </c>
-      <c r="D12" s="936"/>
-      <c r="E12" s="936"/>
-      <c r="F12" s="936"/>
-      <c r="G12" s="936"/>
-      <c r="H12" s="936"/>
+      <c r="D12" s="941"/>
+      <c r="E12" s="941"/>
+      <c r="F12" s="941"/>
+      <c r="G12" s="941"/>
+      <c r="H12" s="941"/>
       <c r="I12" s="15" t="s">
         <v>19</v>
       </c>
@@ -33172,15 +33184,15 @@
       <c r="B13" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="C13" s="936">
+      <c r="C13" s="941">
         <f>+A.Granul!F12</f>
         <v>0</v>
       </c>
-      <c r="D13" s="936"/>
-      <c r="E13" s="936"/>
-      <c r="F13" s="936"/>
-      <c r="G13" s="936"/>
-      <c r="H13" s="936"/>
+      <c r="D13" s="941"/>
+      <c r="E13" s="941"/>
+      <c r="F13" s="941"/>
+      <c r="G13" s="941"/>
+      <c r="H13" s="941"/>
       <c r="I13" s="15" t="s">
         <v>20</v>
       </c>
@@ -33194,8 +33206,8 @@
       <c r="M13" s="156"/>
       <c r="P13" s="159"/>
       <c r="Q13" s="159"/>
-      <c r="R13" s="933"/>
-      <c r="S13" s="933"/>
+      <c r="R13" s="938"/>
+      <c r="S13" s="938"/>
     </row>
     <row r="14" spans="1:19" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="13"/>
@@ -33217,19 +33229,19 @@
       <c r="S14" s="164"/>
     </row>
     <row r="15" spans="1:19" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="938" t="s">
+      <c r="A15" s="943" t="s">
         <v>171</v>
       </c>
-      <c r="B15" s="939"/>
-      <c r="C15" s="939"/>
-      <c r="D15" s="939"/>
-      <c r="E15" s="939"/>
-      <c r="F15" s="939"/>
-      <c r="G15" s="939"/>
-      <c r="H15" s="939"/>
-      <c r="I15" s="939"/>
-      <c r="J15" s="939"/>
-      <c r="K15" s="940"/>
+      <c r="B15" s="944"/>
+      <c r="C15" s="944"/>
+      <c r="D15" s="944"/>
+      <c r="E15" s="944"/>
+      <c r="F15" s="944"/>
+      <c r="G15" s="944"/>
+      <c r="H15" s="944"/>
+      <c r="I15" s="944"/>
+      <c r="J15" s="944"/>
+      <c r="K15" s="945"/>
       <c r="L15" s="156"/>
       <c r="M15" s="156"/>
       <c r="P15" s="159"/>
@@ -33238,19 +33250,19 @@
       <c r="S15" s="164"/>
     </row>
     <row r="16" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="941" t="s">
+      <c r="A16" s="946" t="s">
         <v>191</v>
       </c>
-      <c r="B16" s="942"/>
-      <c r="C16" s="942"/>
-      <c r="D16" s="942"/>
-      <c r="E16" s="942"/>
-      <c r="F16" s="942"/>
-      <c r="G16" s="942"/>
-      <c r="H16" s="942"/>
-      <c r="I16" s="942"/>
-      <c r="J16" s="942"/>
-      <c r="K16" s="943"/>
+      <c r="B16" s="947"/>
+      <c r="C16" s="947"/>
+      <c r="D16" s="947"/>
+      <c r="E16" s="947"/>
+      <c r="F16" s="947"/>
+      <c r="G16" s="947"/>
+      <c r="H16" s="947"/>
+      <c r="I16" s="947"/>
+      <c r="J16" s="947"/>
+      <c r="K16" s="948"/>
       <c r="L16" s="156"/>
       <c r="M16" s="156"/>
       <c r="P16" s="159"/>
@@ -33278,19 +33290,19 @@
       <c r="S17" s="164"/>
     </row>
     <row r="18" spans="1:21" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="944" t="s">
+      <c r="A18" s="949" t="s">
         <v>26</v>
       </c>
-      <c r="B18" s="945"/>
-      <c r="C18" s="945"/>
-      <c r="D18" s="945"/>
-      <c r="E18" s="945"/>
-      <c r="F18" s="945"/>
-      <c r="G18" s="945"/>
-      <c r="H18" s="945"/>
-      <c r="I18" s="945"/>
-      <c r="J18" s="945"/>
-      <c r="K18" s="946"/>
+      <c r="B18" s="950"/>
+      <c r="C18" s="950"/>
+      <c r="D18" s="950"/>
+      <c r="E18" s="950"/>
+      <c r="F18" s="950"/>
+      <c r="G18" s="950"/>
+      <c r="H18" s="950"/>
+      <c r="I18" s="950"/>
+      <c r="J18" s="950"/>
+      <c r="K18" s="951"/>
       <c r="M18" s="156"/>
       <c r="P18" s="159"/>
       <c r="Q18" s="159"/>
@@ -33415,8 +33427,8 @@
     </row>
     <row r="23" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="176"/>
-      <c r="I23" s="947"/>
-      <c r="J23" s="947"/>
+      <c r="I23" s="952"/>
+      <c r="J23" s="952"/>
       <c r="K23" s="177"/>
       <c r="L23" s="156"/>
       <c r="M23" s="178"/>
@@ -33424,41 +33436,41 @@
     </row>
     <row r="24" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="180"/>
-      <c r="D24" s="948" t="s">
+      <c r="D24" s="953" t="s">
         <v>174</v>
       </c>
-      <c r="E24" s="949"/>
-      <c r="F24" s="949"/>
-      <c r="G24" s="950" t="s">
+      <c r="E24" s="954"/>
+      <c r="F24" s="954"/>
+      <c r="G24" s="955" t="s">
         <v>175</v>
       </c>
-      <c r="H24" s="951"/>
-      <c r="I24" s="952"/>
-      <c r="J24" s="952"/>
+      <c r="H24" s="956"/>
+      <c r="I24" s="957"/>
+      <c r="J24" s="957"/>
       <c r="K24" s="181"/>
       <c r="L24" s="156"/>
       <c r="M24" s="182"/>
-      <c r="O24" s="953" t="s">
+      <c r="O24" s="958" t="s">
         <v>174</v>
       </c>
-      <c r="P24" s="954"/>
+      <c r="P24" s="959"/>
       <c r="Q24" s="183" t="s">
         <v>173</v>
       </c>
-      <c r="R24" s="953" t="s">
+      <c r="R24" s="958" t="s">
         <v>175</v>
       </c>
-      <c r="S24" s="955"/>
+      <c r="S24" s="960"/>
       <c r="T24" s="183" t="s">
         <v>173</v>
       </c>
     </row>
     <row r="25" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="180"/>
-      <c r="B25" s="956" t="s">
+      <c r="B25" s="961" t="s">
         <v>176</v>
       </c>
-      <c r="C25" s="957"/>
+      <c r="C25" s="962"/>
       <c r="D25" s="184" t="str">
         <f>IF($Q$24="NO","",O25)</f>
         <v/>
@@ -33479,8 +33491,8 @@
         <f>IF($T$24="NO","",S25)</f>
         <v/>
       </c>
-      <c r="I25" s="952"/>
-      <c r="J25" s="952"/>
+      <c r="I25" s="957"/>
+      <c r="J25" s="957"/>
       <c r="K25" s="181"/>
       <c r="L25" s="156"/>
       <c r="M25" s="182"/>
@@ -33529,8 +33541,8 @@
         <f>IF($T$24="NO","",S26)</f>
         <v/>
       </c>
-      <c r="I26" s="958"/>
-      <c r="J26" s="958"/>
+      <c r="I26" s="963"/>
+      <c r="J26" s="963"/>
       <c r="K26" s="194"/>
       <c r="L26" s="195"/>
       <c r="M26" s="182"/>
@@ -34308,19 +34320,19 @@
       <c r="Q49"/>
     </row>
     <row r="50" spans="1:17" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="937" t="s">
+      <c r="A50" s="942" t="s">
         <v>192</v>
       </c>
-      <c r="B50" s="937"/>
-      <c r="C50" s="937"/>
-      <c r="D50" s="937"/>
-      <c r="E50" s="937"/>
-      <c r="F50" s="937"/>
-      <c r="G50" s="937"/>
-      <c r="H50" s="937"/>
-      <c r="I50" s="937"/>
-      <c r="J50" s="937"/>
-      <c r="K50" s="937"/>
+      <c r="B50" s="942"/>
+      <c r="C50" s="942"/>
+      <c r="D50" s="942"/>
+      <c r="E50" s="942"/>
+      <c r="F50" s="942"/>
+      <c r="G50" s="942"/>
+      <c r="H50" s="942"/>
+      <c r="I50" s="942"/>
+      <c r="J50" s="942"/>
+      <c r="K50" s="942"/>
     </row>
     <row r="51" spans="1:17" ht="15.9" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="52" spans="1:17" ht="15.9" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -34385,15 +34397,15 @@
       <c r="A1" s="94" t="s">
         <v>97</v>
       </c>
-      <c r="B1" s="959" t="s">
+      <c r="B1" s="964" t="s">
         <v>98</v>
       </c>
-      <c r="C1" s="959"/>
-      <c r="D1" s="959"/>
-      <c r="E1" s="959"/>
-      <c r="F1" s="959"/>
-      <c r="G1" s="959"/>
-      <c r="H1" s="959"/>
+      <c r="C1" s="964"/>
+      <c r="D1" s="964"/>
+      <c r="E1" s="964"/>
+      <c r="F1" s="964"/>
+      <c r="G1" s="964"/>
+      <c r="H1" s="964"/>
       <c r="I1" s="94"/>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.25">
@@ -34531,29 +34543,29 @@
     </row>
     <row r="8" spans="1:17" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="94"/>
-      <c r="B8" s="960" t="s">
+      <c r="B8" s="965" t="s">
         <v>110</v>
       </c>
-      <c r="C8" s="960"/>
-      <c r="D8" s="960"/>
+      <c r="C8" s="965"/>
+      <c r="D8" s="965"/>
       <c r="E8" s="103" t="s">
         <v>111</v>
       </c>
       <c r="F8" s="104" t="s">
         <v>112</v>
       </c>
-      <c r="G8" s="961" t="s">
+      <c r="G8" s="966" t="s">
         <v>113</v>
       </c>
-      <c r="H8" s="961"/>
+      <c r="H8" s="966"/>
       <c r="I8" s="94"/>
       <c r="L8" s="247" t="s">
         <v>114</v>
       </c>
-      <c r="M8" s="962" t="s">
+      <c r="M8" s="967" t="s">
         <v>115</v>
       </c>
-      <c r="N8" s="962"/>
+      <c r="N8" s="967"/>
       <c r="O8" s="248" t="s">
         <v>116</v>
       </c>
@@ -34566,13 +34578,13 @@
     </row>
     <row r="9" spans="1:17" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="94"/>
-      <c r="B9" s="963" t="s">
+      <c r="B9" s="968" t="s">
         <v>119</v>
       </c>
-      <c r="C9" s="965" t="s">
+      <c r="C9" s="970" t="s">
         <v>120</v>
       </c>
-      <c r="D9" s="967" t="s">
+      <c r="D9" s="972" t="s">
         <v>121</v>
       </c>
       <c r="E9" s="106" t="s">
@@ -34581,10 +34593,10 @@
       <c r="F9" s="107" t="s">
         <v>123</v>
       </c>
-      <c r="G9" s="968" t="s">
+      <c r="G9" s="973" t="s">
         <v>124</v>
       </c>
-      <c r="H9" s="969"/>
+      <c r="H9" s="974"/>
       <c r="I9" s="94"/>
       <c r="L9" s="249" t="e">
         <f>IF(AND(N_200&lt;50,(100-N_40)&gt;=0.5*(100-N_200),N_200&lt;5,CU&gt;=4,CC&gt;=1,CC&lt;=3),"GW","")</f>
@@ -34613,19 +34625,19 @@
     </row>
     <row r="10" spans="1:17" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="94"/>
-      <c r="B10" s="963"/>
-      <c r="C10" s="965"/>
-      <c r="D10" s="967"/>
+      <c r="B10" s="968"/>
+      <c r="C10" s="970"/>
+      <c r="D10" s="972"/>
       <c r="E10" s="108" t="s">
         <v>125</v>
       </c>
       <c r="F10" s="109" t="s">
         <v>126</v>
       </c>
-      <c r="G10" s="970" t="s">
+      <c r="G10" s="975" t="s">
         <v>127</v>
       </c>
-      <c r="H10" s="971"/>
+      <c r="H10" s="976"/>
       <c r="I10" s="94"/>
       <c r="L10" s="249" t="e">
         <f>IF(AND(N_200&lt;50,(100-N_40)&gt;=0.5*(100-N_200),N_200&lt;5,OR(CU&lt;4,CC&lt;1,CC&gt;3)),"GP","")</f>
@@ -34650,9 +34662,9 @@
     </row>
     <row r="11" spans="1:17" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="94"/>
-      <c r="B11" s="963"/>
-      <c r="C11" s="965"/>
-      <c r="D11" s="967" t="s">
+      <c r="B11" s="968"/>
+      <c r="C11" s="970"/>
+      <c r="D11" s="972" t="s">
         <v>128</v>
       </c>
       <c r="E11" s="108" t="s">
@@ -34664,7 +34676,7 @@
       <c r="G11" s="111" t="s">
         <v>131</v>
       </c>
-      <c r="H11" s="972" t="s">
+      <c r="H11" s="977" t="s">
         <v>132</v>
       </c>
       <c r="I11" s="94"/>
@@ -34685,9 +34697,9 @@
     </row>
     <row r="12" spans="1:17" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="94"/>
-      <c r="B12" s="963"/>
-      <c r="C12" s="966"/>
-      <c r="D12" s="967"/>
+      <c r="B12" s="968"/>
+      <c r="C12" s="971"/>
+      <c r="D12" s="972"/>
       <c r="E12" s="112" t="s">
         <v>133</v>
       </c>
@@ -34697,7 +34709,7 @@
       <c r="G12" s="111" t="s">
         <v>135</v>
       </c>
-      <c r="H12" s="973"/>
+      <c r="H12" s="978"/>
       <c r="I12" s="94"/>
       <c r="L12" s="249" t="e">
         <f>IF(AND(N_200&lt;50,(100-N_40)&gt;=0.5*(100-N_200),N_200&gt;=12,IP&gt;=7,IP&gt;=0.73*(Ll-20)),"GC","")</f>
@@ -34713,11 +34725,11 @@
     </row>
     <row r="13" spans="1:17" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="94"/>
-      <c r="B13" s="963"/>
-      <c r="C13" s="965" t="s">
+      <c r="B13" s="968"/>
+      <c r="C13" s="970" t="s">
         <v>136</v>
       </c>
-      <c r="D13" s="967" t="s">
+      <c r="D13" s="972" t="s">
         <v>137</v>
       </c>
       <c r="E13" s="113" t="s">
@@ -34726,10 +34738,10 @@
       <c r="F13" s="114" t="s">
         <v>139</v>
       </c>
-      <c r="G13" s="974" t="s">
+      <c r="G13" s="979" t="s">
         <v>140</v>
       </c>
-      <c r="H13" s="975"/>
+      <c r="H13" s="980"/>
       <c r="I13" s="94"/>
       <c r="L13" s="249" t="e">
         <f>IF(AND(N_200&lt;50,(100-N_40)&lt;0.5*(100-N_200),N_200&lt;5,CU&gt;=6,CC&gt;=1,CC&lt;=3),"SW","")</f>
@@ -34754,19 +34766,19 @@
     </row>
     <row r="14" spans="1:17" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="94"/>
-      <c r="B14" s="963"/>
-      <c r="C14" s="965"/>
-      <c r="D14" s="967"/>
+      <c r="B14" s="968"/>
+      <c r="C14" s="970"/>
+      <c r="D14" s="972"/>
       <c r="E14" s="113" t="s">
         <v>141</v>
       </c>
       <c r="F14" s="114" t="s">
         <v>142</v>
       </c>
-      <c r="G14" s="974" t="s">
+      <c r="G14" s="979" t="s">
         <v>143</v>
       </c>
-      <c r="H14" s="975"/>
+      <c r="H14" s="980"/>
       <c r="I14" s="94"/>
       <c r="L14" s="249" t="e">
         <f>IF(AND(N_200&lt;50,(100-N_40)&lt;0.5*(100-N_200),N_200&lt;5,OR(CU&lt;6,CC&lt;1,CC&gt;3)),"SP","")</f>
@@ -34791,9 +34803,9 @@
     </row>
     <row r="15" spans="1:17" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="94"/>
-      <c r="B15" s="963"/>
-      <c r="C15" s="965"/>
-      <c r="D15" s="967" t="s">
+      <c r="B15" s="968"/>
+      <c r="C15" s="970"/>
+      <c r="D15" s="972" t="s">
         <v>144</v>
       </c>
       <c r="E15" s="113" t="s">
@@ -34805,7 +34817,7 @@
       <c r="G15" s="116" t="s">
         <v>147</v>
       </c>
-      <c r="H15" s="978" t="s">
+      <c r="H15" s="983" t="s">
         <v>148</v>
       </c>
       <c r="I15" s="94"/>
@@ -34826,9 +34838,9 @@
     </row>
     <row r="16" spans="1:17" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="94"/>
-      <c r="B16" s="964"/>
-      <c r="C16" s="965"/>
-      <c r="D16" s="967"/>
+      <c r="B16" s="969"/>
+      <c r="C16" s="970"/>
+      <c r="D16" s="972"/>
       <c r="E16" s="117" t="s">
         <v>149</v>
       </c>
@@ -34838,7 +34850,7 @@
       <c r="G16" s="114" t="s">
         <v>151</v>
       </c>
-      <c r="H16" s="979"/>
+      <c r="H16" s="984"/>
       <c r="I16" s="94"/>
       <c r="L16" s="249" t="e">
         <f>IF(AND(N_200&lt;50,(100-N_40)&lt;0.5*(100-N_200),N_200&gt;=12,IP&gt;=7,IP&gt;=0.73*(Ll-20)),"SC","")</f>
@@ -34854,23 +34866,23 @@
     </row>
     <row r="17" spans="1:16" ht="48" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="94"/>
-      <c r="B17" s="980" t="s">
+      <c r="B17" s="985" t="s">
         <v>152</v>
       </c>
-      <c r="C17" s="983" t="s">
+      <c r="C17" s="988" t="s">
         <v>153</v>
       </c>
-      <c r="D17" s="984"/>
+      <c r="D17" s="989"/>
       <c r="E17" s="118" t="s">
         <v>154</v>
       </c>
       <c r="F17" s="119" t="s">
         <v>155</v>
       </c>
-      <c r="G17" s="989" t="s">
+      <c r="G17" s="994" t="s">
         <v>156</v>
       </c>
-      <c r="H17" s="990"/>
+      <c r="H17" s="995"/>
       <c r="I17" s="94"/>
       <c r="L17" s="249" t="e">
         <f>IF(AND(OR(L2="Inorganico"),N_200&gt;=50,Ll&lt;50,OR(IP&lt;4,AND(IP&lt;0.73*(Ll-20)))),"ML","")</f>
@@ -34886,17 +34898,17 @@
     </row>
     <row r="18" spans="1:16" ht="50.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="94"/>
-      <c r="B18" s="981"/>
-      <c r="C18" s="985"/>
-      <c r="D18" s="986"/>
+      <c r="B18" s="986"/>
+      <c r="C18" s="990"/>
+      <c r="D18" s="991"/>
       <c r="E18" s="118" t="s">
         <v>157</v>
       </c>
       <c r="F18" s="119" t="s">
         <v>158</v>
       </c>
-      <c r="G18" s="991"/>
-      <c r="H18" s="992"/>
+      <c r="G18" s="996"/>
+      <c r="H18" s="997"/>
       <c r="I18" s="94"/>
       <c r="L18" s="249" t="e">
         <f>IF(AND(OR(L2="Inorganico"),N_200&gt;=50,Ll&lt;50,IP&gt;=7,IP&gt;=0.73*(Ll-20)),"CL","")</f>
@@ -34912,9 +34924,9 @@
     </row>
     <row r="19" spans="1:16" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="94"/>
-      <c r="B19" s="981"/>
-      <c r="C19" s="987"/>
-      <c r="D19" s="988"/>
+      <c r="B19" s="986"/>
+      <c r="C19" s="992"/>
+      <c r="D19" s="993"/>
       <c r="E19" s="118" t="s">
         <v>159</v>
       </c>
@@ -34938,11 +34950,11 @@
     </row>
     <row r="20" spans="1:16" ht="39" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="94"/>
-      <c r="B20" s="981"/>
-      <c r="C20" s="985" t="s">
+      <c r="B20" s="986"/>
+      <c r="C20" s="990" t="s">
         <v>161</v>
       </c>
-      <c r="D20" s="993"/>
+      <c r="D20" s="998"/>
       <c r="E20" s="122" t="s">
         <v>162</v>
       </c>
@@ -34966,9 +34978,9 @@
     </row>
     <row r="21" spans="1:16" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="94"/>
-      <c r="B21" s="981"/>
-      <c r="C21" s="985"/>
-      <c r="D21" s="993"/>
+      <c r="B21" s="986"/>
+      <c r="C21" s="990"/>
+      <c r="D21" s="998"/>
       <c r="E21" s="122" t="s">
         <v>164</v>
       </c>
@@ -34992,9 +35004,9 @@
     </row>
     <row r="22" spans="1:16" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="94"/>
-      <c r="B22" s="981"/>
-      <c r="C22" s="987"/>
-      <c r="D22" s="994"/>
+      <c r="B22" s="986"/>
+      <c r="C22" s="992"/>
+      <c r="D22" s="999"/>
       <c r="E22" s="124" t="s">
         <v>166</v>
       </c>
@@ -35018,11 +35030,11 @@
     </row>
     <row r="23" spans="1:16" ht="39" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="94"/>
-      <c r="B23" s="981"/>
-      <c r="C23" s="983" t="s">
+      <c r="B23" s="986"/>
+      <c r="C23" s="988" t="s">
         <v>168</v>
       </c>
-      <c r="D23" s="984"/>
+      <c r="D23" s="989"/>
       <c r="E23" s="125" t="s">
         <v>169</v>
       </c>
@@ -35046,7 +35058,7 @@
     </row>
     <row r="24" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A24" s="94"/>
-      <c r="B24" s="982"/>
+      <c r="B24" s="987"/>
       <c r="C24" s="127"/>
       <c r="D24" s="128"/>
       <c r="E24" s="129"/>
@@ -35142,10 +35154,10 @@
       <c r="F31" s="135"/>
     </row>
     <row r="32" spans="1:16" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="976" t="s">
+      <c r="A32" s="981" t="s">
         <v>200</v>
       </c>
-      <c r="B32" s="977"/>
+      <c r="B32" s="982"/>
       <c r="F32" s="135"/>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.25">
@@ -35794,71 +35806,71 @@
     </row>
     <row r="4" spans="1:16" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="21"/>
-      <c r="B4" s="1001" t="s">
+      <c r="B4" s="1006" t="s">
         <v>42</v>
       </c>
-      <c r="C4" s="1002"/>
-      <c r="D4" s="1003" t="s">
+      <c r="C4" s="1007"/>
+      <c r="D4" s="1008" t="s">
         <v>43</v>
       </c>
-      <c r="E4" s="1003"/>
-      <c r="F4" s="1003"/>
-      <c r="G4" s="1003"/>
-      <c r="H4" s="1003"/>
-      <c r="I4" s="1003"/>
-      <c r="J4" s="1003"/>
-      <c r="K4" s="1004" t="s">
+      <c r="E4" s="1008"/>
+      <c r="F4" s="1008"/>
+      <c r="G4" s="1008"/>
+      <c r="H4" s="1008"/>
+      <c r="I4" s="1008"/>
+      <c r="J4" s="1008"/>
+      <c r="K4" s="1009" t="s">
         <v>44</v>
       </c>
-      <c r="L4" s="1005"/>
-      <c r="M4" s="1005"/>
-      <c r="N4" s="1005"/>
-      <c r="O4" s="1006"/>
+      <c r="L4" s="1010"/>
+      <c r="M4" s="1010"/>
+      <c r="N4" s="1010"/>
+      <c r="O4" s="1011"/>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5" s="21"/>
-      <c r="B5" s="1007" t="s">
+      <c r="B5" s="1012" t="s">
         <v>45</v>
       </c>
-      <c r="C5" s="1008"/>
-      <c r="D5" s="1011" t="s">
+      <c r="C5" s="1013"/>
+      <c r="D5" s="1016" t="s">
         <v>46</v>
       </c>
-      <c r="E5" s="1012"/>
-      <c r="F5" s="1013" t="s">
+      <c r="E5" s="1017"/>
+      <c r="F5" s="1018" t="s">
         <v>47</v>
       </c>
-      <c r="G5" s="1011" t="s">
+      <c r="G5" s="1016" t="s">
         <v>48</v>
       </c>
-      <c r="H5" s="1015"/>
-      <c r="I5" s="1015"/>
-      <c r="J5" s="1012"/>
-      <c r="K5" s="1016" t="s">
+      <c r="H5" s="1020"/>
+      <c r="I5" s="1020"/>
+      <c r="J5" s="1017"/>
+      <c r="K5" s="1021" t="s">
         <v>49</v>
       </c>
-      <c r="L5" s="1018" t="s">
+      <c r="L5" s="1023" t="s">
         <v>50</v>
       </c>
-      <c r="M5" s="1020" t="s">
+      <c r="M5" s="1025" t="s">
         <v>51</v>
       </c>
-      <c r="N5" s="1022" t="s">
+      <c r="N5" s="1027" t="s">
         <v>52</v>
       </c>
-      <c r="O5" s="1023"/>
+      <c r="O5" s="1028"/>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6" s="21"/>
-      <c r="B6" s="1009"/>
-      <c r="C6" s="1010"/>
+      <c r="B6" s="1014"/>
+      <c r="C6" s="1015"/>
       <c r="D6" s="25" t="s">
         <v>53</v>
       </c>
       <c r="E6" s="26" t="s">
         <v>54</v>
       </c>
-      <c r="F6" s="1014"/>
+      <c r="F6" s="1019"/>
       <c r="G6" s="25" t="s">
         <v>55</v>
       </c>
@@ -35871,9 +35883,9 @@
       <c r="J6" s="26" t="s">
         <v>58</v>
       </c>
-      <c r="K6" s="1017"/>
-      <c r="L6" s="1019"/>
-      <c r="M6" s="1021"/>
+      <c r="K6" s="1022"/>
+      <c r="L6" s="1024"/>
+      <c r="M6" s="1026"/>
       <c r="N6" s="29" t="s">
         <v>59</v>
       </c>
@@ -36273,21 +36285,21 @@
         <f>+D38</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="D23" s="995">
+      <c r="D23" s="1000">
         <v>0</v>
       </c>
-      <c r="E23" s="996"/>
+      <c r="E23" s="1001"/>
       <c r="F23" s="82">
         <v>0</v>
       </c>
-      <c r="G23" s="995">
+      <c r="G23" s="1000">
         <v>0</v>
       </c>
-      <c r="H23" s="997"/>
-      <c r="I23" s="998" t="s">
+      <c r="H23" s="1002"/>
+      <c r="I23" s="1003" t="s">
         <v>87</v>
       </c>
-      <c r="J23" s="996"/>
+      <c r="J23" s="1001"/>
       <c r="K23" s="83" t="s">
         <v>88</v>
       </c>
@@ -36350,11 +36362,11 @@
       <c r="G26" s="88"/>
       <c r="H26" s="23"/>
       <c r="I26" s="23"/>
-      <c r="J26" s="999" t="e">
+      <c r="J26" s="1004" t="e">
         <f>+D31&amp;" "&amp;F38</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="K26" s="1000"/>
+      <c r="K26" s="1005"/>
       <c r="L26" s="21"/>
       <c r="M26" s="21"/>
       <c r="N26" s="21"/>
@@ -36614,10 +36626,10 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="1024" t="s">
+      <c r="A2" s="1029" t="s">
         <v>10</v>
       </c>
-      <c r="B2" s="1024"/>
+      <c r="B2" s="1029"/>
       <c r="C2" s="5" t="s">
         <v>11</v>
       </c>

--- a/app/templates/informes/GranSuelo/Template_GranSuelo.xlsx
+++ b/app/templates/informes/GranSuelo/Template_GranSuelo.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\Documents\crmnew\api-geofal-crm\app\templates\informes\GranSuelo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CBD1F228-E4A5-4B77-B363-0DD4D34E6181}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A45F2533-EC56-46CE-8D18-D5A7B4E89804}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="547" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -180,7 +180,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1031" uniqueCount="578">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1031" uniqueCount="577">
   <si>
     <t>:</t>
   </si>
@@ -2436,10 +2436,7 @@
     <t>- De conformidad con lo dispuesto por el artículo 1321 del Código Civil, queda establecido que en ningún caso la responsabilidad de GEOFAL S.A.C. será mayor al valor del servicio prestado.</t>
   </si>
   <si>
-    <t>Versión: 09 (2026-06-15)</t>
-  </si>
-  <si>
-    <t>Versión: 09 (11-06-2026)</t>
+    <t>Versión: 09 (12-06-2026)</t>
   </si>
 </sst>
 </file>
@@ -26251,7 +26248,7 @@
     </row>
     <row r="94" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A94" s="319" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="B94" s="319"/>
       <c r="C94" s="319"/>

--- a/app/templates/informes/GranSuelo/Template_GranSuelo.xlsx
+++ b/app/templates/informes/GranSuelo/Template_GranSuelo.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24332"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\Documents\crmnew\api-geofal-crm\app\templates\informes\GranSuelo\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Mi unidad\3.0 Formatos e informes\2026\1.0 Informe de ensayo\1.1 Informe Suelo\INFORME ACREDITADO-E ISO\6.1 JUNIO INICIA 15-06-25\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A45F2533-EC56-46CE-8D18-D5A7B4E89804}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B51BFC1-E196-40BA-BECD-65D1712C4C62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="547" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2436,7 +2436,7 @@
     <t>- De conformidad con lo dispuesto por el artículo 1321 del Código Civil, queda establecido que en ningún caso la responsabilidad de GEOFAL S.A.C. será mayor al valor del servicio prestado.</t>
   </si>
   <si>
-    <t>Versión: 09 (12-06-2026)</t>
+    <t>Versión: 09 (2026-06-12)</t>
   </si>
 </sst>
 </file>
@@ -2471,7 +2471,7 @@
     <numFmt numFmtId="188" formatCode="&quot;Ref. Informe N°&quot;000&quot;-26 SU22&quot;"/>
     <numFmt numFmtId="189" formatCode="&quot;FORMATO F-LEM-P-SU-11.01&quot;"/>
   </numFmts>
-  <fonts count="111" x14ac:knownFonts="1">
+  <fonts count="110" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -3177,12 +3177,6 @@
       <b/>
       <sz val="10"/>
       <color theme="1"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="9"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
@@ -5630,7 +5624,7 @@
     <xf numFmtId="0" fontId="1" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="52" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1030">
+  <cellXfs count="1029">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="2" fontId="10" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -7966,6 +7960,80 @@
     <xf numFmtId="0" fontId="23" fillId="0" borderId="156" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="99" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="77" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="97" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="77" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="97" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="77" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="97" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="77" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="97" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="105" fillId="0" borderId="77" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="105" fillId="0" borderId="95" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="105" fillId="0" borderId="97" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="77" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="95" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="97" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="83" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="84" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="155" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="157" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="77" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection hidden="1"/>
@@ -7974,6 +8042,42 @@
       <alignment horizontal="center" vertical="center"/>
       <protection hidden="1"/>
     </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="77" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="97" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="95" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="105" fillId="0" borderId="77" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="105" fillId="0" borderId="95" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="105" fillId="0" borderId="97" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="99" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="83" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="84" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="155" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="157" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="77" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -7993,12 +8097,6 @@
     <xf numFmtId="0" fontId="22" fillId="0" borderId="97" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="77" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="97" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="97" fillId="0" borderId="83" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection hidden="1"/>
@@ -8023,15 +8121,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="105" fillId="0" borderId="77" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="105" fillId="0" borderId="95" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="105" fillId="0" borderId="97" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="77" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -8041,100 +8130,217 @@
     <xf numFmtId="0" fontId="24" fillId="0" borderId="97" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="83" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="84" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="155" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="157" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="77" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="161" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="97" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="162" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="105" fillId="0" borderId="77" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="105" fillId="0" borderId="95" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="105" fillId="0" borderId="97" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="77" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="97" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="95" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="163" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="158" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="159" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="160" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="99" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="99" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="83" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="77" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="95" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="97" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="167" fontId="17" fillId="0" borderId="158" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="17" fillId="0" borderId="160" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="57" fillId="0" borderId="0" xfId="6" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="84" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="155" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="157" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="99" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="77" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="97" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="77" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="12" fontId="17" fillId="0" borderId="99" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="97" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="6" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="6" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="77" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="95" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="97" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="77" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="97" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="118" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="155" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="156" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="157" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="185" fontId="25" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="95" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="167" fontId="17" fillId="0" borderId="161" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="17" fillId="0" borderId="163" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="161" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="163" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="17" fillId="0" borderId="161" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="17" fillId="0" borderId="163" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="77" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="95" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="77" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="97" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="95" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="90" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="148" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="77" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="97" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="97" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="17" fillId="0" borderId="164" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="17" fillId="0" borderId="165" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="17" fillId="0" borderId="161" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="17" fillId="0" borderId="163" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="95" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="164" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="166" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="165" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="188" fontId="17" fillId="0" borderId="86" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
@@ -8157,221 +8363,6 @@
     <xf numFmtId="12" fontId="17" fillId="0" borderId="163" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="161" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="163" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="161" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="162" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="163" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="17" fillId="0" borderId="161" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="17" fillId="0" borderId="163" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="17" fillId="0" borderId="161" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="17" fillId="0" borderId="163" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="99" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="77" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="95" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="97" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="90" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="148" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="77" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="97" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="17" fillId="0" borderId="164" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="17" fillId="0" borderId="165" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="17" fillId="0" borderId="161" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="17" fillId="0" borderId="163" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="95" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="164" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="166" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="165" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="77" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="95" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="97" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="77" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="97" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="118" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="155" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="156" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="157" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="185" fontId="25" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="95" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="57" fillId="0" borderId="0" xfId="6" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="99" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="12" fontId="17" fillId="0" borderId="99" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="6" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="6" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="110" fillId="0" borderId="0" xfId="6" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="158" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="159" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="160" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="77" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="95" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="97" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="167" fontId="17" fillId="0" borderId="158" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="17" fillId="0" borderId="160" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="183" fontId="4" fillId="3" borderId="77" xfId="4" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -8475,6 +8466,78 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="56" fillId="3" borderId="130" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="172" fontId="55" fillId="3" borderId="77" xfId="4" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="172" fontId="55" fillId="3" borderId="95" xfId="4" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="172" fontId="55" fillId="3" borderId="97" xfId="4" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="172" fontId="56" fillId="3" borderId="77" xfId="4" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="172" fontId="56" fillId="3" borderId="97" xfId="4" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="11" fillId="3" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="21" fillId="3" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="83" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="84" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="2" borderId="86" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="2" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="2" borderId="14" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="11" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="172" fontId="54" fillId="3" borderId="77" xfId="4" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="172" fontId="54" fillId="3" borderId="95" xfId="4" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="172" fontId="54" fillId="3" borderId="96" xfId="4" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="172" fontId="54" fillId="3" borderId="1" xfId="4" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="170" fontId="8" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
@@ -8491,77 +8554,62 @@
     <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="4" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="5" fillId="19" borderId="101" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="83" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="5" fillId="19" borderId="102" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="84" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="2" borderId="86" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="11" borderId="79" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="2" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="47" fillId="11" borderId="80" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="2" borderId="14" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="33" fillId="12" borderId="82" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="12" borderId="74" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="12" borderId="91" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="12" borderId="83" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="12" borderId="84" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="12" borderId="86" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="12" borderId="14" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="12" borderId="15" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="12" borderId="16" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="13" borderId="83" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="11" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="172" fontId="54" fillId="3" borderId="77" xfId="4" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="172" fontId="54" fillId="3" borderId="95" xfId="4" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="172" fontId="54" fillId="3" borderId="96" xfId="4" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="172" fontId="54" fillId="3" borderId="1" xfId="4" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="11" fillId="3" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="172" fontId="55" fillId="3" borderId="77" xfId="4" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="172" fontId="55" fillId="3" borderId="95" xfId="4" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="172" fontId="55" fillId="3" borderId="97" xfId="4" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="172" fontId="56" fillId="3" borderId="77" xfId="4" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="172" fontId="56" fillId="3" borderId="97" xfId="4" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="21" fillId="3" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="50" fillId="13" borderId="85" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="13" borderId="87" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="13" borderId="88" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="12" borderId="0" xfId="4" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="12" borderId="10" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="38" fillId="6" borderId="0" xfId="4" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -8613,63 +8661,6 @@
     </xf>
     <xf numFmtId="0" fontId="47" fillId="11" borderId="78" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="19" borderId="101" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="19" borderId="102" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="11" borderId="79" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="11" borderId="80" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="12" borderId="82" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="12" borderId="74" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="12" borderId="91" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="12" borderId="83" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="12" borderId="84" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="12" borderId="86" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="12" borderId="14" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="12" borderId="15" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="12" borderId="16" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="13" borderId="83" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="13" borderId="85" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="13" borderId="87" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="13" borderId="88" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="12" borderId="0" xfId="4" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="12" borderId="10" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="31" fillId="9" borderId="68" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -9186,7 +9177,7 @@
                 <a:cs typeface="Arial"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="es-PE"/>
+            <a:endParaRPr lang="es-ES"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="128847232"/>
@@ -9289,7 +9280,7 @@
                 <a:cs typeface="Arial"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="es-PE"/>
+            <a:endParaRPr lang="es-ES"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="128844928"/>
@@ -9332,7 +9323,7 @@
           <a:cs typeface="Arial"/>
         </a:defRPr>
       </a:pPr>
-      <a:endParaRPr lang="es-PE"/>
+      <a:endParaRPr lang="es-ES"/>
     </a:p>
   </c:txPr>
   <c:printSettings>
@@ -9487,7 +9478,7 @@
                 <a:cs typeface="Arial"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="es-PE"/>
+            <a:endParaRPr lang="es-ES"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="131076096"/>
@@ -9524,7 +9515,7 @@
                 <a:cs typeface="Calibri"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="es-PE"/>
+            <a:endParaRPr lang="es-ES"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="131062016"/>
@@ -9562,7 +9553,7 @@
           <a:cs typeface="Calibri"/>
         </a:defRPr>
       </a:pPr>
-      <a:endParaRPr lang="es-PE"/>
+      <a:endParaRPr lang="es-ES"/>
     </a:p>
   </c:txPr>
   <c:printSettings>
@@ -9714,7 +9705,7 @@
                 <a:cs typeface="Arial"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="es-PE"/>
+            <a:endParaRPr lang="es-ES"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="131115264"/>
@@ -9750,7 +9741,7 @@
                 <a:cs typeface="Calibri"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="es-PE"/>
+            <a:endParaRPr lang="es-ES"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="131113728"/>
@@ -9788,7 +9779,7 @@
           <a:cs typeface="Calibri"/>
         </a:defRPr>
       </a:pPr>
-      <a:endParaRPr lang="es-PE"/>
+      <a:endParaRPr lang="es-ES"/>
     </a:p>
   </c:txPr>
   <c:printSettings>
@@ -9940,7 +9931,7 @@
                 <a:cs typeface="Arial"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="es-PE"/>
+            <a:endParaRPr lang="es-ES"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="131289856"/>
@@ -9977,7 +9968,7 @@
                 <a:cs typeface="Calibri"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="es-PE"/>
+            <a:endParaRPr lang="es-ES"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="131283968"/>
@@ -10015,7 +10006,7 @@
           <a:cs typeface="Calibri"/>
         </a:defRPr>
       </a:pPr>
-      <a:endParaRPr lang="es-PE"/>
+      <a:endParaRPr lang="es-ES"/>
     </a:p>
   </c:txPr>
   <c:printSettings>
@@ -10167,7 +10158,7 @@
                 <a:cs typeface="Arial"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="es-PE"/>
+            <a:endParaRPr lang="es-ES"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="131308544"/>
@@ -10203,7 +10194,7 @@
                 <a:cs typeface="Calibri"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="es-PE"/>
+            <a:endParaRPr lang="es-ES"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="131307008"/>
@@ -10241,7 +10232,7 @@
           <a:cs typeface="Calibri"/>
         </a:defRPr>
       </a:pPr>
-      <a:endParaRPr lang="es-PE"/>
+      <a:endParaRPr lang="es-ES"/>
     </a:p>
   </c:txPr>
   <c:printSettings>
@@ -10393,7 +10384,7 @@
                 <a:cs typeface="Arial"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="es-PE"/>
+            <a:endParaRPr lang="es-ES"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="131409408"/>
@@ -10430,7 +10421,7 @@
                 <a:cs typeface="Calibri"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="es-PE"/>
+            <a:endParaRPr lang="es-ES"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="131407872"/>
@@ -10468,7 +10459,7 @@
           <a:cs typeface="Calibri"/>
         </a:defRPr>
       </a:pPr>
-      <a:endParaRPr lang="es-PE"/>
+      <a:endParaRPr lang="es-ES"/>
     </a:p>
   </c:txPr>
   <c:printSettings>
@@ -10630,7 +10621,7 @@
                 <a:cs typeface="Arial"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="es-PE"/>
+            <a:endParaRPr lang="es-ES"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="131448832"/>
@@ -10666,7 +10657,7 @@
                 <a:cs typeface="Calibri"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="es-PE"/>
+            <a:endParaRPr lang="es-ES"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="131442944"/>
@@ -10705,7 +10696,7 @@
           <a:cs typeface="Calibri"/>
         </a:defRPr>
       </a:pPr>
-      <a:endParaRPr lang="es-PE"/>
+      <a:endParaRPr lang="es-ES"/>
     </a:p>
   </c:txPr>
   <c:printSettings>
@@ -11034,7 +11025,7 @@
                 <a:cs typeface="Arial"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="es-PE"/>
+            <a:endParaRPr lang="es-ES"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="131648128"/>
@@ -11137,7 +11128,7 @@
                 <a:cs typeface="Arial"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="es-PE"/>
+            <a:endParaRPr lang="es-ES"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="131645824"/>
@@ -11186,7 +11177,7 @@
           <a:cs typeface="Arial"/>
         </a:defRPr>
       </a:pPr>
-      <a:endParaRPr lang="es-PE"/>
+      <a:endParaRPr lang="es-ES"/>
     </a:p>
   </c:txPr>
   <c:printSettings>
@@ -11338,7 +11329,7 @@
                 <a:cs typeface="Arial"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="es-PE"/>
+            <a:endParaRPr lang="es-ES"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="130499328"/>
@@ -11375,7 +11366,7 @@
                 <a:cs typeface="Calibri"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="es-PE"/>
+            <a:endParaRPr lang="es-ES"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="130497536"/>
@@ -11413,7 +11404,7 @@
           <a:cs typeface="Calibri"/>
         </a:defRPr>
       </a:pPr>
-      <a:endParaRPr lang="es-PE"/>
+      <a:endParaRPr lang="es-ES"/>
     </a:p>
   </c:txPr>
   <c:printSettings>
@@ -11565,7 +11556,7 @@
                 <a:cs typeface="Arial"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="es-PE"/>
+            <a:endParaRPr lang="es-ES"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="130546688"/>
@@ -11602,7 +11593,7 @@
                 <a:cs typeface="Calibri"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="es-PE"/>
+            <a:endParaRPr lang="es-ES"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="130545152"/>
@@ -11640,7 +11631,7 @@
           <a:cs typeface="Calibri"/>
         </a:defRPr>
       </a:pPr>
-      <a:endParaRPr lang="es-PE"/>
+      <a:endParaRPr lang="es-ES"/>
     </a:p>
   </c:txPr>
   <c:printSettings>
@@ -11780,7 +11771,7 @@
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
-            <a:endParaRPr lang="es-PE"/>
+            <a:endParaRPr lang="es-ES"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="130569728"/>
@@ -11810,7 +11801,7 @@
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
-            <a:endParaRPr lang="es-PE"/>
+            <a:endParaRPr lang="es-ES"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="130568192"/>
@@ -11848,7 +11839,7 @@
           <a:cs typeface="Calibri"/>
         </a:defRPr>
       </a:pPr>
-      <a:endParaRPr lang="es-PE"/>
+      <a:endParaRPr lang="es-ES"/>
     </a:p>
   </c:txPr>
   <c:printSettings>
@@ -12000,7 +11991,7 @@
                 <a:cs typeface="Arial"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="es-PE"/>
+            <a:endParaRPr lang="es-ES"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="130744320"/>
@@ -12037,7 +12028,7 @@
                 <a:cs typeface="Calibri"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="es-PE"/>
+            <a:endParaRPr lang="es-ES"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="130607360"/>
@@ -12075,7 +12066,7 @@
           <a:cs typeface="Calibri"/>
         </a:defRPr>
       </a:pPr>
-      <a:endParaRPr lang="es-PE"/>
+      <a:endParaRPr lang="es-ES"/>
     </a:p>
   </c:txPr>
   <c:printSettings>
@@ -12227,7 +12218,7 @@
                 <a:cs typeface="Arial"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="es-PE"/>
+            <a:endParaRPr lang="es-ES"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="130803968"/>
@@ -12264,7 +12255,7 @@
                 <a:cs typeface="Calibri"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="es-PE"/>
+            <a:endParaRPr lang="es-ES"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="130802432"/>
@@ -12302,7 +12293,7 @@
           <a:cs typeface="Calibri"/>
         </a:defRPr>
       </a:pPr>
-      <a:endParaRPr lang="es-PE"/>
+      <a:endParaRPr lang="es-ES"/>
     </a:p>
   </c:txPr>
   <c:printSettings>
@@ -12454,7 +12445,7 @@
                 <a:cs typeface="Arial"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="es-PE"/>
+            <a:endParaRPr lang="es-ES"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="130904832"/>
@@ -12491,7 +12482,7 @@
                 <a:cs typeface="Calibri"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="es-PE"/>
+            <a:endParaRPr lang="es-ES"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="130890752"/>
@@ -12529,7 +12520,7 @@
           <a:cs typeface="Calibri"/>
         </a:defRPr>
       </a:pPr>
-      <a:endParaRPr lang="es-PE"/>
+      <a:endParaRPr lang="es-ES"/>
     </a:p>
   </c:txPr>
   <c:printSettings>
@@ -12681,7 +12672,7 @@
                 <a:cs typeface="Arial"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="es-PE"/>
+            <a:endParaRPr lang="es-ES"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="130948096"/>
@@ -12718,7 +12709,7 @@
                 <a:cs typeface="Calibri"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="es-PE"/>
+            <a:endParaRPr lang="es-ES"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="130946560"/>
@@ -12756,7 +12747,7 @@
           <a:cs typeface="Calibri"/>
         </a:defRPr>
       </a:pPr>
-      <a:endParaRPr lang="es-PE"/>
+      <a:endParaRPr lang="es-ES"/>
     </a:p>
   </c:txPr>
   <c:printSettings>
@@ -12908,7 +12899,7 @@
                 <a:cs typeface="Arial"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="es-PE"/>
+            <a:endParaRPr lang="es-ES"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="131032576"/>
@@ -12945,7 +12936,7 @@
                 <a:cs typeface="Calibri"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="es-PE"/>
+            <a:endParaRPr lang="es-ES"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="131031040"/>
@@ -12983,7 +12974,7 @@
           <a:cs typeface="Calibri"/>
         </a:defRPr>
       </a:pPr>
-      <a:endParaRPr lang="es-PE"/>
+      <a:endParaRPr lang="es-ES"/>
     </a:p>
   </c:txPr>
   <c:printSettings>
@@ -14619,15 +14610,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>376863</xdr:colOff>
+      <xdr:colOff>277802</xdr:colOff>
       <xdr:row>87</xdr:row>
-      <xdr:rowOff>124461</xdr:rowOff>
+      <xdr:rowOff>360681</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>325480</xdr:colOff>
-      <xdr:row>92</xdr:row>
-      <xdr:rowOff>156716</xdr:rowOff>
+      <xdr:colOff>226419</xdr:colOff>
+      <xdr:row>91</xdr:row>
+      <xdr:rowOff>171956</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -14655,7 +14646,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm rot="60000">
-          <a:off x="3257223" y="16476981"/>
+          <a:off x="3158162" y="16659861"/>
           <a:ext cx="1388797" cy="1060955"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -14670,7 +14661,7 @@
       <xdr:col>11</xdr:col>
       <xdr:colOff>437803</xdr:colOff>
       <xdr:row>87</xdr:row>
-      <xdr:rowOff>76200</xdr:rowOff>
+      <xdr:rowOff>381000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
@@ -14691,8 +14682,8 @@
       </xdr:nvSpPr>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="5901343" y="16428720"/>
-          <a:ext cx="1120458" cy="1021080"/>
+          <a:off x="5901343" y="16680180"/>
+          <a:ext cx="1120458" cy="1112520"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -14774,15 +14765,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>413468</xdr:colOff>
+      <xdr:colOff>283928</xdr:colOff>
       <xdr:row>87</xdr:row>
-      <xdr:rowOff>131859</xdr:rowOff>
+      <xdr:rowOff>276639</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>11</xdr:col>
-      <xdr:colOff>364488</xdr:colOff>
-      <xdr:row>93</xdr:row>
-      <xdr:rowOff>29998</xdr:rowOff>
+      <xdr:colOff>234948</xdr:colOff>
+      <xdr:row>91</xdr:row>
+      <xdr:rowOff>129058</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -14810,7 +14801,7 @@
       </xdr:blipFill>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="4734008" y="16484379"/>
+          <a:off x="4604468" y="16575819"/>
           <a:ext cx="1094020" cy="1102099"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -16403,7 +16394,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="-------"/>
@@ -16462,7 +16453,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="datos de ecuacion del anillo"/>
@@ -16581,7 +16572,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink3.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="-------"/>
@@ -16632,7 +16623,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink4.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="-------"/>
@@ -16684,7 +16675,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink5.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="BGA"/>
@@ -16716,7 +16707,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink6.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="-------"/>
@@ -21627,38 +21618,38 @@
       <c r="O6" s="764"/>
     </row>
     <row r="7" spans="1:21" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="784" t="s">
+      <c r="A7" s="816" t="s">
         <v>21</v>
       </c>
-      <c r="B7" s="784"/>
-      <c r="C7" s="784"/>
-      <c r="D7" s="784"/>
-      <c r="E7" s="784"/>
-      <c r="F7" s="784"/>
-      <c r="G7" s="784"/>
-      <c r="H7" s="784"/>
-      <c r="I7" s="784"/>
-      <c r="J7" s="784"/>
-      <c r="K7" s="784"/>
+      <c r="B7" s="816"/>
+      <c r="C7" s="816"/>
+      <c r="D7" s="816"/>
+      <c r="E7" s="816"/>
+      <c r="F7" s="816"/>
+      <c r="G7" s="816"/>
+      <c r="H7" s="816"/>
+      <c r="I7" s="816"/>
+      <c r="J7" s="816"/>
+      <c r="K7" s="816"/>
       <c r="N7" s="291" t="s">
         <v>447</v>
       </c>
       <c r="O7" s="764"/>
     </row>
     <row r="8" spans="1:21" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="785" t="s">
+      <c r="A8" s="817" t="s">
         <v>480</v>
       </c>
-      <c r="B8" s="785"/>
-      <c r="C8" s="785"/>
-      <c r="D8" s="785"/>
-      <c r="E8" s="785"/>
-      <c r="F8" s="785"/>
-      <c r="G8" s="785"/>
-      <c r="H8" s="785"/>
-      <c r="I8" s="785"/>
-      <c r="J8" s="785"/>
-      <c r="K8" s="785"/>
+      <c r="B8" s="817"/>
+      <c r="C8" s="817"/>
+      <c r="D8" s="817"/>
+      <c r="E8" s="817"/>
+      <c r="F8" s="817"/>
+      <c r="G8" s="817"/>
+      <c r="H8" s="817"/>
+      <c r="I8" s="817"/>
+      <c r="J8" s="817"/>
+      <c r="K8" s="817"/>
       <c r="N8" s="291" t="s">
         <v>553</v>
       </c>
@@ -21684,18 +21675,18 @@
     <row r="10" spans="1:21" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B10" s="487"/>
       <c r="C10" s="487"/>
-      <c r="D10" s="786" t="s">
+      <c r="D10" s="818" t="s">
         <v>481</v>
       </c>
-      <c r="E10" s="787"/>
-      <c r="F10" s="786" t="s">
+      <c r="E10" s="819"/>
+      <c r="F10" s="818" t="s">
         <v>482</v>
       </c>
-      <c r="G10" s="787"/>
-      <c r="H10" s="786" t="s">
+      <c r="G10" s="819"/>
+      <c r="H10" s="818" t="s">
         <v>30</v>
       </c>
-      <c r="I10" s="787"/>
+      <c r="I10" s="819"/>
       <c r="J10" s="683" t="s">
         <v>467</v>
       </c>
@@ -21709,12 +21700,12 @@
       <c r="A11" s="487"/>
       <c r="B11" s="487"/>
       <c r="C11" s="487"/>
-      <c r="D11" s="788"/>
-      <c r="E11" s="789"/>
-      <c r="F11" s="788"/>
-      <c r="G11" s="789"/>
-      <c r="H11" s="788"/>
-      <c r="I11" s="789"/>
+      <c r="D11" s="781"/>
+      <c r="E11" s="782"/>
+      <c r="F11" s="781"/>
+      <c r="G11" s="782"/>
+      <c r="H11" s="781"/>
+      <c r="I11" s="782"/>
       <c r="J11" s="686"/>
       <c r="K11" s="387"/>
       <c r="L11" s="685"/>
@@ -21744,19 +21735,19 @@
       <c r="O12" s="765"/>
     </row>
     <row r="13" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="790" t="s">
+      <c r="A13" s="820" t="s">
         <v>483</v>
       </c>
-      <c r="B13" s="791"/>
-      <c r="C13" s="791"/>
-      <c r="D13" s="791"/>
-      <c r="E13" s="791"/>
-      <c r="F13" s="791"/>
-      <c r="G13" s="791"/>
-      <c r="H13" s="791"/>
-      <c r="I13" s="791"/>
-      <c r="J13" s="791"/>
-      <c r="K13" s="792"/>
+      <c r="B13" s="821"/>
+      <c r="C13" s="821"/>
+      <c r="D13" s="821"/>
+      <c r="E13" s="821"/>
+      <c r="F13" s="821"/>
+      <c r="G13" s="821"/>
+      <c r="H13" s="821"/>
+      <c r="I13" s="821"/>
+      <c r="J13" s="821"/>
+      <c r="K13" s="822"/>
       <c r="L13" s="685"/>
       <c r="M13" s="685"/>
       <c r="N13" s="291" t="s">
@@ -21765,19 +21756,19 @@
       <c r="O13" s="765"/>
     </row>
     <row r="14" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="793" t="s">
+      <c r="A14" s="823" t="s">
         <v>484</v>
       </c>
-      <c r="B14" s="794"/>
-      <c r="C14" s="794"/>
-      <c r="D14" s="794"/>
-      <c r="E14" s="794"/>
-      <c r="F14" s="794"/>
-      <c r="G14" s="794"/>
-      <c r="H14" s="794"/>
-      <c r="I14" s="794"/>
-      <c r="J14" s="794"/>
-      <c r="K14" s="795"/>
+      <c r="B14" s="824"/>
+      <c r="C14" s="824"/>
+      <c r="D14" s="824"/>
+      <c r="E14" s="824"/>
+      <c r="F14" s="824"/>
+      <c r="G14" s="824"/>
+      <c r="H14" s="824"/>
+      <c r="I14" s="824"/>
+      <c r="J14" s="824"/>
+      <c r="K14" s="825"/>
       <c r="L14" s="685"/>
       <c r="M14" s="685"/>
       <c r="N14" s="763"/>
@@ -21797,21 +21788,21 @@
       <c r="U15" s="688"/>
     </row>
     <row r="16" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="796" t="s">
+      <c r="A16" s="806" t="s">
         <v>485</v>
       </c>
-      <c r="B16" s="797"/>
-      <c r="C16" s="798"/>
-      <c r="E16" s="799" t="s">
+      <c r="B16" s="807"/>
+      <c r="C16" s="808"/>
+      <c r="E16" s="826" t="s">
         <v>372</v>
       </c>
-      <c r="F16" s="800"/>
-      <c r="G16" s="800"/>
-      <c r="H16" s="801"/>
-      <c r="J16" s="796" t="s">
+      <c r="F16" s="827"/>
+      <c r="G16" s="827"/>
+      <c r="H16" s="828"/>
+      <c r="J16" s="806" t="s">
         <v>486</v>
       </c>
-      <c r="K16" s="798"/>
+      <c r="K16" s="808"/>
       <c r="M16" s="688"/>
       <c r="N16" s="291" t="s">
         <v>245</v>
@@ -21827,16 +21818,16 @@
       <c r="A17" s="691" t="s">
         <v>487</v>
       </c>
-      <c r="B17" s="780"/>
-      <c r="C17" s="781"/>
+      <c r="B17" s="801"/>
+      <c r="C17" s="802"/>
       <c r="E17" s="692" t="s">
         <v>488</v>
       </c>
       <c r="F17" s="693"/>
       <c r="G17" s="694"/>
       <c r="H17" s="695"/>
-      <c r="J17" s="782"/>
-      <c r="K17" s="783"/>
+      <c r="J17" s="814"/>
+      <c r="K17" s="815"/>
       <c r="M17" s="688"/>
       <c r="N17" s="291" t="s">
         <v>555</v>
@@ -21852,8 +21843,8 @@
       <c r="A18" s="691" t="s">
         <v>489</v>
       </c>
-      <c r="B18" s="780"/>
-      <c r="C18" s="781"/>
+      <c r="B18" s="801"/>
+      <c r="C18" s="802"/>
       <c r="E18" s="692" t="s">
         <v>490</v>
       </c>
@@ -21876,10 +21867,10 @@
       <c r="F19" s="693"/>
       <c r="G19" s="694"/>
       <c r="H19" s="698"/>
-      <c r="J19" s="806" t="s">
+      <c r="J19" s="784" t="s">
         <v>492</v>
       </c>
-      <c r="K19" s="807"/>
+      <c r="K19" s="785"/>
       <c r="M19" s="688"/>
       <c r="N19" s="696"/>
       <c r="O19" s="689"/>
@@ -21890,11 +21881,11 @@
       <c r="U19" s="690"/>
     </row>
     <row r="20" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="808" t="s">
+      <c r="A20" s="791" t="s">
         <v>493</v>
       </c>
-      <c r="B20" s="809"/>
-      <c r="C20" s="810"/>
+      <c r="B20" s="792"/>
+      <c r="C20" s="793"/>
       <c r="E20" s="699" t="s">
         <v>494</v>
       </c>
@@ -21918,8 +21909,8 @@
       <c r="A21" s="691" t="s">
         <v>495</v>
       </c>
-      <c r="B21" s="811"/>
-      <c r="C21" s="812"/>
+      <c r="B21" s="803"/>
+      <c r="C21" s="804"/>
       <c r="E21" s="704"/>
       <c r="F21" s="704"/>
       <c r="G21" s="704"/>
@@ -21940,14 +21931,14 @@
       <c r="A22" s="691" t="s">
         <v>497</v>
       </c>
-      <c r="B22" s="811"/>
-      <c r="C22" s="812"/>
-      <c r="E22" s="806" t="s">
+      <c r="B22" s="803"/>
+      <c r="C22" s="804"/>
+      <c r="E22" s="784" t="s">
         <v>369</v>
       </c>
-      <c r="F22" s="813"/>
-      <c r="G22" s="813"/>
-      <c r="H22" s="807"/>
+      <c r="F22" s="805"/>
+      <c r="G22" s="805"/>
+      <c r="H22" s="785"/>
       <c r="I22" s="705"/>
       <c r="J22" s="488" t="s">
         <v>370</v>
@@ -21983,11 +21974,11 @@
       <c r="U23" s="690"/>
     </row>
     <row r="24" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="796" t="s">
+      <c r="A24" s="806" t="s">
         <v>500</v>
       </c>
-      <c r="B24" s="797"/>
-      <c r="C24" s="798"/>
+      <c r="B24" s="807"/>
+      <c r="C24" s="808"/>
       <c r="E24" s="692" t="s">
         <v>501</v>
       </c>
@@ -22139,8 +22130,8 @@
       <c r="A31" s="709" t="s">
         <v>513</v>
       </c>
-      <c r="B31" s="814"/>
-      <c r="C31" s="814"/>
+      <c r="B31" s="809"/>
+      <c r="C31" s="809"/>
       <c r="E31" s="692" t="s">
         <v>514</v>
       </c>
@@ -22163,8 +22154,8 @@
       <c r="A32" s="709" t="s">
         <v>515</v>
       </c>
-      <c r="B32" s="814"/>
-      <c r="C32" s="814"/>
+      <c r="B32" s="809"/>
+      <c r="C32" s="809"/>
       <c r="E32" s="692" t="s">
         <v>516</v>
       </c>
@@ -22203,17 +22194,17 @@
       <c r="U33" s="690"/>
     </row>
     <row r="34" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="808" t="s">
+      <c r="A34" s="791" t="s">
         <v>518</v>
       </c>
-      <c r="B34" s="809"/>
-      <c r="C34" s="810"/>
-      <c r="E34" s="815" t="s">
+      <c r="B34" s="792"/>
+      <c r="C34" s="793"/>
+      <c r="E34" s="810" t="s">
         <v>519</v>
       </c>
-      <c r="F34" s="816"/>
-      <c r="G34" s="802"/>
-      <c r="H34" s="803"/>
+      <c r="F34" s="811"/>
+      <c r="G34" s="797"/>
+      <c r="H34" s="798"/>
       <c r="I34" s="721"/>
       <c r="J34" s="722" t="s">
         <v>520</v>
@@ -22233,10 +22224,10 @@
       </c>
       <c r="B35" s="704"/>
       <c r="C35" s="725"/>
-      <c r="E35" s="817"/>
-      <c r="F35" s="818"/>
-      <c r="G35" s="804"/>
-      <c r="H35" s="805"/>
+      <c r="E35" s="812"/>
+      <c r="F35" s="813"/>
+      <c r="G35" s="799"/>
+      <c r="H35" s="800"/>
       <c r="J35" s="726" t="s">
         <v>522</v>
       </c>
@@ -22260,19 +22251,19 @@
       <c r="P36" s="688"/>
     </row>
     <row r="37" spans="1:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="808" t="s">
+      <c r="A37" s="791" t="s">
         <v>523</v>
       </c>
-      <c r="B37" s="809"/>
-      <c r="C37" s="810"/>
-      <c r="E37" s="826" t="s">
+      <c r="B37" s="792"/>
+      <c r="C37" s="793"/>
+      <c r="E37" s="794" t="s">
         <v>524</v>
       </c>
-      <c r="F37" s="827"/>
-      <c r="G37" s="827"/>
-      <c r="H37" s="827"/>
-      <c r="I37" s="828"/>
-      <c r="K37" s="819" t="s">
+      <c r="F37" s="795"/>
+      <c r="G37" s="795"/>
+      <c r="H37" s="795"/>
+      <c r="I37" s="796"/>
+      <c r="K37" s="780" t="s">
         <v>525</v>
       </c>
       <c r="L37" s="685"/>
@@ -22285,15 +22276,15 @@
       <c r="E38" s="734" t="s">
         <v>551</v>
       </c>
-      <c r="F38" s="788" t="s">
+      <c r="F38" s="781" t="s">
         <v>526</v>
       </c>
-      <c r="G38" s="789"/>
-      <c r="H38" s="788" t="s">
+      <c r="G38" s="782"/>
+      <c r="H38" s="781" t="s">
         <v>527</v>
       </c>
-      <c r="I38" s="789"/>
-      <c r="K38" s="819"/>
+      <c r="I38" s="782"/>
+      <c r="K38" s="780"/>
       <c r="L38" s="685"/>
     </row>
     <row r="39" spans="1:21" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -22312,10 +22303,10 @@
       <c r="C40" s="737" t="s">
         <v>529</v>
       </c>
-      <c r="D40" s="806" t="s">
+      <c r="D40" s="784" t="s">
         <v>530</v>
       </c>
-      <c r="E40" s="807"/>
+      <c r="E40" s="785"/>
       <c r="I40" s="738" t="s">
         <v>531</v>
       </c>
@@ -22328,10 +22319,10 @@
       <c r="C41" s="737" t="s">
         <v>533</v>
       </c>
-      <c r="D41" s="806" t="s">
+      <c r="D41" s="784" t="s">
         <v>366</v>
       </c>
-      <c r="E41" s="807"/>
+      <c r="E41" s="785"/>
       <c r="J41" s="739"/>
       <c r="L41" s="685"/>
     </row>
@@ -22438,14 +22429,14 @@
       </c>
       <c r="D50" s="742"/>
       <c r="E50" s="749"/>
-      <c r="G50" s="821" t="s">
+      <c r="G50" s="786" t="s">
         <v>541</v>
       </c>
-      <c r="H50" s="822"/>
-      <c r="I50" s="821" t="s">
+      <c r="H50" s="787"/>
+      <c r="I50" s="786" t="s">
         <v>542</v>
       </c>
-      <c r="J50" s="822"/>
+      <c r="J50" s="787"/>
       <c r="L50" s="685"/>
       <c r="M50" s="685"/>
     </row>
@@ -22462,8 +22453,8 @@
         <v>543</v>
       </c>
       <c r="H51" s="751"/>
-      <c r="I51" s="823"/>
-      <c r="J51" s="824"/>
+      <c r="I51" s="788"/>
+      <c r="J51" s="789"/>
       <c r="L51" s="685"/>
       <c r="M51" s="685"/>
     </row>
@@ -22480,8 +22471,8 @@
         <v>545</v>
       </c>
       <c r="H52" s="751"/>
-      <c r="I52" s="823"/>
-      <c r="J52" s="824"/>
+      <c r="I52" s="788"/>
+      <c r="J52" s="789"/>
       <c r="L52" s="685"/>
       <c r="M52" s="685"/>
     </row>
@@ -22611,12 +22602,12 @@
       <c r="B62" s="487"/>
       <c r="C62" s="487"/>
       <c r="D62" s="487"/>
-      <c r="E62" s="825"/>
-      <c r="F62" s="825"/>
-      <c r="G62" s="825"/>
-      <c r="H62" s="825"/>
-      <c r="I62" s="825"/>
-      <c r="J62" s="825"/>
+      <c r="E62" s="790"/>
+      <c r="F62" s="790"/>
+      <c r="G62" s="790"/>
+      <c r="H62" s="790"/>
+      <c r="I62" s="790"/>
+      <c r="J62" s="790"/>
       <c r="K62" s="744"/>
       <c r="L62" s="685"/>
       <c r="M62" s="685"/>
@@ -22643,19 +22634,19 @@
       <c r="G64" s="260"/>
     </row>
     <row r="65" spans="1:11" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="820" t="s">
+      <c r="A65" s="783" t="s">
         <v>550</v>
       </c>
-      <c r="B65" s="820"/>
-      <c r="C65" s="820"/>
-      <c r="D65" s="820"/>
-      <c r="E65" s="820"/>
-      <c r="F65" s="820"/>
-      <c r="G65" s="820"/>
-      <c r="H65" s="820"/>
-      <c r="I65" s="820"/>
-      <c r="J65" s="820"/>
-      <c r="K65" s="820"/>
+      <c r="B65" s="783"/>
+      <c r="C65" s="783"/>
+      <c r="D65" s="783"/>
+      <c r="E65" s="783"/>
+      <c r="F65" s="783"/>
+      <c r="G65" s="783"/>
+      <c r="H65" s="783"/>
+      <c r="I65" s="783"/>
+      <c r="J65" s="783"/>
+      <c r="K65" s="783"/>
     </row>
     <row r="66" spans="1:11" ht="15.9" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="67" spans="1:11" ht="15.9" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -22665,32 +22656,6 @@
     <protectedRange sqref="C10:C11 C62" name="Rango3_3_1_1_1_1_1_2_1"/>
   </protectedRanges>
   <mergeCells count="41">
-    <mergeCell ref="K37:K38"/>
-    <mergeCell ref="F38:G38"/>
-    <mergeCell ref="H38:I38"/>
-    <mergeCell ref="A65:K65"/>
-    <mergeCell ref="D41:E41"/>
-    <mergeCell ref="G50:H50"/>
-    <mergeCell ref="I50:J50"/>
-    <mergeCell ref="I51:J51"/>
-    <mergeCell ref="I52:J52"/>
-    <mergeCell ref="E62:G62"/>
-    <mergeCell ref="H62:J62"/>
-    <mergeCell ref="D40:E40"/>
-    <mergeCell ref="A37:C37"/>
-    <mergeCell ref="E37:I37"/>
-    <mergeCell ref="G34:H35"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="J19:K19"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="E22:H22"/>
-    <mergeCell ref="A24:C24"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="A34:C34"/>
-    <mergeCell ref="E34:F35"/>
     <mergeCell ref="B17:C17"/>
     <mergeCell ref="J17:K17"/>
     <mergeCell ref="A7:K7"/>
@@ -22706,6 +22671,32 @@
     <mergeCell ref="A16:C16"/>
     <mergeCell ref="E16:H16"/>
     <mergeCell ref="J16:K16"/>
+    <mergeCell ref="G34:H35"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="J19:K19"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="E22:H22"/>
+    <mergeCell ref="A24:C24"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="A34:C34"/>
+    <mergeCell ref="E34:F35"/>
+    <mergeCell ref="K37:K38"/>
+    <mergeCell ref="F38:G38"/>
+    <mergeCell ref="H38:I38"/>
+    <mergeCell ref="A65:K65"/>
+    <mergeCell ref="D41:E41"/>
+    <mergeCell ref="G50:H50"/>
+    <mergeCell ref="I50:J50"/>
+    <mergeCell ref="I51:J51"/>
+    <mergeCell ref="I52:J52"/>
+    <mergeCell ref="E62:G62"/>
+    <mergeCell ref="H62:J62"/>
+    <mergeCell ref="D40:E40"/>
+    <mergeCell ref="A37:C37"/>
+    <mergeCell ref="E37:I37"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0" right="0" top="0.39370078740157483" bottom="0" header="0" footer="0"/>
@@ -22870,14 +22861,14 @@
       <c r="L5" s="566"/>
       <c r="M5" s="566"/>
       <c r="N5" s="566"/>
-      <c r="Q5" s="874" t="s">
+      <c r="Q5" s="846" t="s">
         <v>369</v>
       </c>
-      <c r="R5" s="875"/>
-      <c r="S5" s="875"/>
-      <c r="T5" s="875"/>
-      <c r="U5" s="875"/>
-      <c r="V5" s="876"/>
+      <c r="R5" s="847"/>
+      <c r="S5" s="847"/>
+      <c r="T5" s="847"/>
+      <c r="U5" s="847"/>
+      <c r="V5" s="848"/>
       <c r="X5" s="476" t="s">
         <v>370</v>
       </c>
@@ -22938,22 +22929,22 @@
       </c>
     </row>
     <row r="7" spans="1:30" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="784" t="s">
+      <c r="A7" s="816" t="s">
         <v>21</v>
       </c>
-      <c r="B7" s="784"/>
-      <c r="C7" s="784"/>
-      <c r="D7" s="784"/>
-      <c r="E7" s="784"/>
-      <c r="F7" s="784"/>
-      <c r="G7" s="784"/>
-      <c r="H7" s="784"/>
-      <c r="I7" s="784"/>
-      <c r="J7" s="784"/>
-      <c r="K7" s="784"/>
-      <c r="L7" s="784"/>
-      <c r="M7" s="784"/>
-      <c r="N7" s="784"/>
+      <c r="B7" s="816"/>
+      <c r="C7" s="816"/>
+      <c r="D7" s="816"/>
+      <c r="E7" s="816"/>
+      <c r="F7" s="816"/>
+      <c r="G7" s="816"/>
+      <c r="H7" s="816"/>
+      <c r="I7" s="816"/>
+      <c r="J7" s="816"/>
+      <c r="K7" s="816"/>
+      <c r="L7" s="816"/>
+      <c r="M7" s="816"/>
+      <c r="N7" s="816"/>
       <c r="Q7" s="480" t="s">
         <v>422</v>
       </c>
@@ -22992,22 +22983,22 @@
       </c>
     </row>
     <row r="8" spans="1:30" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="886">
+      <c r="A8" s="858">
         <v>0</v>
       </c>
-      <c r="B8" s="886"/>
-      <c r="C8" s="886"/>
-      <c r="D8" s="886"/>
-      <c r="E8" s="886"/>
-      <c r="F8" s="886"/>
-      <c r="G8" s="886"/>
-      <c r="H8" s="886"/>
-      <c r="I8" s="886"/>
-      <c r="J8" s="886"/>
-      <c r="K8" s="886"/>
-      <c r="L8" s="886"/>
-      <c r="M8" s="886"/>
-      <c r="N8" s="886"/>
+      <c r="B8" s="858"/>
+      <c r="C8" s="858"/>
+      <c r="D8" s="858"/>
+      <c r="E8" s="858"/>
+      <c r="F8" s="858"/>
+      <c r="G8" s="858"/>
+      <c r="H8" s="858"/>
+      <c r="I8" s="858"/>
+      <c r="J8" s="858"/>
+      <c r="K8" s="858"/>
+      <c r="L8" s="858"/>
+      <c r="M8" s="858"/>
+      <c r="N8" s="858"/>
       <c r="Q8" s="480" t="s">
         <v>423</v>
       </c>
@@ -23052,18 +23043,18 @@
       <c r="B9" s="287" t="s">
         <v>0</v>
       </c>
-      <c r="C9" s="888">
+      <c r="C9" s="860">
         <f>+FORMATO!O2</f>
         <v>0</v>
       </c>
-      <c r="D9" s="888"/>
-      <c r="E9" s="888"/>
-      <c r="F9" s="888"/>
-      <c r="G9" s="888"/>
-      <c r="H9" s="888"/>
-      <c r="I9" s="888"/>
-      <c r="J9" s="888"/>
-      <c r="K9" s="888"/>
+      <c r="D9" s="860"/>
+      <c r="E9" s="860"/>
+      <c r="F9" s="860"/>
+      <c r="G9" s="860"/>
+      <c r="H9" s="860"/>
+      <c r="I9" s="860"/>
+      <c r="J9" s="860"/>
+      <c r="K9" s="860"/>
       <c r="L9" s="289" t="s">
         <v>31</v>
       </c>
@@ -23108,18 +23099,18 @@
       <c r="B10" s="288" t="s">
         <v>0</v>
       </c>
-      <c r="C10" s="888">
+      <c r="C10" s="860">
         <f>+FORMATO!O3</f>
         <v>0</v>
       </c>
-      <c r="D10" s="888"/>
-      <c r="E10" s="888"/>
-      <c r="F10" s="888"/>
-      <c r="G10" s="888"/>
-      <c r="H10" s="888"/>
-      <c r="I10" s="888"/>
-      <c r="J10" s="888"/>
-      <c r="K10" s="888"/>
+      <c r="D10" s="860"/>
+      <c r="E10" s="860"/>
+      <c r="F10" s="860"/>
+      <c r="G10" s="860"/>
+      <c r="H10" s="860"/>
+      <c r="I10" s="860"/>
+      <c r="J10" s="860"/>
+      <c r="K10" s="860"/>
       <c r="L10" s="768" t="s">
         <v>447</v>
       </c>
@@ -23147,18 +23138,18 @@
       <c r="B11" s="288" t="s">
         <v>0</v>
       </c>
-      <c r="C11" s="888">
+      <c r="C11" s="860">
         <f>+FORMATO!O4</f>
         <v>0</v>
       </c>
-      <c r="D11" s="888"/>
-      <c r="E11" s="888"/>
-      <c r="F11" s="888"/>
-      <c r="G11" s="888"/>
-      <c r="H11" s="888"/>
-      <c r="I11" s="888"/>
-      <c r="J11" s="888"/>
-      <c r="K11" s="888"/>
+      <c r="D11" s="860"/>
+      <c r="E11" s="860"/>
+      <c r="F11" s="860"/>
+      <c r="G11" s="860"/>
+      <c r="H11" s="860"/>
+      <c r="I11" s="860"/>
+      <c r="J11" s="860"/>
+      <c r="K11" s="860"/>
       <c r="L11" s="291" t="s">
         <v>466</v>
       </c>
@@ -23171,14 +23162,14 @@
       </c>
       <c r="O11" s="572"/>
       <c r="P11" s="572"/>
-      <c r="Q11" s="877" t="s">
+      <c r="Q11" s="849" t="s">
         <v>40</v>
       </c>
-      <c r="R11" s="887"/>
-      <c r="S11" s="887"/>
-      <c r="T11" s="887"/>
-      <c r="U11" s="887"/>
-      <c r="V11" s="878"/>
+      <c r="R11" s="859"/>
+      <c r="S11" s="859"/>
+      <c r="T11" s="859"/>
+      <c r="U11" s="859"/>
+      <c r="V11" s="850"/>
       <c r="X11" s="573" t="s">
         <v>198</v>
       </c>
@@ -23199,18 +23190,18 @@
       <c r="B12" s="288" t="s">
         <v>0</v>
       </c>
-      <c r="C12" s="888">
+      <c r="C12" s="860">
         <f>+FORMATO!O5</f>
         <v>0</v>
       </c>
-      <c r="D12" s="888"/>
-      <c r="E12" s="888"/>
-      <c r="F12" s="888"/>
-      <c r="G12" s="888"/>
-      <c r="H12" s="888"/>
-      <c r="I12" s="888"/>
-      <c r="J12" s="888"/>
-      <c r="K12" s="888"/>
+      <c r="D12" s="860"/>
+      <c r="E12" s="860"/>
+      <c r="F12" s="860"/>
+      <c r="G12" s="860"/>
+      <c r="H12" s="860"/>
+      <c r="I12" s="860"/>
+      <c r="J12" s="860"/>
+      <c r="K12" s="860"/>
       <c r="L12" s="768" t="s">
         <v>253</v>
       </c>
@@ -23296,22 +23287,22 @@
       </c>
     </row>
     <row r="14" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="879" t="s">
+      <c r="A14" s="851" t="s">
         <v>250</v>
       </c>
-      <c r="B14" s="880"/>
-      <c r="C14" s="880"/>
-      <c r="D14" s="881"/>
-      <c r="E14" s="880"/>
-      <c r="F14" s="881"/>
-      <c r="G14" s="881"/>
-      <c r="H14" s="881"/>
-      <c r="I14" s="881"/>
-      <c r="J14" s="881"/>
-      <c r="K14" s="881"/>
-      <c r="L14" s="881"/>
-      <c r="M14" s="881"/>
-      <c r="N14" s="882"/>
+      <c r="B14" s="852"/>
+      <c r="C14" s="852"/>
+      <c r="D14" s="853"/>
+      <c r="E14" s="852"/>
+      <c r="F14" s="853"/>
+      <c r="G14" s="853"/>
+      <c r="H14" s="853"/>
+      <c r="I14" s="853"/>
+      <c r="J14" s="853"/>
+      <c r="K14" s="853"/>
+      <c r="L14" s="853"/>
+      <c r="M14" s="853"/>
+      <c r="N14" s="854"/>
       <c r="O14" s="572"/>
       <c r="P14" s="572"/>
       <c r="Q14" s="480" t="s">
@@ -23342,22 +23333,22 @@
       </c>
     </row>
     <row r="15" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="883" t="s">
+      <c r="A15" s="855" t="s">
         <v>479</v>
       </c>
-      <c r="B15" s="884"/>
-      <c r="C15" s="884"/>
-      <c r="D15" s="884"/>
-      <c r="E15" s="884"/>
-      <c r="F15" s="884"/>
-      <c r="G15" s="884"/>
-      <c r="H15" s="884"/>
-      <c r="I15" s="884"/>
-      <c r="J15" s="884"/>
-      <c r="K15" s="884"/>
-      <c r="L15" s="884"/>
-      <c r="M15" s="884"/>
-      <c r="N15" s="885"/>
+      <c r="B15" s="856"/>
+      <c r="C15" s="856"/>
+      <c r="D15" s="856"/>
+      <c r="E15" s="856"/>
+      <c r="F15" s="856"/>
+      <c r="G15" s="856"/>
+      <c r="H15" s="856"/>
+      <c r="I15" s="856"/>
+      <c r="J15" s="856"/>
+      <c r="K15" s="856"/>
+      <c r="L15" s="856"/>
+      <c r="M15" s="856"/>
+      <c r="N15" s="857"/>
       <c r="O15" s="572"/>
       <c r="P15" s="572"/>
       <c r="V15" s="387"/>
@@ -23389,14 +23380,14 @@
       <c r="N16" s="298"/>
       <c r="O16" s="572"/>
       <c r="P16" s="572"/>
-      <c r="Q16" s="877" t="s">
+      <c r="Q16" s="849" t="s">
         <v>438</v>
       </c>
-      <c r="R16" s="887"/>
-      <c r="S16" s="887"/>
-      <c r="T16" s="887"/>
-      <c r="U16" s="887"/>
-      <c r="V16" s="878"/>
+      <c r="R16" s="859"/>
+      <c r="S16" s="859"/>
+      <c r="T16" s="859"/>
+      <c r="U16" s="859"/>
+      <c r="V16" s="850"/>
       <c r="W16" s="580"/>
     </row>
     <row r="17" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -23431,12 +23422,12 @@
         <f>U17+(U17*$Z$14)</f>
         <v>0</v>
       </c>
-      <c r="X17" s="859" t="s">
+      <c r="X17" s="867" t="s">
         <v>433</v>
       </c>
-      <c r="Y17" s="860"/>
-      <c r="Z17" s="860"/>
-      <c r="AA17" s="861"/>
+      <c r="Y17" s="868"/>
+      <c r="Z17" s="868"/>
+      <c r="AA17" s="869"/>
       <c r="AB17" s="601" t="s">
         <v>441</v>
       </c>
@@ -23665,15 +23656,15 @@
       <c r="B23" s="624"/>
       <c r="C23" s="624"/>
       <c r="D23" s="624"/>
-      <c r="E23" s="864" t="s">
+      <c r="E23" s="872" t="s">
         <v>448</v>
       </c>
-      <c r="F23" s="870"/>
-      <c r="G23" s="870"/>
-      <c r="H23" s="870"/>
-      <c r="I23" s="870"/>
-      <c r="J23" s="865"/>
-      <c r="K23" s="862" t="s">
+      <c r="F23" s="878"/>
+      <c r="G23" s="878"/>
+      <c r="H23" s="878"/>
+      <c r="I23" s="878"/>
+      <c r="J23" s="873"/>
+      <c r="K23" s="870" t="s">
         <v>385</v>
       </c>
       <c r="L23" s="624"/>
@@ -23681,10 +23672,10 @@
       <c r="N23" s="307"/>
       <c r="O23" s="572"/>
       <c r="P23" s="585"/>
-      <c r="Q23" s="877" t="s">
+      <c r="Q23" s="849" t="s">
         <v>357</v>
       </c>
-      <c r="R23" s="878"/>
+      <c r="R23" s="850"/>
       <c r="S23" s="388" t="s">
         <v>356</v>
       </c>
@@ -23717,17 +23708,17 @@
       <c r="B24" s="624"/>
       <c r="C24" s="624"/>
       <c r="D24" s="624"/>
-      <c r="E24" s="864" t="s">
+      <c r="E24" s="872" t="s">
         <v>358</v>
       </c>
-      <c r="F24" s="870"/>
-      <c r="G24" s="870"/>
-      <c r="H24" s="865"/>
-      <c r="I24" s="864" t="s">
+      <c r="F24" s="878"/>
+      <c r="G24" s="878"/>
+      <c r="H24" s="873"/>
+      <c r="I24" s="872" t="s">
         <v>457</v>
       </c>
-      <c r="J24" s="865"/>
-      <c r="K24" s="863"/>
+      <c r="J24" s="873"/>
+      <c r="K24" s="871"/>
       <c r="L24" s="624"/>
       <c r="M24" s="634"/>
       <c r="N24" s="307"/>
@@ -23776,16 +23767,16 @@
       <c r="B25" s="626"/>
       <c r="C25" s="626"/>
       <c r="D25" s="626"/>
-      <c r="E25" s="871" t="s">
+      <c r="E25" s="879" t="s">
         <v>350</v>
       </c>
-      <c r="F25" s="872"/>
-      <c r="G25" s="872"/>
-      <c r="H25" s="873"/>
-      <c r="I25" s="866" t="s">
+      <c r="F25" s="880"/>
+      <c r="G25" s="880"/>
+      <c r="H25" s="881"/>
+      <c r="I25" s="874" t="s">
         <v>449</v>
       </c>
-      <c r="J25" s="867"/>
+      <c r="J25" s="875"/>
       <c r="K25" s="620" t="e">
         <f>IF($I$66="Método A",FIXED(($W$25),0),FIXED(($W$25),1))</f>
         <v>#DIV/0!</v>
@@ -23832,16 +23823,16 @@
       <c r="B26" s="626"/>
       <c r="C26" s="626"/>
       <c r="D26" s="626"/>
-      <c r="E26" s="837" t="s">
+      <c r="E26" s="829" t="s">
         <v>351</v>
       </c>
-      <c r="F26" s="838"/>
-      <c r="G26" s="838"/>
-      <c r="H26" s="839"/>
-      <c r="I26" s="868" t="s">
+      <c r="F26" s="830"/>
+      <c r="G26" s="830"/>
+      <c r="H26" s="831"/>
+      <c r="I26" s="876" t="s">
         <v>450</v>
       </c>
-      <c r="J26" s="869"/>
+      <c r="J26" s="877"/>
       <c r="K26" s="621" t="e">
         <f>IF($I$66="Método A",FIXED(($W$26),0),FIXED(($W$26),1))</f>
         <v>#DIV/0!</v>
@@ -23888,16 +23879,16 @@
       <c r="B27" s="627"/>
       <c r="C27" s="627"/>
       <c r="D27" s="627"/>
-      <c r="E27" s="832" t="s">
+      <c r="E27" s="899" t="s">
         <v>353</v>
       </c>
-      <c r="F27" s="833"/>
-      <c r="G27" s="833"/>
-      <c r="H27" s="834"/>
-      <c r="I27" s="835" t="s">
+      <c r="F27" s="900"/>
+      <c r="G27" s="900"/>
+      <c r="H27" s="901"/>
+      <c r="I27" s="863" t="s">
         <v>451</v>
       </c>
-      <c r="J27" s="836"/>
+      <c r="J27" s="864"/>
       <c r="K27" s="621" t="e">
         <f>IF($I$66="Método A",FIXED(($W$27),0),FIXED(($W$27),1))</f>
         <v>#DIV/0!</v>
@@ -23944,16 +23935,16 @@
       <c r="B28" s="626"/>
       <c r="C28" s="626"/>
       <c r="D28" s="626"/>
-      <c r="E28" s="837" t="s">
+      <c r="E28" s="829" t="s">
         <v>352</v>
       </c>
-      <c r="F28" s="838"/>
-      <c r="G28" s="838"/>
-      <c r="H28" s="839"/>
-      <c r="I28" s="835" t="s">
+      <c r="F28" s="830"/>
+      <c r="G28" s="830"/>
+      <c r="H28" s="831"/>
+      <c r="I28" s="863" t="s">
         <v>452</v>
       </c>
-      <c r="J28" s="836"/>
+      <c r="J28" s="864"/>
       <c r="K28" s="621" t="e">
         <f>IF($I$66="Método A",FIXED(($W$28),0),FIXED(($W$28),1))</f>
         <v>#DIV/0!</v>
@@ -24000,16 +23991,16 @@
       <c r="B29" s="626"/>
       <c r="C29" s="626"/>
       <c r="D29" s="626"/>
-      <c r="E29" s="837" t="s">
+      <c r="E29" s="829" t="s">
         <v>354</v>
       </c>
-      <c r="F29" s="838"/>
-      <c r="G29" s="838"/>
-      <c r="H29" s="839"/>
-      <c r="I29" s="835" t="s">
+      <c r="F29" s="830"/>
+      <c r="G29" s="830"/>
+      <c r="H29" s="831"/>
+      <c r="I29" s="863" t="s">
         <v>453</v>
       </c>
-      <c r="J29" s="836"/>
+      <c r="J29" s="864"/>
       <c r="K29" s="621" t="e">
         <f>IF($I$66="Método A",FIXED(($W$29),0),FIXED(($W$29),1))</f>
         <v>#DIV/0!</v>
@@ -24056,16 +24047,16 @@
       <c r="B30" s="626"/>
       <c r="C30" s="626"/>
       <c r="D30" s="626"/>
-      <c r="E30" s="837" t="s">
+      <c r="E30" s="829" t="s">
         <v>355</v>
       </c>
-      <c r="F30" s="838"/>
-      <c r="G30" s="838"/>
-      <c r="H30" s="839"/>
-      <c r="I30" s="835" t="s">
+      <c r="F30" s="830"/>
+      <c r="G30" s="830"/>
+      <c r="H30" s="831"/>
+      <c r="I30" s="863" t="s">
         <v>454</v>
       </c>
-      <c r="J30" s="836"/>
+      <c r="J30" s="864"/>
       <c r="K30" s="621" t="e">
         <f>IF($I$66="Método A",FIXED(($W$30),0),FIXED(($W$30),1))</f>
         <v>#DIV/0!</v>
@@ -24112,16 +24103,16 @@
       <c r="B31" s="626"/>
       <c r="C31" s="626"/>
       <c r="D31" s="626"/>
-      <c r="E31" s="837" t="s">
+      <c r="E31" s="829" t="s">
         <v>231</v>
       </c>
-      <c r="F31" s="838"/>
-      <c r="G31" s="838"/>
-      <c r="H31" s="839"/>
-      <c r="I31" s="840" t="s">
+      <c r="F31" s="830"/>
+      <c r="G31" s="830"/>
+      <c r="H31" s="831"/>
+      <c r="I31" s="865" t="s">
         <v>455</v>
       </c>
-      <c r="J31" s="841"/>
+      <c r="J31" s="866"/>
       <c r="K31" s="621" t="e">
         <f>IF($I$66="Método A",FIXED(($W$31),0),FIXED(($W$31),1))</f>
         <v>#DIV/0!</v>
@@ -24172,16 +24163,16 @@
       <c r="B32" s="626"/>
       <c r="C32" s="626"/>
       <c r="D32" s="626"/>
-      <c r="E32" s="837" t="s">
+      <c r="E32" s="829" t="s">
         <v>232</v>
       </c>
-      <c r="F32" s="838"/>
-      <c r="G32" s="838"/>
-      <c r="H32" s="839"/>
-      <c r="I32" s="840" t="s">
+      <c r="F32" s="830"/>
+      <c r="G32" s="830"/>
+      <c r="H32" s="831"/>
+      <c r="I32" s="865" t="s">
         <v>456</v>
       </c>
-      <c r="J32" s="841"/>
+      <c r="J32" s="866"/>
       <c r="K32" s="621" t="e">
         <f>IF($I$66="Método A",FIXED(($W$32),0),FIXED(($W$32),1))</f>
         <v>#DIV/0!</v>
@@ -24232,16 +24223,16 @@
       <c r="B33" s="626"/>
       <c r="C33" s="626"/>
       <c r="D33" s="626"/>
-      <c r="E33" s="837" t="s">
+      <c r="E33" s="829" t="s">
         <v>238</v>
       </c>
-      <c r="F33" s="838"/>
-      <c r="G33" s="838"/>
-      <c r="H33" s="839"/>
-      <c r="I33" s="842" t="s">
+      <c r="F33" s="830"/>
+      <c r="G33" s="830"/>
+      <c r="H33" s="831"/>
+      <c r="I33" s="861" t="s">
         <v>458</v>
       </c>
-      <c r="J33" s="843"/>
+      <c r="J33" s="862"/>
       <c r="K33" s="621" t="e">
         <f>IF($I$66="Método A",FIXED(($W$33),0),FIXED(($W$33),1))</f>
         <v>#DIV/0!</v>
@@ -24284,16 +24275,16 @@
       <c r="B34" s="626"/>
       <c r="C34" s="626"/>
       <c r="D34" s="626"/>
-      <c r="E34" s="837" t="s">
+      <c r="E34" s="829" t="s">
         <v>418</v>
       </c>
-      <c r="F34" s="838"/>
-      <c r="G34" s="838"/>
-      <c r="H34" s="839"/>
-      <c r="I34" s="842" t="s">
+      <c r="F34" s="830"/>
+      <c r="G34" s="830"/>
+      <c r="H34" s="831"/>
+      <c r="I34" s="861" t="s">
         <v>459</v>
       </c>
-      <c r="J34" s="843"/>
+      <c r="J34" s="862"/>
       <c r="K34" s="621" t="e">
         <f>IF($I$66="Método A",FIXED(($W$34),0),FIXED(($W$34),1))</f>
         <v>#DIV/0!</v>
@@ -24340,16 +24331,16 @@
       <c r="B35" s="626"/>
       <c r="C35" s="626"/>
       <c r="D35" s="626"/>
-      <c r="E35" s="837" t="s">
+      <c r="E35" s="829" t="s">
         <v>239</v>
       </c>
-      <c r="F35" s="838"/>
-      <c r="G35" s="838"/>
-      <c r="H35" s="839"/>
-      <c r="I35" s="842" t="s">
+      <c r="F35" s="830"/>
+      <c r="G35" s="830"/>
+      <c r="H35" s="831"/>
+      <c r="I35" s="861" t="s">
         <v>460</v>
       </c>
-      <c r="J35" s="843"/>
+      <c r="J35" s="862"/>
       <c r="K35" s="621" t="e">
         <f>IF($I$66="Método A",FIXED(($W$35),0),FIXED(($W$35),1))</f>
         <v>#DIV/0!</v>
@@ -24396,16 +24387,16 @@
       <c r="B36" s="626"/>
       <c r="C36" s="626"/>
       <c r="D36" s="626"/>
-      <c r="E36" s="837" t="s">
+      <c r="E36" s="829" t="s">
         <v>241</v>
       </c>
-      <c r="F36" s="838"/>
-      <c r="G36" s="838"/>
-      <c r="H36" s="839"/>
-      <c r="I36" s="842" t="s">
+      <c r="F36" s="830"/>
+      <c r="G36" s="830"/>
+      <c r="H36" s="831"/>
+      <c r="I36" s="861" t="s">
         <v>461</v>
       </c>
-      <c r="J36" s="843"/>
+      <c r="J36" s="862"/>
       <c r="K36" s="621" t="e">
         <f>IF($I$66="Método A",FIXED(($W$36),0),FIXED(($W$36),1))</f>
         <v>#DIV/0!</v>
@@ -24451,16 +24442,16 @@
       <c r="B37" s="626"/>
       <c r="C37" s="626"/>
       <c r="D37" s="626"/>
-      <c r="E37" s="837" t="s">
+      <c r="E37" s="829" t="s">
         <v>240</v>
       </c>
-      <c r="F37" s="838"/>
-      <c r="G37" s="838"/>
-      <c r="H37" s="839"/>
-      <c r="I37" s="842" t="s">
+      <c r="F37" s="830"/>
+      <c r="G37" s="830"/>
+      <c r="H37" s="831"/>
+      <c r="I37" s="861" t="s">
         <v>462</v>
       </c>
-      <c r="J37" s="843"/>
+      <c r="J37" s="862"/>
       <c r="K37" s="621" t="e">
         <f>IF($I$66="Método A",FIXED(($W$37),0),FIXED(($W$37),1))</f>
         <v>#DIV/0!</v>
@@ -24506,16 +24497,16 @@
       <c r="B38" s="626"/>
       <c r="C38" s="626"/>
       <c r="D38" s="626"/>
-      <c r="E38" s="895" t="s">
+      <c r="E38" s="832" t="s">
         <v>242</v>
       </c>
-      <c r="F38" s="896"/>
-      <c r="G38" s="896"/>
-      <c r="H38" s="897"/>
-      <c r="I38" s="901" t="s">
+      <c r="F38" s="833"/>
+      <c r="G38" s="833"/>
+      <c r="H38" s="834"/>
+      <c r="I38" s="840" t="s">
         <v>463</v>
       </c>
-      <c r="J38" s="902"/>
+      <c r="J38" s="841"/>
       <c r="K38" s="317" t="e">
         <f>IF($I$66="Método A",FIXED(($W$38),0),FIXED(($W$38),1))</f>
         <v>#DIV/0!</v>
@@ -24648,12 +24639,12 @@
       <c r="N41" s="313"/>
       <c r="O41" s="572"/>
       <c r="P41" s="572"/>
-      <c r="Q41" s="845" t="s">
+      <c r="Q41" s="882" t="s">
         <v>420</v>
       </c>
-      <c r="R41" s="846"/>
-      <c r="S41" s="846"/>
-      <c r="T41" s="847"/>
+      <c r="R41" s="883"/>
+      <c r="S41" s="883"/>
+      <c r="T41" s="884"/>
       <c r="AA41" s="515"/>
       <c r="AB41" s="515"/>
       <c r="AC41" s="515"/>
@@ -24676,10 +24667,10 @@
       <c r="N42" s="313"/>
       <c r="O42" s="572"/>
       <c r="P42" s="572"/>
-      <c r="Q42" s="848"/>
-      <c r="R42" s="849"/>
-      <c r="S42" s="849"/>
-      <c r="T42" s="850"/>
+      <c r="Q42" s="885"/>
+      <c r="R42" s="886"/>
+      <c r="S42" s="886"/>
+      <c r="T42" s="887"/>
       <c r="U42" s="623"/>
       <c r="V42" s="623"/>
       <c r="AA42" s="515"/>
@@ -24704,10 +24695,10 @@
       <c r="N43" s="313"/>
       <c r="O43" s="572"/>
       <c r="P43" s="572"/>
-      <c r="Q43" s="851" t="s">
+      <c r="Q43" s="888" t="s">
         <v>34</v>
       </c>
-      <c r="R43" s="853" t="e">
+      <c r="R43" s="890" t="e">
         <f>$V$31</f>
         <v>#DIV/0!</v>
       </c>
@@ -24742,8 +24733,8 @@
       <c r="N44" s="313"/>
       <c r="O44" s="572"/>
       <c r="P44" s="572"/>
-      <c r="Q44" s="852"/>
-      <c r="R44" s="854"/>
+      <c r="Q44" s="889"/>
+      <c r="R44" s="891"/>
       <c r="S44" s="311" t="s">
         <v>36</v>
       </c>
@@ -24777,10 +24768,10 @@
       <c r="N45" s="313"/>
       <c r="O45" s="572"/>
       <c r="P45" s="572"/>
-      <c r="Q45" s="855" t="s">
+      <c r="Q45" s="892" t="s">
         <v>37</v>
       </c>
-      <c r="R45" s="857" t="e">
+      <c r="R45" s="894" t="e">
         <f>100-(R43+R48)</f>
         <v>#DIV/0!</v>
       </c>
@@ -24818,8 +24809,8 @@
       <c r="N46" s="313"/>
       <c r="O46" s="572"/>
       <c r="P46" s="572"/>
-      <c r="Q46" s="856"/>
-      <c r="R46" s="858"/>
+      <c r="Q46" s="893"/>
+      <c r="R46" s="895"/>
       <c r="S46" s="311" t="s">
         <v>38</v>
       </c>
@@ -24853,8 +24844,8 @@
       <c r="N47" s="313"/>
       <c r="O47" s="572"/>
       <c r="P47" s="572"/>
-      <c r="Q47" s="852"/>
-      <c r="R47" s="854"/>
+      <c r="Q47" s="889"/>
+      <c r="R47" s="891"/>
       <c r="S47" s="311" t="s">
         <v>36</v>
       </c>
@@ -25455,12 +25446,12 @@
       <c r="F66" s="306"/>
       <c r="G66" s="306"/>
       <c r="H66" s="306"/>
-      <c r="I66" s="890" t="str">
+      <c r="I66" s="836" t="str">
         <f>+R2</f>
         <v>-</v>
       </c>
-      <c r="J66" s="890"/>
-      <c r="K66" s="890"/>
+      <c r="J66" s="836"/>
+      <c r="K66" s="836"/>
       <c r="L66" s="423"/>
       <c r="M66" s="423"/>
       <c r="N66" s="547"/>
@@ -25492,11 +25483,11 @@
       <c r="F67" s="306"/>
       <c r="G67" s="306"/>
       <c r="H67" s="306"/>
-      <c r="I67" s="890" t="s">
+      <c r="I67" s="836" t="s">
         <v>442</v>
       </c>
-      <c r="J67" s="890"/>
-      <c r="K67" s="890"/>
+      <c r="J67" s="836"/>
+      <c r="K67" s="836"/>
       <c r="L67" s="423"/>
       <c r="M67" s="423"/>
       <c r="N67" s="547"/>
@@ -25528,11 +25519,11 @@
       <c r="F68" s="548"/>
       <c r="G68" s="548"/>
       <c r="H68" s="548"/>
-      <c r="I68" s="890" t="s">
+      <c r="I68" s="836" t="s">
         <v>442</v>
       </c>
-      <c r="J68" s="890"/>
-      <c r="K68" s="890"/>
+      <c r="J68" s="836"/>
+      <c r="K68" s="836"/>
       <c r="L68" s="423"/>
       <c r="M68" s="423"/>
       <c r="N68" s="547"/>
@@ -25564,11 +25555,11 @@
       <c r="F69" s="548"/>
       <c r="G69" s="548"/>
       <c r="H69" s="548"/>
-      <c r="I69" s="844" t="s">
+      <c r="I69" s="835" t="s">
         <v>252</v>
       </c>
-      <c r="J69" s="844"/>
-      <c r="K69" s="844"/>
+      <c r="J69" s="835"/>
+      <c r="K69" s="835"/>
       <c r="L69" s="423"/>
       <c r="M69" s="423"/>
       <c r="N69" s="547"/>
@@ -25600,11 +25591,11 @@
       <c r="F70" s="548"/>
       <c r="G70" s="548"/>
       <c r="H70" s="548"/>
-      <c r="I70" s="890" t="s">
+      <c r="I70" s="836" t="s">
         <v>442</v>
       </c>
-      <c r="J70" s="890"/>
-      <c r="K70" s="890"/>
+      <c r="J70" s="836"/>
+      <c r="K70" s="836"/>
       <c r="L70" s="423"/>
       <c r="M70" s="423"/>
       <c r="N70" s="547"/>
@@ -25636,11 +25627,11 @@
       <c r="F71" s="548"/>
       <c r="G71" s="548"/>
       <c r="H71" s="548"/>
-      <c r="I71" s="844" t="s">
+      <c r="I71" s="835" t="s">
         <v>252</v>
       </c>
-      <c r="J71" s="844"/>
-      <c r="K71" s="844"/>
+      <c r="J71" s="835"/>
+      <c r="K71" s="835"/>
       <c r="L71" s="423"/>
       <c r="M71" s="423"/>
       <c r="N71" s="547"/>
@@ -25672,11 +25663,11 @@
       <c r="F72" s="306"/>
       <c r="G72" s="306"/>
       <c r="H72" s="306"/>
-      <c r="I72" s="898" t="s">
+      <c r="I72" s="837" t="s">
         <v>442</v>
       </c>
-      <c r="J72" s="899"/>
-      <c r="K72" s="900"/>
+      <c r="J72" s="838"/>
+      <c r="K72" s="839"/>
       <c r="L72" s="319"/>
       <c r="M72" s="319"/>
       <c r="N72" s="549"/>
@@ -25772,14 +25763,14 @@
       <c r="E75" s="306"/>
       <c r="F75" s="306"/>
       <c r="H75" s="306"/>
-      <c r="I75" s="844"/>
-      <c r="J75" s="844"/>
-      <c r="K75" s="844"/>
-      <c r="L75" s="829">
+      <c r="I75" s="835"/>
+      <c r="J75" s="835"/>
+      <c r="K75" s="835"/>
+      <c r="L75" s="896">
         <v>0</v>
       </c>
-      <c r="M75" s="830"/>
-      <c r="N75" s="831"/>
+      <c r="M75" s="897"/>
+      <c r="N75" s="898"/>
       <c r="O75" s="572"/>
       <c r="P75" s="572"/>
       <c r="Q75" s="426"/>
@@ -25807,11 +25798,11 @@
       <c r="E76" s="306"/>
       <c r="F76" s="306"/>
       <c r="H76" s="306"/>
-      <c r="I76" s="890" t="s">
+      <c r="I76" s="836" t="s">
         <v>442</v>
       </c>
-      <c r="J76" s="890"/>
-      <c r="K76" s="890"/>
+      <c r="J76" s="836"/>
+      <c r="K76" s="836"/>
       <c r="L76" s="306"/>
       <c r="M76" s="306"/>
       <c r="N76" s="554"/>
@@ -25842,12 +25833,12 @@
       <c r="E77" s="306"/>
       <c r="F77" s="306"/>
       <c r="H77" s="306"/>
-      <c r="I77" s="891">
+      <c r="I77" s="843">
         <f>+FORMATO!H19</f>
         <v>0</v>
       </c>
-      <c r="J77" s="844"/>
-      <c r="K77" s="844"/>
+      <c r="J77" s="835"/>
+      <c r="K77" s="835"/>
       <c r="L77" s="306"/>
       <c r="M77" s="306"/>
       <c r="N77" s="554"/>
@@ -25878,12 +25869,12 @@
       <c r="E78" s="306"/>
       <c r="F78" s="306"/>
       <c r="H78" s="306"/>
-      <c r="I78" s="890">
+      <c r="I78" s="836">
         <f>+FORMATO!H20</f>
         <v>0</v>
       </c>
-      <c r="J78" s="890"/>
-      <c r="K78" s="890"/>
+      <c r="J78" s="836"/>
+      <c r="K78" s="836"/>
       <c r="L78" s="306"/>
       <c r="M78" s="306"/>
       <c r="N78" s="554"/>
@@ -25971,22 +25962,22 @@
       <c r="AD80" s="515"/>
     </row>
     <row r="81" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A81" s="893" t="s">
+      <c r="A81" s="845" t="s">
         <v>571</v>
       </c>
-      <c r="B81" s="893"/>
-      <c r="C81" s="893"/>
-      <c r="D81" s="893"/>
-      <c r="E81" s="893"/>
-      <c r="F81" s="893"/>
-      <c r="G81" s="893"/>
-      <c r="H81" s="893"/>
-      <c r="I81" s="893"/>
-      <c r="J81" s="893"/>
-      <c r="K81" s="893"/>
-      <c r="L81" s="893"/>
-      <c r="M81" s="893"/>
-      <c r="N81" s="893"/>
+      <c r="B81" s="845"/>
+      <c r="C81" s="845"/>
+      <c r="D81" s="845"/>
+      <c r="E81" s="845"/>
+      <c r="F81" s="845"/>
+      <c r="G81" s="845"/>
+      <c r="H81" s="845"/>
+      <c r="I81" s="845"/>
+      <c r="J81" s="845"/>
+      <c r="K81" s="845"/>
+      <c r="L81" s="845"/>
+      <c r="M81" s="845"/>
+      <c r="N81" s="845"/>
       <c r="O81" s="428"/>
       <c r="P81" s="428"/>
       <c r="Q81" s="426"/>
@@ -26005,22 +25996,22 @@
       <c r="AD81" s="515"/>
     </row>
     <row r="82" spans="1:30" ht="35.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A82" s="894" t="s">
+      <c r="A82" s="844" t="s">
         <v>572</v>
       </c>
-      <c r="B82" s="894"/>
-      <c r="C82" s="894"/>
-      <c r="D82" s="894"/>
-      <c r="E82" s="894"/>
-      <c r="F82" s="894"/>
-      <c r="G82" s="894"/>
-      <c r="H82" s="894"/>
-      <c r="I82" s="894"/>
-      <c r="J82" s="894"/>
-      <c r="K82" s="894"/>
-      <c r="L82" s="894"/>
-      <c r="M82" s="894"/>
-      <c r="N82" s="894"/>
+      <c r="B82" s="844"/>
+      <c r="C82" s="844"/>
+      <c r="D82" s="844"/>
+      <c r="E82" s="844"/>
+      <c r="F82" s="844"/>
+      <c r="G82" s="844"/>
+      <c r="H82" s="844"/>
+      <c r="I82" s="844"/>
+      <c r="J82" s="844"/>
+      <c r="K82" s="844"/>
+      <c r="L82" s="844"/>
+      <c r="M82" s="844"/>
+      <c r="N82" s="844"/>
       <c r="Q82" s="426"/>
       <c r="R82" s="521"/>
       <c r="S82" s="521"/>
@@ -26037,22 +26028,22 @@
       <c r="AD82" s="515"/>
     </row>
     <row r="83" spans="1:30" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A83" s="892" t="s">
+      <c r="A83" s="844" t="s">
         <v>573</v>
       </c>
-      <c r="B83" s="892"/>
-      <c r="C83" s="892"/>
-      <c r="D83" s="892"/>
-      <c r="E83" s="892"/>
-      <c r="F83" s="892"/>
-      <c r="G83" s="892"/>
-      <c r="H83" s="892"/>
-      <c r="I83" s="892"/>
-      <c r="J83" s="892"/>
-      <c r="K83" s="892"/>
-      <c r="L83" s="892"/>
-      <c r="M83" s="892"/>
-      <c r="N83" s="892"/>
+      <c r="B83" s="844"/>
+      <c r="C83" s="844"/>
+      <c r="D83" s="844"/>
+      <c r="E83" s="844"/>
+      <c r="F83" s="844"/>
+      <c r="G83" s="844"/>
+      <c r="H83" s="844"/>
+      <c r="I83" s="844"/>
+      <c r="J83" s="844"/>
+      <c r="K83" s="844"/>
+      <c r="L83" s="844"/>
+      <c r="M83" s="844"/>
+      <c r="N83" s="844"/>
       <c r="O83" s="430"/>
       <c r="P83" s="430"/>
       <c r="AA83" s="515"/>
@@ -26061,44 +26052,44 @@
       <c r="AD83" s="515"/>
     </row>
     <row r="84" spans="1:30" ht="26.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A84" s="892" t="s">
+      <c r="A84" s="844" t="s">
         <v>574</v>
       </c>
-      <c r="B84" s="892"/>
-      <c r="C84" s="892"/>
-      <c r="D84" s="892"/>
-      <c r="E84" s="892"/>
-      <c r="F84" s="892"/>
-      <c r="G84" s="892"/>
-      <c r="H84" s="892"/>
-      <c r="I84" s="892"/>
-      <c r="J84" s="892"/>
-      <c r="K84" s="892"/>
-      <c r="L84" s="892"/>
-      <c r="M84" s="892"/>
-      <c r="N84" s="892"/>
+      <c r="B84" s="844"/>
+      <c r="C84" s="844"/>
+      <c r="D84" s="844"/>
+      <c r="E84" s="844"/>
+      <c r="F84" s="844"/>
+      <c r="G84" s="844"/>
+      <c r="H84" s="844"/>
+      <c r="I84" s="844"/>
+      <c r="J84" s="844"/>
+      <c r="K84" s="844"/>
+      <c r="L84" s="844"/>
+      <c r="M84" s="844"/>
+      <c r="N84" s="844"/>
       <c r="AA84" s="515"/>
       <c r="AB84" s="515"/>
       <c r="AC84" s="515"/>
       <c r="AD84" s="515"/>
     </row>
     <row r="85" spans="1:30" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A85" s="889" t="s">
+      <c r="A85" s="842" t="s">
         <v>575</v>
       </c>
-      <c r="B85" s="889"/>
-      <c r="C85" s="889"/>
-      <c r="D85" s="889"/>
-      <c r="E85" s="889"/>
-      <c r="F85" s="889"/>
-      <c r="G85" s="889"/>
-      <c r="H85" s="889"/>
-      <c r="I85" s="889"/>
-      <c r="J85" s="889"/>
-      <c r="K85" s="889"/>
-      <c r="L85" s="889"/>
-      <c r="M85" s="889"/>
-      <c r="N85" s="889"/>
+      <c r="B85" s="842"/>
+      <c r="C85" s="842"/>
+      <c r="D85" s="842"/>
+      <c r="E85" s="842"/>
+      <c r="F85" s="842"/>
+      <c r="G85" s="842"/>
+      <c r="H85" s="842"/>
+      <c r="I85" s="842"/>
+      <c r="J85" s="842"/>
+      <c r="K85" s="842"/>
+      <c r="L85" s="842"/>
+      <c r="M85" s="842"/>
+      <c r="N85" s="842"/>
       <c r="AA85" s="515"/>
       <c r="AB85" s="515"/>
       <c r="AC85" s="515"/>
@@ -26138,7 +26129,7 @@
       <c r="AC87" s="515"/>
       <c r="AD87" s="515"/>
     </row>
-    <row r="88" spans="1:30" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:30" ht="43.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="429"/>
       <c r="H88" s="305"/>
       <c r="I88" s="305"/>
@@ -26267,64 +26258,13 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="si9YKf6lzK02//c2fwTL8KrjRlnURqHcXnN/4Q4Sc/5OLW7NoETnKBu47NnAwunXrtWXJH/mdN2Ux3mvT6+loQ==" saltValue="EXqimNx38ue+5mJjmY9JFA==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <protectedRanges>
     <protectedRange sqref="F11:F13 F16" name="Rango3_3_1_1_1_1_1_1_1_1"/>
     <protectedRange sqref="F10" name="Rango3_3_1_1_1_1_1_2_1"/>
   </protectedRanges>
   <dataConsolidate/>
   <mergeCells count="67">
-    <mergeCell ref="E37:H37"/>
-    <mergeCell ref="E38:H38"/>
-    <mergeCell ref="I75:K75"/>
-    <mergeCell ref="I66:K66"/>
-    <mergeCell ref="I67:K67"/>
-    <mergeCell ref="I72:K72"/>
-    <mergeCell ref="I68:K68"/>
-    <mergeCell ref="I69:K69"/>
-    <mergeCell ref="I70:K70"/>
-    <mergeCell ref="I38:J38"/>
-    <mergeCell ref="A85:N85"/>
-    <mergeCell ref="I76:K76"/>
-    <mergeCell ref="I77:K77"/>
-    <mergeCell ref="I78:K78"/>
-    <mergeCell ref="A83:N83"/>
-    <mergeCell ref="A81:N81"/>
-    <mergeCell ref="A82:N82"/>
-    <mergeCell ref="A84:N84"/>
-    <mergeCell ref="Q5:V5"/>
-    <mergeCell ref="A7:N7"/>
-    <mergeCell ref="Q23:R23"/>
-    <mergeCell ref="A14:N14"/>
-    <mergeCell ref="A15:N15"/>
-    <mergeCell ref="A8:N8"/>
-    <mergeCell ref="Q16:V16"/>
-    <mergeCell ref="Q11:V11"/>
-    <mergeCell ref="C10:K10"/>
-    <mergeCell ref="C12:K12"/>
-    <mergeCell ref="C11:K11"/>
-    <mergeCell ref="C9:K9"/>
-    <mergeCell ref="I36:J36"/>
-    <mergeCell ref="I33:J33"/>
-    <mergeCell ref="I30:J30"/>
-    <mergeCell ref="E31:H31"/>
-    <mergeCell ref="I31:J31"/>
-    <mergeCell ref="E32:H32"/>
-    <mergeCell ref="E33:H33"/>
-    <mergeCell ref="X17:AA17"/>
-    <mergeCell ref="K23:K24"/>
-    <mergeCell ref="I24:J24"/>
-    <mergeCell ref="I25:J25"/>
-    <mergeCell ref="I26:J26"/>
-    <mergeCell ref="E23:J23"/>
-    <mergeCell ref="E24:H24"/>
-    <mergeCell ref="E25:H25"/>
-    <mergeCell ref="E26:H26"/>
-    <mergeCell ref="Q41:T42"/>
-    <mergeCell ref="Q43:Q44"/>
-    <mergeCell ref="R43:R44"/>
-    <mergeCell ref="Q45:Q47"/>
-    <mergeCell ref="R45:R47"/>
     <mergeCell ref="L75:N75"/>
     <mergeCell ref="E27:H27"/>
     <mergeCell ref="I27:J27"/>
@@ -26341,6 +26281,57 @@
     <mergeCell ref="I35:J35"/>
     <mergeCell ref="I71:K71"/>
     <mergeCell ref="I37:J37"/>
+    <mergeCell ref="Q41:T42"/>
+    <mergeCell ref="Q43:Q44"/>
+    <mergeCell ref="R43:R44"/>
+    <mergeCell ref="Q45:Q47"/>
+    <mergeCell ref="R45:R47"/>
+    <mergeCell ref="X17:AA17"/>
+    <mergeCell ref="K23:K24"/>
+    <mergeCell ref="I24:J24"/>
+    <mergeCell ref="I25:J25"/>
+    <mergeCell ref="I26:J26"/>
+    <mergeCell ref="E23:J23"/>
+    <mergeCell ref="E24:H24"/>
+    <mergeCell ref="E25:H25"/>
+    <mergeCell ref="E26:H26"/>
+    <mergeCell ref="I36:J36"/>
+    <mergeCell ref="I33:J33"/>
+    <mergeCell ref="I30:J30"/>
+    <mergeCell ref="E31:H31"/>
+    <mergeCell ref="I31:J31"/>
+    <mergeCell ref="E32:H32"/>
+    <mergeCell ref="E33:H33"/>
+    <mergeCell ref="Q5:V5"/>
+    <mergeCell ref="A7:N7"/>
+    <mergeCell ref="Q23:R23"/>
+    <mergeCell ref="A14:N14"/>
+    <mergeCell ref="A15:N15"/>
+    <mergeCell ref="A8:N8"/>
+    <mergeCell ref="Q16:V16"/>
+    <mergeCell ref="Q11:V11"/>
+    <mergeCell ref="C10:K10"/>
+    <mergeCell ref="C12:K12"/>
+    <mergeCell ref="C11:K11"/>
+    <mergeCell ref="C9:K9"/>
+    <mergeCell ref="A85:N85"/>
+    <mergeCell ref="I76:K76"/>
+    <mergeCell ref="I77:K77"/>
+    <mergeCell ref="I78:K78"/>
+    <mergeCell ref="A83:N83"/>
+    <mergeCell ref="A81:N81"/>
+    <mergeCell ref="A82:N82"/>
+    <mergeCell ref="A84:N84"/>
+    <mergeCell ref="E37:H37"/>
+    <mergeCell ref="E38:H38"/>
+    <mergeCell ref="I75:K75"/>
+    <mergeCell ref="I66:K66"/>
+    <mergeCell ref="I67:K67"/>
+    <mergeCell ref="I72:K72"/>
+    <mergeCell ref="I68:K68"/>
+    <mergeCell ref="I69:K69"/>
+    <mergeCell ref="I70:K70"/>
+    <mergeCell ref="I38:J38"/>
   </mergeCells>
   <phoneticPr fontId="12" type="noConversion"/>
   <conditionalFormatting sqref="AA24">
@@ -26412,17 +26403,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="909"/>
-      <c r="B1" s="910"/>
-      <c r="C1" s="915" t="s">
+      <c r="A1" s="908"/>
+      <c r="B1" s="909"/>
+      <c r="C1" s="914" t="s">
         <v>321</v>
       </c>
-      <c r="D1" s="916"/>
-      <c r="E1" s="916"/>
-      <c r="F1" s="916"/>
-      <c r="G1" s="916"/>
-      <c r="H1" s="916"/>
-      <c r="I1" s="917"/>
+      <c r="D1" s="915"/>
+      <c r="E1" s="915"/>
+      <c r="F1" s="915"/>
+      <c r="G1" s="915"/>
+      <c r="H1" s="915"/>
+      <c r="I1" s="916"/>
       <c r="J1" s="343" t="s">
         <v>320</v>
       </c>
@@ -26431,15 +26422,15 @@
       </c>
     </row>
     <row r="2" spans="1:11" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="911"/>
-      <c r="B2" s="912"/>
-      <c r="C2" s="918"/>
-      <c r="D2" s="919"/>
-      <c r="E2" s="919"/>
-      <c r="F2" s="919"/>
-      <c r="G2" s="919"/>
-      <c r="H2" s="919"/>
-      <c r="I2" s="920"/>
+      <c r="A2" s="910"/>
+      <c r="B2" s="911"/>
+      <c r="C2" s="917"/>
+      <c r="D2" s="918"/>
+      <c r="E2" s="918"/>
+      <c r="F2" s="918"/>
+      <c r="G2" s="918"/>
+      <c r="H2" s="918"/>
+      <c r="I2" s="919"/>
       <c r="J2" s="343" t="s">
         <v>318</v>
       </c>
@@ -26448,15 +26439,15 @@
       </c>
     </row>
     <row r="3" spans="1:11" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="911"/>
-      <c r="B3" s="912"/>
-      <c r="C3" s="918"/>
-      <c r="D3" s="919"/>
-      <c r="E3" s="919"/>
-      <c r="F3" s="919"/>
-      <c r="G3" s="919"/>
-      <c r="H3" s="919"/>
-      <c r="I3" s="920"/>
+      <c r="A3" s="910"/>
+      <c r="B3" s="911"/>
+      <c r="C3" s="917"/>
+      <c r="D3" s="918"/>
+      <c r="E3" s="918"/>
+      <c r="F3" s="918"/>
+      <c r="G3" s="918"/>
+      <c r="H3" s="918"/>
+      <c r="I3" s="919"/>
       <c r="J3" s="343" t="s">
         <v>317</v>
       </c>
@@ -26465,15 +26456,15 @@
       </c>
     </row>
     <row r="4" spans="1:11" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="913"/>
-      <c r="B4" s="914"/>
-      <c r="C4" s="921"/>
-      <c r="D4" s="922"/>
-      <c r="E4" s="922"/>
-      <c r="F4" s="922"/>
-      <c r="G4" s="922"/>
-      <c r="H4" s="922"/>
-      <c r="I4" s="923"/>
+      <c r="A4" s="912"/>
+      <c r="B4" s="913"/>
+      <c r="C4" s="920"/>
+      <c r="D4" s="921"/>
+      <c r="E4" s="921"/>
+      <c r="F4" s="921"/>
+      <c r="G4" s="921"/>
+      <c r="H4" s="921"/>
+      <c r="I4" s="922"/>
       <c r="J4" s="343" t="s">
         <v>316</v>
       </c>
@@ -26790,19 +26781,19 @@
       <c r="H32" s="403"/>
     </row>
     <row r="34" spans="1:11" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A34" s="906" t="s">
+      <c r="A34" s="905" t="s">
         <v>309</v>
       </c>
-      <c r="B34" s="907"/>
-      <c r="C34" s="907"/>
-      <c r="D34" s="907"/>
-      <c r="E34" s="907"/>
-      <c r="F34" s="907"/>
-      <c r="G34" s="907"/>
-      <c r="H34" s="907"/>
-      <c r="I34" s="907"/>
-      <c r="J34" s="907"/>
-      <c r="K34" s="908"/>
+      <c r="B34" s="906"/>
+      <c r="C34" s="906"/>
+      <c r="D34" s="906"/>
+      <c r="E34" s="906"/>
+      <c r="F34" s="906"/>
+      <c r="G34" s="906"/>
+      <c r="H34" s="906"/>
+      <c r="I34" s="906"/>
+      <c r="J34" s="906"/>
+      <c r="K34" s="907"/>
     </row>
     <row r="35" spans="1:11" ht="38.4" x14ac:dyDescent="0.25">
       <c r="A35" s="348" t="s">
@@ -31663,19 +31654,19 @@
       <c r="A227" s="775" t="s">
         <v>563</v>
       </c>
-      <c r="B227" s="924" t="s">
+      <c r="B227" s="923" t="s">
         <v>564</v>
       </c>
-      <c r="C227" s="925"/>
+      <c r="C227" s="924"/>
       <c r="D227" s="776"/>
-      <c r="E227" s="926" t="s">
+      <c r="E227" s="925" t="s">
         <v>565</v>
       </c>
-      <c r="F227" s="926"/>
-      <c r="G227" s="927" t="s">
+      <c r="F227" s="925"/>
+      <c r="G227" s="926" t="s">
         <v>566</v>
       </c>
-      <c r="H227" s="928"/>
+      <c r="H227" s="927"/>
     </row>
     <row r="228" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A228" s="403"/>
@@ -31691,19 +31682,19 @@
       <c r="A229" s="777" t="s">
         <v>567</v>
       </c>
-      <c r="B229" s="903">
+      <c r="B229" s="902">
         <v>44944</v>
       </c>
-      <c r="C229" s="904"/>
+      <c r="C229" s="903"/>
       <c r="D229" s="403"/>
-      <c r="E229" s="905" t="s">
+      <c r="E229" s="904" t="s">
         <v>568</v>
       </c>
-      <c r="F229" s="905"/>
-      <c r="G229" s="903">
+      <c r="F229" s="904"/>
+      <c r="G229" s="902">
         <v>44944</v>
       </c>
-      <c r="H229" s="904"/>
+      <c r="H229" s="903"/>
     </row>
     <row r="230" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A230" s="403"/>
@@ -32092,16 +32083,16 @@
     </row>
     <row r="27" spans="1:15" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="401"/>
-      <c r="B27" s="932" t="s">
+      <c r="B27" s="931" t="s">
         <v>398</v>
       </c>
-      <c r="C27" s="934" t="s">
+      <c r="C27" s="933" t="s">
         <v>399</v>
       </c>
-      <c r="D27" s="934" t="s">
+      <c r="D27" s="933" t="s">
         <v>400</v>
       </c>
-      <c r="E27" s="936" t="s">
+      <c r="E27" s="935" t="s">
         <v>401</v>
       </c>
       <c r="H27" s="405"/>
@@ -32120,10 +32111,10 @@
     </row>
     <row r="28" spans="1:15" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28" s="401"/>
-      <c r="B28" s="933"/>
-      <c r="C28" s="935"/>
-      <c r="D28" s="935"/>
-      <c r="E28" s="937"/>
+      <c r="B28" s="932"/>
+      <c r="C28" s="934"/>
+      <c r="D28" s="934"/>
+      <c r="E28" s="936"/>
       <c r="H28" s="405"/>
       <c r="I28" s="401"/>
       <c r="J28" s="334" t="s">
@@ -32645,11 +32636,11 @@
       <c r="H45" s="327"/>
     </row>
     <row r="46" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A46" s="929" t="s">
+      <c r="A46" s="928" t="s">
         <v>334</v>
       </c>
-      <c r="B46" s="930"/>
-      <c r="C46" s="931"/>
+      <c r="B46" s="929"/>
+      <c r="C46" s="930"/>
       <c r="D46" s="647">
         <v>45792</v>
       </c>
@@ -33068,35 +33059,35 @@
       <c r="K7" s="150"/>
     </row>
     <row r="8" spans="1:19" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="939" t="s">
+      <c r="A8" s="960" t="s">
         <v>21</v>
       </c>
-      <c r="B8" s="939"/>
-      <c r="C8" s="939"/>
-      <c r="D8" s="939"/>
-      <c r="E8" s="939"/>
-      <c r="F8" s="939"/>
-      <c r="G8" s="939"/>
-      <c r="H8" s="939"/>
-      <c r="I8" s="939"/>
-      <c r="J8" s="939"/>
-      <c r="K8" s="939"/>
+      <c r="B8" s="960"/>
+      <c r="C8" s="960"/>
+      <c r="D8" s="960"/>
+      <c r="E8" s="960"/>
+      <c r="F8" s="960"/>
+      <c r="G8" s="960"/>
+      <c r="H8" s="960"/>
+      <c r="I8" s="960"/>
+      <c r="J8" s="960"/>
+      <c r="K8" s="960"/>
     </row>
     <row r="9" spans="1:19" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="940">
+      <c r="A9" s="961">
         <f>+K13</f>
         <v>10</v>
       </c>
-      <c r="B9" s="940"/>
-      <c r="C9" s="940"/>
-      <c r="D9" s="940"/>
-      <c r="E9" s="940"/>
-      <c r="F9" s="940"/>
-      <c r="G9" s="940"/>
-      <c r="H9" s="940"/>
-      <c r="I9" s="940"/>
-      <c r="J9" s="940"/>
-      <c r="K9" s="940"/>
+      <c r="B9" s="961"/>
+      <c r="C9" s="961"/>
+      <c r="D9" s="961"/>
+      <c r="E9" s="961"/>
+      <c r="F9" s="961"/>
+      <c r="G9" s="961"/>
+      <c r="H9" s="961"/>
+      <c r="I9" s="961"/>
+      <c r="J9" s="961"/>
+      <c r="K9" s="961"/>
       <c r="O9" s="151"/>
     </row>
     <row r="10" spans="1:19" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
@@ -33119,15 +33110,15 @@
       <c r="B11" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="C11" s="941">
+      <c r="C11" s="962">
         <f>+A.Granul!F10</f>
         <v>0</v>
       </c>
-      <c r="D11" s="941"/>
-      <c r="E11" s="941"/>
-      <c r="F11" s="941"/>
-      <c r="G11" s="941"/>
-      <c r="H11" s="941"/>
+      <c r="D11" s="962"/>
+      <c r="E11" s="962"/>
+      <c r="F11" s="962"/>
+      <c r="G11" s="962"/>
+      <c r="H11" s="962"/>
       <c r="I11" s="153" t="s">
         <v>31</v>
       </c>
@@ -33148,15 +33139,15 @@
       <c r="B12" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="C12" s="941">
+      <c r="C12" s="962">
         <f>+A.Granul!F11</f>
         <v>0</v>
       </c>
-      <c r="D12" s="941"/>
-      <c r="E12" s="941"/>
-      <c r="F12" s="941"/>
-      <c r="G12" s="941"/>
-      <c r="H12" s="941"/>
+      <c r="D12" s="962"/>
+      <c r="E12" s="962"/>
+      <c r="F12" s="962"/>
+      <c r="G12" s="962"/>
+      <c r="H12" s="962"/>
       <c r="I12" s="15" t="s">
         <v>19</v>
       </c>
@@ -33181,15 +33172,15 @@
       <c r="B13" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="C13" s="941">
+      <c r="C13" s="962">
         <f>+A.Granul!F12</f>
         <v>0</v>
       </c>
-      <c r="D13" s="941"/>
-      <c r="E13" s="941"/>
-      <c r="F13" s="941"/>
-      <c r="G13" s="941"/>
-      <c r="H13" s="941"/>
+      <c r="D13" s="962"/>
+      <c r="E13" s="962"/>
+      <c r="F13" s="962"/>
+      <c r="G13" s="962"/>
+      <c r="H13" s="962"/>
       <c r="I13" s="15" t="s">
         <v>20</v>
       </c>
@@ -33203,8 +33194,8 @@
       <c r="M13" s="156"/>
       <c r="P13" s="159"/>
       <c r="Q13" s="159"/>
-      <c r="R13" s="938"/>
-      <c r="S13" s="938"/>
+      <c r="R13" s="959"/>
+      <c r="S13" s="959"/>
     </row>
     <row r="14" spans="1:19" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="13"/>
@@ -33226,19 +33217,19 @@
       <c r="S14" s="164"/>
     </row>
     <row r="15" spans="1:19" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="943" t="s">
+      <c r="A15" s="945" t="s">
         <v>171</v>
       </c>
-      <c r="B15" s="944"/>
-      <c r="C15" s="944"/>
-      <c r="D15" s="944"/>
-      <c r="E15" s="944"/>
-      <c r="F15" s="944"/>
-      <c r="G15" s="944"/>
-      <c r="H15" s="944"/>
-      <c r="I15" s="944"/>
-      <c r="J15" s="944"/>
-      <c r="K15" s="945"/>
+      <c r="B15" s="946"/>
+      <c r="C15" s="946"/>
+      <c r="D15" s="946"/>
+      <c r="E15" s="946"/>
+      <c r="F15" s="946"/>
+      <c r="G15" s="946"/>
+      <c r="H15" s="946"/>
+      <c r="I15" s="946"/>
+      <c r="J15" s="946"/>
+      <c r="K15" s="947"/>
       <c r="L15" s="156"/>
       <c r="M15" s="156"/>
       <c r="P15" s="159"/>
@@ -33247,19 +33238,19 @@
       <c r="S15" s="164"/>
     </row>
     <row r="16" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="946" t="s">
+      <c r="A16" s="948" t="s">
         <v>191</v>
       </c>
-      <c r="B16" s="947"/>
-      <c r="C16" s="947"/>
-      <c r="D16" s="947"/>
-      <c r="E16" s="947"/>
-      <c r="F16" s="947"/>
-      <c r="G16" s="947"/>
-      <c r="H16" s="947"/>
-      <c r="I16" s="947"/>
-      <c r="J16" s="947"/>
-      <c r="K16" s="948"/>
+      <c r="B16" s="949"/>
+      <c r="C16" s="949"/>
+      <c r="D16" s="949"/>
+      <c r="E16" s="949"/>
+      <c r="F16" s="949"/>
+      <c r="G16" s="949"/>
+      <c r="H16" s="949"/>
+      <c r="I16" s="949"/>
+      <c r="J16" s="949"/>
+      <c r="K16" s="950"/>
       <c r="L16" s="156"/>
       <c r="M16" s="156"/>
       <c r="P16" s="159"/>
@@ -33287,19 +33278,19 @@
       <c r="S17" s="164"/>
     </row>
     <row r="18" spans="1:21" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="949" t="s">
+      <c r="A18" s="951" t="s">
         <v>26</v>
       </c>
-      <c r="B18" s="950"/>
-      <c r="C18" s="950"/>
-      <c r="D18" s="950"/>
-      <c r="E18" s="950"/>
-      <c r="F18" s="950"/>
-      <c r="G18" s="950"/>
-      <c r="H18" s="950"/>
-      <c r="I18" s="950"/>
-      <c r="J18" s="950"/>
-      <c r="K18" s="951"/>
+      <c r="B18" s="952"/>
+      <c r="C18" s="952"/>
+      <c r="D18" s="952"/>
+      <c r="E18" s="952"/>
+      <c r="F18" s="952"/>
+      <c r="G18" s="952"/>
+      <c r="H18" s="952"/>
+      <c r="I18" s="952"/>
+      <c r="J18" s="952"/>
+      <c r="K18" s="953"/>
       <c r="M18" s="156"/>
       <c r="P18" s="159"/>
       <c r="Q18" s="159"/>
@@ -33424,8 +33415,8 @@
     </row>
     <row r="23" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="176"/>
-      <c r="I23" s="952"/>
-      <c r="J23" s="952"/>
+      <c r="I23" s="954"/>
+      <c r="J23" s="954"/>
       <c r="K23" s="177"/>
       <c r="L23" s="156"/>
       <c r="M23" s="178"/>
@@ -33433,41 +33424,41 @@
     </row>
     <row r="24" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="180"/>
-      <c r="D24" s="953" t="s">
+      <c r="D24" s="955" t="s">
         <v>174</v>
       </c>
-      <c r="E24" s="954"/>
-      <c r="F24" s="954"/>
-      <c r="G24" s="955" t="s">
+      <c r="E24" s="956"/>
+      <c r="F24" s="956"/>
+      <c r="G24" s="957" t="s">
         <v>175</v>
       </c>
-      <c r="H24" s="956"/>
-      <c r="I24" s="957"/>
-      <c r="J24" s="957"/>
+      <c r="H24" s="958"/>
+      <c r="I24" s="942"/>
+      <c r="J24" s="942"/>
       <c r="K24" s="181"/>
       <c r="L24" s="156"/>
       <c r="M24" s="182"/>
-      <c r="O24" s="958" t="s">
+      <c r="O24" s="937" t="s">
         <v>174</v>
       </c>
-      <c r="P24" s="959"/>
+      <c r="P24" s="938"/>
       <c r="Q24" s="183" t="s">
         <v>173</v>
       </c>
-      <c r="R24" s="958" t="s">
+      <c r="R24" s="937" t="s">
         <v>175</v>
       </c>
-      <c r="S24" s="960"/>
+      <c r="S24" s="939"/>
       <c r="T24" s="183" t="s">
         <v>173</v>
       </c>
     </row>
     <row r="25" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="180"/>
-      <c r="B25" s="961" t="s">
+      <c r="B25" s="940" t="s">
         <v>176</v>
       </c>
-      <c r="C25" s="962"/>
+      <c r="C25" s="941"/>
       <c r="D25" s="184" t="str">
         <f>IF($Q$24="NO","",O25)</f>
         <v/>
@@ -33488,8 +33479,8 @@
         <f>IF($T$24="NO","",S25)</f>
         <v/>
       </c>
-      <c r="I25" s="957"/>
-      <c r="J25" s="957"/>
+      <c r="I25" s="942"/>
+      <c r="J25" s="942"/>
       <c r="K25" s="181"/>
       <c r="L25" s="156"/>
       <c r="M25" s="182"/>
@@ -33538,8 +33529,8 @@
         <f>IF($T$24="NO","",S26)</f>
         <v/>
       </c>
-      <c r="I26" s="963"/>
-      <c r="J26" s="963"/>
+      <c r="I26" s="943"/>
+      <c r="J26" s="943"/>
       <c r="K26" s="194"/>
       <c r="L26" s="195"/>
       <c r="M26" s="182"/>
@@ -34317,19 +34308,19 @@
       <c r="Q49"/>
     </row>
     <row r="50" spans="1:17" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="942" t="s">
+      <c r="A50" s="944" t="s">
         <v>192</v>
       </c>
-      <c r="B50" s="942"/>
-      <c r="C50" s="942"/>
-      <c r="D50" s="942"/>
-      <c r="E50" s="942"/>
-      <c r="F50" s="942"/>
-      <c r="G50" s="942"/>
-      <c r="H50" s="942"/>
-      <c r="I50" s="942"/>
-      <c r="J50" s="942"/>
-      <c r="K50" s="942"/>
+      <c r="B50" s="944"/>
+      <c r="C50" s="944"/>
+      <c r="D50" s="944"/>
+      <c r="E50" s="944"/>
+      <c r="F50" s="944"/>
+      <c r="G50" s="944"/>
+      <c r="H50" s="944"/>
+      <c r="I50" s="944"/>
+      <c r="J50" s="944"/>
+      <c r="K50" s="944"/>
     </row>
     <row r="51" spans="1:17" ht="15.9" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="52" spans="1:17" ht="15.9" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -34339,11 +34330,12 @@
     <protectedRange sqref="C11" name="Rango3_3_1_1_1_1_1_2_1"/>
   </protectedRanges>
   <mergeCells count="19">
-    <mergeCell ref="O24:P24"/>
-    <mergeCell ref="R24:S24"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="I25:J25"/>
-    <mergeCell ref="I26:J26"/>
+    <mergeCell ref="R13:S13"/>
+    <mergeCell ref="A8:K8"/>
+    <mergeCell ref="A9:K9"/>
+    <mergeCell ref="C11:H11"/>
+    <mergeCell ref="C12:H12"/>
+    <mergeCell ref="C13:H13"/>
     <mergeCell ref="A50:K50"/>
     <mergeCell ref="A15:K15"/>
     <mergeCell ref="A16:K16"/>
@@ -34352,12 +34344,11 @@
     <mergeCell ref="D24:F24"/>
     <mergeCell ref="G24:H24"/>
     <mergeCell ref="I24:J24"/>
-    <mergeCell ref="R13:S13"/>
-    <mergeCell ref="A8:K8"/>
-    <mergeCell ref="A9:K9"/>
-    <mergeCell ref="C11:H11"/>
-    <mergeCell ref="C12:H12"/>
-    <mergeCell ref="C13:H13"/>
+    <mergeCell ref="O24:P24"/>
+    <mergeCell ref="R24:S24"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="I25:J25"/>
+    <mergeCell ref="I26:J26"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Q24 T24" xr:uid="{00000000-0002-0000-0300-000000000000}">
@@ -34394,15 +34385,15 @@
       <c r="A1" s="94" t="s">
         <v>97</v>
       </c>
-      <c r="B1" s="964" t="s">
+      <c r="B1" s="982" t="s">
         <v>98</v>
       </c>
-      <c r="C1" s="964"/>
-      <c r="D1" s="964"/>
-      <c r="E1" s="964"/>
-      <c r="F1" s="964"/>
-      <c r="G1" s="964"/>
-      <c r="H1" s="964"/>
+      <c r="C1" s="982"/>
+      <c r="D1" s="982"/>
+      <c r="E1" s="982"/>
+      <c r="F1" s="982"/>
+      <c r="G1" s="982"/>
+      <c r="H1" s="982"/>
       <c r="I1" s="94"/>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.25">
@@ -34540,29 +34531,29 @@
     </row>
     <row r="8" spans="1:17" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="94"/>
-      <c r="B8" s="965" t="s">
+      <c r="B8" s="983" t="s">
         <v>110</v>
       </c>
-      <c r="C8" s="965"/>
-      <c r="D8" s="965"/>
+      <c r="C8" s="983"/>
+      <c r="D8" s="983"/>
       <c r="E8" s="103" t="s">
         <v>111</v>
       </c>
       <c r="F8" s="104" t="s">
         <v>112</v>
       </c>
-      <c r="G8" s="966" t="s">
+      <c r="G8" s="984" t="s">
         <v>113</v>
       </c>
-      <c r="H8" s="966"/>
+      <c r="H8" s="984"/>
       <c r="I8" s="94"/>
       <c r="L8" s="247" t="s">
         <v>114</v>
       </c>
-      <c r="M8" s="967" t="s">
+      <c r="M8" s="985" t="s">
         <v>115</v>
       </c>
-      <c r="N8" s="967"/>
+      <c r="N8" s="985"/>
       <c r="O8" s="248" t="s">
         <v>116</v>
       </c>
@@ -34575,13 +34566,13 @@
     </row>
     <row r="9" spans="1:17" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="94"/>
-      <c r="B9" s="968" t="s">
+      <c r="B9" s="986" t="s">
         <v>119</v>
       </c>
-      <c r="C9" s="970" t="s">
+      <c r="C9" s="988" t="s">
         <v>120</v>
       </c>
-      <c r="D9" s="972" t="s">
+      <c r="D9" s="990" t="s">
         <v>121</v>
       </c>
       <c r="E9" s="106" t="s">
@@ -34590,10 +34581,10 @@
       <c r="F9" s="107" t="s">
         <v>123</v>
       </c>
-      <c r="G9" s="973" t="s">
+      <c r="G9" s="991" t="s">
         <v>124</v>
       </c>
-      <c r="H9" s="974"/>
+      <c r="H9" s="992"/>
       <c r="I9" s="94"/>
       <c r="L9" s="249" t="e">
         <f>IF(AND(N_200&lt;50,(100-N_40)&gt;=0.5*(100-N_200),N_200&lt;5,CU&gt;=4,CC&gt;=1,CC&lt;=3),"GW","")</f>
@@ -34622,19 +34613,19 @@
     </row>
     <row r="10" spans="1:17" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="94"/>
-      <c r="B10" s="968"/>
-      <c r="C10" s="970"/>
-      <c r="D10" s="972"/>
+      <c r="B10" s="986"/>
+      <c r="C10" s="988"/>
+      <c r="D10" s="990"/>
       <c r="E10" s="108" t="s">
         <v>125</v>
       </c>
       <c r="F10" s="109" t="s">
         <v>126</v>
       </c>
-      <c r="G10" s="975" t="s">
+      <c r="G10" s="993" t="s">
         <v>127</v>
       </c>
-      <c r="H10" s="976"/>
+      <c r="H10" s="994"/>
       <c r="I10" s="94"/>
       <c r="L10" s="249" t="e">
         <f>IF(AND(N_200&lt;50,(100-N_40)&gt;=0.5*(100-N_200),N_200&lt;5,OR(CU&lt;4,CC&lt;1,CC&gt;3)),"GP","")</f>
@@ -34659,9 +34650,9 @@
     </row>
     <row r="11" spans="1:17" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="94"/>
-      <c r="B11" s="968"/>
-      <c r="C11" s="970"/>
-      <c r="D11" s="972" t="s">
+      <c r="B11" s="986"/>
+      <c r="C11" s="988"/>
+      <c r="D11" s="990" t="s">
         <v>128</v>
       </c>
       <c r="E11" s="108" t="s">
@@ -34673,7 +34664,7 @@
       <c r="G11" s="111" t="s">
         <v>131</v>
       </c>
-      <c r="H11" s="977" t="s">
+      <c r="H11" s="995" t="s">
         <v>132</v>
       </c>
       <c r="I11" s="94"/>
@@ -34694,9 +34685,9 @@
     </row>
     <row r="12" spans="1:17" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="94"/>
-      <c r="B12" s="968"/>
-      <c r="C12" s="971"/>
-      <c r="D12" s="972"/>
+      <c r="B12" s="986"/>
+      <c r="C12" s="989"/>
+      <c r="D12" s="990"/>
       <c r="E12" s="112" t="s">
         <v>133</v>
       </c>
@@ -34706,7 +34697,7 @@
       <c r="G12" s="111" t="s">
         <v>135</v>
       </c>
-      <c r="H12" s="978"/>
+      <c r="H12" s="996"/>
       <c r="I12" s="94"/>
       <c r="L12" s="249" t="e">
         <f>IF(AND(N_200&lt;50,(100-N_40)&gt;=0.5*(100-N_200),N_200&gt;=12,IP&gt;=7,IP&gt;=0.73*(Ll-20)),"GC","")</f>
@@ -34722,11 +34713,11 @@
     </row>
     <row r="13" spans="1:17" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="94"/>
-      <c r="B13" s="968"/>
-      <c r="C13" s="970" t="s">
+      <c r="B13" s="986"/>
+      <c r="C13" s="988" t="s">
         <v>136</v>
       </c>
-      <c r="D13" s="972" t="s">
+      <c r="D13" s="990" t="s">
         <v>137</v>
       </c>
       <c r="E13" s="113" t="s">
@@ -34735,10 +34726,10 @@
       <c r="F13" s="114" t="s">
         <v>139</v>
       </c>
-      <c r="G13" s="979" t="s">
+      <c r="G13" s="997" t="s">
         <v>140</v>
       </c>
-      <c r="H13" s="980"/>
+      <c r="H13" s="998"/>
       <c r="I13" s="94"/>
       <c r="L13" s="249" t="e">
         <f>IF(AND(N_200&lt;50,(100-N_40)&lt;0.5*(100-N_200),N_200&lt;5,CU&gt;=6,CC&gt;=1,CC&lt;=3),"SW","")</f>
@@ -34763,19 +34754,19 @@
     </row>
     <row r="14" spans="1:17" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="94"/>
-      <c r="B14" s="968"/>
-      <c r="C14" s="970"/>
-      <c r="D14" s="972"/>
+      <c r="B14" s="986"/>
+      <c r="C14" s="988"/>
+      <c r="D14" s="990"/>
       <c r="E14" s="113" t="s">
         <v>141</v>
       </c>
       <c r="F14" s="114" t="s">
         <v>142</v>
       </c>
-      <c r="G14" s="979" t="s">
+      <c r="G14" s="997" t="s">
         <v>143</v>
       </c>
-      <c r="H14" s="980"/>
+      <c r="H14" s="998"/>
       <c r="I14" s="94"/>
       <c r="L14" s="249" t="e">
         <f>IF(AND(N_200&lt;50,(100-N_40)&lt;0.5*(100-N_200),N_200&lt;5,OR(CU&lt;6,CC&lt;1,CC&gt;3)),"SP","")</f>
@@ -34800,9 +34791,9 @@
     </row>
     <row r="15" spans="1:17" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="94"/>
-      <c r="B15" s="968"/>
-      <c r="C15" s="970"/>
-      <c r="D15" s="972" t="s">
+      <c r="B15" s="986"/>
+      <c r="C15" s="988"/>
+      <c r="D15" s="990" t="s">
         <v>144</v>
       </c>
       <c r="E15" s="113" t="s">
@@ -34814,7 +34805,7 @@
       <c r="G15" s="116" t="s">
         <v>147</v>
       </c>
-      <c r="H15" s="983" t="s">
+      <c r="H15" s="965" t="s">
         <v>148</v>
       </c>
       <c r="I15" s="94"/>
@@ -34835,9 +34826,9 @@
     </row>
     <row r="16" spans="1:17" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="94"/>
-      <c r="B16" s="969"/>
-      <c r="C16" s="970"/>
-      <c r="D16" s="972"/>
+      <c r="B16" s="987"/>
+      <c r="C16" s="988"/>
+      <c r="D16" s="990"/>
       <c r="E16" s="117" t="s">
         <v>149</v>
       </c>
@@ -34847,7 +34838,7 @@
       <c r="G16" s="114" t="s">
         <v>151</v>
       </c>
-      <c r="H16" s="984"/>
+      <c r="H16" s="966"/>
       <c r="I16" s="94"/>
       <c r="L16" s="249" t="e">
         <f>IF(AND(N_200&lt;50,(100-N_40)&lt;0.5*(100-N_200),N_200&gt;=12,IP&gt;=7,IP&gt;=0.73*(Ll-20)),"SC","")</f>
@@ -34863,23 +34854,23 @@
     </row>
     <row r="17" spans="1:16" ht="48" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="94"/>
-      <c r="B17" s="985" t="s">
+      <c r="B17" s="967" t="s">
         <v>152</v>
       </c>
-      <c r="C17" s="988" t="s">
+      <c r="C17" s="970" t="s">
         <v>153</v>
       </c>
-      <c r="D17" s="989"/>
+      <c r="D17" s="971"/>
       <c r="E17" s="118" t="s">
         <v>154</v>
       </c>
       <c r="F17" s="119" t="s">
         <v>155</v>
       </c>
-      <c r="G17" s="994" t="s">
+      <c r="G17" s="976" t="s">
         <v>156</v>
       </c>
-      <c r="H17" s="995"/>
+      <c r="H17" s="977"/>
       <c r="I17" s="94"/>
       <c r="L17" s="249" t="e">
         <f>IF(AND(OR(L2="Inorganico"),N_200&gt;=50,Ll&lt;50,OR(IP&lt;4,AND(IP&lt;0.73*(Ll-20)))),"ML","")</f>
@@ -34895,17 +34886,17 @@
     </row>
     <row r="18" spans="1:16" ht="50.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="94"/>
-      <c r="B18" s="986"/>
-      <c r="C18" s="990"/>
-      <c r="D18" s="991"/>
+      <c r="B18" s="968"/>
+      <c r="C18" s="972"/>
+      <c r="D18" s="973"/>
       <c r="E18" s="118" t="s">
         <v>157</v>
       </c>
       <c r="F18" s="119" t="s">
         <v>158</v>
       </c>
-      <c r="G18" s="996"/>
-      <c r="H18" s="997"/>
+      <c r="G18" s="978"/>
+      <c r="H18" s="979"/>
       <c r="I18" s="94"/>
       <c r="L18" s="249" t="e">
         <f>IF(AND(OR(L2="Inorganico"),N_200&gt;=50,Ll&lt;50,IP&gt;=7,IP&gt;=0.73*(Ll-20)),"CL","")</f>
@@ -34921,9 +34912,9 @@
     </row>
     <row r="19" spans="1:16" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="94"/>
-      <c r="B19" s="986"/>
-      <c r="C19" s="992"/>
-      <c r="D19" s="993"/>
+      <c r="B19" s="968"/>
+      <c r="C19" s="974"/>
+      <c r="D19" s="975"/>
       <c r="E19" s="118" t="s">
         <v>159</v>
       </c>
@@ -34947,11 +34938,11 @@
     </row>
     <row r="20" spans="1:16" ht="39" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="94"/>
-      <c r="B20" s="986"/>
-      <c r="C20" s="990" t="s">
+      <c r="B20" s="968"/>
+      <c r="C20" s="972" t="s">
         <v>161</v>
       </c>
-      <c r="D20" s="998"/>
+      <c r="D20" s="980"/>
       <c r="E20" s="122" t="s">
         <v>162</v>
       </c>
@@ -34975,9 +34966,9 @@
     </row>
     <row r="21" spans="1:16" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="94"/>
-      <c r="B21" s="986"/>
-      <c r="C21" s="990"/>
-      <c r="D21" s="998"/>
+      <c r="B21" s="968"/>
+      <c r="C21" s="972"/>
+      <c r="D21" s="980"/>
       <c r="E21" s="122" t="s">
         <v>164</v>
       </c>
@@ -35001,9 +34992,9 @@
     </row>
     <row r="22" spans="1:16" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="94"/>
-      <c r="B22" s="986"/>
-      <c r="C22" s="992"/>
-      <c r="D22" s="999"/>
+      <c r="B22" s="968"/>
+      <c r="C22" s="974"/>
+      <c r="D22" s="981"/>
       <c r="E22" s="124" t="s">
         <v>166</v>
       </c>
@@ -35027,11 +35018,11 @@
     </row>
     <row r="23" spans="1:16" ht="39" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="94"/>
-      <c r="B23" s="986"/>
-      <c r="C23" s="988" t="s">
+      <c r="B23" s="968"/>
+      <c r="C23" s="970" t="s">
         <v>168</v>
       </c>
-      <c r="D23" s="989"/>
+      <c r="D23" s="971"/>
       <c r="E23" s="125" t="s">
         <v>169</v>
       </c>
@@ -35055,7 +35046,7 @@
     </row>
     <row r="24" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A24" s="94"/>
-      <c r="B24" s="987"/>
+      <c r="B24" s="969"/>
       <c r="C24" s="127"/>
       <c r="D24" s="128"/>
       <c r="E24" s="129"/>
@@ -35151,10 +35142,10 @@
       <c r="F31" s="135"/>
     </row>
     <row r="32" spans="1:16" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="981" t="s">
+      <c r="A32" s="963" t="s">
         <v>200</v>
       </c>
-      <c r="B32" s="982"/>
+      <c r="B32" s="964"/>
       <c r="F32" s="135"/>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.25">
@@ -35705,13 +35696,6 @@
     </row>
   </sheetData>
   <mergeCells count="23">
-    <mergeCell ref="A32:B32"/>
-    <mergeCell ref="H15:H16"/>
-    <mergeCell ref="B17:B24"/>
-    <mergeCell ref="C17:D19"/>
-    <mergeCell ref="G17:H18"/>
-    <mergeCell ref="C20:D22"/>
-    <mergeCell ref="C23:D23"/>
     <mergeCell ref="B1:H1"/>
     <mergeCell ref="B8:D8"/>
     <mergeCell ref="G8:H8"/>
@@ -35728,6 +35712,13 @@
     <mergeCell ref="G13:H13"/>
     <mergeCell ref="G14:H14"/>
     <mergeCell ref="D15:D16"/>
+    <mergeCell ref="A32:B32"/>
+    <mergeCell ref="H15:H16"/>
+    <mergeCell ref="B17:B24"/>
+    <mergeCell ref="C17:D19"/>
+    <mergeCell ref="G17:H18"/>
+    <mergeCell ref="C20:D22"/>
+    <mergeCell ref="C23:D23"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -35803,71 +35794,71 @@
     </row>
     <row r="4" spans="1:16" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="21"/>
-      <c r="B4" s="1006" t="s">
+      <c r="B4" s="1005" t="s">
         <v>42</v>
       </c>
-      <c r="C4" s="1007"/>
-      <c r="D4" s="1008" t="s">
+      <c r="C4" s="1006"/>
+      <c r="D4" s="1007" t="s">
         <v>43</v>
       </c>
-      <c r="E4" s="1008"/>
-      <c r="F4" s="1008"/>
-      <c r="G4" s="1008"/>
-      <c r="H4" s="1008"/>
-      <c r="I4" s="1008"/>
-      <c r="J4" s="1008"/>
-      <c r="K4" s="1009" t="s">
+      <c r="E4" s="1007"/>
+      <c r="F4" s="1007"/>
+      <c r="G4" s="1007"/>
+      <c r="H4" s="1007"/>
+      <c r="I4" s="1007"/>
+      <c r="J4" s="1007"/>
+      <c r="K4" s="1008" t="s">
         <v>44</v>
       </c>
-      <c r="L4" s="1010"/>
-      <c r="M4" s="1010"/>
-      <c r="N4" s="1010"/>
-      <c r="O4" s="1011"/>
+      <c r="L4" s="1009"/>
+      <c r="M4" s="1009"/>
+      <c r="N4" s="1009"/>
+      <c r="O4" s="1010"/>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5" s="21"/>
-      <c r="B5" s="1012" t="s">
+      <c r="B5" s="1011" t="s">
         <v>45</v>
       </c>
-      <c r="C5" s="1013"/>
-      <c r="D5" s="1016" t="s">
+      <c r="C5" s="1012"/>
+      <c r="D5" s="1015" t="s">
         <v>46</v>
       </c>
-      <c r="E5" s="1017"/>
-      <c r="F5" s="1018" t="s">
+      <c r="E5" s="1016"/>
+      <c r="F5" s="1017" t="s">
         <v>47</v>
       </c>
-      <c r="G5" s="1016" t="s">
+      <c r="G5" s="1015" t="s">
         <v>48</v>
       </c>
-      <c r="H5" s="1020"/>
-      <c r="I5" s="1020"/>
-      <c r="J5" s="1017"/>
-      <c r="K5" s="1021" t="s">
+      <c r="H5" s="1019"/>
+      <c r="I5" s="1019"/>
+      <c r="J5" s="1016"/>
+      <c r="K5" s="1020" t="s">
         <v>49</v>
       </c>
-      <c r="L5" s="1023" t="s">
+      <c r="L5" s="1022" t="s">
         <v>50</v>
       </c>
-      <c r="M5" s="1025" t="s">
+      <c r="M5" s="1024" t="s">
         <v>51</v>
       </c>
-      <c r="N5" s="1027" t="s">
+      <c r="N5" s="1026" t="s">
         <v>52</v>
       </c>
-      <c r="O5" s="1028"/>
+      <c r="O5" s="1027"/>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6" s="21"/>
-      <c r="B6" s="1014"/>
-      <c r="C6" s="1015"/>
+      <c r="B6" s="1013"/>
+      <c r="C6" s="1014"/>
       <c r="D6" s="25" t="s">
         <v>53</v>
       </c>
       <c r="E6" s="26" t="s">
         <v>54</v>
       </c>
-      <c r="F6" s="1019"/>
+      <c r="F6" s="1018"/>
       <c r="G6" s="25" t="s">
         <v>55</v>
       </c>
@@ -35880,9 +35871,9 @@
       <c r="J6" s="26" t="s">
         <v>58</v>
       </c>
-      <c r="K6" s="1022"/>
-      <c r="L6" s="1024"/>
-      <c r="M6" s="1026"/>
+      <c r="K6" s="1021"/>
+      <c r="L6" s="1023"/>
+      <c r="M6" s="1025"/>
       <c r="N6" s="29" t="s">
         <v>59</v>
       </c>
@@ -36282,21 +36273,21 @@
         <f>+D38</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="D23" s="1000">
+      <c r="D23" s="999">
         <v>0</v>
       </c>
-      <c r="E23" s="1001"/>
+      <c r="E23" s="1000"/>
       <c r="F23" s="82">
         <v>0</v>
       </c>
-      <c r="G23" s="1000">
+      <c r="G23" s="999">
         <v>0</v>
       </c>
-      <c r="H23" s="1002"/>
-      <c r="I23" s="1003" t="s">
+      <c r="H23" s="1001"/>
+      <c r="I23" s="1002" t="s">
         <v>87</v>
       </c>
-      <c r="J23" s="1001"/>
+      <c r="J23" s="1000"/>
       <c r="K23" s="83" t="s">
         <v>88</v>
       </c>
@@ -36359,11 +36350,11 @@
       <c r="G26" s="88"/>
       <c r="H26" s="23"/>
       <c r="I26" s="23"/>
-      <c r="J26" s="1004" t="e">
+      <c r="J26" s="1003" t="e">
         <f>+D31&amp;" "&amp;F38</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="K26" s="1005"/>
+      <c r="K26" s="1004"/>
       <c r="L26" s="21"/>
       <c r="M26" s="21"/>
       <c r="N26" s="21"/>
@@ -36623,10 +36614,10 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="1029" t="s">
+      <c r="A2" s="1028" t="s">
         <v>10</v>
       </c>
-      <c r="B2" s="1029"/>
+      <c r="B2" s="1028"/>
       <c r="C2" s="5" t="s">
         <v>11</v>
       </c>
